--- a/artfynd/A 29945-2025 artfynd.xlsx
+++ b/artfynd/A 29945-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY270"/>
+  <dimension ref="A1:AY275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11351,7 +11351,7 @@
         <v>127272192</v>
       </c>
       <c r="B104" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>127283121</v>
       </c>
       <c r="B105" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>127275526</v>
       </c>
       <c r="B106" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>127274454</v>
       </c>
       <c r="B107" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>127282929</v>
       </c>
       <c r="B108" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11868,10 +11868,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127273473</v>
+        <v>127273727</v>
       </c>
       <c r="B109" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11879,39 +11879,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>440721</v>
+        <v>440754</v>
       </c>
       <c r="R109" t="n">
-        <v>6761996</v>
+        <v>6762035</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11980,10 +11975,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127273727</v>
+        <v>127282909</v>
       </c>
       <c r="B110" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12011,14 +12006,14 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>440754</v>
+        <v>440797</v>
       </c>
       <c r="R110" t="n">
-        <v>6762035</v>
+        <v>6762555</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12048,19 +12043,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12075,22 +12060,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127282909</v>
+        <v>127282922</v>
       </c>
       <c r="B111" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12122,10 +12107,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>440797</v>
+        <v>440685</v>
       </c>
       <c r="R111" t="n">
-        <v>6762555</v>
+        <v>6762213</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12184,10 +12169,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127282922</v>
+        <v>127282903</v>
       </c>
       <c r="B112" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12219,10 +12204,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>440685</v>
+        <v>440760</v>
       </c>
       <c r="R112" t="n">
-        <v>6762213</v>
+        <v>6762626</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12281,10 +12266,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127282903</v>
+        <v>127282896</v>
       </c>
       <c r="B113" t="n">
-        <v>79011</v>
+        <v>78772</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12292,21 +12277,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12316,10 +12301,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>440760</v>
+        <v>440416</v>
       </c>
       <c r="R113" t="n">
-        <v>6762626</v>
+        <v>6762406</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12378,10 +12363,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127282896</v>
+        <v>127274251</v>
       </c>
       <c r="B114" t="n">
-        <v>78769</v>
+        <v>79014</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12389,34 +12374,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>440416</v>
+        <v>440687</v>
       </c>
       <c r="R114" t="n">
-        <v>6762406</v>
+        <v>6762120</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12446,9 +12431,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12463,22 +12458,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127274251</v>
+        <v>127273473</v>
       </c>
       <c r="B115" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12486,34 +12481,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>440687</v>
+        <v>440721</v>
       </c>
       <c r="R115" t="n">
-        <v>6762120</v>
+        <v>6761996</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12689,10 +12689,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127273755</v>
+        <v>127274057</v>
       </c>
       <c r="B117" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12700,34 +12700,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>440744</v>
+        <v>440706</v>
       </c>
       <c r="R117" t="n">
-        <v>6762065</v>
+        <v>6762058</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12796,32 +12801,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127276304</v>
+        <v>127274061</v>
       </c>
       <c r="B118" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12831,10 +12836,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>440642</v>
+        <v>440706</v>
       </c>
       <c r="R118" t="n">
-        <v>6762606</v>
+        <v>6762058</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12866,7 +12871,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12876,7 +12881,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12903,10 +12908,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127275131</v>
+        <v>127283110</v>
       </c>
       <c r="B119" t="n">
-        <v>79011</v>
+        <v>79015</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12914,16 +12919,16 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -12934,14 +12939,14 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>440709</v>
+        <v>440835</v>
       </c>
       <c r="R119" t="n">
-        <v>6762405</v>
+        <v>6762564</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12971,19 +12976,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12998,22 +12993,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127271820</v>
+        <v>127273755</v>
       </c>
       <c r="B120" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13041,17 +13036,17 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>440446</v>
+        <v>440744</v>
       </c>
       <c r="R120" t="n">
-        <v>6762469</v>
+        <v>6762065</v>
       </c>
       <c r="S120" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13080,7 +13075,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13090,7 +13085,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13105,22 +13100,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127283110</v>
+        <v>127276304</v>
       </c>
       <c r="B121" t="n">
-        <v>79012</v>
+        <v>79014</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13128,16 +13123,16 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -13148,14 +13143,14 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>440835</v>
+        <v>440642</v>
       </c>
       <c r="R121" t="n">
-        <v>6762564</v>
+        <v>6762606</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13185,9 +13180,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13202,22 +13207,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127274057</v>
+        <v>127275131</v>
       </c>
       <c r="B122" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13225,39 +13230,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>440706</v>
+        <v>440709</v>
       </c>
       <c r="R122" t="n">
-        <v>6762058</v>
+        <v>6762405</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13326,48 +13326,48 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127274061</v>
+        <v>127271820</v>
       </c>
       <c r="B123" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>440706</v>
+        <v>440446</v>
       </c>
       <c r="R123" t="n">
-        <v>6762058</v>
+        <v>6762469</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13421,12 +13421,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -13436,7 +13436,7 @@
         <v>127283139</v>
       </c>
       <c r="B124" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>127283131</v>
       </c>
       <c r="B125" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>127283135</v>
       </c>
       <c r="B126" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>127273828</v>
       </c>
       <c r="B127" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>127275968</v>
       </c>
       <c r="B128" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14050,10 +14050,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127276148</v>
+        <v>127283109</v>
       </c>
       <c r="B130" t="n">
-        <v>57654</v>
+        <v>79015</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14061,39 +14061,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>230405</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>440657</v>
+        <v>440875</v>
       </c>
       <c r="R130" t="n">
-        <v>6762603</v>
+        <v>6762453</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14123,19 +14118,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14150,22 +14135,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127272305</v>
+        <v>127274657</v>
       </c>
       <c r="B131" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14173,39 +14158,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>440675</v>
+        <v>440689</v>
       </c>
       <c r="R131" t="n">
-        <v>6762165</v>
+        <v>6762214</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14252,7 +14232,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Diameter ca 4 till 5 cm</t>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14279,10 +14259,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127271765</v>
+        <v>127283117</v>
       </c>
       <c r="B132" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14290,39 +14270,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>440627</v>
+        <v>440863</v>
       </c>
       <c r="R132" t="n">
-        <v>6762119</v>
+        <v>6762603</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14352,24 +14327,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Miljöbild för området</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14384,22 +14344,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127276450</v>
+        <v>127273051</v>
       </c>
       <c r="B133" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14407,42 +14367,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>440582</v>
+        <v>440681</v>
       </c>
       <c r="R133" t="n">
-        <v>6762684</v>
+        <v>6762197</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14471,7 +14426,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14481,7 +14436,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14496,22 +14451,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127274657</v>
+        <v>127282932</v>
       </c>
       <c r="B134" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14539,14 +14494,14 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>440689</v>
+        <v>440427</v>
       </c>
       <c r="R134" t="n">
-        <v>6762214</v>
+        <v>6762470</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14576,24 +14531,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14608,22 +14548,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127283117</v>
+        <v>127282912</v>
       </c>
       <c r="B135" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14651,14 +14591,14 @@
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>440863</v>
+        <v>440936</v>
       </c>
       <c r="R135" t="n">
-        <v>6762603</v>
+        <v>6762564</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14705,22 +14645,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127273051</v>
+        <v>127282926</v>
       </c>
       <c r="B136" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14748,17 +14688,17 @@
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>440681</v>
+        <v>440497</v>
       </c>
       <c r="R136" t="n">
-        <v>6762197</v>
+        <v>6762331</v>
       </c>
       <c r="S136" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14785,19 +14725,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>12:38</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14812,22 +14742,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127282932</v>
+        <v>127283130</v>
       </c>
       <c r="B137" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14855,14 +14785,14 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>440427</v>
+        <v>440697</v>
       </c>
       <c r="R137" t="n">
-        <v>6762470</v>
+        <v>6762237</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14909,22 +14839,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127282912</v>
+        <v>127276216</v>
       </c>
       <c r="B138" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14952,14 +14882,14 @@
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>440936</v>
+        <v>440657</v>
       </c>
       <c r="R138" t="n">
-        <v>6762564</v>
+        <v>6762603</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14989,9 +14919,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15006,22 +14946,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127282926</v>
+        <v>127273488</v>
       </c>
       <c r="B139" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15049,14 +14989,14 @@
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>440497</v>
+        <v>440721</v>
       </c>
       <c r="R139" t="n">
-        <v>6762331</v>
+        <v>6761996</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15086,9 +15026,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15103,22 +15053,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127283130</v>
+        <v>127276148</v>
       </c>
       <c r="B140" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15126,34 +15076,39 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>440697</v>
+        <v>440657</v>
       </c>
       <c r="R140" t="n">
-        <v>6762237</v>
+        <v>6762603</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15183,9 +15138,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15200,22 +15165,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127276216</v>
+        <v>127272305</v>
       </c>
       <c r="B141" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15223,34 +15188,39 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>440657</v>
+        <v>440675</v>
       </c>
       <c r="R141" t="n">
-        <v>6762603</v>
+        <v>6762165</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15282,7 +15252,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15292,7 +15262,12 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Diameter ca 4 till 5 cm</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15319,10 +15294,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127273488</v>
+        <v>127271765</v>
       </c>
       <c r="B142" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15330,34 +15305,39 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>440721</v>
+        <v>440627</v>
       </c>
       <c r="R142" t="n">
-        <v>6761996</v>
+        <v>6762119</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15400,6 +15380,11 @@
       <c r="AB142" t="inlineStr">
         <is>
           <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Miljöbild för området</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15426,45 +15411,50 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127283108</v>
+        <v>127276450</v>
       </c>
       <c r="B143" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>440442</v>
+        <v>440582</v>
       </c>
       <c r="R143" t="n">
-        <v>6762471</v>
+        <v>6762684</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15494,9 +15484,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15511,19 +15511,19 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127282895</v>
+        <v>127283108</v>
       </c>
       <c r="B144" t="n">
         <v>8447</v>
@@ -15554,14 +15554,14 @@
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>440382</v>
+        <v>440442</v>
       </c>
       <c r="R144" t="n">
-        <v>6762379</v>
+        <v>6762471</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15608,57 +15608,57 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127283109</v>
+        <v>127282895</v>
       </c>
       <c r="B145" t="n">
-        <v>79012</v>
+        <v>8447</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>440875</v>
+        <v>440382</v>
       </c>
       <c r="R145" t="n">
-        <v>6762453</v>
+        <v>6762379</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15705,12 +15705,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
@@ -15720,7 +15720,7 @@
         <v>127283142</v>
       </c>
       <c r="B146" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>127274917</v>
       </c>
       <c r="B147" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>127283119</v>
       </c>
       <c r="B148" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>127272858</v>
       </c>
       <c r="B149" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>127273038</v>
       </c>
       <c r="B150" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>127274822</v>
       </c>
       <c r="B151" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>127275416</v>
       </c>
       <c r="B152" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>127273932</v>
       </c>
       <c r="B153" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16553,10 +16553,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127272237</v>
+        <v>127282904</v>
       </c>
       <c r="B154" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16564,39 +16564,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>440675</v>
+        <v>440776</v>
       </c>
       <c r="R154" t="n">
-        <v>6762165</v>
+        <v>6762632</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16626,19 +16621,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16653,22 +16638,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127282904</v>
+        <v>127282914</v>
       </c>
       <c r="B155" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16700,10 +16685,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>440776</v>
+        <v>440924</v>
       </c>
       <c r="R155" t="n">
-        <v>6762632</v>
+        <v>6762509</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16762,10 +16747,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127282914</v>
+        <v>127283105</v>
       </c>
       <c r="B156" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16773,34 +16758,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>440924</v>
+        <v>440909</v>
       </c>
       <c r="R156" t="n">
-        <v>6762509</v>
+        <v>6762467</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16847,22 +16832,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127283105</v>
+        <v>127274354</v>
       </c>
       <c r="B157" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16870,34 +16855,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>440909</v>
+        <v>440686</v>
       </c>
       <c r="R157" t="n">
-        <v>6762467</v>
+        <v>6762176</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16927,9 +16912,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16944,22 +16939,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127274354</v>
+        <v>127272746</v>
       </c>
       <c r="B158" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16987,17 +16982,17 @@
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>440686</v>
+        <v>440503</v>
       </c>
       <c r="R158" t="n">
-        <v>6762176</v>
+        <v>6762308</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17026,7 +17021,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17036,7 +17031,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17051,22 +17046,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127272746</v>
+        <v>127272237</v>
       </c>
       <c r="B159" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17074,37 +17069,42 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>440503</v>
+        <v>440675</v>
       </c>
       <c r="R159" t="n">
-        <v>6762308</v>
+        <v>6762165</v>
       </c>
       <c r="S159" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17143,7 +17143,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17158,22 +17158,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127282900</v>
+        <v>127275098</v>
       </c>
       <c r="B160" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17181,34 +17181,39 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>440757</v>
+        <v>440679</v>
       </c>
       <c r="R160" t="n">
-        <v>6762544</v>
+        <v>6762388</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17238,9 +17243,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17255,22 +17270,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127276426</v>
+        <v>127282900</v>
       </c>
       <c r="B161" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17298,14 +17313,14 @@
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>440582</v>
+        <v>440757</v>
       </c>
       <c r="R161" t="n">
-        <v>6762684</v>
+        <v>6762544</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17335,19 +17350,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17362,22 +17367,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127275877</v>
+        <v>127276426</v>
       </c>
       <c r="B162" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17409,10 +17414,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>440732</v>
+        <v>440582</v>
       </c>
       <c r="R162" t="n">
-        <v>6762635</v>
+        <v>6762684</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17481,10 +17486,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127273900</v>
+        <v>127275877</v>
       </c>
       <c r="B163" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17512,17 +17517,17 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>440903</v>
+        <v>440732</v>
       </c>
       <c r="R163" t="n">
-        <v>6762450</v>
+        <v>6762635</v>
       </c>
       <c r="S163" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -17551,7 +17556,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17561,7 +17566,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17576,22 +17581,22 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127282902</v>
+        <v>127273900</v>
       </c>
       <c r="B164" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17619,17 +17624,17 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>440760</v>
+        <v>440903</v>
       </c>
       <c r="R164" t="n">
-        <v>6762569</v>
+        <v>6762450</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -17656,9 +17661,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17673,22 +17688,22 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127273086</v>
+        <v>127282902</v>
       </c>
       <c r="B165" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17716,17 +17731,17 @@
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>440694</v>
+        <v>440760</v>
       </c>
       <c r="R165" t="n">
-        <v>6762204</v>
+        <v>6762569</v>
       </c>
       <c r="S165" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -17753,19 +17768,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>12:40</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17780,22 +17785,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127283137</v>
+        <v>127273086</v>
       </c>
       <c r="B166" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17823,17 +17828,17 @@
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>440354</v>
+        <v>440694</v>
       </c>
       <c r="R166" t="n">
-        <v>6762415</v>
+        <v>6762204</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17860,9 +17865,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17877,22 +17892,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127274348</v>
+        <v>127283137</v>
       </c>
       <c r="B167" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17900,39 +17915,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>440686</v>
+        <v>440354</v>
       </c>
       <c r="R167" t="n">
-        <v>6762176</v>
+        <v>6762415</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17962,19 +17972,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z167" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17989,22 +17989,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127275098</v>
+        <v>127274348</v>
       </c>
       <c r="B168" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18012,16 +18012,16 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -18041,10 +18041,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>440679</v>
+        <v>440686</v>
       </c>
       <c r="R168" t="n">
-        <v>6762388</v>
+        <v>6762176</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18116,7 +18116,7 @@
         <v>127273853</v>
       </c>
       <c r="B169" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>127270744</v>
       </c>
       <c r="B170" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>127275337</v>
       </c>
       <c r="B171" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>127282927</v>
       </c>
       <c r="B172" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18531,10 +18531,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127283115</v>
+        <v>127283128</v>
       </c>
       <c r="B173" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18566,10 +18566,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>440803</v>
+        <v>440822</v>
       </c>
       <c r="R173" t="n">
-        <v>6762557</v>
+        <v>6762415</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18628,10 +18628,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127283134</v>
+        <v>127274114</v>
       </c>
       <c r="B174" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18659,14 +18659,14 @@
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>440487</v>
+        <v>440711</v>
       </c>
       <c r="R174" t="n">
-        <v>6762321</v>
+        <v>6762111</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18696,9 +18696,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18713,22 +18723,22 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127283133</v>
+        <v>127283115</v>
       </c>
       <c r="B175" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18760,10 +18770,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>440598</v>
+        <v>440803</v>
       </c>
       <c r="R175" t="n">
-        <v>6762206</v>
+        <v>6762557</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18822,10 +18832,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127283128</v>
+        <v>127283134</v>
       </c>
       <c r="B176" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18857,10 +18867,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>440822</v>
+        <v>440487</v>
       </c>
       <c r="R176" t="n">
-        <v>6762415</v>
+        <v>6762321</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18919,10 +18929,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127274114</v>
+        <v>127283133</v>
       </c>
       <c r="B177" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18950,14 +18960,14 @@
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>440711</v>
+        <v>440598</v>
       </c>
       <c r="R177" t="n">
-        <v>6762111</v>
+        <v>6762206</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18987,19 +18997,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19014,12 +19014,12 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
@@ -19357,10 +19357,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127274154</v>
+        <v>127283127</v>
       </c>
       <c r="B181" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19368,42 +19368,37 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>440946</v>
+        <v>440843</v>
       </c>
       <c r="R181" t="n">
-        <v>6762537</v>
+        <v>6762431</v>
       </c>
       <c r="S181" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -19430,24 +19425,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19462,22 +19442,22 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127283127</v>
+        <v>127283116</v>
       </c>
       <c r="B182" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19509,10 +19489,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>440843</v>
+        <v>440823</v>
       </c>
       <c r="R182" t="n">
-        <v>6762431</v>
+        <v>6762604</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19571,10 +19551,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127283116</v>
+        <v>127282906</v>
       </c>
       <c r="B183" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19602,14 +19582,14 @@
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>440823</v>
+        <v>440782</v>
       </c>
       <c r="R183" t="n">
-        <v>6762604</v>
+        <v>6762562</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19656,22 +19636,22 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127282906</v>
+        <v>127275778</v>
       </c>
       <c r="B184" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19699,17 +19679,17 @@
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>440782</v>
+        <v>440761</v>
       </c>
       <c r="R184" t="n">
-        <v>6762562</v>
+        <v>6762597</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19736,9 +19716,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19753,22 +19743,22 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127275778</v>
+        <v>127282925</v>
       </c>
       <c r="B185" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19796,17 +19786,17 @@
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>440761</v>
+        <v>440619</v>
       </c>
       <c r="R185" t="n">
-        <v>6762597</v>
+        <v>6762184</v>
       </c>
       <c r="S185" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -19833,19 +19823,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>15:06</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>15:06</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19860,22 +19840,22 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127282925</v>
+        <v>127274154</v>
       </c>
       <c r="B186" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19883,37 +19863,42 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>440619</v>
+        <v>440946</v>
       </c>
       <c r="R186" t="n">
-        <v>6762184</v>
+        <v>6762537</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19940,9 +19925,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19957,22 +19957,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127274877</v>
+        <v>127282924</v>
       </c>
       <c r="B187" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19980,42 +19980,37 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>440752</v>
+        <v>440623</v>
       </c>
       <c r="R187" t="n">
-        <v>6762337</v>
+        <v>6762194</v>
       </c>
       <c r="S187" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -20042,19 +20037,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20069,22 +20054,22 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127282924</v>
+        <v>127283136</v>
       </c>
       <c r="B188" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20112,14 +20097,14 @@
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>440623</v>
+        <v>440394</v>
       </c>
       <c r="R188" t="n">
-        <v>6762194</v>
+        <v>6762413</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20166,22 +20151,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127283136</v>
+        <v>127283138</v>
       </c>
       <c r="B189" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20213,10 +20198,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>440394</v>
+        <v>440335</v>
       </c>
       <c r="R189" t="n">
-        <v>6762413</v>
+        <v>6762400</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20275,10 +20260,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127283138</v>
+        <v>127282907</v>
       </c>
       <c r="B190" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20306,14 +20291,14 @@
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>440335</v>
+        <v>440793</v>
       </c>
       <c r="R190" t="n">
-        <v>6762400</v>
+        <v>6762525</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20360,22 +20345,22 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127282907</v>
+        <v>127283118</v>
       </c>
       <c r="B191" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20403,14 +20388,14 @@
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>440793</v>
+        <v>440868</v>
       </c>
       <c r="R191" t="n">
-        <v>6762525</v>
+        <v>6762583</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20457,22 +20442,22 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127283118</v>
+        <v>127283113</v>
       </c>
       <c r="B192" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20504,10 +20489,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>440868</v>
+        <v>440768</v>
       </c>
       <c r="R192" t="n">
-        <v>6762583</v>
+        <v>6762554</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20566,10 +20551,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127283113</v>
+        <v>127274877</v>
       </c>
       <c r="B193" t="n">
-        <v>79011</v>
+        <v>57817</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20577,37 +20562,42 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>440768</v>
+        <v>440752</v>
       </c>
       <c r="R193" t="n">
-        <v>6762554</v>
+        <v>6762337</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -20634,9 +20624,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20651,12 +20651,12 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
@@ -20770,10 +20770,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127276018</v>
+        <v>127274677</v>
       </c>
       <c r="B195" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20781,34 +20781,39 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>440697</v>
+        <v>440689</v>
       </c>
       <c r="R195" t="n">
-        <v>6762625</v>
+        <v>6762214</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20840,7 +20845,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -20850,7 +20855,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20877,48 +20882,48 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127275350</v>
+        <v>127283143</v>
       </c>
       <c r="B196" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>440851</v>
+        <v>440337</v>
       </c>
       <c r="R196" t="n">
-        <v>6762513</v>
+        <v>6762397</v>
       </c>
       <c r="S196" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -20945,19 +20950,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20972,57 +20967,57 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127283124</v>
+        <v>127272174</v>
       </c>
       <c r="B197" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>440965</v>
+        <v>440657</v>
       </c>
       <c r="R197" t="n">
-        <v>6762540</v>
+        <v>6762157</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21052,9 +21047,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21069,22 +21074,22 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127272147</v>
+        <v>127276018</v>
       </c>
       <c r="B198" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21112,17 +21117,17 @@
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>440498</v>
+        <v>440697</v>
       </c>
       <c r="R198" t="n">
-        <v>6762428</v>
+        <v>6762625</v>
       </c>
       <c r="S198" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -21151,7 +21156,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21161,7 +21166,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21176,60 +21181,60 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127283143</v>
+        <v>127275350</v>
       </c>
       <c r="B199" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>440337</v>
+        <v>440851</v>
       </c>
       <c r="R199" t="n">
-        <v>6762397</v>
+        <v>6762513</v>
       </c>
       <c r="S199" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -21256,9 +21261,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21273,57 +21288,57 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127272174</v>
+        <v>127283124</v>
       </c>
       <c r="B200" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>440657</v>
+        <v>440965</v>
       </c>
       <c r="R200" t="n">
-        <v>6762157</v>
+        <v>6762540</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21353,19 +21368,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21380,22 +21385,22 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127274677</v>
+        <v>127272147</v>
       </c>
       <c r="B201" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21403,42 +21408,37 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>440689</v>
+        <v>440498</v>
       </c>
       <c r="R201" t="n">
-        <v>6762214</v>
+        <v>6762428</v>
       </c>
       <c r="S201" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21477,7 +21477,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21492,22 +21492,22 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127283114</v>
+        <v>127275348</v>
       </c>
       <c r="B202" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21535,14 +21535,14 @@
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>440806</v>
+        <v>440677</v>
       </c>
       <c r="R202" t="n">
-        <v>6762533</v>
+        <v>6762469</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21572,9 +21572,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21589,22 +21599,22 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127271427</v>
+        <v>127282910</v>
       </c>
       <c r="B203" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21612,37 +21622,37 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>440457</v>
+        <v>440807</v>
       </c>
       <c r="R203" t="n">
-        <v>6762399</v>
+        <v>6762574</v>
       </c>
       <c r="S203" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -21669,19 +21679,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21696,22 +21696,22 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127275348</v>
+        <v>127271972</v>
       </c>
       <c r="B204" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21739,17 +21739,17 @@
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>440677</v>
+        <v>440460</v>
       </c>
       <c r="R204" t="n">
-        <v>6762469</v>
+        <v>6762457</v>
       </c>
       <c r="S204" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -21788,7 +21788,12 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>På Gran</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21803,22 +21808,22 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>127282910</v>
+        <v>127272958</v>
       </c>
       <c r="B205" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21846,17 +21851,17 @@
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>440807</v>
+        <v>440619</v>
       </c>
       <c r="R205" t="n">
-        <v>6762574</v>
+        <v>6762170</v>
       </c>
       <c r="S205" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -21883,9 +21888,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -21900,22 +21915,22 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127271972</v>
+        <v>127283114</v>
       </c>
       <c r="B206" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21943,17 +21958,17 @@
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>440460</v>
+        <v>440806</v>
       </c>
       <c r="R206" t="n">
-        <v>6762457</v>
+        <v>6762533</v>
       </c>
       <c r="S206" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -21980,24 +21995,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>På Gran</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22012,22 +22012,22 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127272958</v>
+        <v>127282897</v>
       </c>
       <c r="B207" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22055,17 +22055,17 @@
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>440619</v>
+        <v>440613</v>
       </c>
       <c r="R207" t="n">
-        <v>6762170</v>
+        <v>6762197</v>
       </c>
       <c r="S207" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -22092,19 +22092,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z207" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB207" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22119,22 +22109,22 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127282897</v>
+        <v>127282920</v>
       </c>
       <c r="B208" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22166,10 +22156,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>440613</v>
+        <v>440696</v>
       </c>
       <c r="R208" t="n">
-        <v>6762197</v>
+        <v>6762239</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22228,10 +22218,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127282920</v>
+        <v>127271427</v>
       </c>
       <c r="B209" t="n">
-        <v>79011</v>
+        <v>57817</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -22239,37 +22229,37 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>440696</v>
+        <v>440457</v>
       </c>
       <c r="R209" t="n">
-        <v>6762239</v>
+        <v>6762399</v>
       </c>
       <c r="S209" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -22296,9 +22286,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -22313,22 +22313,22 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127274242</v>
+        <v>127282901</v>
       </c>
       <c r="B210" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -22336,39 +22336,34 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>440697</v>
+        <v>440751</v>
       </c>
       <c r="R210" t="n">
-        <v>6762119</v>
+        <v>6762564</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22398,19 +22393,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -22425,22 +22410,22 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127282901</v>
+        <v>127283112</v>
       </c>
       <c r="B211" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -22468,14 +22453,14 @@
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>440751</v>
+        <v>440663</v>
       </c>
       <c r="R211" t="n">
-        <v>6762564</v>
+        <v>6762599</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22522,22 +22507,22 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127283112</v>
+        <v>127283102</v>
       </c>
       <c r="B212" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -22545,21 +22530,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22569,10 +22554,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>440663</v>
+        <v>440726</v>
       </c>
       <c r="R212" t="n">
-        <v>6762599</v>
+        <v>6762638</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22631,10 +22616,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127283102</v>
+        <v>127272352</v>
       </c>
       <c r="B213" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -22642,34 +22627,34 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>440726</v>
+        <v>440685</v>
       </c>
       <c r="R213" t="n">
-        <v>6762638</v>
+        <v>6762109</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22699,9 +22684,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA213" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -22716,22 +22711,22 @@
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127272352</v>
+        <v>127273790</v>
       </c>
       <c r="B214" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -22759,17 +22754,17 @@
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>440685</v>
+        <v>440854</v>
       </c>
       <c r="R214" t="n">
-        <v>6762109</v>
+        <v>6762427</v>
       </c>
       <c r="S214" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -22798,7 +22793,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -22808,7 +22803,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -22823,22 +22818,22 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127273790</v>
+        <v>127273057</v>
       </c>
       <c r="B215" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -22870,10 +22865,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>440854</v>
+        <v>440681</v>
       </c>
       <c r="R215" t="n">
-        <v>6762427</v>
+        <v>6762195</v>
       </c>
       <c r="S215" t="n">
         <v>9</v>
@@ -22905,7 +22900,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -22915,7 +22910,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -22942,10 +22937,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127273057</v>
+        <v>127274242</v>
       </c>
       <c r="B216" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22953,37 +22948,42 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>440681</v>
+        <v>440697</v>
       </c>
       <c r="R216" t="n">
-        <v>6762195</v>
+        <v>6762119</v>
       </c>
       <c r="S216" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -23022,7 +23022,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23037,12 +23037,12 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
@@ -23052,7 +23052,7 @@
         <v>127283104</v>
       </c>
       <c r="B217" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23146,10 +23146,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127283141</v>
+        <v>127283106</v>
       </c>
       <c r="B218" t="n">
-        <v>78678</v>
+        <v>78773</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23157,21 +23157,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -23181,10 +23181,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>440651</v>
+        <v>440504</v>
       </c>
       <c r="R218" t="n">
-        <v>6762611</v>
+        <v>6762388</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23243,32 +23243,32 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127283107</v>
+        <v>127283141</v>
       </c>
       <c r="B219" t="n">
-        <v>8447</v>
+        <v>78681</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -23278,10 +23278,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>440636</v>
+        <v>440651</v>
       </c>
       <c r="R219" t="n">
-        <v>6762585</v>
+        <v>6762611</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23340,10 +23340,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127283106</v>
+        <v>127282898</v>
       </c>
       <c r="B220" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -23351,34 +23351,34 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>440504</v>
+        <v>440741</v>
       </c>
       <c r="R220" t="n">
-        <v>6762388</v>
+        <v>6762609</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23425,22 +23425,22 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127282898</v>
+        <v>127283122</v>
       </c>
       <c r="B221" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23468,14 +23468,14 @@
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>440741</v>
+        <v>440912</v>
       </c>
       <c r="R221" t="n">
-        <v>6762609</v>
+        <v>6762579</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23522,22 +23522,22 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127283122</v>
+        <v>127282915</v>
       </c>
       <c r="B222" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23565,14 +23565,14 @@
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>440912</v>
+        <v>440946</v>
       </c>
       <c r="R222" t="n">
-        <v>6762579</v>
+        <v>6762514</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23619,22 +23619,22 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127282915</v>
+        <v>127275040</v>
       </c>
       <c r="B223" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23662,14 +23662,14 @@
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>440946</v>
+        <v>440745</v>
       </c>
       <c r="R223" t="n">
-        <v>6762514</v>
+        <v>6762369</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23699,9 +23699,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA223" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -23716,22 +23731,22 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127275040</v>
+        <v>127282899</v>
       </c>
       <c r="B224" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23759,14 +23774,14 @@
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>440745</v>
+        <v>440763</v>
       </c>
       <c r="R224" t="n">
-        <v>6762369</v>
+        <v>6762529</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23796,24 +23811,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB224" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -23828,22 +23828,22 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127282899</v>
+        <v>127283100</v>
       </c>
       <c r="B225" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23851,34 +23851,34 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>440763</v>
+        <v>440686</v>
       </c>
       <c r="R225" t="n">
-        <v>6762529</v>
+        <v>6762630</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23925,44 +23925,44 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127283100</v>
+        <v>127283107</v>
       </c>
       <c r="B226" t="n">
-        <v>79629</v>
+        <v>8447</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23972,10 +23972,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>440686</v>
+        <v>440636</v>
       </c>
       <c r="R226" t="n">
-        <v>6762630</v>
+        <v>6762585</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24034,48 +24034,48 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127275544</v>
+        <v>127283126</v>
       </c>
       <c r="B227" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>440811</v>
+        <v>440923</v>
       </c>
       <c r="R227" t="n">
-        <v>6762474</v>
+        <v>6762482</v>
       </c>
       <c r="S227" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -24102,19 +24102,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z227" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA227" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB227" t="inlineStr">
-        <is>
-          <t>14:44</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24129,22 +24119,22 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127283126</v>
+        <v>127282918</v>
       </c>
       <c r="B228" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -24172,14 +24162,14 @@
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>440923</v>
+        <v>440832</v>
       </c>
       <c r="R228" t="n">
-        <v>6762482</v>
+        <v>6762387</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24226,22 +24216,22 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127282918</v>
+        <v>127282917</v>
       </c>
       <c r="B229" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24273,10 +24263,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>440832</v>
+        <v>440919</v>
       </c>
       <c r="R229" t="n">
-        <v>6762387</v>
+        <v>6762497</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24335,10 +24325,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127282917</v>
+        <v>127283125</v>
       </c>
       <c r="B230" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24366,14 +24356,14 @@
       <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>440919</v>
+        <v>440989</v>
       </c>
       <c r="R230" t="n">
-        <v>6762497</v>
+        <v>6762519</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24420,22 +24410,22 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127283125</v>
+        <v>127273660</v>
       </c>
       <c r="B231" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24463,14 +24453,14 @@
       <c r="I231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>440989</v>
+        <v>440742</v>
       </c>
       <c r="R231" t="n">
-        <v>6762519</v>
+        <v>6762004</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24500,9 +24490,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24517,22 +24517,22 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127273660</v>
+        <v>127275120</v>
       </c>
       <c r="B232" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24560,17 +24560,17 @@
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>440742</v>
+        <v>440897</v>
       </c>
       <c r="R232" t="n">
-        <v>6762004</v>
+        <v>6762548</v>
       </c>
       <c r="S232" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -24609,7 +24609,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24624,60 +24624,60 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127275120</v>
+        <v>127273585</v>
       </c>
       <c r="B233" t="n">
-        <v>79011</v>
+        <v>91683</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>440897</v>
+        <v>440742</v>
       </c>
       <c r="R233" t="n">
-        <v>6762548</v>
+        <v>6762004</v>
       </c>
       <c r="S233" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -24706,7 +24706,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -24716,7 +24716,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -24731,60 +24731,60 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>127273585</v>
+        <v>127275544</v>
       </c>
       <c r="B234" t="n">
-        <v>91677</v>
+        <v>8447</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>2062</v>
+        <v>106545</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>440742</v>
+        <v>440811</v>
       </c>
       <c r="R234" t="n">
-        <v>6762004</v>
+        <v>6762474</v>
       </c>
       <c r="S234" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -24823,7 +24823,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -24838,22 +24838,22 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>127275615</v>
+        <v>127283123</v>
       </c>
       <c r="B235" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24861,42 +24861,37 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>440778</v>
+        <v>440917</v>
       </c>
       <c r="R235" t="n">
-        <v>6762552</v>
+        <v>6762578</v>
       </c>
       <c r="S235" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -24923,19 +24918,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z235" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA235" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB235" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -24950,22 +24935,22 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127283123</v>
+        <v>127282930</v>
       </c>
       <c r="B236" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24993,14 +24978,14 @@
       <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>440917</v>
+        <v>440417</v>
       </c>
       <c r="R236" t="n">
-        <v>6762578</v>
+        <v>6762463</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -25047,22 +25032,22 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127282930</v>
+        <v>127271487</v>
       </c>
       <c r="B237" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -25090,14 +25075,14 @@
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>440417</v>
+        <v>440596</v>
       </c>
       <c r="R237" t="n">
-        <v>6762463</v>
+        <v>6762126</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25127,9 +25112,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA237" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB237" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25144,22 +25139,22 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>127271487</v>
+        <v>127283132</v>
       </c>
       <c r="B238" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -25187,14 +25182,14 @@
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>440596</v>
+        <v>440679</v>
       </c>
       <c r="R238" t="n">
-        <v>6762126</v>
+        <v>6762203</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25224,19 +25219,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z238" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB238" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -25251,22 +25236,22 @@
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>127283132</v>
+        <v>127282933</v>
       </c>
       <c r="B239" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -25294,14 +25279,14 @@
       <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>440679</v>
+        <v>440395</v>
       </c>
       <c r="R239" t="n">
-        <v>6762203</v>
+        <v>6762359</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25348,22 +25333,22 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127282933</v>
+        <v>127273778</v>
       </c>
       <c r="B240" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -25391,14 +25376,14 @@
       <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>440395</v>
+        <v>440734</v>
       </c>
       <c r="R240" t="n">
-        <v>6762359</v>
+        <v>6762076</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25428,9 +25413,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA240" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB240" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -25445,22 +25440,22 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>127273778</v>
+        <v>127282911</v>
       </c>
       <c r="B241" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -25488,14 +25483,14 @@
       <c r="I241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>440734</v>
+        <v>440874</v>
       </c>
       <c r="R241" t="n">
-        <v>6762076</v>
+        <v>6762606</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25525,19 +25520,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z241" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB241" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -25552,22 +25537,22 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>127282911</v>
+        <v>127271764</v>
       </c>
       <c r="B242" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -25595,17 +25580,17 @@
       <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>440874</v>
+        <v>440418</v>
       </c>
       <c r="R242" t="n">
-        <v>6762606</v>
+        <v>6762449</v>
       </c>
       <c r="S242" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -25632,9 +25617,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA242" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -25649,22 +25644,22 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127271764</v>
+        <v>127275615</v>
       </c>
       <c r="B243" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25672,34 +25667,39 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P243" t="inlineStr">
         <is>
           <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>440418</v>
+        <v>440778</v>
       </c>
       <c r="R243" t="n">
-        <v>6762449</v>
+        <v>6762552</v>
       </c>
       <c r="S243" t="n">
         <v>9</v>
@@ -25731,7 +25731,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -25741,7 +25741,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -25880,32 +25880,32 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127282894</v>
+        <v>127282891</v>
       </c>
       <c r="B245" t="n">
-        <v>79035</v>
+        <v>79632</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25915,10 +25915,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>440951</v>
+        <v>440416</v>
       </c>
       <c r="R245" t="n">
-        <v>6762514</v>
+        <v>6762406</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25977,32 +25977,32 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127282891</v>
+        <v>127282894</v>
       </c>
       <c r="B246" t="n">
-        <v>79629</v>
+        <v>79038</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -26012,10 +26012,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>440416</v>
+        <v>440951</v>
       </c>
       <c r="R246" t="n">
-        <v>6762406</v>
+        <v>6762514</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -26077,7 +26077,7 @@
         <v>127274466</v>
       </c>
       <c r="B247" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>127272935</v>
       </c>
       <c r="B248" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>127272422</v>
       </c>
       <c r="B249" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>127270746</v>
       </c>
       <c r="B250" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>127271817</v>
       </c>
       <c r="B251" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26958,7 +26958,7 @@
         <v>127282913</v>
       </c>
       <c r="B255" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>127282928</v>
       </c>
       <c r="B256" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>127282908</v>
       </c>
       <c r="B257" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>127271449</v>
       </c>
       <c r="B258" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>127282893</v>
       </c>
       <c r="B259" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>127282916</v>
       </c>
       <c r="B260" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -27550,7 +27550,7 @@
         <v>127274471</v>
       </c>
       <c r="B261" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -27654,10 +27654,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>127282905</v>
+        <v>127276264</v>
       </c>
       <c r="B262" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -27665,34 +27665,39 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>440780</v>
+        <v>440642</v>
       </c>
       <c r="R262" t="n">
-        <v>6762578</v>
+        <v>6762606</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27722,9 +27727,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA262" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -27739,57 +27754,57 @@
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>127282934</v>
+        <v>127274680</v>
       </c>
       <c r="B263" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>440387</v>
+        <v>440689</v>
       </c>
       <c r="R263" t="n">
-        <v>6762369</v>
+        <v>6762214</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27819,9 +27834,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA263" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -27836,22 +27861,22 @@
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>127275330</v>
+        <v>127282905</v>
       </c>
       <c r="B264" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -27879,17 +27904,17 @@
       <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>440868</v>
+        <v>440780</v>
       </c>
       <c r="R264" t="n">
-        <v>6762512</v>
+        <v>6762578</v>
       </c>
       <c r="S264" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -27916,19 +27941,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z264" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA264" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB264" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -27943,22 +27958,22 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>127282923</v>
+        <v>127282934</v>
       </c>
       <c r="B265" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -27990,10 +28005,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>440658</v>
+        <v>440387</v>
       </c>
       <c r="R265" t="n">
-        <v>6762202</v>
+        <v>6762369</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -28052,10 +28067,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>127275346</v>
+        <v>127275330</v>
       </c>
       <c r="B266" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -28087,10 +28102,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>440853</v>
+        <v>440868</v>
       </c>
       <c r="R266" t="n">
-        <v>6762514</v>
+        <v>6762512</v>
       </c>
       <c r="S266" t="n">
         <v>9</v>
@@ -28122,7 +28137,7 @@
       </c>
       <c r="Z266" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
@@ -28132,7 +28147,7 @@
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -28159,10 +28174,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>127282921</v>
+        <v>127282923</v>
       </c>
       <c r="B267" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -28194,10 +28209,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>440680</v>
+        <v>440658</v>
       </c>
       <c r="R267" t="n">
-        <v>6762218</v>
+        <v>6762202</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -28256,32 +28271,32 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>127272941</v>
+        <v>127275346</v>
       </c>
       <c r="B268" t="n">
-        <v>79035</v>
+        <v>79014</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -28291,10 +28306,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>440613</v>
+        <v>440853</v>
       </c>
       <c r="R268" t="n">
-        <v>6762174</v>
+        <v>6762514</v>
       </c>
       <c r="S268" t="n">
         <v>9</v>
@@ -28326,7 +28341,7 @@
       </c>
       <c r="Z268" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
@@ -28336,7 +28351,7 @@
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -28363,45 +28378,45 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>127274680</v>
+        <v>127282921</v>
       </c>
       <c r="B269" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>440689</v>
+        <v>440680</v>
       </c>
       <c r="R269" t="n">
-        <v>6762214</v>
+        <v>6762218</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -28431,19 +28446,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z269" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA269" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB269" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -28458,65 +28463,60 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>127276264</v>
+        <v>127272941</v>
       </c>
       <c r="B270" t="n">
-        <v>57654</v>
+        <v>79038</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
-      <c r="M270" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>440642</v>
+        <v>440613</v>
       </c>
       <c r="R270" t="n">
-        <v>6762606</v>
+        <v>6762174</v>
       </c>
       <c r="S270" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T270" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
       </c>
       <c r="Z270" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
@@ -28555,7 +28555,7 @@
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -28570,15 +28570,565 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>127330369</v>
+      </c>
+      <c r="B271" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr"/>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr"/>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>Dovsjövasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q271" t="n">
+        <v>440593</v>
+      </c>
+      <c r="R271" t="n">
+        <v>6762491</v>
+      </c>
+      <c r="S271" t="n">
+        <v>50</v>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
+      <c r="AD271" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE271" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG271" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT271" t="inlineStr"/>
+      <c r="AW271" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX271" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>127330346</v>
+      </c>
+      <c r="B272" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr"/>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>Dovsjövasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q272" t="n">
+        <v>440504</v>
+      </c>
+      <c r="R272" t="n">
+        <v>6762230</v>
+      </c>
+      <c r="S272" t="n">
+        <v>50</v>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD272" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE272" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG272" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT272" t="inlineStr"/>
+      <c r="AW272" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX272" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>127330161</v>
+      </c>
+      <c r="B273" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr"/>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>Dovsjövasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q273" t="n">
+        <v>440669</v>
+      </c>
+      <c r="R273" t="n">
+        <v>6762400</v>
+      </c>
+      <c r="S273" t="n">
+        <v>50</v>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD273" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE273" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG273" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT273" t="inlineStr"/>
+      <c r="AW273" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX273" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>127330473</v>
+      </c>
+      <c r="B274" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr"/>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>Dovsjövasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q274" t="n">
+        <v>440553</v>
+      </c>
+      <c r="R274" t="n">
+        <v>6762570</v>
+      </c>
+      <c r="S274" t="n">
+        <v>50</v>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
+        </is>
+      </c>
+      <c r="AD274" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE274" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG274" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT274" t="inlineStr"/>
+      <c r="AW274" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX274" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>127330280</v>
+      </c>
+      <c r="B275" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr"/>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>Dovsjövasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q275" t="n">
+        <v>440863</v>
+      </c>
+      <c r="R275" t="n">
+        <v>6762560</v>
+      </c>
+      <c r="S275" t="n">
+        <v>50</v>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD275" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE275" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG275" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT275" t="inlineStr"/>
+      <c r="AW275" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX275" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY275" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29945-2025 artfynd.xlsx
+++ b/artfynd/A 29945-2025 artfynd.xlsx
@@ -11348,7 +11348,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127272192</v>
+        <v>127275526</v>
       </c>
       <c r="B104" t="n">
         <v>79014</v>
@@ -11379,17 +11379,17 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>440522</v>
+        <v>440688</v>
       </c>
       <c r="R104" t="n">
-        <v>6762378</v>
+        <v>6762488</v>
       </c>
       <c r="S104" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11428,7 +11428,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11443,19 +11448,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127283121</v>
+        <v>127282929</v>
       </c>
       <c r="B105" t="n">
         <v>79014</v>
@@ -11486,14 +11491,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>440883</v>
+        <v>440440</v>
       </c>
       <c r="R105" t="n">
-        <v>6762587</v>
+        <v>6762463</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11540,19 +11545,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127275526</v>
+        <v>127272192</v>
       </c>
       <c r="B106" t="n">
         <v>79014</v>
@@ -11583,17 +11588,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>440688</v>
+        <v>440522</v>
       </c>
       <c r="R106" t="n">
-        <v>6762488</v>
+        <v>6762378</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11622,7 +11627,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11632,12 +11637,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11652,19 +11652,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127274454</v>
+        <v>127283121</v>
       </c>
       <c r="B107" t="n">
         <v>79014</v>
@@ -11695,17 +11695,17 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>440926</v>
+        <v>440883</v>
       </c>
       <c r="R107" t="n">
-        <v>6762599</v>
+        <v>6762587</v>
       </c>
       <c r="S107" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11732,19 +11732,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11759,19 +11749,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127282929</v>
+        <v>127274454</v>
       </c>
       <c r="B108" t="n">
         <v>79014</v>
@@ -11802,17 +11792,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>440440</v>
+        <v>440926</v>
       </c>
       <c r="R108" t="n">
-        <v>6762463</v>
+        <v>6762599</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11839,9 +11829,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11856,22 +11856,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127273727</v>
+        <v>127282896</v>
       </c>
       <c r="B109" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11879,34 +11879,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>440754</v>
+        <v>440416</v>
       </c>
       <c r="R109" t="n">
-        <v>6762035</v>
+        <v>6762406</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11936,19 +11936,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11963,19 +11953,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127282909</v>
+        <v>127274251</v>
       </c>
       <c r="B110" t="n">
         <v>79014</v>
@@ -12006,14 +11996,14 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>440797</v>
+        <v>440687</v>
       </c>
       <c r="R110" t="n">
-        <v>6762555</v>
+        <v>6762120</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12043,9 +12033,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12060,19 +12060,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127282922</v>
+        <v>127273727</v>
       </c>
       <c r="B111" t="n">
         <v>79014</v>
@@ -12103,14 +12103,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>440685</v>
+        <v>440754</v>
       </c>
       <c r="R111" t="n">
-        <v>6762213</v>
+        <v>6762035</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12140,9 +12140,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12157,19 +12167,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127282903</v>
+        <v>127282909</v>
       </c>
       <c r="B112" t="n">
         <v>79014</v>
@@ -12204,10 +12214,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>440760</v>
+        <v>440797</v>
       </c>
       <c r="R112" t="n">
-        <v>6762626</v>
+        <v>6762555</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12266,10 +12276,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127282896</v>
+        <v>127282922</v>
       </c>
       <c r="B113" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12277,21 +12287,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12301,10 +12311,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>440416</v>
+        <v>440685</v>
       </c>
       <c r="R113" t="n">
-        <v>6762406</v>
+        <v>6762213</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12363,7 +12373,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127274251</v>
+        <v>127282903</v>
       </c>
       <c r="B114" t="n">
         <v>79014</v>
@@ -12394,14 +12404,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>440687</v>
+        <v>440760</v>
       </c>
       <c r="R114" t="n">
-        <v>6762120</v>
+        <v>6762626</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12431,19 +12441,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12458,12 +12458,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -12689,10 +12689,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127274057</v>
+        <v>127276304</v>
       </c>
       <c r="B117" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12700,39 +12700,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>440706</v>
+        <v>440642</v>
       </c>
       <c r="R117" t="n">
-        <v>6762058</v>
+        <v>6762606</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12764,7 +12759,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12774,7 +12769,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12801,32 +12796,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127274061</v>
+        <v>127273755</v>
       </c>
       <c r="B118" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12836,10 +12831,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>440706</v>
+        <v>440744</v>
       </c>
       <c r="R118" t="n">
-        <v>6762058</v>
+        <v>6762065</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12908,10 +12903,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127283110</v>
+        <v>127275131</v>
       </c>
       <c r="B119" t="n">
-        <v>79015</v>
+        <v>79014</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12919,16 +12914,16 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -12939,14 +12934,14 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>440835</v>
+        <v>440709</v>
       </c>
       <c r="R119" t="n">
-        <v>6762564</v>
+        <v>6762405</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12976,9 +12971,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12993,19 +12998,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127273755</v>
+        <v>127271820</v>
       </c>
       <c r="B120" t="n">
         <v>79014</v>
@@ -13036,17 +13041,17 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>440744</v>
+        <v>440446</v>
       </c>
       <c r="R120" t="n">
-        <v>6762065</v>
+        <v>6762469</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13075,7 +13080,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13085,7 +13090,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13100,22 +13105,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127276304</v>
+        <v>127274057</v>
       </c>
       <c r="B121" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13123,34 +13128,39 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>440642</v>
+        <v>440706</v>
       </c>
       <c r="R121" t="n">
-        <v>6762606</v>
+        <v>6762058</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13182,7 +13192,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13192,7 +13202,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13219,32 +13229,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127275131</v>
+        <v>127274061</v>
       </c>
       <c r="B122" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13254,10 +13264,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>440709</v>
+        <v>440706</v>
       </c>
       <c r="R122" t="n">
-        <v>6762405</v>
+        <v>6762058</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13326,10 +13336,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127271820</v>
+        <v>127283110</v>
       </c>
       <c r="B123" t="n">
-        <v>79014</v>
+        <v>79015</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13337,16 +13347,16 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -13357,17 +13367,17 @@
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>440446</v>
+        <v>440835</v>
       </c>
       <c r="R123" t="n">
-        <v>6762469</v>
+        <v>6762564</v>
       </c>
       <c r="S123" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13394,19 +13404,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13421,22 +13421,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127283139</v>
+        <v>127271992</v>
       </c>
       <c r="B124" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13444,34 +13444,39 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>440723</v>
+        <v>440647</v>
       </c>
       <c r="R124" t="n">
-        <v>6762373</v>
+        <v>6762125</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13501,9 +13506,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13518,22 +13533,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127283131</v>
+        <v>127275968</v>
       </c>
       <c r="B125" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13541,34 +13556,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>440682</v>
+        <v>440723</v>
       </c>
       <c r="R125" t="n">
-        <v>6762208</v>
+        <v>6762648</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13598,9 +13613,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13615,19 +13640,19 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127283135</v>
+        <v>127283139</v>
       </c>
       <c r="B126" t="n">
         <v>79014</v>
@@ -13662,10 +13687,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>440456</v>
+        <v>440723</v>
       </c>
       <c r="R126" t="n">
-        <v>6762461</v>
+        <v>6762373</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13724,7 +13749,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127273828</v>
+        <v>127283131</v>
       </c>
       <c r="B127" t="n">
         <v>79014</v>
@@ -13755,17 +13780,17 @@
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>440882</v>
+        <v>440682</v>
       </c>
       <c r="R127" t="n">
-        <v>6762435</v>
+        <v>6762208</v>
       </c>
       <c r="S127" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13792,19 +13817,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13819,22 +13834,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127275968</v>
+        <v>127283135</v>
       </c>
       <c r="B128" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13842,34 +13857,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>440723</v>
+        <v>440456</v>
       </c>
       <c r="R128" t="n">
-        <v>6762648</v>
+        <v>6762461</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13899,19 +13914,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13926,22 +13931,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127271992</v>
+        <v>127273828</v>
       </c>
       <c r="B129" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13949,42 +13954,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>440647</v>
+        <v>440882</v>
       </c>
       <c r="R129" t="n">
-        <v>6762125</v>
+        <v>6762435</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14038,22 +14038,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127283109</v>
+        <v>127274657</v>
       </c>
       <c r="B130" t="n">
-        <v>79015</v>
+        <v>79014</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14061,16 +14061,16 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -14081,14 +14081,14 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>440875</v>
+        <v>440689</v>
       </c>
       <c r="R130" t="n">
-        <v>6762453</v>
+        <v>6762214</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14118,9 +14118,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14135,19 +14150,19 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127274657</v>
+        <v>127276216</v>
       </c>
       <c r="B131" t="n">
         <v>79014</v>
@@ -14182,10 +14197,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>440689</v>
+        <v>440657</v>
       </c>
       <c r="R131" t="n">
-        <v>6762214</v>
+        <v>6762603</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14217,7 +14232,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14227,12 +14242,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14259,7 +14269,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127283117</v>
+        <v>127273488</v>
       </c>
       <c r="B132" t="n">
         <v>79014</v>
@@ -14290,14 +14300,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>440863</v>
+        <v>440721</v>
       </c>
       <c r="R132" t="n">
-        <v>6762603</v>
+        <v>6761996</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14327,9 +14337,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14344,22 +14364,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127273051</v>
+        <v>127276148</v>
       </c>
       <c r="B133" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14367,37 +14387,42 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>440681</v>
+        <v>440657</v>
       </c>
       <c r="R133" t="n">
-        <v>6762197</v>
+        <v>6762603</v>
       </c>
       <c r="S133" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14426,7 +14451,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14436,7 +14461,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14451,22 +14476,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127282932</v>
+        <v>127272305</v>
       </c>
       <c r="B134" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14474,34 +14499,39 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>440427</v>
+        <v>440675</v>
       </c>
       <c r="R134" t="n">
-        <v>6762470</v>
+        <v>6762165</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14531,9 +14561,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Diameter ca 4 till 5 cm</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14548,22 +14593,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127282912</v>
+        <v>127271765</v>
       </c>
       <c r="B135" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14571,34 +14616,39 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>440936</v>
+        <v>440627</v>
       </c>
       <c r="R135" t="n">
-        <v>6762564</v>
+        <v>6762119</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14628,9 +14678,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Miljöbild för området</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14645,22 +14710,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127282926</v>
+        <v>127276450</v>
       </c>
       <c r="B136" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14668,34 +14733,39 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>440497</v>
+        <v>440582</v>
       </c>
       <c r="R136" t="n">
-        <v>6762331</v>
+        <v>6762684</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14725,9 +14795,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14742,19 +14822,19 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127283130</v>
+        <v>127283117</v>
       </c>
       <c r="B137" t="n">
         <v>79014</v>
@@ -14789,10 +14869,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>440697</v>
+        <v>440863</v>
       </c>
       <c r="R137" t="n">
-        <v>6762237</v>
+        <v>6762603</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14851,7 +14931,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127276216</v>
+        <v>127273051</v>
       </c>
       <c r="B138" t="n">
         <v>79014</v>
@@ -14882,17 +14962,17 @@
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>440657</v>
+        <v>440681</v>
       </c>
       <c r="R138" t="n">
-        <v>6762603</v>
+        <v>6762197</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14921,7 +15001,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14931,7 +15011,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14946,19 +15026,19 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127273488</v>
+        <v>127282932</v>
       </c>
       <c r="B139" t="n">
         <v>79014</v>
@@ -14989,14 +15069,14 @@
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>440721</v>
+        <v>440427</v>
       </c>
       <c r="R139" t="n">
-        <v>6761996</v>
+        <v>6762470</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15026,19 +15106,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15053,22 +15123,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127276148</v>
+        <v>127282912</v>
       </c>
       <c r="B140" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15076,39 +15146,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>440657</v>
+        <v>440936</v>
       </c>
       <c r="R140" t="n">
-        <v>6762603</v>
+        <v>6762564</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15138,19 +15203,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15165,22 +15220,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127272305</v>
+        <v>127282926</v>
       </c>
       <c r="B141" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15188,39 +15243,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>440675</v>
+        <v>440497</v>
       </c>
       <c r="R141" t="n">
-        <v>6762165</v>
+        <v>6762331</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15250,24 +15300,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Diameter ca 4 till 5 cm</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15282,22 +15317,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127271765</v>
+        <v>127283130</v>
       </c>
       <c r="B142" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15305,39 +15340,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>440627</v>
+        <v>440697</v>
       </c>
       <c r="R142" t="n">
-        <v>6762119</v>
+        <v>6762237</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15367,24 +15397,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Miljöbild för området</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15399,62 +15414,57 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127276450</v>
+        <v>127283108</v>
       </c>
       <c r="B143" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>440582</v>
+        <v>440442</v>
       </c>
       <c r="R143" t="n">
-        <v>6762684</v>
+        <v>6762471</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15484,19 +15494,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15511,19 +15511,19 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127283108</v>
+        <v>127282895</v>
       </c>
       <c r="B144" t="n">
         <v>8447</v>
@@ -15554,14 +15554,14 @@
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>440442</v>
+        <v>440382</v>
       </c>
       <c r="R144" t="n">
-        <v>6762471</v>
+        <v>6762379</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15608,57 +15608,57 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127282895</v>
+        <v>127283109</v>
       </c>
       <c r="B145" t="n">
-        <v>8447</v>
+        <v>79015</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>440382</v>
+        <v>440875</v>
       </c>
       <c r="R145" t="n">
-        <v>6762379</v>
+        <v>6762453</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15705,12 +15705,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
@@ -15921,7 +15921,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127283119</v>
+        <v>127272858</v>
       </c>
       <c r="B148" t="n">
         <v>79014</v>
@@ -15952,17 +15952,17 @@
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>440881</v>
+        <v>440609</v>
       </c>
       <c r="R148" t="n">
-        <v>6762591</v>
+        <v>6762190</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15989,9 +15989,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16006,19 +16016,19 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127272858</v>
+        <v>127283119</v>
       </c>
       <c r="B149" t="n">
         <v>79014</v>
@@ -16049,17 +16059,17 @@
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>440609</v>
+        <v>440881</v>
       </c>
       <c r="R149" t="n">
-        <v>6762190</v>
+        <v>6762591</v>
       </c>
       <c r="S149" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16086,19 +16096,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16113,12 +16113,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
@@ -16747,10 +16747,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127283105</v>
+        <v>127274354</v>
       </c>
       <c r="B156" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16758,34 +16758,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>440909</v>
+        <v>440686</v>
       </c>
       <c r="R156" t="n">
-        <v>6762467</v>
+        <v>6762176</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16815,9 +16815,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16832,19 +16842,19 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127274354</v>
+        <v>127272746</v>
       </c>
       <c r="B157" t="n">
         <v>79014</v>
@@ -16875,17 +16885,17 @@
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>440686</v>
+        <v>440503</v>
       </c>
       <c r="R157" t="n">
-        <v>6762176</v>
+        <v>6762308</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16914,7 +16924,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16924,7 +16934,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16939,22 +16949,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127272746</v>
+        <v>127283105</v>
       </c>
       <c r="B158" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16962,37 +16972,37 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>440503</v>
+        <v>440909</v>
       </c>
       <c r="R158" t="n">
-        <v>6762308</v>
+        <v>6762467</v>
       </c>
       <c r="S158" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17019,19 +17029,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17046,12 +17046,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -17170,10 +17170,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127275098</v>
+        <v>127282902</v>
       </c>
       <c r="B160" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17181,39 +17181,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>440679</v>
+        <v>440760</v>
       </c>
       <c r="R160" t="n">
-        <v>6762388</v>
+        <v>6762569</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17243,19 +17238,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17270,12 +17255,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -17700,7 +17685,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127282902</v>
+        <v>127273086</v>
       </c>
       <c r="B165" t="n">
         <v>79014</v>
@@ -17731,17 +17716,17 @@
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>440760</v>
+        <v>440694</v>
       </c>
       <c r="R165" t="n">
-        <v>6762569</v>
+        <v>6762204</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -17768,9 +17753,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17785,19 +17780,19 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127273086</v>
+        <v>127283137</v>
       </c>
       <c r="B166" t="n">
         <v>79014</v>
@@ -17828,17 +17823,17 @@
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>440694</v>
+        <v>440354</v>
       </c>
       <c r="R166" t="n">
-        <v>6762204</v>
+        <v>6762415</v>
       </c>
       <c r="S166" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17865,19 +17860,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>12:40</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17892,22 +17877,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127283137</v>
+        <v>127274348</v>
       </c>
       <c r="B167" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17915,34 +17900,39 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>440354</v>
+        <v>440686</v>
       </c>
       <c r="R167" t="n">
-        <v>6762415</v>
+        <v>6762176</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17972,9 +17962,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17989,22 +17989,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127274348</v>
+        <v>127275098</v>
       </c>
       <c r="B168" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18012,16 +18012,16 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -18041,10 +18041,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>440686</v>
+        <v>440679</v>
       </c>
       <c r="R168" t="n">
-        <v>6762176</v>
+        <v>6762388</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18113,48 +18113,48 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127273853</v>
+        <v>127271802</v>
       </c>
       <c r="B169" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>440887</v>
+        <v>440627</v>
       </c>
       <c r="R169" t="n">
-        <v>6762439</v>
+        <v>6762119</v>
       </c>
       <c r="S169" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18193,7 +18193,12 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Rikligt med torrakor med spår efter Mindre Märgborre i området</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18208,60 +18213,65 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127270744</v>
+        <v>127271251</v>
       </c>
       <c r="B170" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>440351</v>
+        <v>440375</v>
       </c>
       <c r="R170" t="n">
-        <v>6762480</v>
+        <v>6762366</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18290,7 +18300,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18300,7 +18310,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18315,60 +18325,60 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127275337</v>
+        <v>127276271</v>
       </c>
       <c r="B171" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>440855</v>
+        <v>440642</v>
       </c>
       <c r="R171" t="n">
-        <v>6762513</v>
+        <v>6762606</v>
       </c>
       <c r="S171" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18397,7 +18407,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18407,7 +18417,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18422,19 +18432,19 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127282927</v>
+        <v>127273853</v>
       </c>
       <c r="B172" t="n">
         <v>79014</v>
@@ -18465,17 +18475,17 @@
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>440488</v>
+        <v>440887</v>
       </c>
       <c r="R172" t="n">
-        <v>6762419</v>
+        <v>6762439</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18502,9 +18512,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18519,19 +18539,19 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127283128</v>
+        <v>127270744</v>
       </c>
       <c r="B173" t="n">
         <v>79014</v>
@@ -18562,14 +18582,14 @@
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>440822</v>
+        <v>440351</v>
       </c>
       <c r="R173" t="n">
-        <v>6762415</v>
+        <v>6762480</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18599,9 +18619,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18616,19 +18646,19 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127274114</v>
+        <v>127275337</v>
       </c>
       <c r="B174" t="n">
         <v>79014</v>
@@ -18659,17 +18689,17 @@
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>440711</v>
+        <v>440855</v>
       </c>
       <c r="R174" t="n">
-        <v>6762111</v>
+        <v>6762513</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -18698,7 +18728,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -18708,7 +18738,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18723,19 +18753,19 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127283115</v>
+        <v>127282927</v>
       </c>
       <c r="B175" t="n">
         <v>79014</v>
@@ -18766,14 +18796,14 @@
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>440803</v>
+        <v>440488</v>
       </c>
       <c r="R175" t="n">
-        <v>6762557</v>
+        <v>6762419</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18820,19 +18850,19 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127283134</v>
+        <v>127283128</v>
       </c>
       <c r="B176" t="n">
         <v>79014</v>
@@ -18867,10 +18897,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>440487</v>
+        <v>440822</v>
       </c>
       <c r="R176" t="n">
-        <v>6762321</v>
+        <v>6762415</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18929,7 +18959,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127283133</v>
+        <v>127274114</v>
       </c>
       <c r="B177" t="n">
         <v>79014</v>
@@ -18960,14 +18990,14 @@
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>440598</v>
+        <v>440711</v>
       </c>
       <c r="R177" t="n">
-        <v>6762206</v>
+        <v>6762111</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18997,9 +19027,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19014,57 +19054,57 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127271802</v>
+        <v>127283115</v>
       </c>
       <c r="B178" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>440627</v>
+        <v>440803</v>
       </c>
       <c r="R178" t="n">
-        <v>6762119</v>
+        <v>6762557</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19094,24 +19134,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Rikligt med torrakor med spår efter Mindre Märgborre i området</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19126,65 +19151,60 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127271251</v>
+        <v>127283134</v>
       </c>
       <c r="B179" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>440375</v>
+        <v>440487</v>
       </c>
       <c r="R179" t="n">
-        <v>6762366</v>
+        <v>6762321</v>
       </c>
       <c r="S179" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19211,19 +19231,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>10:53</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19238,57 +19248,57 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127276271</v>
+        <v>127283133</v>
       </c>
       <c r="B180" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>440642</v>
+        <v>440598</v>
       </c>
       <c r="R180" t="n">
-        <v>6762606</v>
+        <v>6762206</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19318,19 +19328,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19345,12 +19345,12 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
@@ -20770,10 +20770,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127274677</v>
+        <v>127276018</v>
       </c>
       <c r="B195" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20781,39 +20781,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>440689</v>
+        <v>440697</v>
       </c>
       <c r="R195" t="n">
-        <v>6762214</v>
+        <v>6762625</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20845,7 +20840,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -20855,7 +20850,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20882,48 +20877,48 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127283143</v>
+        <v>127275350</v>
       </c>
       <c r="B196" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>440337</v>
+        <v>440851</v>
       </c>
       <c r="R196" t="n">
-        <v>6762397</v>
+        <v>6762513</v>
       </c>
       <c r="S196" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -20950,9 +20945,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20967,57 +20972,57 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127272174</v>
+        <v>127283124</v>
       </c>
       <c r="B197" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>440657</v>
+        <v>440965</v>
       </c>
       <c r="R197" t="n">
-        <v>6762157</v>
+        <v>6762540</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21047,19 +21052,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21074,19 +21069,19 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127276018</v>
+        <v>127272147</v>
       </c>
       <c r="B198" t="n">
         <v>79014</v>
@@ -21117,17 +21112,17 @@
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>440697</v>
+        <v>440498</v>
       </c>
       <c r="R198" t="n">
-        <v>6762625</v>
+        <v>6762428</v>
       </c>
       <c r="S198" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -21156,7 +21151,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21166,7 +21161,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21181,22 +21176,22 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127275350</v>
+        <v>127274677</v>
       </c>
       <c r="B199" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21204,37 +21199,42 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>440851</v>
+        <v>440689</v>
       </c>
       <c r="R199" t="n">
-        <v>6762513</v>
+        <v>6762214</v>
       </c>
       <c r="S199" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21288,44 +21288,44 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127283124</v>
+        <v>127283143</v>
       </c>
       <c r="B200" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21335,10 +21335,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>440965</v>
+        <v>440337</v>
       </c>
       <c r="R200" t="n">
-        <v>6762540</v>
+        <v>6762397</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21397,48 +21397,48 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127272147</v>
+        <v>127272174</v>
       </c>
       <c r="B201" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>440498</v>
+        <v>440657</v>
       </c>
       <c r="R201" t="n">
-        <v>6762428</v>
+        <v>6762157</v>
       </c>
       <c r="S201" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21477,7 +21477,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21492,22 +21492,22 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127275348</v>
+        <v>127271427</v>
       </c>
       <c r="B202" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21515,37 +21515,37 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>440677</v>
+        <v>440457</v>
       </c>
       <c r="R202" t="n">
-        <v>6762469</v>
+        <v>6762399</v>
       </c>
       <c r="S202" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -21584,7 +21584,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21599,19 +21599,19 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127282910</v>
+        <v>127275348</v>
       </c>
       <c r="B203" t="n">
         <v>79014</v>
@@ -21642,14 +21642,14 @@
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>440807</v>
+        <v>440677</v>
       </c>
       <c r="R203" t="n">
-        <v>6762574</v>
+        <v>6762469</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21679,9 +21679,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21696,19 +21706,19 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127271972</v>
+        <v>127282910</v>
       </c>
       <c r="B204" t="n">
         <v>79014</v>
@@ -21739,17 +21749,17 @@
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>440460</v>
+        <v>440807</v>
       </c>
       <c r="R204" t="n">
-        <v>6762457</v>
+        <v>6762574</v>
       </c>
       <c r="S204" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -21776,24 +21786,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>På Gran</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21808,19 +21803,19 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>127272958</v>
+        <v>127271972</v>
       </c>
       <c r="B205" t="n">
         <v>79014</v>
@@ -21855,10 +21850,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>440619</v>
+        <v>440460</v>
       </c>
       <c r="R205" t="n">
-        <v>6762170</v>
+        <v>6762457</v>
       </c>
       <c r="S205" t="n">
         <v>9</v>
@@ -21890,7 +21885,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -21900,7 +21895,12 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>På Gran</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -21927,7 +21927,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127283114</v>
+        <v>127272958</v>
       </c>
       <c r="B206" t="n">
         <v>79014</v>
@@ -21958,17 +21958,17 @@
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>440806</v>
+        <v>440619</v>
       </c>
       <c r="R206" t="n">
-        <v>6762533</v>
+        <v>6762170</v>
       </c>
       <c r="S206" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -21995,9 +21995,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22012,19 +22022,19 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127282897</v>
+        <v>127283114</v>
       </c>
       <c r="B207" t="n">
         <v>79014</v>
@@ -22055,14 +22065,14 @@
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>440613</v>
+        <v>440806</v>
       </c>
       <c r="R207" t="n">
-        <v>6762197</v>
+        <v>6762533</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22109,19 +22119,19 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127282920</v>
+        <v>127282897</v>
       </c>
       <c r="B208" t="n">
         <v>79014</v>
@@ -22156,10 +22166,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>440696</v>
+        <v>440613</v>
       </c>
       <c r="R208" t="n">
-        <v>6762239</v>
+        <v>6762197</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22218,10 +22228,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127271427</v>
+        <v>127282920</v>
       </c>
       <c r="B209" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -22229,37 +22239,37 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>440457</v>
+        <v>440696</v>
       </c>
       <c r="R209" t="n">
-        <v>6762399</v>
+        <v>6762239</v>
       </c>
       <c r="S209" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -22286,19 +22296,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -22313,22 +22313,22 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127282901</v>
+        <v>127283102</v>
       </c>
       <c r="B210" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -22336,34 +22336,34 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>440751</v>
+        <v>440726</v>
       </c>
       <c r="R210" t="n">
-        <v>6762564</v>
+        <v>6762638</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22410,22 +22410,22 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127283112</v>
+        <v>127283104</v>
       </c>
       <c r="B211" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -22433,21 +22433,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -22457,10 +22457,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>440663</v>
+        <v>440766</v>
       </c>
       <c r="R211" t="n">
-        <v>6762599</v>
+        <v>6762565</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22519,10 +22519,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127283102</v>
+        <v>127274242</v>
       </c>
       <c r="B212" t="n">
-        <v>79632</v>
+        <v>57654</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -22530,34 +22530,39 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>440726</v>
+        <v>440697</v>
       </c>
       <c r="R212" t="n">
-        <v>6762638</v>
+        <v>6762119</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22587,9 +22592,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -22604,19 +22619,19 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127272352</v>
+        <v>127282901</v>
       </c>
       <c r="B213" t="n">
         <v>79014</v>
@@ -22647,14 +22662,14 @@
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>440685</v>
+        <v>440751</v>
       </c>
       <c r="R213" t="n">
-        <v>6762109</v>
+        <v>6762564</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22684,19 +22699,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z213" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA213" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB213" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -22711,19 +22716,19 @@
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127273790</v>
+        <v>127283112</v>
       </c>
       <c r="B214" t="n">
         <v>79014</v>
@@ -22754,17 +22759,17 @@
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>440854</v>
+        <v>440663</v>
       </c>
       <c r="R214" t="n">
-        <v>6762427</v>
+        <v>6762599</v>
       </c>
       <c r="S214" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -22791,19 +22796,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z214" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA214" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB214" t="inlineStr">
-        <is>
-          <t>13:15</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -22818,19 +22813,19 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127273057</v>
+        <v>127272352</v>
       </c>
       <c r="B215" t="n">
         <v>79014</v>
@@ -22861,17 +22856,17 @@
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>440681</v>
+        <v>440685</v>
       </c>
       <c r="R215" t="n">
-        <v>6762195</v>
+        <v>6762109</v>
       </c>
       <c r="S215" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -22900,7 +22895,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -22910,7 +22905,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -22925,22 +22920,22 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127274242</v>
+        <v>127273790</v>
       </c>
       <c r="B216" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22948,42 +22943,37 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>440697</v>
+        <v>440854</v>
       </c>
       <c r="R216" t="n">
-        <v>6762119</v>
+        <v>6762427</v>
       </c>
       <c r="S216" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -23012,7 +23002,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -23022,7 +23012,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23037,22 +23027,22 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127283104</v>
+        <v>127273057</v>
       </c>
       <c r="B217" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23060,37 +23050,37 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>440766</v>
+        <v>440681</v>
       </c>
       <c r="R217" t="n">
-        <v>6762565</v>
+        <v>6762195</v>
       </c>
       <c r="S217" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -23117,9 +23107,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
       <c r="AA217" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -23134,22 +23134,22 @@
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127283106</v>
+        <v>127283141</v>
       </c>
       <c r="B218" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23157,21 +23157,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -23181,10 +23181,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>440504</v>
+        <v>440651</v>
       </c>
       <c r="R218" t="n">
-        <v>6762388</v>
+        <v>6762611</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23243,10 +23243,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127283141</v>
+        <v>127283106</v>
       </c>
       <c r="B219" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23254,21 +23254,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -23278,10 +23278,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>440651</v>
+        <v>440504</v>
       </c>
       <c r="R219" t="n">
-        <v>6762611</v>
+        <v>6762388</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23340,7 +23340,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127282898</v>
+        <v>127282915</v>
       </c>
       <c r="B220" t="n">
         <v>79014</v>
@@ -23375,10 +23375,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>440741</v>
+        <v>440946</v>
       </c>
       <c r="R220" t="n">
-        <v>6762609</v>
+        <v>6762514</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23437,7 +23437,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127283122</v>
+        <v>127275040</v>
       </c>
       <c r="B221" t="n">
         <v>79014</v>
@@ -23468,14 +23468,14 @@
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>440912</v>
+        <v>440745</v>
       </c>
       <c r="R221" t="n">
-        <v>6762579</v>
+        <v>6762369</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23505,9 +23505,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -23522,22 +23537,22 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127282915</v>
+        <v>127283100</v>
       </c>
       <c r="B222" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23545,34 +23560,34 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>440946</v>
+        <v>440686</v>
       </c>
       <c r="R222" t="n">
-        <v>6762514</v>
+        <v>6762630</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23619,19 +23634,19 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127275040</v>
+        <v>127282898</v>
       </c>
       <c r="B223" t="n">
         <v>79014</v>
@@ -23662,14 +23677,14 @@
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>440745</v>
+        <v>440741</v>
       </c>
       <c r="R223" t="n">
-        <v>6762369</v>
+        <v>6762609</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23699,24 +23714,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z223" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA223" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB223" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -23731,19 +23731,19 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127282899</v>
+        <v>127283122</v>
       </c>
       <c r="B224" t="n">
         <v>79014</v>
@@ -23774,14 +23774,14 @@
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>440763</v>
+        <v>440912</v>
       </c>
       <c r="R224" t="n">
-        <v>6762529</v>
+        <v>6762579</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23828,22 +23828,22 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127283100</v>
+        <v>127282899</v>
       </c>
       <c r="B225" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23851,34 +23851,34 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>440686</v>
+        <v>440763</v>
       </c>
       <c r="R225" t="n">
-        <v>6762630</v>
+        <v>6762529</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23925,12 +23925,12 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
@@ -24034,45 +24034,45 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127283126</v>
+        <v>127273585</v>
       </c>
       <c r="B227" t="n">
-        <v>79014</v>
+        <v>91683</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>440923</v>
+        <v>440742</v>
       </c>
       <c r="R227" t="n">
-        <v>6762482</v>
+        <v>6762004</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24102,9 +24102,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA227" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24119,19 +24129,19 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127282918</v>
+        <v>127273660</v>
       </c>
       <c r="B228" t="n">
         <v>79014</v>
@@ -24162,14 +24172,14 @@
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>440832</v>
+        <v>440742</v>
       </c>
       <c r="R228" t="n">
-        <v>6762387</v>
+        <v>6762004</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24199,9 +24209,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA228" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -24216,19 +24236,19 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127282917</v>
+        <v>127283126</v>
       </c>
       <c r="B229" t="n">
         <v>79014</v>
@@ -24259,14 +24279,14 @@
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>440919</v>
+        <v>440923</v>
       </c>
       <c r="R229" t="n">
-        <v>6762497</v>
+        <v>6762482</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24313,19 +24333,19 @@
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127283125</v>
+        <v>127282918</v>
       </c>
       <c r="B230" t="n">
         <v>79014</v>
@@ -24356,14 +24376,14 @@
       <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>440989</v>
+        <v>440832</v>
       </c>
       <c r="R230" t="n">
-        <v>6762519</v>
+        <v>6762387</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24410,19 +24430,19 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127273660</v>
+        <v>127282917</v>
       </c>
       <c r="B231" t="n">
         <v>79014</v>
@@ -24453,14 +24473,14 @@
       <c r="I231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>440742</v>
+        <v>440919</v>
       </c>
       <c r="R231" t="n">
-        <v>6762004</v>
+        <v>6762497</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24490,19 +24510,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z231" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB231" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24517,19 +24527,19 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127275120</v>
+        <v>127283125</v>
       </c>
       <c r="B232" t="n">
         <v>79014</v>
@@ -24560,17 +24570,17 @@
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>440897</v>
+        <v>440989</v>
       </c>
       <c r="R232" t="n">
-        <v>6762548</v>
+        <v>6762519</v>
       </c>
       <c r="S232" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -24597,19 +24607,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z232" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB232" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24624,60 +24624,60 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127273585</v>
+        <v>127275120</v>
       </c>
       <c r="B233" t="n">
-        <v>91683</v>
+        <v>79014</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>440742</v>
+        <v>440897</v>
       </c>
       <c r="R233" t="n">
-        <v>6762004</v>
+        <v>6762548</v>
       </c>
       <c r="S233" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -24706,7 +24706,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -24716,7 +24716,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -24731,12 +24731,12 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
@@ -24850,7 +24850,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>127283123</v>
+        <v>127282930</v>
       </c>
       <c r="B235" t="n">
         <v>79014</v>
@@ -24881,14 +24881,14 @@
       <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>440917</v>
+        <v>440417</v>
       </c>
       <c r="R235" t="n">
-        <v>6762578</v>
+        <v>6762463</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24935,22 +24935,22 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127282930</v>
+        <v>127275615</v>
       </c>
       <c r="B236" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24958,37 +24958,42 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>440417</v>
+        <v>440778</v>
       </c>
       <c r="R236" t="n">
-        <v>6762463</v>
+        <v>6762552</v>
       </c>
       <c r="S236" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -25015,9 +25020,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA236" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -25032,19 +25047,19 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127271487</v>
+        <v>127283123</v>
       </c>
       <c r="B237" t="n">
         <v>79014</v>
@@ -25075,14 +25090,14 @@
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>440596</v>
+        <v>440917</v>
       </c>
       <c r="R237" t="n">
-        <v>6762126</v>
+        <v>6762578</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25112,19 +25127,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z237" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA237" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB237" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25139,19 +25144,19 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>127283132</v>
+        <v>127271487</v>
       </c>
       <c r="B238" t="n">
         <v>79014</v>
@@ -25182,14 +25187,14 @@
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>440679</v>
+        <v>440596</v>
       </c>
       <c r="R238" t="n">
-        <v>6762203</v>
+        <v>6762126</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25219,9 +25224,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -25236,19 +25251,19 @@
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>127282933</v>
+        <v>127283132</v>
       </c>
       <c r="B239" t="n">
         <v>79014</v>
@@ -25279,14 +25294,14 @@
       <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>440395</v>
+        <v>440679</v>
       </c>
       <c r="R239" t="n">
-        <v>6762359</v>
+        <v>6762203</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25333,19 +25348,19 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127273778</v>
+        <v>127282933</v>
       </c>
       <c r="B240" t="n">
         <v>79014</v>
@@ -25376,14 +25391,14 @@
       <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>440734</v>
+        <v>440395</v>
       </c>
       <c r="R240" t="n">
-        <v>6762076</v>
+        <v>6762359</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25413,19 +25428,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z240" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA240" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB240" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -25440,19 +25445,19 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>127282911</v>
+        <v>127273778</v>
       </c>
       <c r="B241" t="n">
         <v>79014</v>
@@ -25483,14 +25488,14 @@
       <c r="I241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>440874</v>
+        <v>440734</v>
       </c>
       <c r="R241" t="n">
-        <v>6762606</v>
+        <v>6762076</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25520,9 +25525,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB241" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -25537,19 +25552,19 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>127271764</v>
+        <v>127282911</v>
       </c>
       <c r="B242" t="n">
         <v>79014</v>
@@ -25580,17 +25595,17 @@
       <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>440418</v>
+        <v>440874</v>
       </c>
       <c r="R242" t="n">
-        <v>6762449</v>
+        <v>6762606</v>
       </c>
       <c r="S242" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -25617,19 +25632,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z242" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA242" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB242" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -25644,22 +25649,22 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127275615</v>
+        <v>127271764</v>
       </c>
       <c r="B243" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25667,39 +25672,34 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P243" t="inlineStr">
         <is>
           <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>440778</v>
+        <v>440418</v>
       </c>
       <c r="R243" t="n">
-        <v>6762552</v>
+        <v>6762449</v>
       </c>
       <c r="S243" t="n">
         <v>9</v>
@@ -25731,7 +25731,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -25741,7 +25741,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -25880,32 +25880,32 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127282891</v>
+        <v>127282894</v>
       </c>
       <c r="B245" t="n">
-        <v>79632</v>
+        <v>79038</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25915,10 +25915,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>440416</v>
+        <v>440951</v>
       </c>
       <c r="R245" t="n">
-        <v>6762406</v>
+        <v>6762514</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25977,32 +25977,32 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127282894</v>
+        <v>127282891</v>
       </c>
       <c r="B246" t="n">
-        <v>79038</v>
+        <v>79632</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -26012,10 +26012,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>440951</v>
+        <v>440416</v>
       </c>
       <c r="R246" t="n">
-        <v>6762514</v>
+        <v>6762406</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -26181,7 +26181,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>127272935</v>
+        <v>127272422</v>
       </c>
       <c r="B248" t="n">
         <v>79014</v>
@@ -26212,17 +26212,17 @@
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>440613</v>
+        <v>440682</v>
       </c>
       <c r="R248" t="n">
-        <v>6762174</v>
+        <v>6762093</v>
       </c>
       <c r="S248" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -26261,7 +26261,12 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>Garnlav på äldre tall, sannoligt äldre än 200 år</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26276,19 +26281,19 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>127272422</v>
+        <v>127272935</v>
       </c>
       <c r="B249" t="n">
         <v>79014</v>
@@ -26319,17 +26324,17 @@
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>440682</v>
+        <v>440613</v>
       </c>
       <c r="R249" t="n">
-        <v>6762093</v>
+        <v>6762174</v>
       </c>
       <c r="S249" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -26358,7 +26363,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -26368,12 +26373,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>Garnlav på äldre tall, sannoligt äldre än 200 år</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -26388,12 +26388,12 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
@@ -27654,10 +27654,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>127276264</v>
+        <v>127282921</v>
       </c>
       <c r="B262" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -27665,39 +27665,34 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>440642</v>
+        <v>440680</v>
       </c>
       <c r="R262" t="n">
-        <v>6762606</v>
+        <v>6762218</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27727,19 +27722,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z262" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA262" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB262" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -27754,22 +27739,22 @@
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>127274680</v>
+        <v>127272941</v>
       </c>
       <c r="B263" t="n">
-        <v>8447</v>
+        <v>79038</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -27777,37 +27762,37 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>106545</v>
+        <v>6434</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>440689</v>
+        <v>440613</v>
       </c>
       <c r="R263" t="n">
-        <v>6762214</v>
+        <v>6762174</v>
       </c>
       <c r="S263" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -27836,7 +27821,7 @@
       </c>
       <c r="Z263" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
@@ -27846,7 +27831,7 @@
       </c>
       <c r="AB263" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -27861,12 +27846,12 @@
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
@@ -28378,10 +28363,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>127282921</v>
+        <v>127276264</v>
       </c>
       <c r="B269" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -28389,34 +28374,39 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>440680</v>
+        <v>440642</v>
       </c>
       <c r="R269" t="n">
-        <v>6762218</v>
+        <v>6762606</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -28446,9 +28436,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA269" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -28463,22 +28463,22 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>127272941</v>
+        <v>127274680</v>
       </c>
       <c r="B270" t="n">
-        <v>79038</v>
+        <v>8447</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -28486,37 +28486,37 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6434</v>
+        <v>106545</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>440613</v>
+        <v>440689</v>
       </c>
       <c r="R270" t="n">
-        <v>6762174</v>
+        <v>6762214</v>
       </c>
       <c r="S270" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T270" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
       </c>
       <c r="Z270" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
@@ -28555,7 +28555,7 @@
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -28570,12 +28570,12 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>

--- a/artfynd/A 29945-2025 artfynd.xlsx
+++ b/artfynd/A 29945-2025 artfynd.xlsx
@@ -11348,7 +11348,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127275526</v>
+        <v>127272192</v>
       </c>
       <c r="B104" t="n">
         <v>79014</v>
@@ -11379,17 +11379,17 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>440688</v>
+        <v>440522</v>
       </c>
       <c r="R104" t="n">
-        <v>6762488</v>
+        <v>6762378</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11428,12 +11428,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11448,19 +11443,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127282929</v>
+        <v>127283121</v>
       </c>
       <c r="B105" t="n">
         <v>79014</v>
@@ -11491,14 +11486,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>440440</v>
+        <v>440883</v>
       </c>
       <c r="R105" t="n">
-        <v>6762463</v>
+        <v>6762587</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11545,19 +11540,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127272192</v>
+        <v>127274454</v>
       </c>
       <c r="B106" t="n">
         <v>79014</v>
@@ -11592,10 +11587,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>440522</v>
+        <v>440926</v>
       </c>
       <c r="R106" t="n">
-        <v>6762378</v>
+        <v>6762599</v>
       </c>
       <c r="S106" t="n">
         <v>9</v>
@@ -11627,7 +11622,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11637,7 +11632,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11664,7 +11659,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127283121</v>
+        <v>127275526</v>
       </c>
       <c r="B107" t="n">
         <v>79014</v>
@@ -11695,14 +11690,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>440883</v>
+        <v>440688</v>
       </c>
       <c r="R107" t="n">
-        <v>6762587</v>
+        <v>6762488</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11732,9 +11727,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11749,19 +11759,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127274454</v>
+        <v>127282929</v>
       </c>
       <c r="B108" t="n">
         <v>79014</v>
@@ -11792,17 +11802,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>440926</v>
+        <v>440440</v>
       </c>
       <c r="R108" t="n">
-        <v>6762599</v>
+        <v>6762463</v>
       </c>
       <c r="S108" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11829,19 +11839,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11856,12 +11856,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -13433,10 +13433,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127271992</v>
+        <v>127275968</v>
       </c>
       <c r="B124" t="n">
-        <v>57654</v>
+        <v>79632</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13444,39 +13444,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>440647</v>
+        <v>440723</v>
       </c>
       <c r="R124" t="n">
-        <v>6762125</v>
+        <v>6762648</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13508,7 +13503,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13518,7 +13513,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13545,10 +13540,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127275968</v>
+        <v>127283139</v>
       </c>
       <c r="B125" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13556,34 +13551,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
         <v>440723</v>
       </c>
       <c r="R125" t="n">
-        <v>6762648</v>
+        <v>6762373</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13613,19 +13608,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13640,19 +13625,19 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127283139</v>
+        <v>127283131</v>
       </c>
       <c r="B126" t="n">
         <v>79014</v>
@@ -13687,10 +13672,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>440723</v>
+        <v>440682</v>
       </c>
       <c r="R126" t="n">
-        <v>6762373</v>
+        <v>6762208</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13749,7 +13734,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127283131</v>
+        <v>127283135</v>
       </c>
       <c r="B127" t="n">
         <v>79014</v>
@@ -13784,10 +13769,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>440682</v>
+        <v>440456</v>
       </c>
       <c r="R127" t="n">
-        <v>6762208</v>
+        <v>6762461</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13846,7 +13831,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127283135</v>
+        <v>127273828</v>
       </c>
       <c r="B128" t="n">
         <v>79014</v>
@@ -13877,17 +13862,17 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>440456</v>
+        <v>440882</v>
       </c>
       <c r="R128" t="n">
-        <v>6762461</v>
+        <v>6762435</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13914,9 +13899,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13931,22 +13926,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127273828</v>
+        <v>127271992</v>
       </c>
       <c r="B129" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13954,37 +13949,42 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>440882</v>
+        <v>440647</v>
       </c>
       <c r="R129" t="n">
-        <v>6762435</v>
+        <v>6762125</v>
       </c>
       <c r="S129" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14038,12 +14038,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -20770,10 +20770,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127276018</v>
+        <v>127274677</v>
       </c>
       <c r="B195" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20781,34 +20781,39 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>440697</v>
+        <v>440689</v>
       </c>
       <c r="R195" t="n">
-        <v>6762625</v>
+        <v>6762214</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20840,7 +20845,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -20850,7 +20855,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20877,48 +20882,48 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127275350</v>
+        <v>127283143</v>
       </c>
       <c r="B196" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>440851</v>
+        <v>440337</v>
       </c>
       <c r="R196" t="n">
-        <v>6762513</v>
+        <v>6762397</v>
       </c>
       <c r="S196" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -20945,19 +20950,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20972,57 +20967,57 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127283124</v>
+        <v>127272174</v>
       </c>
       <c r="B197" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>440965</v>
+        <v>440657</v>
       </c>
       <c r="R197" t="n">
-        <v>6762540</v>
+        <v>6762157</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21052,9 +21047,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21069,19 +21074,19 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127272147</v>
+        <v>127276018</v>
       </c>
       <c r="B198" t="n">
         <v>79014</v>
@@ -21112,17 +21117,17 @@
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>440498</v>
+        <v>440697</v>
       </c>
       <c r="R198" t="n">
-        <v>6762428</v>
+        <v>6762625</v>
       </c>
       <c r="S198" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -21151,7 +21156,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21161,7 +21166,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21176,22 +21181,22 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127274677</v>
+        <v>127275350</v>
       </c>
       <c r="B199" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21199,42 +21204,37 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>440689</v>
+        <v>440851</v>
       </c>
       <c r="R199" t="n">
-        <v>6762214</v>
+        <v>6762513</v>
       </c>
       <c r="S199" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21288,44 +21288,44 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127283143</v>
+        <v>127283124</v>
       </c>
       <c r="B200" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21335,10 +21335,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>440337</v>
+        <v>440965</v>
       </c>
       <c r="R200" t="n">
-        <v>6762397</v>
+        <v>6762540</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21397,48 +21397,48 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127272174</v>
+        <v>127272147</v>
       </c>
       <c r="B201" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>440657</v>
+        <v>440498</v>
       </c>
       <c r="R201" t="n">
-        <v>6762157</v>
+        <v>6762428</v>
       </c>
       <c r="S201" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21477,7 +21477,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21492,22 +21492,22 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127271427</v>
+        <v>127275348</v>
       </c>
       <c r="B202" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21515,37 +21515,37 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>440457</v>
+        <v>440677</v>
       </c>
       <c r="R202" t="n">
-        <v>6762399</v>
+        <v>6762469</v>
       </c>
       <c r="S202" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -21584,7 +21584,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21599,19 +21599,19 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127275348</v>
+        <v>127282910</v>
       </c>
       <c r="B203" t="n">
         <v>79014</v>
@@ -21642,14 +21642,14 @@
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>440677</v>
+        <v>440807</v>
       </c>
       <c r="R203" t="n">
-        <v>6762469</v>
+        <v>6762574</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21679,19 +21679,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21706,19 +21696,19 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127282910</v>
+        <v>127271972</v>
       </c>
       <c r="B204" t="n">
         <v>79014</v>
@@ -21749,17 +21739,17 @@
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>440807</v>
+        <v>440460</v>
       </c>
       <c r="R204" t="n">
-        <v>6762574</v>
+        <v>6762457</v>
       </c>
       <c r="S204" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -21786,9 +21776,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>På Gran</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21803,19 +21808,19 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>127271972</v>
+        <v>127272958</v>
       </c>
       <c r="B205" t="n">
         <v>79014</v>
@@ -21850,10 +21855,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>440460</v>
+        <v>440619</v>
       </c>
       <c r="R205" t="n">
-        <v>6762457</v>
+        <v>6762170</v>
       </c>
       <c r="S205" t="n">
         <v>9</v>
@@ -21885,7 +21890,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -21895,12 +21900,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>På Gran</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -21927,7 +21927,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127272958</v>
+        <v>127283114</v>
       </c>
       <c r="B206" t="n">
         <v>79014</v>
@@ -21958,17 +21958,17 @@
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>440619</v>
+        <v>440806</v>
       </c>
       <c r="R206" t="n">
-        <v>6762170</v>
+        <v>6762533</v>
       </c>
       <c r="S206" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -21995,19 +21995,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22022,19 +22012,19 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127283114</v>
+        <v>127282897</v>
       </c>
       <c r="B207" t="n">
         <v>79014</v>
@@ -22065,14 +22055,14 @@
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>440806</v>
+        <v>440613</v>
       </c>
       <c r="R207" t="n">
-        <v>6762533</v>
+        <v>6762197</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22119,19 +22109,19 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127282897</v>
+        <v>127282920</v>
       </c>
       <c r="B208" t="n">
         <v>79014</v>
@@ -22166,10 +22156,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>440613</v>
+        <v>440696</v>
       </c>
       <c r="R208" t="n">
-        <v>6762197</v>
+        <v>6762239</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22228,10 +22218,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127282920</v>
+        <v>127271427</v>
       </c>
       <c r="B209" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -22239,37 +22229,37 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>440696</v>
+        <v>440457</v>
       </c>
       <c r="R209" t="n">
-        <v>6762239</v>
+        <v>6762399</v>
       </c>
       <c r="S209" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -22296,9 +22286,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -22313,12 +22313,12 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
@@ -24850,48 +24850,53 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>127282930</v>
+        <v>127275970</v>
       </c>
       <c r="B235" t="n">
-        <v>79014</v>
+        <v>5196</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>440417</v>
+        <v>440685</v>
       </c>
       <c r="R235" t="n">
-        <v>6762463</v>
+        <v>6762673</v>
       </c>
       <c r="S235" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -24918,9 +24923,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA235" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -24935,22 +24950,22 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127275615</v>
+        <v>127282930</v>
       </c>
       <c r="B236" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24958,42 +24973,37 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>440778</v>
+        <v>440417</v>
       </c>
       <c r="R236" t="n">
-        <v>6762552</v>
+        <v>6762463</v>
       </c>
       <c r="S236" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -25020,19 +25030,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z236" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA236" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB236" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -25047,22 +25047,22 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127283123</v>
+        <v>127275615</v>
       </c>
       <c r="B237" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -25070,37 +25070,42 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>440917</v>
+        <v>440778</v>
       </c>
       <c r="R237" t="n">
-        <v>6762578</v>
+        <v>6762552</v>
       </c>
       <c r="S237" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -25127,9 +25132,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA237" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB237" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25144,19 +25159,19 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>127271487</v>
+        <v>127283123</v>
       </c>
       <c r="B238" t="n">
         <v>79014</v>
@@ -25187,14 +25202,14 @@
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>440596</v>
+        <v>440917</v>
       </c>
       <c r="R238" t="n">
-        <v>6762126</v>
+        <v>6762578</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25224,19 +25239,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z238" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB238" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -25251,19 +25256,19 @@
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>127283132</v>
+        <v>127271487</v>
       </c>
       <c r="B239" t="n">
         <v>79014</v>
@@ -25294,14 +25299,14 @@
       <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>440679</v>
+        <v>440596</v>
       </c>
       <c r="R239" t="n">
-        <v>6762203</v>
+        <v>6762126</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25331,9 +25336,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA239" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -25348,19 +25363,19 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127282933</v>
+        <v>127283132</v>
       </c>
       <c r="B240" t="n">
         <v>79014</v>
@@ -25391,14 +25406,14 @@
       <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>440395</v>
+        <v>440679</v>
       </c>
       <c r="R240" t="n">
-        <v>6762359</v>
+        <v>6762203</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25445,19 +25460,19 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>127273778</v>
+        <v>127282933</v>
       </c>
       <c r="B241" t="n">
         <v>79014</v>
@@ -25488,14 +25503,14 @@
       <c r="I241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>440734</v>
+        <v>440395</v>
       </c>
       <c r="R241" t="n">
-        <v>6762076</v>
+        <v>6762359</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25525,19 +25540,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z241" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB241" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -25552,19 +25557,19 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>127282911</v>
+        <v>127273778</v>
       </c>
       <c r="B242" t="n">
         <v>79014</v>
@@ -25595,14 +25600,14 @@
       <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>440874</v>
+        <v>440734</v>
       </c>
       <c r="R242" t="n">
-        <v>6762606</v>
+        <v>6762076</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25632,9 +25637,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA242" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -25649,19 +25664,19 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127271764</v>
+        <v>127282911</v>
       </c>
       <c r="B243" t="n">
         <v>79014</v>
@@ -25692,17 +25707,17 @@
       <c r="I243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>440418</v>
+        <v>440874</v>
       </c>
       <c r="R243" t="n">
-        <v>6762449</v>
+        <v>6762606</v>
       </c>
       <c r="S243" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -25729,19 +25744,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z243" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA243" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB243" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -25756,62 +25761,57 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>127275970</v>
+        <v>127271764</v>
       </c>
       <c r="B244" t="n">
-        <v>5196</v>
+        <v>79014</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P244" t="inlineStr">
         <is>
           <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>440685</v>
+        <v>440418</v>
       </c>
       <c r="R244" t="n">
-        <v>6762673</v>
+        <v>6762449</v>
       </c>
       <c r="S244" t="n">
         <v>9</v>
@@ -25843,7 +25843,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -25853,7 +25853,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -25880,48 +25880,48 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127282894</v>
+        <v>127272935</v>
       </c>
       <c r="B245" t="n">
-        <v>79038</v>
+        <v>79014</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>440951</v>
+        <v>440613</v>
       </c>
       <c r="R245" t="n">
-        <v>6762514</v>
+        <v>6762174</v>
       </c>
       <c r="S245" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -25948,9 +25948,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AA245" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -25965,22 +25975,22 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127282891</v>
+        <v>127270746</v>
       </c>
       <c r="B246" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25988,37 +25998,37 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>440416</v>
+        <v>440308</v>
       </c>
       <c r="R246" t="n">
-        <v>6762406</v>
+        <v>6762456</v>
       </c>
       <c r="S246" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -26045,9 +26055,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA246" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -26062,19 +26082,19 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>127274466</v>
+        <v>127271817</v>
       </c>
       <c r="B247" t="n">
         <v>79014</v>
@@ -26105,17 +26125,17 @@
       <c r="I247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>440914</v>
+        <v>440623</v>
       </c>
       <c r="R247" t="n">
-        <v>6762585</v>
+        <v>6762126</v>
       </c>
       <c r="S247" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -26144,7 +26164,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -26154,7 +26174,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -26169,57 +26189,57 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>127272422</v>
+        <v>127282894</v>
       </c>
       <c r="B248" t="n">
-        <v>79014</v>
+        <v>79038</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>440682</v>
+        <v>440951</v>
       </c>
       <c r="R248" t="n">
-        <v>6762093</v>
+        <v>6762514</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -26249,24 +26269,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z248" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA248" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB248" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC248" t="inlineStr">
-        <is>
-          <t>Garnlav på äldre tall, sannoligt äldre än 200 år</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26281,22 +26286,22 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>127272935</v>
+        <v>127282891</v>
       </c>
       <c r="B249" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26304,37 +26309,37 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>440613</v>
+        <v>440416</v>
       </c>
       <c r="R249" t="n">
-        <v>6762174</v>
+        <v>6762406</v>
       </c>
       <c r="S249" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -26361,19 +26366,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z249" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AA249" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB249" t="inlineStr">
-        <is>
-          <t>12:31</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -26388,19 +26383,19 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>127270746</v>
+        <v>127274466</v>
       </c>
       <c r="B250" t="n">
         <v>79014</v>
@@ -26435,10 +26430,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>440308</v>
+        <v>440914</v>
       </c>
       <c r="R250" t="n">
-        <v>6762456</v>
+        <v>6762585</v>
       </c>
       <c r="S250" t="n">
         <v>9</v>
@@ -26470,7 +26465,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -26480,7 +26475,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -26507,7 +26502,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>127271817</v>
+        <v>127272422</v>
       </c>
       <c r="B251" t="n">
         <v>79014</v>
@@ -26542,10 +26537,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>440623</v>
+        <v>440682</v>
       </c>
       <c r="R251" t="n">
-        <v>6762126</v>
+        <v>6762093</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26588,6 +26583,11 @@
       <c r="AB251" t="inlineStr">
         <is>
           <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>Garnlav på äldre tall, sannoligt äldre än 200 år</t>
         </is>
       </c>
       <c r="AD251" t="b">

--- a/artfynd/A 29945-2025 artfynd.xlsx
+++ b/artfynd/A 29945-2025 artfynd.xlsx
@@ -11552,7 +11552,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127274454</v>
+        <v>127275526</v>
       </c>
       <c r="B106" t="n">
         <v>79014</v>
@@ -11583,17 +11583,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>440926</v>
+        <v>440688</v>
       </c>
       <c r="R106" t="n">
-        <v>6762599</v>
+        <v>6762488</v>
       </c>
       <c r="S106" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11632,7 +11632,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11647,19 +11652,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127275526</v>
+        <v>127274454</v>
       </c>
       <c r="B107" t="n">
         <v>79014</v>
@@ -11690,17 +11695,17 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>440688</v>
+        <v>440926</v>
       </c>
       <c r="R107" t="n">
-        <v>6762488</v>
+        <v>6762599</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11729,7 +11734,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11739,12 +11744,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11759,12 +11759,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -11868,10 +11868,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127282896</v>
+        <v>127273473</v>
       </c>
       <c r="B109" t="n">
-        <v>78772</v>
+        <v>57657</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11879,34 +11879,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>440416</v>
+        <v>440721</v>
       </c>
       <c r="R109" t="n">
-        <v>6762406</v>
+        <v>6761996</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11936,9 +11941,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11953,19 +11968,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127274251</v>
+        <v>127273727</v>
       </c>
       <c r="B110" t="n">
         <v>79014</v>
@@ -12000,10 +12015,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>440687</v>
+        <v>440754</v>
       </c>
       <c r="R110" t="n">
-        <v>6762120</v>
+        <v>6762035</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12072,7 +12087,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127273727</v>
+        <v>127282909</v>
       </c>
       <c r="B111" t="n">
         <v>79014</v>
@@ -12103,14 +12118,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>440754</v>
+        <v>440797</v>
       </c>
       <c r="R111" t="n">
-        <v>6762035</v>
+        <v>6762555</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12140,19 +12155,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12167,19 +12172,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127282909</v>
+        <v>127282922</v>
       </c>
       <c r="B112" t="n">
         <v>79014</v>
@@ -12214,10 +12219,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>440797</v>
+        <v>440685</v>
       </c>
       <c r="R112" t="n">
-        <v>6762555</v>
+        <v>6762213</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12276,7 +12281,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127282922</v>
+        <v>127282903</v>
       </c>
       <c r="B113" t="n">
         <v>79014</v>
@@ -12311,10 +12316,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>440685</v>
+        <v>440760</v>
       </c>
       <c r="R113" t="n">
-        <v>6762213</v>
+        <v>6762626</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12373,7 +12378,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127282903</v>
+        <v>127274251</v>
       </c>
       <c r="B114" t="n">
         <v>79014</v>
@@ -12404,14 +12409,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>440760</v>
+        <v>440687</v>
       </c>
       <c r="R114" t="n">
-        <v>6762626</v>
+        <v>6762120</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12441,9 +12446,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12458,62 +12473,57 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127273473</v>
+        <v>127272135</v>
       </c>
       <c r="B115" t="n">
-        <v>57657</v>
+        <v>8447</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>440721</v>
+        <v>440647</v>
       </c>
       <c r="R115" t="n">
-        <v>6761996</v>
+        <v>6762125</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12582,45 +12592,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127272135</v>
+        <v>127282896</v>
       </c>
       <c r="B116" t="n">
-        <v>8447</v>
+        <v>78772</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>440647</v>
+        <v>440416</v>
       </c>
       <c r="R116" t="n">
-        <v>6762125</v>
+        <v>6762406</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12650,19 +12660,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12677,19 +12677,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127276304</v>
+        <v>127273755</v>
       </c>
       <c r="B117" t="n">
         <v>79014</v>
@@ -12724,10 +12724,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>440642</v>
+        <v>440744</v>
       </c>
       <c r="R117" t="n">
-        <v>6762606</v>
+        <v>6762065</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12769,7 +12769,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12796,7 +12796,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127273755</v>
+        <v>127276304</v>
       </c>
       <c r="B118" t="n">
         <v>79014</v>
@@ -12831,10 +12831,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>440744</v>
+        <v>440642</v>
       </c>
       <c r="R118" t="n">
-        <v>6762065</v>
+        <v>6762606</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12866,7 +12866,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12876,7 +12876,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14050,45 +14050,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127274657</v>
+        <v>127283108</v>
       </c>
       <c r="B130" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>440689</v>
+        <v>440442</v>
       </c>
       <c r="R130" t="n">
-        <v>6762214</v>
+        <v>6762471</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14118,24 +14118,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14150,57 +14135,57 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127276216</v>
+        <v>127282895</v>
       </c>
       <c r="B131" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>440657</v>
+        <v>440382</v>
       </c>
       <c r="R131" t="n">
-        <v>6762603</v>
+        <v>6762379</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14230,19 +14215,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14257,22 +14232,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127273488</v>
+        <v>127283109</v>
       </c>
       <c r="B132" t="n">
-        <v>79014</v>
+        <v>79015</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14280,16 +14255,16 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -14300,14 +14275,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>440721</v>
+        <v>440875</v>
       </c>
       <c r="R132" t="n">
-        <v>6761996</v>
+        <v>6762453</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14337,19 +14312,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14364,22 +14329,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127276148</v>
+        <v>127273051</v>
       </c>
       <c r="B133" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14387,42 +14352,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>440657</v>
+        <v>440681</v>
       </c>
       <c r="R133" t="n">
-        <v>6762603</v>
+        <v>6762197</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14451,7 +14411,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14461,7 +14421,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14476,22 +14436,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127272305</v>
+        <v>127276216</v>
       </c>
       <c r="B134" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14499,39 +14459,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>440675</v>
+        <v>440657</v>
       </c>
       <c r="R134" t="n">
-        <v>6762165</v>
+        <v>6762603</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14563,7 +14518,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14573,12 +14528,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Diameter ca 4 till 5 cm</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14605,7 +14555,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127271765</v>
+        <v>127276450</v>
       </c>
       <c r="B135" t="n">
         <v>57654</v>
@@ -14636,7 +14586,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -14645,10 +14595,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>440627</v>
+        <v>440582</v>
       </c>
       <c r="R135" t="n">
-        <v>6762119</v>
+        <v>6762684</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14680,7 +14630,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14690,12 +14640,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Miljöbild för området</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14722,7 +14667,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127276450</v>
+        <v>127272305</v>
       </c>
       <c r="B136" t="n">
         <v>57654</v>
@@ -14762,10 +14707,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>440582</v>
+        <v>440675</v>
       </c>
       <c r="R136" t="n">
-        <v>6762684</v>
+        <v>6762165</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14797,7 +14742,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14807,7 +14752,12 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Diameter ca 4 till 5 cm</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14834,10 +14784,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127283117</v>
+        <v>127271765</v>
       </c>
       <c r="B137" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14845,34 +14795,39 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>440863</v>
+        <v>440627</v>
       </c>
       <c r="R137" t="n">
-        <v>6762603</v>
+        <v>6762119</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14902,9 +14857,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Miljöbild för området</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14919,22 +14889,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127273051</v>
+        <v>127276148</v>
       </c>
       <c r="B138" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14942,37 +14912,42 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>440681</v>
+        <v>440657</v>
       </c>
       <c r="R138" t="n">
-        <v>6762197</v>
+        <v>6762603</v>
       </c>
       <c r="S138" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15001,7 +14976,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15011,7 +14986,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15026,19 +15001,19 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127282932</v>
+        <v>127274657</v>
       </c>
       <c r="B139" t="n">
         <v>79014</v>
@@ -15069,14 +15044,14 @@
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>440427</v>
+        <v>440689</v>
       </c>
       <c r="R139" t="n">
-        <v>6762470</v>
+        <v>6762214</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15106,9 +15081,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15123,19 +15113,19 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127282912</v>
+        <v>127283117</v>
       </c>
       <c r="B140" t="n">
         <v>79014</v>
@@ -15166,14 +15156,14 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>440936</v>
+        <v>440863</v>
       </c>
       <c r="R140" t="n">
-        <v>6762564</v>
+        <v>6762603</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15220,19 +15210,19 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127282926</v>
+        <v>127282932</v>
       </c>
       <c r="B141" t="n">
         <v>79014</v>
@@ -15267,10 +15257,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>440497</v>
+        <v>440427</v>
       </c>
       <c r="R141" t="n">
-        <v>6762331</v>
+        <v>6762470</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15329,7 +15319,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127283130</v>
+        <v>127282912</v>
       </c>
       <c r="B142" t="n">
         <v>79014</v>
@@ -15360,14 +15350,14 @@
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>440697</v>
+        <v>440936</v>
       </c>
       <c r="R142" t="n">
-        <v>6762237</v>
+        <v>6762564</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15414,57 +15404,57 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127283108</v>
+        <v>127282926</v>
       </c>
       <c r="B143" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>440442</v>
+        <v>440497</v>
       </c>
       <c r="R143" t="n">
-        <v>6762471</v>
+        <v>6762331</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15511,57 +15501,57 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127282895</v>
+        <v>127283130</v>
       </c>
       <c r="B144" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>440382</v>
+        <v>440697</v>
       </c>
       <c r="R144" t="n">
-        <v>6762379</v>
+        <v>6762237</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15608,22 +15598,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127283109</v>
+        <v>127273488</v>
       </c>
       <c r="B145" t="n">
-        <v>79015</v>
+        <v>79014</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15631,16 +15621,16 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -15651,14 +15641,14 @@
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>440875</v>
+        <v>440721</v>
       </c>
       <c r="R145" t="n">
-        <v>6762453</v>
+        <v>6761996</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15688,9 +15678,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15705,60 +15705,60 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127283142</v>
+        <v>127274917</v>
       </c>
       <c r="B146" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>440744</v>
+        <v>440752</v>
       </c>
       <c r="R146" t="n">
-        <v>6762615</v>
+        <v>6762337</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15785,9 +15785,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15802,19 +15812,19 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127274917</v>
+        <v>127273038</v>
       </c>
       <c r="B147" t="n">
         <v>79014</v>
@@ -15845,17 +15855,17 @@
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>440752</v>
+        <v>440688</v>
       </c>
       <c r="R147" t="n">
-        <v>6762337</v>
+        <v>6762199</v>
       </c>
       <c r="S147" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15884,7 +15894,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15894,7 +15904,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15909,60 +15919,60 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127272858</v>
+        <v>127283142</v>
       </c>
       <c r="B148" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>440609</v>
+        <v>440744</v>
       </c>
       <c r="R148" t="n">
-        <v>6762190</v>
+        <v>6762615</v>
       </c>
       <c r="S148" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15989,19 +15999,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16016,12 +16016,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -16125,7 +16125,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127273038</v>
+        <v>127272858</v>
       </c>
       <c r="B150" t="n">
         <v>79014</v>
@@ -16160,10 +16160,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>440688</v>
+        <v>440609</v>
       </c>
       <c r="R150" t="n">
-        <v>6762199</v>
+        <v>6762190</v>
       </c>
       <c r="S150" t="n">
         <v>9</v>
@@ -16195,7 +16195,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16205,7 +16205,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16553,10 +16553,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127282904</v>
+        <v>127283105</v>
       </c>
       <c r="B154" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16564,34 +16564,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>440776</v>
+        <v>440909</v>
       </c>
       <c r="R154" t="n">
-        <v>6762632</v>
+        <v>6762467</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16638,19 +16638,19 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127282914</v>
+        <v>127274354</v>
       </c>
       <c r="B155" t="n">
         <v>79014</v>
@@ -16681,14 +16681,14 @@
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>440924</v>
+        <v>440686</v>
       </c>
       <c r="R155" t="n">
-        <v>6762509</v>
+        <v>6762176</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16718,9 +16718,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16735,22 +16745,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127274354</v>
+        <v>127272237</v>
       </c>
       <c r="B156" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16758,34 +16768,39 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>440686</v>
+        <v>440675</v>
       </c>
       <c r="R156" t="n">
-        <v>6762176</v>
+        <v>6762165</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16854,7 +16869,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127272746</v>
+        <v>127282904</v>
       </c>
       <c r="B157" t="n">
         <v>79014</v>
@@ -16885,17 +16900,17 @@
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>440503</v>
+        <v>440776</v>
       </c>
       <c r="R157" t="n">
-        <v>6762308</v>
+        <v>6762632</v>
       </c>
       <c r="S157" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16922,19 +16937,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16949,22 +16954,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127283105</v>
+        <v>127282914</v>
       </c>
       <c r="B158" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16972,34 +16977,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>440909</v>
+        <v>440924</v>
       </c>
       <c r="R158" t="n">
-        <v>6762467</v>
+        <v>6762509</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17046,22 +17051,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127272237</v>
+        <v>127272746</v>
       </c>
       <c r="B159" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17069,42 +17074,37 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>440675</v>
+        <v>440503</v>
       </c>
       <c r="R159" t="n">
-        <v>6762165</v>
+        <v>6762308</v>
       </c>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17143,7 +17143,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17158,22 +17158,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127282902</v>
+        <v>127274348</v>
       </c>
       <c r="B160" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17181,34 +17181,39 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>440760</v>
+        <v>440686</v>
       </c>
       <c r="R160" t="n">
-        <v>6762569</v>
+        <v>6762176</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17238,9 +17243,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17255,22 +17270,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127282900</v>
+        <v>127275098</v>
       </c>
       <c r="B161" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17278,34 +17293,39 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>440757</v>
+        <v>440679</v>
       </c>
       <c r="R161" t="n">
-        <v>6762544</v>
+        <v>6762388</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17335,9 +17355,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17352,19 +17382,19 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127276426</v>
+        <v>127282900</v>
       </c>
       <c r="B162" t="n">
         <v>79014</v>
@@ -17395,14 +17425,14 @@
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>440582</v>
+        <v>440757</v>
       </c>
       <c r="R162" t="n">
-        <v>6762684</v>
+        <v>6762544</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17432,19 +17462,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17459,19 +17479,19 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127275877</v>
+        <v>127276426</v>
       </c>
       <c r="B163" t="n">
         <v>79014</v>
@@ -17506,10 +17526,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>440732</v>
+        <v>440582</v>
       </c>
       <c r="R163" t="n">
-        <v>6762635</v>
+        <v>6762684</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17578,7 +17598,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127273900</v>
+        <v>127275877</v>
       </c>
       <c r="B164" t="n">
         <v>79014</v>
@@ -17609,17 +17629,17 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>440903</v>
+        <v>440732</v>
       </c>
       <c r="R164" t="n">
-        <v>6762450</v>
+        <v>6762635</v>
       </c>
       <c r="S164" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -17648,7 +17668,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17658,7 +17678,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17673,19 +17693,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127273086</v>
+        <v>127273900</v>
       </c>
       <c r="B165" t="n">
         <v>79014</v>
@@ -17720,10 +17740,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>440694</v>
+        <v>440903</v>
       </c>
       <c r="R165" t="n">
-        <v>6762204</v>
+        <v>6762450</v>
       </c>
       <c r="S165" t="n">
         <v>9</v>
@@ -17755,7 +17775,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17765,7 +17785,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17792,7 +17812,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127283137</v>
+        <v>127282902</v>
       </c>
       <c r="B166" t="n">
         <v>79014</v>
@@ -17823,14 +17843,14 @@
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>440354</v>
+        <v>440760</v>
       </c>
       <c r="R166" t="n">
-        <v>6762415</v>
+        <v>6762569</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17877,22 +17897,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127274348</v>
+        <v>127273086</v>
       </c>
       <c r="B167" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17900,42 +17920,37 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>440686</v>
+        <v>440694</v>
       </c>
       <c r="R167" t="n">
-        <v>6762176</v>
+        <v>6762204</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -17964,7 +17979,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -17974,7 +17989,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17989,22 +18004,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127275098</v>
+        <v>127283137</v>
       </c>
       <c r="B168" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18012,39 +18027,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>440679</v>
+        <v>440354</v>
       </c>
       <c r="R168" t="n">
-        <v>6762388</v>
+        <v>6762415</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18074,19 +18084,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18101,60 +18101,60 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127271802</v>
+        <v>127273853</v>
       </c>
       <c r="B169" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>440627</v>
+        <v>440887</v>
       </c>
       <c r="R169" t="n">
-        <v>6762119</v>
+        <v>6762439</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18193,12 +18193,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Rikligt med torrakor med spår efter Mindre Märgborre i området</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18213,65 +18208,60 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127271251</v>
+        <v>127270744</v>
       </c>
       <c r="B170" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>440375</v>
+        <v>440351</v>
       </c>
       <c r="R170" t="n">
-        <v>6762366</v>
+        <v>6762480</v>
       </c>
       <c r="S170" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18300,7 +18290,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18310,7 +18300,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18325,57 +18315,57 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127276271</v>
+        <v>127282927</v>
       </c>
       <c r="B171" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>440642</v>
+        <v>440488</v>
       </c>
       <c r="R171" t="n">
-        <v>6762606</v>
+        <v>6762419</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18405,19 +18395,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18432,19 +18412,19 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127273853</v>
+        <v>127283128</v>
       </c>
       <c r="B172" t="n">
         <v>79014</v>
@@ -18475,17 +18455,17 @@
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>440887</v>
+        <v>440822</v>
       </c>
       <c r="R172" t="n">
-        <v>6762439</v>
+        <v>6762415</v>
       </c>
       <c r="S172" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18512,19 +18492,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18539,19 +18509,19 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127270744</v>
+        <v>127274114</v>
       </c>
       <c r="B173" t="n">
         <v>79014</v>
@@ -18586,10 +18556,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>440351</v>
+        <v>440711</v>
       </c>
       <c r="R173" t="n">
-        <v>6762480</v>
+        <v>6762111</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18658,7 +18628,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127275337</v>
+        <v>127283115</v>
       </c>
       <c r="B174" t="n">
         <v>79014</v>
@@ -18689,17 +18659,17 @@
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>440855</v>
+        <v>440803</v>
       </c>
       <c r="R174" t="n">
-        <v>6762513</v>
+        <v>6762557</v>
       </c>
       <c r="S174" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -18726,19 +18696,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>14:33</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18753,19 +18713,19 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127282927</v>
+        <v>127283134</v>
       </c>
       <c r="B175" t="n">
         <v>79014</v>
@@ -18796,14 +18756,14 @@
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>440488</v>
+        <v>440487</v>
       </c>
       <c r="R175" t="n">
-        <v>6762419</v>
+        <v>6762321</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18850,19 +18810,19 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127283128</v>
+        <v>127283133</v>
       </c>
       <c r="B176" t="n">
         <v>79014</v>
@@ -18897,10 +18857,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>440822</v>
+        <v>440598</v>
       </c>
       <c r="R176" t="n">
-        <v>6762415</v>
+        <v>6762206</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18959,7 +18919,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127274114</v>
+        <v>127275337</v>
       </c>
       <c r="B177" t="n">
         <v>79014</v>
@@ -18990,17 +18950,17 @@
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>440711</v>
+        <v>440855</v>
       </c>
       <c r="R177" t="n">
-        <v>6762111</v>
+        <v>6762513</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -19029,7 +18989,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19039,7 +18999,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19054,57 +19014,57 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127283115</v>
+        <v>127271802</v>
       </c>
       <c r="B178" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>440803</v>
+        <v>440627</v>
       </c>
       <c r="R178" t="n">
-        <v>6762557</v>
+        <v>6762119</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19134,9 +19094,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>Rikligt med torrakor med spår efter Mindre Märgborre i området</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19151,60 +19126,65 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127283134</v>
+        <v>127271251</v>
       </c>
       <c r="B179" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>440487</v>
+        <v>440375</v>
       </c>
       <c r="R179" t="n">
-        <v>6762321</v>
+        <v>6762366</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19231,9 +19211,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19248,57 +19238,57 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127283133</v>
+        <v>127276271</v>
       </c>
       <c r="B180" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>440598</v>
+        <v>440642</v>
       </c>
       <c r="R180" t="n">
-        <v>6762206</v>
+        <v>6762606</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19328,9 +19318,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19345,12 +19345,12 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
@@ -20882,45 +20882,45 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127283143</v>
+        <v>127276018</v>
       </c>
       <c r="B196" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>440337</v>
+        <v>440697</v>
       </c>
       <c r="R196" t="n">
-        <v>6762397</v>
+        <v>6762625</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20950,9 +20950,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20967,60 +20977,60 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127272174</v>
+        <v>127275350</v>
       </c>
       <c r="B197" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>440657</v>
+        <v>440851</v>
       </c>
       <c r="R197" t="n">
-        <v>6762157</v>
+        <v>6762513</v>
       </c>
       <c r="S197" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -21049,7 +21059,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -21059,7 +21069,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21074,19 +21084,19 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127276018</v>
+        <v>127283124</v>
       </c>
       <c r="B198" t="n">
         <v>79014</v>
@@ -21117,14 +21127,14 @@
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>440697</v>
+        <v>440965</v>
       </c>
       <c r="R198" t="n">
-        <v>6762625</v>
+        <v>6762540</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21154,19 +21164,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21181,19 +21181,19 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127275350</v>
+        <v>127272147</v>
       </c>
       <c r="B199" t="n">
         <v>79014</v>
@@ -21228,10 +21228,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>440851</v>
+        <v>440498</v>
       </c>
       <c r="R199" t="n">
-        <v>6762513</v>
+        <v>6762428</v>
       </c>
       <c r="S199" t="n">
         <v>9</v>
@@ -21263,7 +21263,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21300,32 +21300,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127283124</v>
+        <v>127283143</v>
       </c>
       <c r="B200" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21335,10 +21335,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>440965</v>
+        <v>440337</v>
       </c>
       <c r="R200" t="n">
-        <v>6762540</v>
+        <v>6762397</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21397,48 +21397,48 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127272147</v>
+        <v>127272174</v>
       </c>
       <c r="B201" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>440498</v>
+        <v>440657</v>
       </c>
       <c r="R201" t="n">
-        <v>6762428</v>
+        <v>6762157</v>
       </c>
       <c r="S201" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21477,7 +21477,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21492,19 +21492,19 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127275348</v>
+        <v>127272958</v>
       </c>
       <c r="B202" t="n">
         <v>79014</v>
@@ -21535,17 +21535,17 @@
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>440677</v>
+        <v>440619</v>
       </c>
       <c r="R202" t="n">
-        <v>6762469</v>
+        <v>6762170</v>
       </c>
       <c r="S202" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -21584,7 +21584,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21599,22 +21599,22 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127282910</v>
+        <v>127271427</v>
       </c>
       <c r="B203" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21622,37 +21622,37 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>440807</v>
+        <v>440457</v>
       </c>
       <c r="R203" t="n">
-        <v>6762574</v>
+        <v>6762399</v>
       </c>
       <c r="S203" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -21679,9 +21679,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21696,19 +21706,19 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127271972</v>
+        <v>127275348</v>
       </c>
       <c r="B204" t="n">
         <v>79014</v>
@@ -21739,17 +21749,17 @@
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>440460</v>
+        <v>440677</v>
       </c>
       <c r="R204" t="n">
-        <v>6762457</v>
+        <v>6762469</v>
       </c>
       <c r="S204" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -21778,7 +21788,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -21788,12 +21798,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>På Gran</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21808,19 +21813,19 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>127272958</v>
+        <v>127282910</v>
       </c>
       <c r="B205" t="n">
         <v>79014</v>
@@ -21851,17 +21856,17 @@
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>440619</v>
+        <v>440807</v>
       </c>
       <c r="R205" t="n">
-        <v>6762170</v>
+        <v>6762574</v>
       </c>
       <c r="S205" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -21888,19 +21893,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -21915,19 +21910,19 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127283114</v>
+        <v>127271972</v>
       </c>
       <c r="B206" t="n">
         <v>79014</v>
@@ -21958,17 +21953,17 @@
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>440806</v>
+        <v>440460</v>
       </c>
       <c r="R206" t="n">
-        <v>6762533</v>
+        <v>6762457</v>
       </c>
       <c r="S206" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -21995,9 +21990,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>På Gran</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22012,19 +22022,19 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127282897</v>
+        <v>127283114</v>
       </c>
       <c r="B207" t="n">
         <v>79014</v>
@@ -22055,14 +22065,14 @@
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>440613</v>
+        <v>440806</v>
       </c>
       <c r="R207" t="n">
-        <v>6762197</v>
+        <v>6762533</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22109,19 +22119,19 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127282920</v>
+        <v>127282897</v>
       </c>
       <c r="B208" t="n">
         <v>79014</v>
@@ -22156,10 +22166,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>440696</v>
+        <v>440613</v>
       </c>
       <c r="R208" t="n">
-        <v>6762239</v>
+        <v>6762197</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22218,10 +22228,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127271427</v>
+        <v>127282920</v>
       </c>
       <c r="B209" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -22229,37 +22239,37 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>440457</v>
+        <v>440696</v>
       </c>
       <c r="R209" t="n">
-        <v>6762399</v>
+        <v>6762239</v>
       </c>
       <c r="S209" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -22286,19 +22296,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -22313,12 +22313,12 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
@@ -23146,32 +23146,32 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127283141</v>
+        <v>127283107</v>
       </c>
       <c r="B218" t="n">
-        <v>78681</v>
+        <v>8447</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -23181,10 +23181,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>440651</v>
+        <v>440636</v>
       </c>
       <c r="R218" t="n">
-        <v>6762611</v>
+        <v>6762585</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23340,10 +23340,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127282915</v>
+        <v>127283141</v>
       </c>
       <c r="B220" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -23351,34 +23351,34 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>440946</v>
+        <v>440651</v>
       </c>
       <c r="R220" t="n">
-        <v>6762514</v>
+        <v>6762611</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23425,22 +23425,22 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127275040</v>
+        <v>127283100</v>
       </c>
       <c r="B221" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23448,34 +23448,34 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>440745</v>
+        <v>440686</v>
       </c>
       <c r="R221" t="n">
-        <v>6762369</v>
+        <v>6762630</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23505,24 +23505,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z221" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB221" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -23537,22 +23522,22 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127283100</v>
+        <v>127282898</v>
       </c>
       <c r="B222" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23560,34 +23545,34 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>440686</v>
+        <v>440741</v>
       </c>
       <c r="R222" t="n">
-        <v>6762630</v>
+        <v>6762609</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23634,19 +23619,19 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127282898</v>
+        <v>127283122</v>
       </c>
       <c r="B223" t="n">
         <v>79014</v>
@@ -23677,14 +23662,14 @@
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>440741</v>
+        <v>440912</v>
       </c>
       <c r="R223" t="n">
-        <v>6762609</v>
+        <v>6762579</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23731,19 +23716,19 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127283122</v>
+        <v>127282915</v>
       </c>
       <c r="B224" t="n">
         <v>79014</v>
@@ -23774,14 +23759,14 @@
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>440912</v>
+        <v>440946</v>
       </c>
       <c r="R224" t="n">
-        <v>6762579</v>
+        <v>6762514</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23828,19 +23813,19 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127282899</v>
+        <v>127275040</v>
       </c>
       <c r="B225" t="n">
         <v>79014</v>
@@ -23871,14 +23856,14 @@
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>440763</v>
+        <v>440745</v>
       </c>
       <c r="R225" t="n">
-        <v>6762529</v>
+        <v>6762369</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23908,9 +23893,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA225" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -23925,57 +23925,57 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127283107</v>
+        <v>127282899</v>
       </c>
       <c r="B226" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>440636</v>
+        <v>440763</v>
       </c>
       <c r="R226" t="n">
-        <v>6762585</v>
+        <v>6762529</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24022,60 +24022,60 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127273585</v>
+        <v>127275544</v>
       </c>
       <c r="B227" t="n">
-        <v>91683</v>
+        <v>8447</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>2062</v>
+        <v>106545</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>440742</v>
+        <v>440811</v>
       </c>
       <c r="R227" t="n">
-        <v>6762004</v>
+        <v>6762474</v>
       </c>
       <c r="S227" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24129,44 +24129,44 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127273660</v>
+        <v>127273585</v>
       </c>
       <c r="B228" t="n">
-        <v>79014</v>
+        <v>91684</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -24636,7 +24636,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127275120</v>
+        <v>127273660</v>
       </c>
       <c r="B233" t="n">
         <v>79014</v>
@@ -24667,17 +24667,17 @@
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>440897</v>
+        <v>440742</v>
       </c>
       <c r="R233" t="n">
-        <v>6762548</v>
+        <v>6762004</v>
       </c>
       <c r="S233" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -24706,7 +24706,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -24716,7 +24716,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -24731,44 +24731,44 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>127275544</v>
+        <v>127275120</v>
       </c>
       <c r="B234" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -24778,10 +24778,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>440811</v>
+        <v>440897</v>
       </c>
       <c r="R234" t="n">
-        <v>6762474</v>
+        <v>6762548</v>
       </c>
       <c r="S234" t="n">
         <v>9</v>
@@ -24813,7 +24813,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -24823,7 +24823,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -24850,53 +24850,48 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>127275970</v>
+        <v>127283123</v>
       </c>
       <c r="B235" t="n">
-        <v>5196</v>
+        <v>79014</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>440685</v>
+        <v>440917</v>
       </c>
       <c r="R235" t="n">
-        <v>6762673</v>
+        <v>6762578</v>
       </c>
       <c r="S235" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -24923,19 +24918,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z235" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA235" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB235" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -24950,12 +24935,12 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
@@ -25059,10 +25044,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127275615</v>
+        <v>127271487</v>
       </c>
       <c r="B237" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -25070,42 +25055,37 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>440778</v>
+        <v>440596</v>
       </c>
       <c r="R237" t="n">
-        <v>6762552</v>
+        <v>6762126</v>
       </c>
       <c r="S237" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -25134,7 +25114,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -25144,7 +25124,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25159,19 +25139,19 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>127283123</v>
+        <v>127283132</v>
       </c>
       <c r="B238" t="n">
         <v>79014</v>
@@ -25206,10 +25186,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>440917</v>
+        <v>440679</v>
       </c>
       <c r="R238" t="n">
-        <v>6762578</v>
+        <v>6762203</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25268,7 +25248,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>127271487</v>
+        <v>127282933</v>
       </c>
       <c r="B239" t="n">
         <v>79014</v>
@@ -25299,14 +25279,14 @@
       <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>440596</v>
+        <v>440395</v>
       </c>
       <c r="R239" t="n">
-        <v>6762126</v>
+        <v>6762359</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25336,19 +25316,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z239" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA239" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB239" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -25363,19 +25333,19 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127283132</v>
+        <v>127282911</v>
       </c>
       <c r="B240" t="n">
         <v>79014</v>
@@ -25406,14 +25376,14 @@
       <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>440679</v>
+        <v>440874</v>
       </c>
       <c r="R240" t="n">
-        <v>6762203</v>
+        <v>6762606</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25460,19 +25430,19 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>127282933</v>
+        <v>127271764</v>
       </c>
       <c r="B241" t="n">
         <v>79014</v>
@@ -25503,17 +25473,17 @@
       <c r="I241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>440395</v>
+        <v>440418</v>
       </c>
       <c r="R241" t="n">
-        <v>6762359</v>
+        <v>6762449</v>
       </c>
       <c r="S241" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -25540,9 +25510,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB241" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -25557,60 +25537,65 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>127273778</v>
+        <v>127275970</v>
       </c>
       <c r="B242" t="n">
-        <v>79014</v>
+        <v>5196</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>440734</v>
+        <v>440685</v>
       </c>
       <c r="R242" t="n">
-        <v>6762076</v>
+        <v>6762673</v>
       </c>
       <c r="S242" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -25639,7 +25624,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -25649,7 +25634,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -25664,19 +25649,19 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127282911</v>
+        <v>127273778</v>
       </c>
       <c r="B243" t="n">
         <v>79014</v>
@@ -25707,14 +25692,14 @@
       <c r="I243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>440874</v>
+        <v>440734</v>
       </c>
       <c r="R243" t="n">
-        <v>6762606</v>
+        <v>6762076</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25744,9 +25729,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA243" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB243" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -25761,22 +25756,22 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>127271764</v>
+        <v>127275615</v>
       </c>
       <c r="B244" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25784,34 +25779,39 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P244" t="inlineStr">
         <is>
           <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>440418</v>
+        <v>440778</v>
       </c>
       <c r="R244" t="n">
-        <v>6762449</v>
+        <v>6762552</v>
       </c>
       <c r="S244" t="n">
         <v>9</v>
@@ -25843,7 +25843,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -25853,7 +25853,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -25880,48 +25880,48 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127272935</v>
+        <v>127282894</v>
       </c>
       <c r="B245" t="n">
-        <v>79014</v>
+        <v>79038</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>440613</v>
+        <v>440951</v>
       </c>
       <c r="R245" t="n">
-        <v>6762174</v>
+        <v>6762514</v>
       </c>
       <c r="S245" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -25948,19 +25948,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z245" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AA245" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB245" t="inlineStr">
-        <is>
-          <t>12:31</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -25975,22 +25965,22 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127270746</v>
+        <v>127282891</v>
       </c>
       <c r="B246" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25998,37 +25988,37 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>440308</v>
+        <v>440416</v>
       </c>
       <c r="R246" t="n">
-        <v>6762456</v>
+        <v>6762406</v>
       </c>
       <c r="S246" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -26055,19 +26045,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z246" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA246" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB246" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -26082,19 +26062,19 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>127271817</v>
+        <v>127270746</v>
       </c>
       <c r="B247" t="n">
         <v>79014</v>
@@ -26125,17 +26105,17 @@
       <c r="I247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>440623</v>
+        <v>440308</v>
       </c>
       <c r="R247" t="n">
-        <v>6762126</v>
+        <v>6762456</v>
       </c>
       <c r="S247" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -26189,57 +26169,57 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>127282894</v>
+        <v>127271817</v>
       </c>
       <c r="B248" t="n">
-        <v>79038</v>
+        <v>79014</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>440951</v>
+        <v>440623</v>
       </c>
       <c r="R248" t="n">
-        <v>6762514</v>
+        <v>6762126</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -26269,9 +26249,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA248" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26286,22 +26276,22 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>127282891</v>
+        <v>127273433</v>
       </c>
       <c r="B249" t="n">
-        <v>79632</v>
+        <v>57654</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26309,34 +26299,39 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>440416</v>
+        <v>440726</v>
       </c>
       <c r="R249" t="n">
-        <v>6762406</v>
+        <v>6761979</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -26366,9 +26361,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA249" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>Hackhål/bohål</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -26383,12 +26393,12 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
@@ -26502,7 +26512,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>127272422</v>
+        <v>127272935</v>
       </c>
       <c r="B251" t="n">
         <v>79014</v>
@@ -26533,17 +26543,17 @@
       <c r="I251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>440682</v>
+        <v>440613</v>
       </c>
       <c r="R251" t="n">
-        <v>6762093</v>
+        <v>6762174</v>
       </c>
       <c r="S251" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -26572,7 +26582,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -26582,12 +26592,7 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>Garnlav på äldre tall, sannoligt äldre än 200 år</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -26602,22 +26607,22 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>127272190</v>
+        <v>127272422</v>
       </c>
       <c r="B252" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -26625,39 +26630,34 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
-      <c r="M252" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P252" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>440657</v>
+        <v>440682</v>
       </c>
       <c r="R252" t="n">
-        <v>6762157</v>
+        <v>6762093</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26700,6 +26700,11 @@
       <c r="AB252" t="inlineStr">
         <is>
           <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>Garnlav på äldre tall, sannoligt äldre än 200 år</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -26838,7 +26843,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>127273433</v>
+        <v>127272190</v>
       </c>
       <c r="B254" t="n">
         <v>57654</v>
@@ -26869,7 +26874,7 @@
       <c r="I254" t="inlineStr"/>
       <c r="M254" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P254" t="inlineStr">
@@ -26878,10 +26883,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>440726</v>
+        <v>440657</v>
       </c>
       <c r="R254" t="n">
-        <v>6761979</v>
+        <v>6762157</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26924,11 +26929,6 @@
       <c r="AB254" t="inlineStr">
         <is>
           <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>Hackhål/bohål</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -27356,7 +27356,7 @@
         <v>127282893</v>
       </c>
       <c r="B259" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -27654,45 +27654,45 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>127282921</v>
+        <v>127274680</v>
       </c>
       <c r="B262" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>440680</v>
+        <v>440689</v>
       </c>
       <c r="R262" t="n">
-        <v>6762218</v>
+        <v>6762214</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27722,9 +27722,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA262" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -27739,12 +27749,12 @@
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
@@ -27858,10 +27868,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>127282905</v>
+        <v>127276264</v>
       </c>
       <c r="B264" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -27869,34 +27879,39 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>440780</v>
+        <v>440642</v>
       </c>
       <c r="R264" t="n">
-        <v>6762578</v>
+        <v>6762606</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27926,9 +27941,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA264" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB264" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -27943,19 +27968,19 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>127282934</v>
+        <v>127282905</v>
       </c>
       <c r="B265" t="n">
         <v>79014</v>
@@ -27990,10 +28015,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>440387</v>
+        <v>440780</v>
       </c>
       <c r="R265" t="n">
-        <v>6762369</v>
+        <v>6762578</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -28052,7 +28077,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>127275330</v>
+        <v>127282934</v>
       </c>
       <c r="B266" t="n">
         <v>79014</v>
@@ -28083,17 +28108,17 @@
       <c r="I266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>440868</v>
+        <v>440387</v>
       </c>
       <c r="R266" t="n">
-        <v>6762512</v>
+        <v>6762369</v>
       </c>
       <c r="S266" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -28120,19 +28145,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z266" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA266" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB266" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -28147,19 +28162,19 @@
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>127282923</v>
+        <v>127275330</v>
       </c>
       <c r="B267" t="n">
         <v>79014</v>
@@ -28190,17 +28205,17 @@
       <c r="I267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>440658</v>
+        <v>440868</v>
       </c>
       <c r="R267" t="n">
-        <v>6762202</v>
+        <v>6762512</v>
       </c>
       <c r="S267" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -28227,9 +28242,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA267" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -28244,19 +28269,19 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>127275346</v>
+        <v>127282923</v>
       </c>
       <c r="B268" t="n">
         <v>79014</v>
@@ -28287,17 +28312,17 @@
       <c r="I268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>440853</v>
+        <v>440658</v>
       </c>
       <c r="R268" t="n">
-        <v>6762514</v>
+        <v>6762202</v>
       </c>
       <c r="S268" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -28324,19 +28349,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z268" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA268" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB268" t="inlineStr">
-        <is>
-          <t>14:33</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -28351,22 +28366,22 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>127276264</v>
+        <v>127275346</v>
       </c>
       <c r="B269" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -28374,42 +28389,37 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>440642</v>
+        <v>440853</v>
       </c>
       <c r="R269" t="n">
-        <v>6762606</v>
+        <v>6762514</v>
       </c>
       <c r="S269" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -28438,7 +28448,7 @@
       </c>
       <c r="Z269" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
@@ -28448,7 +28458,7 @@
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -28463,57 +28473,57 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>127274680</v>
+        <v>127282921</v>
       </c>
       <c r="B270" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>440689</v>
+        <v>440680</v>
       </c>
       <c r="R270" t="n">
-        <v>6762214</v>
+        <v>6762218</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28543,19 +28553,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z270" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA270" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB270" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -28570,12 +28570,12 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>

--- a/artfynd/A 29945-2025 artfynd.xlsx
+++ b/artfynd/A 29945-2025 artfynd.xlsx
@@ -11868,10 +11868,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127273473</v>
+        <v>127282896</v>
       </c>
       <c r="B109" t="n">
-        <v>57657</v>
+        <v>78772</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11879,39 +11879,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>440721</v>
+        <v>440416</v>
       </c>
       <c r="R109" t="n">
-        <v>6761996</v>
+        <v>6762406</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11941,19 +11936,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11968,22 +11953,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127273727</v>
+        <v>127273473</v>
       </c>
       <c r="B110" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11991,34 +11976,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>440754</v>
+        <v>440721</v>
       </c>
       <c r="R110" t="n">
-        <v>6762035</v>
+        <v>6761996</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12087,45 +12077,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127282909</v>
+        <v>127272135</v>
       </c>
       <c r="B111" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>440797</v>
+        <v>440647</v>
       </c>
       <c r="R111" t="n">
-        <v>6762555</v>
+        <v>6762125</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12155,9 +12145,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12172,19 +12172,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127282922</v>
+        <v>127273727</v>
       </c>
       <c r="B112" t="n">
         <v>79014</v>
@@ -12215,14 +12215,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>440685</v>
+        <v>440754</v>
       </c>
       <c r="R112" t="n">
-        <v>6762213</v>
+        <v>6762035</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12252,9 +12252,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12269,19 +12279,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127282903</v>
+        <v>127282909</v>
       </c>
       <c r="B113" t="n">
         <v>79014</v>
@@ -12316,10 +12326,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>440760</v>
+        <v>440797</v>
       </c>
       <c r="R113" t="n">
-        <v>6762626</v>
+        <v>6762555</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12378,7 +12388,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127274251</v>
+        <v>127282922</v>
       </c>
       <c r="B114" t="n">
         <v>79014</v>
@@ -12409,14 +12419,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>440687</v>
+        <v>440685</v>
       </c>
       <c r="R114" t="n">
-        <v>6762120</v>
+        <v>6762213</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12446,19 +12456,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12473,57 +12473,57 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127272135</v>
+        <v>127282903</v>
       </c>
       <c r="B115" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>440647</v>
+        <v>440760</v>
       </c>
       <c r="R115" t="n">
-        <v>6762125</v>
+        <v>6762626</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12553,19 +12553,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12580,22 +12570,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127282896</v>
+        <v>127274251</v>
       </c>
       <c r="B116" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12603,34 +12593,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>440416</v>
+        <v>440687</v>
       </c>
       <c r="R116" t="n">
-        <v>6762406</v>
+        <v>6762120</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12660,9 +12650,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12677,44 +12677,44 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127273755</v>
+        <v>127274061</v>
       </c>
       <c r="B117" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12724,10 +12724,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>440744</v>
+        <v>440706</v>
       </c>
       <c r="R117" t="n">
-        <v>6762065</v>
+        <v>6762058</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12796,10 +12796,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127276304</v>
+        <v>127283110</v>
       </c>
       <c r="B118" t="n">
-        <v>79014</v>
+        <v>79015</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12807,16 +12807,16 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -12827,14 +12827,14 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>440642</v>
+        <v>440835</v>
       </c>
       <c r="R118" t="n">
-        <v>6762606</v>
+        <v>6762564</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12864,19 +12864,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12891,19 +12881,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127275131</v>
+        <v>127273755</v>
       </c>
       <c r="B119" t="n">
         <v>79014</v>
@@ -12938,10 +12928,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>440709</v>
+        <v>440744</v>
       </c>
       <c r="R119" t="n">
-        <v>6762405</v>
+        <v>6762065</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13010,7 +13000,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127271820</v>
+        <v>127276304</v>
       </c>
       <c r="B120" t="n">
         <v>79014</v>
@@ -13041,17 +13031,17 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>440446</v>
+        <v>440642</v>
       </c>
       <c r="R120" t="n">
-        <v>6762469</v>
+        <v>6762606</v>
       </c>
       <c r="S120" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13080,7 +13070,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13090,7 +13080,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13105,22 +13095,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127274057</v>
+        <v>127275131</v>
       </c>
       <c r="B121" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13128,39 +13118,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>440706</v>
+        <v>440709</v>
       </c>
       <c r="R121" t="n">
-        <v>6762058</v>
+        <v>6762405</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13229,48 +13214,48 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127274061</v>
+        <v>127271820</v>
       </c>
       <c r="B122" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>440706</v>
+        <v>440446</v>
       </c>
       <c r="R122" t="n">
-        <v>6762058</v>
+        <v>6762469</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13299,7 +13284,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13309,7 +13294,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13324,22 +13309,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127283110</v>
+        <v>127274057</v>
       </c>
       <c r="B123" t="n">
-        <v>79015</v>
+        <v>57654</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13347,34 +13332,39 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>230405</v>
+        <v>100049</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>440835</v>
+        <v>440706</v>
       </c>
       <c r="R123" t="n">
-        <v>6762564</v>
+        <v>6762058</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13404,9 +13394,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13421,12 +13421,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -13540,10 +13540,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127283139</v>
+        <v>127271992</v>
       </c>
       <c r="B125" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13551,34 +13551,39 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>440723</v>
+        <v>440647</v>
       </c>
       <c r="R125" t="n">
-        <v>6762373</v>
+        <v>6762125</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13608,9 +13613,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13625,19 +13640,19 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127283131</v>
+        <v>127283139</v>
       </c>
       <c r="B126" t="n">
         <v>79014</v>
@@ -13672,10 +13687,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>440682</v>
+        <v>440723</v>
       </c>
       <c r="R126" t="n">
-        <v>6762208</v>
+        <v>6762373</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13734,7 +13749,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127283135</v>
+        <v>127283131</v>
       </c>
       <c r="B127" t="n">
         <v>79014</v>
@@ -13769,10 +13784,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>440456</v>
+        <v>440682</v>
       </c>
       <c r="R127" t="n">
-        <v>6762461</v>
+        <v>6762208</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13831,7 +13846,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127273828</v>
+        <v>127283135</v>
       </c>
       <c r="B128" t="n">
         <v>79014</v>
@@ -13862,17 +13877,17 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>440882</v>
+        <v>440456</v>
       </c>
       <c r="R128" t="n">
-        <v>6762435</v>
+        <v>6762461</v>
       </c>
       <c r="S128" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13899,19 +13914,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13926,22 +13931,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127271992</v>
+        <v>127273828</v>
       </c>
       <c r="B129" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13949,42 +13954,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>440647</v>
+        <v>440882</v>
       </c>
       <c r="R129" t="n">
-        <v>6762125</v>
+        <v>6762435</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14038,60 +14038,60 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127283108</v>
+        <v>127273051</v>
       </c>
       <c r="B130" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>440442</v>
+        <v>440681</v>
       </c>
       <c r="R130" t="n">
-        <v>6762471</v>
+        <v>6762197</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14118,9 +14118,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14135,57 +14145,57 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127282895</v>
+        <v>127276216</v>
       </c>
       <c r="B131" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>440382</v>
+        <v>440657</v>
       </c>
       <c r="R131" t="n">
-        <v>6762379</v>
+        <v>6762603</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14215,9 +14225,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14232,22 +14252,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127283109</v>
+        <v>127276450</v>
       </c>
       <c r="B132" t="n">
-        <v>79015</v>
+        <v>57654</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14255,34 +14275,39 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>230405</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>440875</v>
+        <v>440582</v>
       </c>
       <c r="R132" t="n">
-        <v>6762453</v>
+        <v>6762684</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14312,9 +14337,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14329,22 +14364,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127273051</v>
+        <v>127272305</v>
       </c>
       <c r="B133" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14352,37 +14387,42 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>440681</v>
+        <v>440675</v>
       </c>
       <c r="R133" t="n">
-        <v>6762197</v>
+        <v>6762165</v>
       </c>
       <c r="S133" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14411,7 +14451,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14421,7 +14461,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Diameter ca 4 till 5 cm</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14436,22 +14481,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127276216</v>
+        <v>127271765</v>
       </c>
       <c r="B134" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14459,34 +14504,39 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>440657</v>
+        <v>440627</v>
       </c>
       <c r="R134" t="n">
-        <v>6762603</v>
+        <v>6762119</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14518,7 +14568,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14528,7 +14578,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Miljöbild för området</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14555,7 +14610,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127276450</v>
+        <v>127276148</v>
       </c>
       <c r="B135" t="n">
         <v>57654</v>
@@ -14586,7 +14641,7 @@
       <c r="I135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -14595,10 +14650,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>440582</v>
+        <v>440657</v>
       </c>
       <c r="R135" t="n">
-        <v>6762684</v>
+        <v>6762603</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14667,50 +14722,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127272305</v>
+        <v>127283108</v>
       </c>
       <c r="B136" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>440675</v>
+        <v>440442</v>
       </c>
       <c r="R136" t="n">
-        <v>6762165</v>
+        <v>6762471</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14740,24 +14790,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Diameter ca 4 till 5 cm</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14772,62 +14807,57 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127271765</v>
+        <v>127282895</v>
       </c>
       <c r="B137" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>440627</v>
+        <v>440382</v>
       </c>
       <c r="R137" t="n">
-        <v>6762119</v>
+        <v>6762379</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14857,24 +14887,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Miljöbild för området</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14889,22 +14904,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127276148</v>
+        <v>127274657</v>
       </c>
       <c r="B138" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14912,39 +14927,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>440657</v>
+        <v>440689</v>
       </c>
       <c r="R138" t="n">
-        <v>6762603</v>
+        <v>6762214</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14976,7 +14986,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14986,7 +14996,12 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15013,7 +15028,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127274657</v>
+        <v>127283117</v>
       </c>
       <c r="B139" t="n">
         <v>79014</v>
@@ -15044,14 +15059,14 @@
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>440689</v>
+        <v>440863</v>
       </c>
       <c r="R139" t="n">
-        <v>6762214</v>
+        <v>6762603</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15081,24 +15096,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15113,19 +15113,19 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127283117</v>
+        <v>127282932</v>
       </c>
       <c r="B140" t="n">
         <v>79014</v>
@@ -15156,14 +15156,14 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>440863</v>
+        <v>440427</v>
       </c>
       <c r="R140" t="n">
-        <v>6762603</v>
+        <v>6762470</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15210,19 +15210,19 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127282932</v>
+        <v>127282912</v>
       </c>
       <c r="B141" t="n">
         <v>79014</v>
@@ -15257,10 +15257,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>440427</v>
+        <v>440936</v>
       </c>
       <c r="R141" t="n">
-        <v>6762470</v>
+        <v>6762564</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15319,7 +15319,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127282912</v>
+        <v>127282926</v>
       </c>
       <c r="B142" t="n">
         <v>79014</v>
@@ -15354,10 +15354,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>440936</v>
+        <v>440497</v>
       </c>
       <c r="R142" t="n">
-        <v>6762564</v>
+        <v>6762331</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15416,7 +15416,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127282926</v>
+        <v>127283130</v>
       </c>
       <c r="B143" t="n">
         <v>79014</v>
@@ -15447,14 +15447,14 @@
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>440497</v>
+        <v>440697</v>
       </c>
       <c r="R143" t="n">
-        <v>6762331</v>
+        <v>6762237</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15501,19 +15501,19 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127283130</v>
+        <v>127273488</v>
       </c>
       <c r="B144" t="n">
         <v>79014</v>
@@ -15544,14 +15544,14 @@
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>440697</v>
+        <v>440721</v>
       </c>
       <c r="R144" t="n">
-        <v>6762237</v>
+        <v>6761996</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15581,9 +15581,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15598,22 +15608,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127273488</v>
+        <v>127283109</v>
       </c>
       <c r="B145" t="n">
-        <v>79014</v>
+        <v>79015</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15621,16 +15631,16 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -15641,14 +15651,14 @@
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>440721</v>
+        <v>440875</v>
       </c>
       <c r="R145" t="n">
-        <v>6761996</v>
+        <v>6762453</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15678,19 +15688,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15705,12 +15705,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
@@ -18113,7 +18113,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127273853</v>
+        <v>127275337</v>
       </c>
       <c r="B169" t="n">
         <v>79014</v>
@@ -18148,10 +18148,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>440887</v>
+        <v>440855</v>
       </c>
       <c r="R169" t="n">
-        <v>6762439</v>
+        <v>6762513</v>
       </c>
       <c r="S169" t="n">
         <v>9</v>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18220,32 +18220,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127270744</v>
+        <v>127271802</v>
       </c>
       <c r="B170" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18255,10 +18255,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>440351</v>
+        <v>440627</v>
       </c>
       <c r="R170" t="n">
-        <v>6762480</v>
+        <v>6762119</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18301,6 +18301,11 @@
       <c r="AB170" t="inlineStr">
         <is>
           <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Rikligt med torrakor med spår efter Mindre Märgborre i området</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18327,48 +18332,53 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127282927</v>
+        <v>127271251</v>
       </c>
       <c r="B171" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>440488</v>
+        <v>440375</v>
       </c>
       <c r="R171" t="n">
-        <v>6762419</v>
+        <v>6762366</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18395,9 +18405,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18412,57 +18432,57 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127283128</v>
+        <v>127276271</v>
       </c>
       <c r="B172" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>440822</v>
+        <v>440642</v>
       </c>
       <c r="R172" t="n">
-        <v>6762415</v>
+        <v>6762606</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18492,9 +18512,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18509,19 +18539,19 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127274114</v>
+        <v>127273853</v>
       </c>
       <c r="B173" t="n">
         <v>79014</v>
@@ -18552,17 +18582,17 @@
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>440711</v>
+        <v>440887</v>
       </c>
       <c r="R173" t="n">
-        <v>6762111</v>
+        <v>6762439</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18591,7 +18621,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -18601,7 +18631,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18616,19 +18646,19 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127283115</v>
+        <v>127270744</v>
       </c>
       <c r="B174" t="n">
         <v>79014</v>
@@ -18659,14 +18689,14 @@
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>440803</v>
+        <v>440351</v>
       </c>
       <c r="R174" t="n">
-        <v>6762557</v>
+        <v>6762480</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18696,9 +18726,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18713,19 +18753,19 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127283134</v>
+        <v>127282927</v>
       </c>
       <c r="B175" t="n">
         <v>79014</v>
@@ -18756,14 +18796,14 @@
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>440487</v>
+        <v>440488</v>
       </c>
       <c r="R175" t="n">
-        <v>6762321</v>
+        <v>6762419</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18810,19 +18850,19 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127283133</v>
+        <v>127283128</v>
       </c>
       <c r="B176" t="n">
         <v>79014</v>
@@ -18857,10 +18897,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>440598</v>
+        <v>440822</v>
       </c>
       <c r="R176" t="n">
-        <v>6762206</v>
+        <v>6762415</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18919,7 +18959,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127275337</v>
+        <v>127274114</v>
       </c>
       <c r="B177" t="n">
         <v>79014</v>
@@ -18950,17 +18990,17 @@
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>440855</v>
+        <v>440711</v>
       </c>
       <c r="R177" t="n">
-        <v>6762513</v>
+        <v>6762111</v>
       </c>
       <c r="S177" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -18989,7 +19029,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -18999,7 +19039,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19014,57 +19054,57 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127271802</v>
+        <v>127283115</v>
       </c>
       <c r="B178" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>440627</v>
+        <v>440803</v>
       </c>
       <c r="R178" t="n">
-        <v>6762119</v>
+        <v>6762557</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19094,24 +19134,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Rikligt med torrakor med spår efter Mindre Märgborre i området</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19126,65 +19151,60 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127271251</v>
+        <v>127283134</v>
       </c>
       <c r="B179" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>440375</v>
+        <v>440487</v>
       </c>
       <c r="R179" t="n">
-        <v>6762366</v>
+        <v>6762321</v>
       </c>
       <c r="S179" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19211,19 +19231,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>10:53</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19238,57 +19248,57 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127276271</v>
+        <v>127283133</v>
       </c>
       <c r="B180" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>440642</v>
+        <v>440598</v>
       </c>
       <c r="R180" t="n">
-        <v>6762606</v>
+        <v>6762206</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19318,19 +19328,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19345,12 +19345,12 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
@@ -19969,10 +19969,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127282924</v>
+        <v>127274877</v>
       </c>
       <c r="B187" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19980,37 +19980,42 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>440623</v>
+        <v>440752</v>
       </c>
       <c r="R187" t="n">
-        <v>6762194</v>
+        <v>6762337</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -20037,9 +20042,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20054,57 +20069,57 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127283136</v>
+        <v>127276155</v>
       </c>
       <c r="B188" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>440394</v>
+        <v>440657</v>
       </c>
       <c r="R188" t="n">
-        <v>6762413</v>
+        <v>6762603</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20134,9 +20149,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20151,19 +20176,19 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127283138</v>
+        <v>127282924</v>
       </c>
       <c r="B189" t="n">
         <v>79014</v>
@@ -20194,14 +20219,14 @@
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>440335</v>
+        <v>440623</v>
       </c>
       <c r="R189" t="n">
-        <v>6762400</v>
+        <v>6762194</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20248,19 +20273,19 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127282907</v>
+        <v>127283136</v>
       </c>
       <c r="B190" t="n">
         <v>79014</v>
@@ -20291,14 +20316,14 @@
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>440793</v>
+        <v>440394</v>
       </c>
       <c r="R190" t="n">
-        <v>6762525</v>
+        <v>6762413</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20345,19 +20370,19 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127283118</v>
+        <v>127283138</v>
       </c>
       <c r="B191" t="n">
         <v>79014</v>
@@ -20392,10 +20417,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>440868</v>
+        <v>440335</v>
       </c>
       <c r="R191" t="n">
-        <v>6762583</v>
+        <v>6762400</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20454,7 +20479,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127283113</v>
+        <v>127282907</v>
       </c>
       <c r="B192" t="n">
         <v>79014</v>
@@ -20485,14 +20510,14 @@
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>440768</v>
+        <v>440793</v>
       </c>
       <c r="R192" t="n">
-        <v>6762554</v>
+        <v>6762525</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20539,22 +20564,22 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127274877</v>
+        <v>127283118</v>
       </c>
       <c r="B193" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20562,42 +20587,37 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>440752</v>
+        <v>440868</v>
       </c>
       <c r="R193" t="n">
-        <v>6762337</v>
+        <v>6762583</v>
       </c>
       <c r="S193" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -20624,19 +20644,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20651,57 +20661,57 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127276155</v>
+        <v>127283113</v>
       </c>
       <c r="B194" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>440657</v>
+        <v>440768</v>
       </c>
       <c r="R194" t="n">
-        <v>6762603</v>
+        <v>6762554</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20731,19 +20741,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20758,22 +20758,22 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127274677</v>
+        <v>127276018</v>
       </c>
       <c r="B195" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20781,39 +20781,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>440689</v>
+        <v>440697</v>
       </c>
       <c r="R195" t="n">
-        <v>6762214</v>
+        <v>6762625</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20845,7 +20840,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -20855,7 +20850,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20882,7 +20877,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127276018</v>
+        <v>127275350</v>
       </c>
       <c r="B196" t="n">
         <v>79014</v>
@@ -20913,17 +20908,17 @@
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>440697</v>
+        <v>440851</v>
       </c>
       <c r="R196" t="n">
-        <v>6762625</v>
+        <v>6762513</v>
       </c>
       <c r="S196" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -20952,7 +20947,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -20962,7 +20957,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20977,19 +20972,19 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127275350</v>
+        <v>127283124</v>
       </c>
       <c r="B197" t="n">
         <v>79014</v>
@@ -21020,17 +21015,17 @@
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>440851</v>
+        <v>440965</v>
       </c>
       <c r="R197" t="n">
-        <v>6762513</v>
+        <v>6762540</v>
       </c>
       <c r="S197" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -21057,19 +21052,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21084,19 +21069,19 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127283124</v>
+        <v>127272147</v>
       </c>
       <c r="B198" t="n">
         <v>79014</v>
@@ -21127,17 +21112,17 @@
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>440965</v>
+        <v>440498</v>
       </c>
       <c r="R198" t="n">
-        <v>6762540</v>
+        <v>6762428</v>
       </c>
       <c r="S198" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -21164,9 +21149,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21181,60 +21176,60 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127272147</v>
+        <v>127283143</v>
       </c>
       <c r="B199" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>440498</v>
+        <v>440337</v>
       </c>
       <c r="R199" t="n">
-        <v>6762428</v>
+        <v>6762397</v>
       </c>
       <c r="S199" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -21261,19 +21256,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z199" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21288,19 +21273,19 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127283143</v>
+        <v>127272174</v>
       </c>
       <c r="B200" t="n">
         <v>8447</v>
@@ -21331,14 +21316,14 @@
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>440337</v>
+        <v>440657</v>
       </c>
       <c r="R200" t="n">
-        <v>6762397</v>
+        <v>6762157</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21368,9 +21353,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21385,57 +21380,62 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127272174</v>
+        <v>127274677</v>
       </c>
       <c r="B201" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>440657</v>
+        <v>440689</v>
       </c>
       <c r="R201" t="n">
-        <v>6762157</v>
+        <v>6762214</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -23146,32 +23146,32 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127283107</v>
+        <v>127283106</v>
       </c>
       <c r="B218" t="n">
-        <v>8447</v>
+        <v>78773</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -23181,10 +23181,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>440636</v>
+        <v>440504</v>
       </c>
       <c r="R218" t="n">
-        <v>6762585</v>
+        <v>6762388</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23243,10 +23243,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127283106</v>
+        <v>127283141</v>
       </c>
       <c r="B219" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23254,21 +23254,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -23278,10 +23278,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>440504</v>
+        <v>440651</v>
       </c>
       <c r="R219" t="n">
-        <v>6762388</v>
+        <v>6762611</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23340,10 +23340,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127283141</v>
+        <v>127283100</v>
       </c>
       <c r="B220" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -23351,21 +23351,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -23375,10 +23375,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>440651</v>
+        <v>440686</v>
       </c>
       <c r="R220" t="n">
-        <v>6762611</v>
+        <v>6762630</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23437,10 +23437,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127283100</v>
+        <v>127282898</v>
       </c>
       <c r="B221" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23448,34 +23448,34 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>440686</v>
+        <v>440741</v>
       </c>
       <c r="R221" t="n">
-        <v>6762630</v>
+        <v>6762609</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23522,19 +23522,19 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127282898</v>
+        <v>127283122</v>
       </c>
       <c r="B222" t="n">
         <v>79014</v>
@@ -23565,14 +23565,14 @@
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>440741</v>
+        <v>440912</v>
       </c>
       <c r="R222" t="n">
-        <v>6762609</v>
+        <v>6762579</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23619,19 +23619,19 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127283122</v>
+        <v>127282915</v>
       </c>
       <c r="B223" t="n">
         <v>79014</v>
@@ -23662,14 +23662,14 @@
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>440912</v>
+        <v>440946</v>
       </c>
       <c r="R223" t="n">
-        <v>6762579</v>
+        <v>6762514</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23716,19 +23716,19 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127282915</v>
+        <v>127275040</v>
       </c>
       <c r="B224" t="n">
         <v>79014</v>
@@ -23759,14 +23759,14 @@
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>440946</v>
+        <v>440745</v>
       </c>
       <c r="R224" t="n">
-        <v>6762514</v>
+        <v>6762369</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23796,9 +23796,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -23813,19 +23828,19 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127275040</v>
+        <v>127282899</v>
       </c>
       <c r="B225" t="n">
         <v>79014</v>
@@ -23856,14 +23871,14 @@
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>440745</v>
+        <v>440763</v>
       </c>
       <c r="R225" t="n">
-        <v>6762369</v>
+        <v>6762529</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23893,24 +23908,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z225" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA225" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB225" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC225" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -23925,57 +23925,57 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127282899</v>
+        <v>127283107</v>
       </c>
       <c r="B226" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>440763</v>
+        <v>440636</v>
       </c>
       <c r="R226" t="n">
-        <v>6762529</v>
+        <v>6762585</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24022,12 +24022,12 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>

--- a/artfynd/A 29945-2025 artfynd.xlsx
+++ b/artfynd/A 29945-2025 artfynd.xlsx
@@ -11868,10 +11868,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127282896</v>
+        <v>127273727</v>
       </c>
       <c r="B109" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11879,34 +11879,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>440416</v>
+        <v>440754</v>
       </c>
       <c r="R109" t="n">
-        <v>6762406</v>
+        <v>6762035</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11936,9 +11936,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11953,22 +11963,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127273473</v>
+        <v>127282909</v>
       </c>
       <c r="B110" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11976,39 +11986,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>440721</v>
+        <v>440797</v>
       </c>
       <c r="R110" t="n">
-        <v>6761996</v>
+        <v>6762555</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12038,19 +12043,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12065,57 +12060,57 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127272135</v>
+        <v>127282922</v>
       </c>
       <c r="B111" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>440647</v>
+        <v>440685</v>
       </c>
       <c r="R111" t="n">
-        <v>6762125</v>
+        <v>6762213</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12145,19 +12140,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12172,19 +12157,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127273727</v>
+        <v>127282903</v>
       </c>
       <c r="B112" t="n">
         <v>79014</v>
@@ -12215,14 +12200,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>440754</v>
+        <v>440760</v>
       </c>
       <c r="R112" t="n">
-        <v>6762035</v>
+        <v>6762626</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12252,19 +12237,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12279,22 +12254,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127282909</v>
+        <v>127282896</v>
       </c>
       <c r="B113" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12302,21 +12277,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12326,10 +12301,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>440797</v>
+        <v>440416</v>
       </c>
       <c r="R113" t="n">
-        <v>6762555</v>
+        <v>6762406</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12388,7 +12363,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127282922</v>
+        <v>127274251</v>
       </c>
       <c r="B114" t="n">
         <v>79014</v>
@@ -12419,14 +12394,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>440685</v>
+        <v>440687</v>
       </c>
       <c r="R114" t="n">
-        <v>6762213</v>
+        <v>6762120</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12456,9 +12431,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12473,22 +12458,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127282903</v>
+        <v>127273473</v>
       </c>
       <c r="B115" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12496,34 +12481,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>440760</v>
+        <v>440721</v>
       </c>
       <c r="R115" t="n">
-        <v>6762626</v>
+        <v>6761996</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12553,9 +12543,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12570,44 +12570,44 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127274251</v>
+        <v>127272135</v>
       </c>
       <c r="B116" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12617,10 +12617,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>440687</v>
+        <v>440647</v>
       </c>
       <c r="R116" t="n">
-        <v>6762120</v>
+        <v>6762125</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12689,32 +12689,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127274061</v>
+        <v>127273755</v>
       </c>
       <c r="B117" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12724,10 +12724,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>440706</v>
+        <v>440744</v>
       </c>
       <c r="R117" t="n">
-        <v>6762058</v>
+        <v>6762065</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12796,10 +12796,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127283110</v>
+        <v>127276304</v>
       </c>
       <c r="B118" t="n">
-        <v>79015</v>
+        <v>79014</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12807,16 +12807,16 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -12827,14 +12827,14 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>440835</v>
+        <v>440642</v>
       </c>
       <c r="R118" t="n">
-        <v>6762564</v>
+        <v>6762606</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12864,9 +12864,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12881,19 +12891,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127273755</v>
+        <v>127275131</v>
       </c>
       <c r="B119" t="n">
         <v>79014</v>
@@ -12928,10 +12938,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>440744</v>
+        <v>440709</v>
       </c>
       <c r="R119" t="n">
-        <v>6762065</v>
+        <v>6762405</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13000,7 +13010,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127276304</v>
+        <v>127271820</v>
       </c>
       <c r="B120" t="n">
         <v>79014</v>
@@ -13031,17 +13041,17 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>440642</v>
+        <v>440446</v>
       </c>
       <c r="R120" t="n">
-        <v>6762606</v>
+        <v>6762469</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13070,7 +13080,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13080,7 +13090,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13095,22 +13105,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127275131</v>
+        <v>127274057</v>
       </c>
       <c r="B121" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13118,34 +13128,39 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>440709</v>
+        <v>440706</v>
       </c>
       <c r="R121" t="n">
-        <v>6762405</v>
+        <v>6762058</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13214,48 +13229,48 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127271820</v>
+        <v>127274061</v>
       </c>
       <c r="B122" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>440446</v>
+        <v>440706</v>
       </c>
       <c r="R122" t="n">
-        <v>6762469</v>
+        <v>6762058</v>
       </c>
       <c r="S122" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13284,7 +13299,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13294,7 +13309,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13309,22 +13324,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127274057</v>
+        <v>127283110</v>
       </c>
       <c r="B123" t="n">
-        <v>57654</v>
+        <v>79015</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13332,39 +13347,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>230405</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>440706</v>
+        <v>440835</v>
       </c>
       <c r="R123" t="n">
-        <v>6762058</v>
+        <v>6762564</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13394,19 +13404,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13421,22 +13421,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127275968</v>
+        <v>127283139</v>
       </c>
       <c r="B124" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13444,34 +13444,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
         <v>440723</v>
       </c>
       <c r="R124" t="n">
-        <v>6762648</v>
+        <v>6762373</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13501,19 +13501,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13528,22 +13518,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127271992</v>
+        <v>127283131</v>
       </c>
       <c r="B125" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13551,39 +13541,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>440647</v>
+        <v>440682</v>
       </c>
       <c r="R125" t="n">
-        <v>6762125</v>
+        <v>6762208</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13613,19 +13598,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13640,19 +13615,19 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127283139</v>
+        <v>127283135</v>
       </c>
       <c r="B126" t="n">
         <v>79014</v>
@@ -13687,10 +13662,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>440723</v>
+        <v>440456</v>
       </c>
       <c r="R126" t="n">
-        <v>6762373</v>
+        <v>6762461</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13749,7 +13724,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127283131</v>
+        <v>127273828</v>
       </c>
       <c r="B127" t="n">
         <v>79014</v>
@@ -13780,17 +13755,17 @@
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>440682</v>
+        <v>440882</v>
       </c>
       <c r="R127" t="n">
-        <v>6762208</v>
+        <v>6762435</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13817,9 +13792,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13834,22 +13819,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127283135</v>
+        <v>127275968</v>
       </c>
       <c r="B128" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13857,34 +13842,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>440456</v>
+        <v>440723</v>
       </c>
       <c r="R128" t="n">
-        <v>6762461</v>
+        <v>6762648</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13914,9 +13899,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13931,22 +13926,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127273828</v>
+        <v>127271992</v>
       </c>
       <c r="B129" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13954,37 +13949,42 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>440882</v>
+        <v>440647</v>
       </c>
       <c r="R129" t="n">
-        <v>6762435</v>
+        <v>6762125</v>
       </c>
       <c r="S129" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14038,60 +14038,60 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127273051</v>
+        <v>127283108</v>
       </c>
       <c r="B130" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>440681</v>
+        <v>440442</v>
       </c>
       <c r="R130" t="n">
-        <v>6762197</v>
+        <v>6762471</v>
       </c>
       <c r="S130" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14118,19 +14118,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>12:38</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14145,57 +14135,57 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127276216</v>
+        <v>127282895</v>
       </c>
       <c r="B131" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>440657</v>
+        <v>440382</v>
       </c>
       <c r="R131" t="n">
-        <v>6762603</v>
+        <v>6762379</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14225,19 +14215,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14252,22 +14232,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127276450</v>
+        <v>127274657</v>
       </c>
       <c r="B132" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14275,39 +14255,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>440582</v>
+        <v>440689</v>
       </c>
       <c r="R132" t="n">
-        <v>6762684</v>
+        <v>6762214</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14339,7 +14314,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14349,7 +14324,12 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14376,10 +14356,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127272305</v>
+        <v>127283117</v>
       </c>
       <c r="B133" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14387,39 +14367,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>440675</v>
+        <v>440863</v>
       </c>
       <c r="R133" t="n">
-        <v>6762165</v>
+        <v>6762603</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14449,24 +14424,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Diameter ca 4 till 5 cm</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14481,22 +14441,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127271765</v>
+        <v>127273051</v>
       </c>
       <c r="B134" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14504,42 +14464,37 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>440627</v>
+        <v>440681</v>
       </c>
       <c r="R134" t="n">
-        <v>6762119</v>
+        <v>6762197</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14568,7 +14523,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14578,12 +14533,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Miljöbild för området</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14598,22 +14548,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127276148</v>
+        <v>127282932</v>
       </c>
       <c r="B135" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14621,39 +14571,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>440657</v>
+        <v>440427</v>
       </c>
       <c r="R135" t="n">
-        <v>6762603</v>
+        <v>6762470</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14683,19 +14628,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14710,57 +14645,57 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127283108</v>
+        <v>127282912</v>
       </c>
       <c r="B136" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>440442</v>
+        <v>440936</v>
       </c>
       <c r="R136" t="n">
-        <v>6762471</v>
+        <v>6762564</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14807,44 +14742,44 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127282895</v>
+        <v>127282926</v>
       </c>
       <c r="B137" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14854,10 +14789,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>440382</v>
+        <v>440497</v>
       </c>
       <c r="R137" t="n">
-        <v>6762379</v>
+        <v>6762331</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14916,7 +14851,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127274657</v>
+        <v>127283130</v>
       </c>
       <c r="B138" t="n">
         <v>79014</v>
@@ -14947,14 +14882,14 @@
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>440689</v>
+        <v>440697</v>
       </c>
       <c r="R138" t="n">
-        <v>6762214</v>
+        <v>6762237</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14984,24 +14919,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15016,19 +14936,19 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127283117</v>
+        <v>127276216</v>
       </c>
       <c r="B139" t="n">
         <v>79014</v>
@@ -15059,11 +14979,11 @@
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>440863</v>
+        <v>440657</v>
       </c>
       <c r="R139" t="n">
         <v>6762603</v>
@@ -15096,9 +15016,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15113,19 +15043,19 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127282932</v>
+        <v>127273488</v>
       </c>
       <c r="B140" t="n">
         <v>79014</v>
@@ -15156,14 +15086,14 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>440427</v>
+        <v>440721</v>
       </c>
       <c r="R140" t="n">
-        <v>6762470</v>
+        <v>6761996</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15193,9 +15123,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15210,22 +15150,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127282912</v>
+        <v>127276148</v>
       </c>
       <c r="B141" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15233,34 +15173,39 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>440936</v>
+        <v>440657</v>
       </c>
       <c r="R141" t="n">
-        <v>6762564</v>
+        <v>6762603</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15290,9 +15235,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15307,22 +15262,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127282926</v>
+        <v>127272305</v>
       </c>
       <c r="B142" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15330,34 +15285,39 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>440497</v>
+        <v>440675</v>
       </c>
       <c r="R142" t="n">
-        <v>6762331</v>
+        <v>6762165</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15387,9 +15347,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Diameter ca 4 till 5 cm</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15404,22 +15379,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127283130</v>
+        <v>127271765</v>
       </c>
       <c r="B143" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15427,34 +15402,39 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>440697</v>
+        <v>440627</v>
       </c>
       <c r="R143" t="n">
-        <v>6762237</v>
+        <v>6762119</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15484,9 +15464,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Miljöbild för området</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15501,22 +15496,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127273488</v>
+        <v>127276450</v>
       </c>
       <c r="B144" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15524,34 +15519,39 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>440721</v>
+        <v>440582</v>
       </c>
       <c r="R144" t="n">
-        <v>6761996</v>
+        <v>6762684</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15583,7 +15583,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15593,7 +15593,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15717,48 +15717,48 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127274917</v>
+        <v>127283142</v>
       </c>
       <c r="B146" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>440752</v>
+        <v>440744</v>
       </c>
       <c r="R146" t="n">
-        <v>6762337</v>
+        <v>6762615</v>
       </c>
       <c r="S146" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15785,19 +15785,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15812,19 +15802,19 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127273038</v>
+        <v>127274917</v>
       </c>
       <c r="B147" t="n">
         <v>79014</v>
@@ -15855,17 +15845,17 @@
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>440688</v>
+        <v>440752</v>
       </c>
       <c r="R147" t="n">
-        <v>6762199</v>
+        <v>6762337</v>
       </c>
       <c r="S147" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15894,7 +15884,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15904,7 +15894,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15919,44 +15909,44 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127283142</v>
+        <v>127283119</v>
       </c>
       <c r="B148" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15966,10 +15956,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>440744</v>
+        <v>440881</v>
       </c>
       <c r="R148" t="n">
-        <v>6762615</v>
+        <v>6762591</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16028,7 +16018,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127283119</v>
+        <v>127272858</v>
       </c>
       <c r="B149" t="n">
         <v>79014</v>
@@ -16059,17 +16049,17 @@
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>440881</v>
+        <v>440609</v>
       </c>
       <c r="R149" t="n">
-        <v>6762591</v>
+        <v>6762190</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16096,9 +16086,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16113,19 +16113,19 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127272858</v>
+        <v>127273038</v>
       </c>
       <c r="B150" t="n">
         <v>79014</v>
@@ -16160,10 +16160,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>440609</v>
+        <v>440688</v>
       </c>
       <c r="R150" t="n">
-        <v>6762190</v>
+        <v>6762199</v>
       </c>
       <c r="S150" t="n">
         <v>9</v>
@@ -16195,7 +16195,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16205,7 +16205,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16553,10 +16553,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127283105</v>
+        <v>127272237</v>
       </c>
       <c r="B154" t="n">
-        <v>79632</v>
+        <v>57657</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16564,34 +16564,39 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>440909</v>
+        <v>440675</v>
       </c>
       <c r="R154" t="n">
-        <v>6762467</v>
+        <v>6762165</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16621,9 +16626,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16638,19 +16653,19 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127274354</v>
+        <v>127282904</v>
       </c>
       <c r="B155" t="n">
         <v>79014</v>
@@ -16681,14 +16696,14 @@
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>440686</v>
+        <v>440776</v>
       </c>
       <c r="R155" t="n">
-        <v>6762176</v>
+        <v>6762632</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16718,19 +16733,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16745,22 +16750,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127272237</v>
+        <v>127282914</v>
       </c>
       <c r="B156" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16768,39 +16773,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>440675</v>
+        <v>440924</v>
       </c>
       <c r="R156" t="n">
-        <v>6762165</v>
+        <v>6762509</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16830,19 +16830,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16857,19 +16847,19 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127282904</v>
+        <v>127274354</v>
       </c>
       <c r="B157" t="n">
         <v>79014</v>
@@ -16900,14 +16890,14 @@
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>440776</v>
+        <v>440686</v>
       </c>
       <c r="R157" t="n">
-        <v>6762632</v>
+        <v>6762176</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16937,9 +16927,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16954,19 +16954,19 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127282914</v>
+        <v>127272746</v>
       </c>
       <c r="B158" t="n">
         <v>79014</v>
@@ -16997,17 +16997,17 @@
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>440924</v>
+        <v>440503</v>
       </c>
       <c r="R158" t="n">
-        <v>6762509</v>
+        <v>6762308</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17034,9 +17034,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17051,22 +17061,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127272746</v>
+        <v>127283105</v>
       </c>
       <c r="B159" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17074,37 +17084,37 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>440503</v>
+        <v>440909</v>
       </c>
       <c r="R159" t="n">
-        <v>6762308</v>
+        <v>6762467</v>
       </c>
       <c r="S159" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17131,19 +17141,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17158,22 +17158,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127274348</v>
+        <v>127282900</v>
       </c>
       <c r="B160" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17181,39 +17181,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>440686</v>
+        <v>440757</v>
       </c>
       <c r="R160" t="n">
-        <v>6762176</v>
+        <v>6762544</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17243,19 +17238,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17270,22 +17255,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127275098</v>
+        <v>127276426</v>
       </c>
       <c r="B161" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17293,39 +17278,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>440679</v>
+        <v>440582</v>
       </c>
       <c r="R161" t="n">
-        <v>6762388</v>
+        <v>6762684</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17357,7 +17337,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17367,7 +17347,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17394,7 +17374,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127282900</v>
+        <v>127275877</v>
       </c>
       <c r="B162" t="n">
         <v>79014</v>
@@ -17425,14 +17405,14 @@
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>440757</v>
+        <v>440732</v>
       </c>
       <c r="R162" t="n">
-        <v>6762544</v>
+        <v>6762635</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17462,9 +17442,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17479,19 +17469,19 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127276426</v>
+        <v>127273900</v>
       </c>
       <c r="B163" t="n">
         <v>79014</v>
@@ -17522,17 +17512,17 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>440582</v>
+        <v>440903</v>
       </c>
       <c r="R163" t="n">
-        <v>6762684</v>
+        <v>6762450</v>
       </c>
       <c r="S163" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -17561,7 +17551,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17571,7 +17561,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17586,19 +17576,19 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127275877</v>
+        <v>127282902</v>
       </c>
       <c r="B164" t="n">
         <v>79014</v>
@@ -17629,14 +17619,14 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>440732</v>
+        <v>440760</v>
       </c>
       <c r="R164" t="n">
-        <v>6762635</v>
+        <v>6762569</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17666,19 +17656,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17693,19 +17673,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127273900</v>
+        <v>127273086</v>
       </c>
       <c r="B165" t="n">
         <v>79014</v>
@@ -17740,10 +17720,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>440903</v>
+        <v>440694</v>
       </c>
       <c r="R165" t="n">
-        <v>6762450</v>
+        <v>6762204</v>
       </c>
       <c r="S165" t="n">
         <v>9</v>
@@ -17775,7 +17755,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17785,7 +17765,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17812,7 +17792,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127282902</v>
+        <v>127283137</v>
       </c>
       <c r="B166" t="n">
         <v>79014</v>
@@ -17843,14 +17823,14 @@
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>440760</v>
+        <v>440354</v>
       </c>
       <c r="R166" t="n">
-        <v>6762569</v>
+        <v>6762415</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17897,22 +17877,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127273086</v>
+        <v>127275098</v>
       </c>
       <c r="B167" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17920,37 +17900,42 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>440694</v>
+        <v>440679</v>
       </c>
       <c r="R167" t="n">
-        <v>6762204</v>
+        <v>6762388</v>
       </c>
       <c r="S167" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -17979,7 +17964,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -17989,7 +17974,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18004,22 +17989,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127283137</v>
+        <v>127274348</v>
       </c>
       <c r="B168" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18027,34 +18012,39 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>440354</v>
+        <v>440686</v>
       </c>
       <c r="R168" t="n">
-        <v>6762415</v>
+        <v>6762176</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18084,9 +18074,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18101,60 +18101,60 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127275337</v>
+        <v>127271802</v>
       </c>
       <c r="B169" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>440855</v>
+        <v>440627</v>
       </c>
       <c r="R169" t="n">
-        <v>6762513</v>
+        <v>6762119</v>
       </c>
       <c r="S169" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18193,7 +18193,12 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Rikligt med torrakor med spår efter Mindre Märgborre i området</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18208,19 +18213,19 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127271802</v>
+        <v>127271251</v>
       </c>
       <c r="B170" t="n">
         <v>8447</v>
@@ -18249,19 +18254,24 @@
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>440627</v>
+        <v>440375</v>
       </c>
       <c r="R170" t="n">
-        <v>6762119</v>
+        <v>6762366</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18290,7 +18300,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18300,12 +18310,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Rikligt med torrakor med spår efter Mindre Märgborre i området</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18320,19 +18325,19 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127271251</v>
+        <v>127276271</v>
       </c>
       <c r="B171" t="n">
         <v>8447</v>
@@ -18361,24 +18366,19 @@
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>440375</v>
+        <v>440642</v>
       </c>
       <c r="R171" t="n">
-        <v>6762366</v>
+        <v>6762606</v>
       </c>
       <c r="S171" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18432,60 +18432,60 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127276271</v>
+        <v>127273853</v>
       </c>
       <c r="B172" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>440642</v>
+        <v>440887</v>
       </c>
       <c r="R172" t="n">
-        <v>6762606</v>
+        <v>6762439</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18539,19 +18539,19 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127273853</v>
+        <v>127270744</v>
       </c>
       <c r="B173" t="n">
         <v>79014</v>
@@ -18582,17 +18582,17 @@
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>440887</v>
+        <v>440351</v>
       </c>
       <c r="R173" t="n">
-        <v>6762439</v>
+        <v>6762480</v>
       </c>
       <c r="S173" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -18631,7 +18631,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18646,19 +18646,19 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127270744</v>
+        <v>127275337</v>
       </c>
       <c r="B174" t="n">
         <v>79014</v>
@@ -18689,17 +18689,17 @@
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>440351</v>
+        <v>440855</v>
       </c>
       <c r="R174" t="n">
-        <v>6762480</v>
+        <v>6762513</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -18738,7 +18738,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18753,12 +18753,12 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
@@ -19357,7 +19357,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127283127</v>
+        <v>127282906</v>
       </c>
       <c r="B181" t="n">
         <v>79014</v>
@@ -19388,14 +19388,14 @@
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>440843</v>
+        <v>440782</v>
       </c>
       <c r="R181" t="n">
-        <v>6762431</v>
+        <v>6762562</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19442,22 +19442,22 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127283116</v>
+        <v>127274154</v>
       </c>
       <c r="B182" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19465,37 +19465,42 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>440823</v>
+        <v>440946</v>
       </c>
       <c r="R182" t="n">
-        <v>6762604</v>
+        <v>6762537</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -19522,9 +19527,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19539,19 +19559,19 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127282906</v>
+        <v>127283127</v>
       </c>
       <c r="B183" t="n">
         <v>79014</v>
@@ -19582,14 +19602,14 @@
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>440782</v>
+        <v>440843</v>
       </c>
       <c r="R183" t="n">
-        <v>6762562</v>
+        <v>6762431</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19636,19 +19656,19 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127275778</v>
+        <v>127283116</v>
       </c>
       <c r="B184" t="n">
         <v>79014</v>
@@ -19679,17 +19699,17 @@
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>440761</v>
+        <v>440823</v>
       </c>
       <c r="R184" t="n">
-        <v>6762597</v>
+        <v>6762604</v>
       </c>
       <c r="S184" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19716,19 +19736,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>15:06</t>
-        </is>
-      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>15:06</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19743,19 +19753,19 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127282925</v>
+        <v>127275778</v>
       </c>
       <c r="B185" t="n">
         <v>79014</v>
@@ -19786,17 +19796,17 @@
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>440619</v>
+        <v>440761</v>
       </c>
       <c r="R185" t="n">
-        <v>6762184</v>
+        <v>6762597</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -19823,9 +19833,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19840,22 +19860,22 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127274154</v>
+        <v>127282925</v>
       </c>
       <c r="B186" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19863,42 +19883,37 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>440946</v>
+        <v>440619</v>
       </c>
       <c r="R186" t="n">
-        <v>6762537</v>
+        <v>6762184</v>
       </c>
       <c r="S186" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19925,24 +19940,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19957,65 +19957,60 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127274877</v>
+        <v>127276155</v>
       </c>
       <c r="B187" t="n">
-        <v>57817</v>
+        <v>8447</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>440752</v>
+        <v>440657</v>
       </c>
       <c r="R187" t="n">
-        <v>6762337</v>
+        <v>6762603</v>
       </c>
       <c r="S187" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -20044,7 +20039,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20054,7 +20049,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20081,48 +20076,53 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127276155</v>
+        <v>127274877</v>
       </c>
       <c r="B188" t="n">
-        <v>8447</v>
+        <v>57817</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>440657</v>
+        <v>440752</v>
       </c>
       <c r="R188" t="n">
-        <v>6762603</v>
+        <v>6762337</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -20161,7 +20161,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21188,45 +21188,50 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127283143</v>
+        <v>127274677</v>
       </c>
       <c r="B199" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>440337</v>
+        <v>440689</v>
       </c>
       <c r="R199" t="n">
-        <v>6762397</v>
+        <v>6762214</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21256,9 +21261,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21273,19 +21288,19 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127272174</v>
+        <v>127283143</v>
       </c>
       <c r="B200" t="n">
         <v>8447</v>
@@ -21316,14 +21331,14 @@
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>440657</v>
+        <v>440337</v>
       </c>
       <c r="R200" t="n">
-        <v>6762157</v>
+        <v>6762397</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21353,19 +21368,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21380,62 +21385,57 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127274677</v>
+        <v>127272174</v>
       </c>
       <c r="B201" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>440689</v>
+        <v>440657</v>
       </c>
       <c r="R201" t="n">
-        <v>6762214</v>
+        <v>6762157</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21504,7 +21504,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127272958</v>
+        <v>127275348</v>
       </c>
       <c r="B202" t="n">
         <v>79014</v>
@@ -21535,17 +21535,17 @@
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>440619</v>
+        <v>440677</v>
       </c>
       <c r="R202" t="n">
-        <v>6762170</v>
+        <v>6762469</v>
       </c>
       <c r="S202" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -21584,7 +21584,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21599,22 +21599,22 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127271427</v>
+        <v>127282910</v>
       </c>
       <c r="B203" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21622,37 +21622,37 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>440457</v>
+        <v>440807</v>
       </c>
       <c r="R203" t="n">
-        <v>6762399</v>
+        <v>6762574</v>
       </c>
       <c r="S203" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -21679,19 +21679,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21706,19 +21696,19 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127275348</v>
+        <v>127271972</v>
       </c>
       <c r="B204" t="n">
         <v>79014</v>
@@ -21749,17 +21739,17 @@
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>440677</v>
+        <v>440460</v>
       </c>
       <c r="R204" t="n">
-        <v>6762469</v>
+        <v>6762457</v>
       </c>
       <c r="S204" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -21788,7 +21778,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -21798,7 +21788,12 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>På Gran</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21813,19 +21808,19 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>127282910</v>
+        <v>127272958</v>
       </c>
       <c r="B205" t="n">
         <v>79014</v>
@@ -21856,17 +21851,17 @@
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>440807</v>
+        <v>440619</v>
       </c>
       <c r="R205" t="n">
-        <v>6762574</v>
+        <v>6762170</v>
       </c>
       <c r="S205" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -21893,9 +21888,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -21910,19 +21915,19 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127271972</v>
+        <v>127283114</v>
       </c>
       <c r="B206" t="n">
         <v>79014</v>
@@ -21953,17 +21958,17 @@
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>440460</v>
+        <v>440806</v>
       </c>
       <c r="R206" t="n">
-        <v>6762457</v>
+        <v>6762533</v>
       </c>
       <c r="S206" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -21990,24 +21995,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>På Gran</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22022,19 +22012,19 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127283114</v>
+        <v>127282897</v>
       </c>
       <c r="B207" t="n">
         <v>79014</v>
@@ -22065,14 +22055,14 @@
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>440806</v>
+        <v>440613</v>
       </c>
       <c r="R207" t="n">
-        <v>6762533</v>
+        <v>6762197</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22119,19 +22109,19 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127282897</v>
+        <v>127282920</v>
       </c>
       <c r="B208" t="n">
         <v>79014</v>
@@ -22166,10 +22156,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>440613</v>
+        <v>440696</v>
       </c>
       <c r="R208" t="n">
-        <v>6762197</v>
+        <v>6762239</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22228,10 +22218,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127282920</v>
+        <v>127271427</v>
       </c>
       <c r="B209" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -22239,37 +22229,37 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>440696</v>
+        <v>440457</v>
       </c>
       <c r="R209" t="n">
-        <v>6762239</v>
+        <v>6762399</v>
       </c>
       <c r="S209" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -22296,9 +22286,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -22313,22 +22313,22 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127283102</v>
+        <v>127274242</v>
       </c>
       <c r="B210" t="n">
-        <v>79632</v>
+        <v>57654</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -22336,34 +22336,39 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>440726</v>
+        <v>440697</v>
       </c>
       <c r="R210" t="n">
-        <v>6762638</v>
+        <v>6762119</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22393,9 +22398,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -22410,22 +22425,22 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127283104</v>
+        <v>127282901</v>
       </c>
       <c r="B211" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -22433,34 +22448,34 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>440766</v>
+        <v>440751</v>
       </c>
       <c r="R211" t="n">
-        <v>6762565</v>
+        <v>6762564</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22507,22 +22522,22 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127274242</v>
+        <v>127283112</v>
       </c>
       <c r="B212" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -22530,39 +22545,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>440697</v>
+        <v>440663</v>
       </c>
       <c r="R212" t="n">
-        <v>6762119</v>
+        <v>6762599</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22592,19 +22602,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z212" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -22619,19 +22619,19 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127282901</v>
+        <v>127272352</v>
       </c>
       <c r="B213" t="n">
         <v>79014</v>
@@ -22662,14 +22662,14 @@
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>440751</v>
+        <v>440685</v>
       </c>
       <c r="R213" t="n">
-        <v>6762564</v>
+        <v>6762109</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22699,9 +22699,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA213" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -22716,19 +22726,19 @@
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127283112</v>
+        <v>127273790</v>
       </c>
       <c r="B214" t="n">
         <v>79014</v>
@@ -22759,17 +22769,17 @@
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>440663</v>
+        <v>440854</v>
       </c>
       <c r="R214" t="n">
-        <v>6762599</v>
+        <v>6762427</v>
       </c>
       <c r="S214" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -22796,9 +22806,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA214" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -22813,19 +22833,19 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127272352</v>
+        <v>127273057</v>
       </c>
       <c r="B215" t="n">
         <v>79014</v>
@@ -22856,17 +22876,17 @@
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>440685</v>
+        <v>440681</v>
       </c>
       <c r="R215" t="n">
-        <v>6762109</v>
+        <v>6762195</v>
       </c>
       <c r="S215" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -22895,7 +22915,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -22905,7 +22925,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -22920,22 +22940,22 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127273790</v>
+        <v>127283104</v>
       </c>
       <c r="B216" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22943,37 +22963,37 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>440854</v>
+        <v>440766</v>
       </c>
       <c r="R216" t="n">
-        <v>6762427</v>
+        <v>6762565</v>
       </c>
       <c r="S216" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -23000,19 +23020,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z216" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB216" t="inlineStr">
-        <is>
-          <t>13:15</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23027,22 +23037,22 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127273057</v>
+        <v>127283102</v>
       </c>
       <c r="B217" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23050,37 +23060,37 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>440681</v>
+        <v>440726</v>
       </c>
       <c r="R217" t="n">
-        <v>6762195</v>
+        <v>6762638</v>
       </c>
       <c r="S217" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -23107,19 +23117,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z217" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
       <c r="AA217" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB217" t="inlineStr">
-        <is>
-          <t>12:39</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -23134,44 +23134,44 @@
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127283106</v>
+        <v>127283107</v>
       </c>
       <c r="B218" t="n">
-        <v>78773</v>
+        <v>8447</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -23181,10 +23181,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>440504</v>
+        <v>440636</v>
       </c>
       <c r="R218" t="n">
-        <v>6762388</v>
+        <v>6762585</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23243,10 +23243,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127283141</v>
+        <v>127283106</v>
       </c>
       <c r="B219" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23254,21 +23254,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -23278,10 +23278,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>440651</v>
+        <v>440504</v>
       </c>
       <c r="R219" t="n">
-        <v>6762611</v>
+        <v>6762388</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23340,10 +23340,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127283100</v>
+        <v>127282898</v>
       </c>
       <c r="B220" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -23351,34 +23351,34 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>440686</v>
+        <v>440741</v>
       </c>
       <c r="R220" t="n">
-        <v>6762630</v>
+        <v>6762609</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23425,19 +23425,19 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127282898</v>
+        <v>127283122</v>
       </c>
       <c r="B221" t="n">
         <v>79014</v>
@@ -23468,14 +23468,14 @@
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>440741</v>
+        <v>440912</v>
       </c>
       <c r="R221" t="n">
-        <v>6762609</v>
+        <v>6762579</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23522,19 +23522,19 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127283122</v>
+        <v>127282915</v>
       </c>
       <c r="B222" t="n">
         <v>79014</v>
@@ -23565,14 +23565,14 @@
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>440912</v>
+        <v>440946</v>
       </c>
       <c r="R222" t="n">
-        <v>6762579</v>
+        <v>6762514</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23619,19 +23619,19 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127282915</v>
+        <v>127275040</v>
       </c>
       <c r="B223" t="n">
         <v>79014</v>
@@ -23662,14 +23662,14 @@
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>440946</v>
+        <v>440745</v>
       </c>
       <c r="R223" t="n">
-        <v>6762514</v>
+        <v>6762369</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23699,9 +23699,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA223" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -23716,19 +23731,19 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127275040</v>
+        <v>127282899</v>
       </c>
       <c r="B224" t="n">
         <v>79014</v>
@@ -23759,14 +23774,14 @@
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>440745</v>
+        <v>440763</v>
       </c>
       <c r="R224" t="n">
-        <v>6762369</v>
+        <v>6762529</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23796,24 +23811,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB224" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -23828,22 +23828,22 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127282899</v>
+        <v>127283100</v>
       </c>
       <c r="B225" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23851,34 +23851,34 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>440763</v>
+        <v>440686</v>
       </c>
       <c r="R225" t="n">
-        <v>6762529</v>
+        <v>6762630</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23925,44 +23925,44 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127283107</v>
+        <v>127283141</v>
       </c>
       <c r="B226" t="n">
-        <v>8447</v>
+        <v>78681</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23972,10 +23972,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>440636</v>
+        <v>440651</v>
       </c>
       <c r="R226" t="n">
-        <v>6762585</v>
+        <v>6762611</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24034,48 +24034,48 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127275544</v>
+        <v>127273585</v>
       </c>
       <c r="B227" t="n">
-        <v>8447</v>
+        <v>91684</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>106545</v>
+        <v>2062</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>440811</v>
+        <v>440742</v>
       </c>
       <c r="R227" t="n">
-        <v>6762474</v>
+        <v>6762004</v>
       </c>
       <c r="S227" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24129,57 +24129,57 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127273585</v>
+        <v>127283126</v>
       </c>
       <c r="B228" t="n">
-        <v>91684</v>
+        <v>79014</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>440742</v>
+        <v>440923</v>
       </c>
       <c r="R228" t="n">
-        <v>6762004</v>
+        <v>6762482</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24209,19 +24209,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z228" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA228" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB228" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -24236,19 +24226,19 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127283126</v>
+        <v>127282918</v>
       </c>
       <c r="B229" t="n">
         <v>79014</v>
@@ -24279,14 +24269,14 @@
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>440923</v>
+        <v>440832</v>
       </c>
       <c r="R229" t="n">
-        <v>6762482</v>
+        <v>6762387</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24333,19 +24323,19 @@
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127282918</v>
+        <v>127282917</v>
       </c>
       <c r="B230" t="n">
         <v>79014</v>
@@ -24380,10 +24370,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>440832</v>
+        <v>440919</v>
       </c>
       <c r="R230" t="n">
-        <v>6762387</v>
+        <v>6762497</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24442,7 +24432,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127282917</v>
+        <v>127283125</v>
       </c>
       <c r="B231" t="n">
         <v>79014</v>
@@ -24473,14 +24463,14 @@
       <c r="I231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>440919</v>
+        <v>440989</v>
       </c>
       <c r="R231" t="n">
-        <v>6762497</v>
+        <v>6762519</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24527,19 +24517,19 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127283125</v>
+        <v>127273660</v>
       </c>
       <c r="B232" t="n">
         <v>79014</v>
@@ -24570,14 +24560,14 @@
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>440989</v>
+        <v>440742</v>
       </c>
       <c r="R232" t="n">
-        <v>6762519</v>
+        <v>6762004</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24607,9 +24597,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24624,19 +24624,19 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127273660</v>
+        <v>127275120</v>
       </c>
       <c r="B233" t="n">
         <v>79014</v>
@@ -24667,17 +24667,17 @@
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>440742</v>
+        <v>440897</v>
       </c>
       <c r="R233" t="n">
-        <v>6762004</v>
+        <v>6762548</v>
       </c>
       <c r="S233" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -24706,7 +24706,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -24716,7 +24716,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -24731,44 +24731,44 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>127275120</v>
+        <v>127275544</v>
       </c>
       <c r="B234" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -24778,10 +24778,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>440897</v>
+        <v>440811</v>
       </c>
       <c r="R234" t="n">
-        <v>6762548</v>
+        <v>6762474</v>
       </c>
       <c r="S234" t="n">
         <v>9</v>
@@ -24813,7 +24813,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -24823,7 +24823,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -25345,7 +25345,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127282911</v>
+        <v>127273778</v>
       </c>
       <c r="B240" t="n">
         <v>79014</v>
@@ -25376,14 +25376,14 @@
       <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>440874</v>
+        <v>440734</v>
       </c>
       <c r="R240" t="n">
-        <v>6762606</v>
+        <v>6762076</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25413,9 +25413,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA240" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB240" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -25430,19 +25440,19 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>127271764</v>
+        <v>127282911</v>
       </c>
       <c r="B241" t="n">
         <v>79014</v>
@@ -25473,17 +25483,17 @@
       <c r="I241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>440418</v>
+        <v>440874</v>
       </c>
       <c r="R241" t="n">
-        <v>6762449</v>
+        <v>6762606</v>
       </c>
       <c r="S241" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -25510,19 +25520,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z241" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB241" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -25537,62 +25537,57 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>127275970</v>
+        <v>127271764</v>
       </c>
       <c r="B242" t="n">
-        <v>5196</v>
+        <v>79014</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P242" t="inlineStr">
         <is>
           <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>440685</v>
+        <v>440418</v>
       </c>
       <c r="R242" t="n">
-        <v>6762673</v>
+        <v>6762449</v>
       </c>
       <c r="S242" t="n">
         <v>9</v>
@@ -25624,7 +25619,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -25634,7 +25629,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -25661,10 +25656,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127273778</v>
+        <v>127275615</v>
       </c>
       <c r="B243" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25672,37 +25667,42 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>440734</v>
+        <v>440778</v>
       </c>
       <c r="R243" t="n">
-        <v>6762076</v>
+        <v>6762552</v>
       </c>
       <c r="S243" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -25741,7 +25741,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -25756,39 +25756,39 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>127275615</v>
+        <v>127275970</v>
       </c>
       <c r="B244" t="n">
-        <v>57654</v>
+        <v>5196</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -25799,7 +25799,7 @@
       <c r="I244" t="inlineStr"/>
       <c r="M244" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
@@ -25808,10 +25808,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>440778</v>
+        <v>440685</v>
       </c>
       <c r="R244" t="n">
-        <v>6762552</v>
+        <v>6762673</v>
       </c>
       <c r="S244" t="n">
         <v>9</v>
@@ -25843,7 +25843,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -25853,7 +25853,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -25977,10 +25977,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127282891</v>
+        <v>127274466</v>
       </c>
       <c r="B246" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25988,37 +25988,37 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>440416</v>
+        <v>440914</v>
       </c>
       <c r="R246" t="n">
-        <v>6762406</v>
+        <v>6762585</v>
       </c>
       <c r="S246" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -26045,9 +26045,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA246" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -26062,19 +26072,19 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>127270746</v>
+        <v>127272935</v>
       </c>
       <c r="B247" t="n">
         <v>79014</v>
@@ -26109,10 +26119,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>440308</v>
+        <v>440613</v>
       </c>
       <c r="R247" t="n">
-        <v>6762456</v>
+        <v>6762174</v>
       </c>
       <c r="S247" t="n">
         <v>9</v>
@@ -26144,7 +26154,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -26154,7 +26164,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -26181,7 +26191,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>127271817</v>
+        <v>127272422</v>
       </c>
       <c r="B248" t="n">
         <v>79014</v>
@@ -26216,10 +26226,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>440623</v>
+        <v>440682</v>
       </c>
       <c r="R248" t="n">
-        <v>6762126</v>
+        <v>6762093</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -26262,6 +26272,11 @@
       <c r="AB248" t="inlineStr">
         <is>
           <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>Garnlav på äldre tall, sannoligt äldre än 200 år</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26288,10 +26303,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>127273433</v>
+        <v>127270746</v>
       </c>
       <c r="B249" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26299,42 +26314,37 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>440726</v>
+        <v>440308</v>
       </c>
       <c r="R249" t="n">
-        <v>6761979</v>
+        <v>6762456</v>
       </c>
       <c r="S249" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -26374,11 +26384,6 @@
       <c r="AB249" t="inlineStr">
         <is>
           <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>Hackhål/bohål</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -26393,19 +26398,19 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>127274466</v>
+        <v>127271817</v>
       </c>
       <c r="B250" t="n">
         <v>79014</v>
@@ -26436,17 +26441,17 @@
       <c r="I250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>440914</v>
+        <v>440623</v>
       </c>
       <c r="R250" t="n">
-        <v>6762585</v>
+        <v>6762126</v>
       </c>
       <c r="S250" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -26475,7 +26480,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -26485,7 +26490,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -26500,22 +26505,22 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>127272935</v>
+        <v>127282891</v>
       </c>
       <c r="B251" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26523,37 +26528,37 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>440613</v>
+        <v>440416</v>
       </c>
       <c r="R251" t="n">
-        <v>6762174</v>
+        <v>6762406</v>
       </c>
       <c r="S251" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -26580,19 +26585,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z251" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB251" t="inlineStr">
-        <is>
-          <t>12:31</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -26607,22 +26602,22 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>127272422</v>
+        <v>127272190</v>
       </c>
       <c r="B252" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -26630,34 +26625,39 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P252" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>440682</v>
+        <v>440657</v>
       </c>
       <c r="R252" t="n">
-        <v>6762093</v>
+        <v>6762157</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26700,11 +26700,6 @@
       <c r="AB252" t="inlineStr">
         <is>
           <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC252" t="inlineStr">
-        <is>
-          <t>Garnlav på äldre tall, sannoligt äldre än 200 år</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -26843,7 +26838,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>127272190</v>
+        <v>127273433</v>
       </c>
       <c r="B254" t="n">
         <v>57654</v>
@@ -26874,7 +26869,7 @@
       <c r="I254" t="inlineStr"/>
       <c r="M254" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P254" t="inlineStr">
@@ -26883,10 +26878,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>440657</v>
+        <v>440726</v>
       </c>
       <c r="R254" t="n">
-        <v>6762157</v>
+        <v>6761979</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26929,6 +26924,11 @@
       <c r="AB254" t="inlineStr">
         <is>
           <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>Hackhål/bohål</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -27654,45 +27654,45 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>127274680</v>
+        <v>127282905</v>
       </c>
       <c r="B262" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>440689</v>
+        <v>440780</v>
       </c>
       <c r="R262" t="n">
-        <v>6762214</v>
+        <v>6762578</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27722,19 +27722,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z262" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA262" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB262" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -27749,60 +27739,60 @@
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>127272941</v>
+        <v>127282934</v>
       </c>
       <c r="B263" t="n">
-        <v>79038</v>
+        <v>79014</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>440613</v>
+        <v>440387</v>
       </c>
       <c r="R263" t="n">
-        <v>6762174</v>
+        <v>6762369</v>
       </c>
       <c r="S263" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -27829,19 +27819,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z263" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AA263" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB263" t="inlineStr">
-        <is>
-          <t>12:31</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -27856,22 +27836,22 @@
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>127276264</v>
+        <v>127275330</v>
       </c>
       <c r="B264" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -27879,42 +27859,37 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
-      <c r="M264" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>440642</v>
+        <v>440868</v>
       </c>
       <c r="R264" t="n">
-        <v>6762606</v>
+        <v>6762512</v>
       </c>
       <c r="S264" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -27943,7 +27918,7 @@
       </c>
       <c r="Z264" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
@@ -27953,7 +27928,7 @@
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -27968,19 +27943,19 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>127282905</v>
+        <v>127282923</v>
       </c>
       <c r="B265" t="n">
         <v>79014</v>
@@ -28015,10 +27990,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>440780</v>
+        <v>440658</v>
       </c>
       <c r="R265" t="n">
-        <v>6762578</v>
+        <v>6762202</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -28077,7 +28052,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>127282934</v>
+        <v>127275346</v>
       </c>
       <c r="B266" t="n">
         <v>79014</v>
@@ -28108,17 +28083,17 @@
       <c r="I266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>440387</v>
+        <v>440853</v>
       </c>
       <c r="R266" t="n">
-        <v>6762369</v>
+        <v>6762514</v>
       </c>
       <c r="S266" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -28145,9 +28120,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA266" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB266" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -28162,19 +28147,19 @@
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>127275330</v>
+        <v>127282921</v>
       </c>
       <c r="B267" t="n">
         <v>79014</v>
@@ -28205,17 +28190,17 @@
       <c r="I267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>440868</v>
+        <v>440680</v>
       </c>
       <c r="R267" t="n">
-        <v>6762512</v>
+        <v>6762218</v>
       </c>
       <c r="S267" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -28242,19 +28227,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z267" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA267" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB267" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -28269,60 +28244,60 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>127282923</v>
+        <v>127272941</v>
       </c>
       <c r="B268" t="n">
-        <v>79014</v>
+        <v>79038</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>440658</v>
+        <v>440613</v>
       </c>
       <c r="R268" t="n">
-        <v>6762202</v>
+        <v>6762174</v>
       </c>
       <c r="S268" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -28349,9 +28324,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AA268" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -28366,22 +28351,22 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>127275346</v>
+        <v>127276264</v>
       </c>
       <c r="B269" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -28389,37 +28374,42 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>440853</v>
+        <v>440642</v>
       </c>
       <c r="R269" t="n">
-        <v>6762514</v>
+        <v>6762606</v>
       </c>
       <c r="S269" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -28448,7 +28438,7 @@
       </c>
       <c r="Z269" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
@@ -28458,7 +28448,7 @@
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -28473,57 +28463,57 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>127282921</v>
+        <v>127274680</v>
       </c>
       <c r="B270" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>440680</v>
+        <v>440689</v>
       </c>
       <c r="R270" t="n">
-        <v>6762218</v>
+        <v>6762214</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28553,9 +28543,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA270" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -28570,12 +28570,12 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>

--- a/artfynd/A 29945-2025 artfynd.xlsx
+++ b/artfynd/A 29945-2025 artfynd.xlsx
@@ -16553,10 +16553,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127272237</v>
+        <v>127282904</v>
       </c>
       <c r="B154" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16564,39 +16564,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>440675</v>
+        <v>440776</v>
       </c>
       <c r="R154" t="n">
-        <v>6762165</v>
+        <v>6762632</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16626,19 +16621,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16653,19 +16638,19 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127282904</v>
+        <v>127282914</v>
       </c>
       <c r="B155" t="n">
         <v>79014</v>
@@ -16700,10 +16685,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>440776</v>
+        <v>440924</v>
       </c>
       <c r="R155" t="n">
-        <v>6762632</v>
+        <v>6762509</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16762,7 +16747,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127282914</v>
+        <v>127274354</v>
       </c>
       <c r="B156" t="n">
         <v>79014</v>
@@ -16793,14 +16778,14 @@
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>440924</v>
+        <v>440686</v>
       </c>
       <c r="R156" t="n">
-        <v>6762509</v>
+        <v>6762176</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16830,9 +16815,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16847,19 +16842,19 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127274354</v>
+        <v>127272746</v>
       </c>
       <c r="B157" t="n">
         <v>79014</v>
@@ -16890,17 +16885,17 @@
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>440686</v>
+        <v>440503</v>
       </c>
       <c r="R157" t="n">
-        <v>6762176</v>
+        <v>6762308</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16929,7 +16924,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16939,7 +16934,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16954,22 +16949,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127272746</v>
+        <v>127272237</v>
       </c>
       <c r="B158" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16977,37 +16972,42 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>440503</v>
+        <v>440675</v>
       </c>
       <c r="R158" t="n">
-        <v>6762308</v>
+        <v>6762165</v>
       </c>
       <c r="S158" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17046,7 +17046,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17061,12 +17061,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -17889,10 +17889,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127275098</v>
+        <v>127274348</v>
       </c>
       <c r="B167" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17900,16 +17900,16 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -17929,10 +17929,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>440679</v>
+        <v>440686</v>
       </c>
       <c r="R167" t="n">
-        <v>6762388</v>
+        <v>6762176</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18001,10 +18001,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127274348</v>
+        <v>127275098</v>
       </c>
       <c r="B168" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18012,16 +18012,16 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -18041,10 +18041,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>440686</v>
+        <v>440679</v>
       </c>
       <c r="R168" t="n">
-        <v>6762176</v>
+        <v>6762388</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19969,45 +19969,45 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127276155</v>
+        <v>127282924</v>
       </c>
       <c r="B187" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>440657</v>
+        <v>440623</v>
       </c>
       <c r="R187" t="n">
-        <v>6762603</v>
+        <v>6762194</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20037,19 +20037,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20064,22 +20054,22 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127274877</v>
+        <v>127283136</v>
       </c>
       <c r="B188" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20087,42 +20077,37 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>440752</v>
+        <v>440394</v>
       </c>
       <c r="R188" t="n">
-        <v>6762337</v>
+        <v>6762413</v>
       </c>
       <c r="S188" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -20149,19 +20134,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z188" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20176,19 +20151,19 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127282924</v>
+        <v>127283138</v>
       </c>
       <c r="B189" t="n">
         <v>79014</v>
@@ -20219,14 +20194,14 @@
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>440623</v>
+        <v>440335</v>
       </c>
       <c r="R189" t="n">
-        <v>6762194</v>
+        <v>6762400</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20273,19 +20248,19 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127283136</v>
+        <v>127282907</v>
       </c>
       <c r="B190" t="n">
         <v>79014</v>
@@ -20316,14 +20291,14 @@
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>440394</v>
+        <v>440793</v>
       </c>
       <c r="R190" t="n">
-        <v>6762413</v>
+        <v>6762525</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20370,19 +20345,19 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127283138</v>
+        <v>127283118</v>
       </c>
       <c r="B191" t="n">
         <v>79014</v>
@@ -20417,10 +20392,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>440335</v>
+        <v>440868</v>
       </c>
       <c r="R191" t="n">
-        <v>6762400</v>
+        <v>6762583</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20479,7 +20454,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127282907</v>
+        <v>127283113</v>
       </c>
       <c r="B192" t="n">
         <v>79014</v>
@@ -20510,14 +20485,14 @@
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>440793</v>
+        <v>440768</v>
       </c>
       <c r="R192" t="n">
-        <v>6762525</v>
+        <v>6762554</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20564,22 +20539,22 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127283118</v>
+        <v>127274877</v>
       </c>
       <c r="B193" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20587,37 +20562,42 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>440868</v>
+        <v>440752</v>
       </c>
       <c r="R193" t="n">
-        <v>6762583</v>
+        <v>6762337</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -20644,9 +20624,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20661,57 +20651,57 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127283113</v>
+        <v>127276155</v>
       </c>
       <c r="B194" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>440768</v>
+        <v>440657</v>
       </c>
       <c r="R194" t="n">
-        <v>6762554</v>
+        <v>6762603</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20741,9 +20731,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20758,12 +20758,12 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
@@ -22325,10 +22325,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127274242</v>
+        <v>127282901</v>
       </c>
       <c r="B210" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -22336,39 +22336,34 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>440697</v>
+        <v>440751</v>
       </c>
       <c r="R210" t="n">
-        <v>6762119</v>
+        <v>6762564</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22398,19 +22393,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -22425,19 +22410,19 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127282901</v>
+        <v>127283112</v>
       </c>
       <c r="B211" t="n">
         <v>79014</v>
@@ -22468,14 +22453,14 @@
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>440751</v>
+        <v>440663</v>
       </c>
       <c r="R211" t="n">
-        <v>6762564</v>
+        <v>6762599</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22522,19 +22507,19 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127283112</v>
+        <v>127272352</v>
       </c>
       <c r="B212" t="n">
         <v>79014</v>
@@ -22565,14 +22550,14 @@
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>440663</v>
+        <v>440685</v>
       </c>
       <c r="R212" t="n">
-        <v>6762599</v>
+        <v>6762109</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22602,9 +22587,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -22619,19 +22614,19 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127272352</v>
+        <v>127273790</v>
       </c>
       <c r="B213" t="n">
         <v>79014</v>
@@ -22662,17 +22657,17 @@
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>440685</v>
+        <v>440854</v>
       </c>
       <c r="R213" t="n">
-        <v>6762109</v>
+        <v>6762427</v>
       </c>
       <c r="S213" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -22701,7 +22696,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -22711,7 +22706,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -22726,19 +22721,19 @@
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127273790</v>
+        <v>127273057</v>
       </c>
       <c r="B214" t="n">
         <v>79014</v>
@@ -22773,10 +22768,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>440854</v>
+        <v>440681</v>
       </c>
       <c r="R214" t="n">
-        <v>6762427</v>
+        <v>6762195</v>
       </c>
       <c r="S214" t="n">
         <v>9</v>
@@ -22808,7 +22803,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -22818,7 +22813,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -22845,10 +22840,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127273057</v>
+        <v>127274242</v>
       </c>
       <c r="B215" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -22856,37 +22851,42 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>440681</v>
+        <v>440697</v>
       </c>
       <c r="R215" t="n">
-        <v>6762195</v>
+        <v>6762119</v>
       </c>
       <c r="S215" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -22925,7 +22925,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -22940,12 +22940,12 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
@@ -24034,45 +24034,45 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127273585</v>
+        <v>127283126</v>
       </c>
       <c r="B227" t="n">
-        <v>91684</v>
+        <v>79014</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>440742</v>
+        <v>440923</v>
       </c>
       <c r="R227" t="n">
-        <v>6762004</v>
+        <v>6762482</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24102,19 +24102,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z227" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA227" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB227" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24129,19 +24119,19 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127283126</v>
+        <v>127282918</v>
       </c>
       <c r="B228" t="n">
         <v>79014</v>
@@ -24172,14 +24162,14 @@
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>440923</v>
+        <v>440832</v>
       </c>
       <c r="R228" t="n">
-        <v>6762482</v>
+        <v>6762387</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24226,19 +24216,19 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127282918</v>
+        <v>127282917</v>
       </c>
       <c r="B229" t="n">
         <v>79014</v>
@@ -24273,10 +24263,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>440832</v>
+        <v>440919</v>
       </c>
       <c r="R229" t="n">
-        <v>6762387</v>
+        <v>6762497</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24335,7 +24325,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127282917</v>
+        <v>127283125</v>
       </c>
       <c r="B230" t="n">
         <v>79014</v>
@@ -24366,14 +24356,14 @@
       <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>440919</v>
+        <v>440989</v>
       </c>
       <c r="R230" t="n">
-        <v>6762497</v>
+        <v>6762519</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24420,19 +24410,19 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127283125</v>
+        <v>127273660</v>
       </c>
       <c r="B231" t="n">
         <v>79014</v>
@@ -24463,14 +24453,14 @@
       <c r="I231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>440989</v>
+        <v>440742</v>
       </c>
       <c r="R231" t="n">
-        <v>6762519</v>
+        <v>6762004</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24500,9 +24490,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24517,19 +24517,19 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127273660</v>
+        <v>127275120</v>
       </c>
       <c r="B232" t="n">
         <v>79014</v>
@@ -24560,17 +24560,17 @@
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>440742</v>
+        <v>440897</v>
       </c>
       <c r="R232" t="n">
-        <v>6762004</v>
+        <v>6762548</v>
       </c>
       <c r="S232" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -24609,7 +24609,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24624,60 +24624,60 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127275120</v>
+        <v>127273585</v>
       </c>
       <c r="B233" t="n">
-        <v>79014</v>
+        <v>91684</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>440897</v>
+        <v>440742</v>
       </c>
       <c r="R233" t="n">
-        <v>6762548</v>
+        <v>6762004</v>
       </c>
       <c r="S233" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -24706,7 +24706,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -24716,7 +24716,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -24731,12 +24731,12 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>

--- a/artfynd/A 29945-2025 artfynd.xlsx
+++ b/artfynd/A 29945-2025 artfynd.xlsx
@@ -12689,10 +12689,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127273755</v>
+        <v>127274057</v>
       </c>
       <c r="B117" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12700,34 +12700,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>440744</v>
+        <v>440706</v>
       </c>
       <c r="R117" t="n">
-        <v>6762065</v>
+        <v>6762058</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12796,10 +12801,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127276304</v>
+        <v>127283110</v>
       </c>
       <c r="B118" t="n">
-        <v>79014</v>
+        <v>79015</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12807,16 +12812,16 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -12827,14 +12832,14 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>440642</v>
+        <v>440835</v>
       </c>
       <c r="R118" t="n">
-        <v>6762606</v>
+        <v>6762564</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12864,19 +12869,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12891,44 +12886,44 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127275131</v>
+        <v>127274061</v>
       </c>
       <c r="B119" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12938,10 +12933,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>440709</v>
+        <v>440706</v>
       </c>
       <c r="R119" t="n">
-        <v>6762405</v>
+        <v>6762058</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13010,7 +13005,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127271820</v>
+        <v>127273755</v>
       </c>
       <c r="B120" t="n">
         <v>79014</v>
@@ -13041,17 +13036,17 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>440446</v>
+        <v>440744</v>
       </c>
       <c r="R120" t="n">
-        <v>6762469</v>
+        <v>6762065</v>
       </c>
       <c r="S120" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13080,7 +13075,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13090,7 +13085,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13105,22 +13100,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127274057</v>
+        <v>127276304</v>
       </c>
       <c r="B121" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13128,39 +13123,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>440706</v>
+        <v>440642</v>
       </c>
       <c r="R121" t="n">
-        <v>6762058</v>
+        <v>6762606</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13192,7 +13182,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13202,7 +13192,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13229,32 +13219,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127274061</v>
+        <v>127275131</v>
       </c>
       <c r="B122" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13264,10 +13254,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>440706</v>
+        <v>440709</v>
       </c>
       <c r="R122" t="n">
-        <v>6762058</v>
+        <v>6762405</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13336,10 +13326,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127283110</v>
+        <v>127271820</v>
       </c>
       <c r="B123" t="n">
-        <v>79015</v>
+        <v>79014</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13347,16 +13337,16 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -13367,17 +13357,17 @@
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>440835</v>
+        <v>440446</v>
       </c>
       <c r="R123" t="n">
-        <v>6762564</v>
+        <v>6762469</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13404,9 +13394,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13421,12 +13421,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -14244,10 +14244,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127274657</v>
+        <v>127283109</v>
       </c>
       <c r="B132" t="n">
-        <v>79014</v>
+        <v>79015</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14255,16 +14255,16 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -14275,14 +14275,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>440689</v>
+        <v>440875</v>
       </c>
       <c r="R132" t="n">
-        <v>6762214</v>
+        <v>6762453</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14312,24 +14312,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14344,19 +14329,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127283117</v>
+        <v>127274657</v>
       </c>
       <c r="B133" t="n">
         <v>79014</v>
@@ -14387,14 +14372,14 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>440863</v>
+        <v>440689</v>
       </c>
       <c r="R133" t="n">
-        <v>6762603</v>
+        <v>6762214</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14424,9 +14409,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14441,19 +14441,19 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127273051</v>
+        <v>127283117</v>
       </c>
       <c r="B134" t="n">
         <v>79014</v>
@@ -14484,17 +14484,17 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>440681</v>
+        <v>440863</v>
       </c>
       <c r="R134" t="n">
-        <v>6762197</v>
+        <v>6762603</v>
       </c>
       <c r="S134" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14521,19 +14521,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>12:38</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14548,19 +14538,19 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127282932</v>
+        <v>127273051</v>
       </c>
       <c r="B135" t="n">
         <v>79014</v>
@@ -14591,17 +14581,17 @@
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>440427</v>
+        <v>440681</v>
       </c>
       <c r="R135" t="n">
-        <v>6762470</v>
+        <v>6762197</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14628,9 +14618,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14645,19 +14645,19 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127282912</v>
+        <v>127282932</v>
       </c>
       <c r="B136" t="n">
         <v>79014</v>
@@ -14692,10 +14692,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>440936</v>
+        <v>440427</v>
       </c>
       <c r="R136" t="n">
-        <v>6762564</v>
+        <v>6762470</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14754,7 +14754,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127282926</v>
+        <v>127282912</v>
       </c>
       <c r="B137" t="n">
         <v>79014</v>
@@ -14789,10 +14789,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>440497</v>
+        <v>440936</v>
       </c>
       <c r="R137" t="n">
-        <v>6762331</v>
+        <v>6762564</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14851,7 +14851,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127283130</v>
+        <v>127282926</v>
       </c>
       <c r="B138" t="n">
         <v>79014</v>
@@ -14882,14 +14882,14 @@
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>440697</v>
+        <v>440497</v>
       </c>
       <c r="R138" t="n">
-        <v>6762237</v>
+        <v>6762331</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14936,19 +14936,19 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127276216</v>
+        <v>127283130</v>
       </c>
       <c r="B139" t="n">
         <v>79014</v>
@@ -14979,14 +14979,14 @@
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>440657</v>
+        <v>440697</v>
       </c>
       <c r="R139" t="n">
-        <v>6762603</v>
+        <v>6762237</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15016,19 +15016,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15043,19 +15033,19 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127273488</v>
+        <v>127276216</v>
       </c>
       <c r="B140" t="n">
         <v>79014</v>
@@ -15090,10 +15080,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>440721</v>
+        <v>440657</v>
       </c>
       <c r="R140" t="n">
-        <v>6761996</v>
+        <v>6762603</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15125,7 +15115,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15135,7 +15125,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15162,10 +15152,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127276148</v>
+        <v>127273488</v>
       </c>
       <c r="B141" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15173,39 +15163,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>440657</v>
+        <v>440721</v>
       </c>
       <c r="R141" t="n">
-        <v>6762603</v>
+        <v>6761996</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15237,7 +15222,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15247,7 +15232,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15274,7 +15259,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127272305</v>
+        <v>127276148</v>
       </c>
       <c r="B142" t="n">
         <v>57654</v>
@@ -15305,7 +15290,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -15314,10 +15299,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>440675</v>
+        <v>440657</v>
       </c>
       <c r="R142" t="n">
-        <v>6762165</v>
+        <v>6762603</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15349,7 +15334,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15359,12 +15344,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Diameter ca 4 till 5 cm</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15391,7 +15371,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127271765</v>
+        <v>127272305</v>
       </c>
       <c r="B143" t="n">
         <v>57654</v>
@@ -15422,7 +15402,7 @@
       <c r="I143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -15431,10 +15411,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>440627</v>
+        <v>440675</v>
       </c>
       <c r="R143" t="n">
-        <v>6762119</v>
+        <v>6762165</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15481,7 +15461,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Miljöbild för området</t>
+          <t>Diameter ca 4 till 5 cm</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15508,7 +15488,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127276450</v>
+        <v>127271765</v>
       </c>
       <c r="B144" t="n">
         <v>57654</v>
@@ -15539,7 +15519,7 @@
       <c r="I144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -15548,10 +15528,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>440582</v>
+        <v>440627</v>
       </c>
       <c r="R144" t="n">
-        <v>6762684</v>
+        <v>6762119</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15583,7 +15563,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15593,7 +15573,12 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Miljöbild för området</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15620,10 +15605,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127283109</v>
+        <v>127276450</v>
       </c>
       <c r="B145" t="n">
-        <v>79015</v>
+        <v>57654</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15631,34 +15616,39 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>230405</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>440875</v>
+        <v>440582</v>
       </c>
       <c r="R145" t="n">
-        <v>6762453</v>
+        <v>6762684</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15688,9 +15678,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15705,12 +15705,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
@@ -17170,10 +17170,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127282900</v>
+        <v>127274348</v>
       </c>
       <c r="B160" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17181,34 +17181,39 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>440757</v>
+        <v>440686</v>
       </c>
       <c r="R160" t="n">
-        <v>6762544</v>
+        <v>6762176</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17238,9 +17243,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17255,22 +17270,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127276426</v>
+        <v>127275098</v>
       </c>
       <c r="B161" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17278,34 +17293,39 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>440582</v>
+        <v>440679</v>
       </c>
       <c r="R161" t="n">
-        <v>6762684</v>
+        <v>6762388</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17337,7 +17357,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17347,7 +17367,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17374,7 +17394,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127275877</v>
+        <v>127282900</v>
       </c>
       <c r="B162" t="n">
         <v>79014</v>
@@ -17405,14 +17425,14 @@
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>440732</v>
+        <v>440757</v>
       </c>
       <c r="R162" t="n">
-        <v>6762635</v>
+        <v>6762544</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17442,19 +17462,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17469,19 +17479,19 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127273900</v>
+        <v>127276426</v>
       </c>
       <c r="B163" t="n">
         <v>79014</v>
@@ -17512,17 +17522,17 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>440903</v>
+        <v>440582</v>
       </c>
       <c r="R163" t="n">
-        <v>6762450</v>
+        <v>6762684</v>
       </c>
       <c r="S163" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -17551,7 +17561,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17561,7 +17571,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17576,19 +17586,19 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127282902</v>
+        <v>127275877</v>
       </c>
       <c r="B164" t="n">
         <v>79014</v>
@@ -17619,14 +17629,14 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>440760</v>
+        <v>440732</v>
       </c>
       <c r="R164" t="n">
-        <v>6762569</v>
+        <v>6762635</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17656,9 +17666,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17673,19 +17693,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127273086</v>
+        <v>127273900</v>
       </c>
       <c r="B165" t="n">
         <v>79014</v>
@@ -17720,10 +17740,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>440694</v>
+        <v>440903</v>
       </c>
       <c r="R165" t="n">
-        <v>6762204</v>
+        <v>6762450</v>
       </c>
       <c r="S165" t="n">
         <v>9</v>
@@ -17755,7 +17775,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17765,7 +17785,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17792,7 +17812,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127283137</v>
+        <v>127282902</v>
       </c>
       <c r="B166" t="n">
         <v>79014</v>
@@ -17823,14 +17843,14 @@
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>440354</v>
+        <v>440760</v>
       </c>
       <c r="R166" t="n">
-        <v>6762415</v>
+        <v>6762569</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17877,22 +17897,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127274348</v>
+        <v>127273086</v>
       </c>
       <c r="B167" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17900,42 +17920,37 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>440686</v>
+        <v>440694</v>
       </c>
       <c r="R167" t="n">
-        <v>6762176</v>
+        <v>6762204</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -17964,7 +17979,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -17974,7 +17989,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17989,22 +18004,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127275098</v>
+        <v>127283137</v>
       </c>
       <c r="B168" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18012,39 +18027,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>440679</v>
+        <v>440354</v>
       </c>
       <c r="R168" t="n">
-        <v>6762388</v>
+        <v>6762415</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18074,19 +18084,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18101,12 +18101,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
@@ -19357,10 +19357,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127282906</v>
+        <v>127274154</v>
       </c>
       <c r="B181" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19368,37 +19368,42 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>440782</v>
+        <v>440946</v>
       </c>
       <c r="R181" t="n">
-        <v>6762562</v>
+        <v>6762537</v>
       </c>
       <c r="S181" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -19425,9 +19430,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19442,22 +19462,22 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127274154</v>
+        <v>127283116</v>
       </c>
       <c r="B182" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19465,42 +19485,37 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>440946</v>
+        <v>440823</v>
       </c>
       <c r="R182" t="n">
-        <v>6762537</v>
+        <v>6762604</v>
       </c>
       <c r="S182" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -19527,24 +19542,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z182" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB182" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19559,19 +19559,19 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127283127</v>
+        <v>127282906</v>
       </c>
       <c r="B183" t="n">
         <v>79014</v>
@@ -19602,14 +19602,14 @@
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>440843</v>
+        <v>440782</v>
       </c>
       <c r="R183" t="n">
-        <v>6762431</v>
+        <v>6762562</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19656,19 +19656,19 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127283116</v>
+        <v>127275778</v>
       </c>
       <c r="B184" t="n">
         <v>79014</v>
@@ -19699,17 +19699,17 @@
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>440823</v>
+        <v>440761</v>
       </c>
       <c r="R184" t="n">
-        <v>6762604</v>
+        <v>6762597</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19736,9 +19736,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19753,19 +19763,19 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127275778</v>
+        <v>127282925</v>
       </c>
       <c r="B185" t="n">
         <v>79014</v>
@@ -19796,17 +19806,17 @@
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>440761</v>
+        <v>440619</v>
       </c>
       <c r="R185" t="n">
-        <v>6762597</v>
+        <v>6762184</v>
       </c>
       <c r="S185" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -19833,19 +19843,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>15:06</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>15:06</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19860,19 +19860,19 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127282925</v>
+        <v>127283127</v>
       </c>
       <c r="B186" t="n">
         <v>79014</v>
@@ -19903,14 +19903,14 @@
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>440619</v>
+        <v>440843</v>
       </c>
       <c r="R186" t="n">
-        <v>6762184</v>
+        <v>6762431</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19957,57 +19957,57 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127282924</v>
+        <v>127276155</v>
       </c>
       <c r="B187" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>440623</v>
+        <v>440657</v>
       </c>
       <c r="R187" t="n">
-        <v>6762194</v>
+        <v>6762603</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20037,9 +20037,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20054,22 +20064,22 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127283136</v>
+        <v>127274877</v>
       </c>
       <c r="B188" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20077,37 +20087,42 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>440394</v>
+        <v>440752</v>
       </c>
       <c r="R188" t="n">
-        <v>6762413</v>
+        <v>6762337</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -20134,9 +20149,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20151,19 +20176,19 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127283138</v>
+        <v>127282924</v>
       </c>
       <c r="B189" t="n">
         <v>79014</v>
@@ -20194,14 +20219,14 @@
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>440335</v>
+        <v>440623</v>
       </c>
       <c r="R189" t="n">
-        <v>6762400</v>
+        <v>6762194</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20248,19 +20273,19 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127282907</v>
+        <v>127283136</v>
       </c>
       <c r="B190" t="n">
         <v>79014</v>
@@ -20291,14 +20316,14 @@
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>440793</v>
+        <v>440394</v>
       </c>
       <c r="R190" t="n">
-        <v>6762525</v>
+        <v>6762413</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20345,19 +20370,19 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127283118</v>
+        <v>127283138</v>
       </c>
       <c r="B191" t="n">
         <v>79014</v>
@@ -20392,10 +20417,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>440868</v>
+        <v>440335</v>
       </c>
       <c r="R191" t="n">
-        <v>6762583</v>
+        <v>6762400</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20454,7 +20479,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127283113</v>
+        <v>127282907</v>
       </c>
       <c r="B192" t="n">
         <v>79014</v>
@@ -20485,14 +20510,14 @@
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>440768</v>
+        <v>440793</v>
       </c>
       <c r="R192" t="n">
-        <v>6762554</v>
+        <v>6762525</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20539,22 +20564,22 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127274877</v>
+        <v>127283118</v>
       </c>
       <c r="B193" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20562,42 +20587,37 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>440752</v>
+        <v>440868</v>
       </c>
       <c r="R193" t="n">
-        <v>6762337</v>
+        <v>6762583</v>
       </c>
       <c r="S193" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -20624,19 +20644,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20651,57 +20661,57 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127276155</v>
+        <v>127283113</v>
       </c>
       <c r="B194" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>440657</v>
+        <v>440768</v>
       </c>
       <c r="R194" t="n">
-        <v>6762603</v>
+        <v>6762554</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20731,19 +20741,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20758,12 +20758,12 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
@@ -22325,10 +22325,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127282901</v>
+        <v>127274242</v>
       </c>
       <c r="B210" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -22336,34 +22336,39 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>440751</v>
+        <v>440697</v>
       </c>
       <c r="R210" t="n">
-        <v>6762564</v>
+        <v>6762119</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22393,9 +22398,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -22410,19 +22425,19 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127283112</v>
+        <v>127282901</v>
       </c>
       <c r="B211" t="n">
         <v>79014</v>
@@ -22453,14 +22468,14 @@
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>440663</v>
+        <v>440751</v>
       </c>
       <c r="R211" t="n">
-        <v>6762599</v>
+        <v>6762564</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22507,19 +22522,19 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127272352</v>
+        <v>127283112</v>
       </c>
       <c r="B212" t="n">
         <v>79014</v>
@@ -22550,14 +22565,14 @@
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>440685</v>
+        <v>440663</v>
       </c>
       <c r="R212" t="n">
-        <v>6762109</v>
+        <v>6762599</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22587,19 +22602,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z212" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -22614,19 +22619,19 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127273790</v>
+        <v>127272352</v>
       </c>
       <c r="B213" t="n">
         <v>79014</v>
@@ -22657,17 +22662,17 @@
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>440854</v>
+        <v>440685</v>
       </c>
       <c r="R213" t="n">
-        <v>6762427</v>
+        <v>6762109</v>
       </c>
       <c r="S213" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -22696,7 +22701,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -22706,7 +22711,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -22721,19 +22726,19 @@
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127273057</v>
+        <v>127273790</v>
       </c>
       <c r="B214" t="n">
         <v>79014</v>
@@ -22768,10 +22773,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>440681</v>
+        <v>440854</v>
       </c>
       <c r="R214" t="n">
-        <v>6762195</v>
+        <v>6762427</v>
       </c>
       <c r="S214" t="n">
         <v>9</v>
@@ -22803,7 +22808,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -22813,7 +22818,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -22840,10 +22845,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127274242</v>
+        <v>127273057</v>
       </c>
       <c r="B215" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -22851,42 +22856,37 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>440697</v>
+        <v>440681</v>
       </c>
       <c r="R215" t="n">
-        <v>6762119</v>
+        <v>6762195</v>
       </c>
       <c r="S215" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -22925,7 +22925,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -22940,12 +22940,12 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
@@ -23146,45 +23146,45 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127283107</v>
+        <v>127282898</v>
       </c>
       <c r="B218" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>440636</v>
+        <v>440741</v>
       </c>
       <c r="R218" t="n">
-        <v>6762585</v>
+        <v>6762609</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23231,22 +23231,22 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127283106</v>
+        <v>127283122</v>
       </c>
       <c r="B219" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23254,21 +23254,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -23278,10 +23278,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>440504</v>
+        <v>440912</v>
       </c>
       <c r="R219" t="n">
-        <v>6762388</v>
+        <v>6762579</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23340,7 +23340,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127282898</v>
+        <v>127282915</v>
       </c>
       <c r="B220" t="n">
         <v>79014</v>
@@ -23375,10 +23375,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>440741</v>
+        <v>440946</v>
       </c>
       <c r="R220" t="n">
-        <v>6762609</v>
+        <v>6762514</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23437,7 +23437,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127283122</v>
+        <v>127275040</v>
       </c>
       <c r="B221" t="n">
         <v>79014</v>
@@ -23468,14 +23468,14 @@
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>440912</v>
+        <v>440745</v>
       </c>
       <c r="R221" t="n">
-        <v>6762579</v>
+        <v>6762369</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23505,9 +23505,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -23522,19 +23537,19 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127282915</v>
+        <v>127282899</v>
       </c>
       <c r="B222" t="n">
         <v>79014</v>
@@ -23569,10 +23584,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>440946</v>
+        <v>440763</v>
       </c>
       <c r="R222" t="n">
-        <v>6762514</v>
+        <v>6762529</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23631,10 +23646,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127275040</v>
+        <v>127283141</v>
       </c>
       <c r="B223" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23642,34 +23657,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>440745</v>
+        <v>440651</v>
       </c>
       <c r="R223" t="n">
-        <v>6762369</v>
+        <v>6762611</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23699,24 +23714,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z223" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA223" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB223" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -23731,22 +23731,22 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127282899</v>
+        <v>127283100</v>
       </c>
       <c r="B224" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23754,34 +23754,34 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>440763</v>
+        <v>440686</v>
       </c>
       <c r="R224" t="n">
-        <v>6762529</v>
+        <v>6762630</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23828,44 +23828,44 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127283100</v>
+        <v>127283107</v>
       </c>
       <c r="B225" t="n">
-        <v>79632</v>
+        <v>8447</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23875,10 +23875,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>440686</v>
+        <v>440636</v>
       </c>
       <c r="R225" t="n">
-        <v>6762630</v>
+        <v>6762585</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23937,10 +23937,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127283141</v>
+        <v>127283106</v>
       </c>
       <c r="B226" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23948,21 +23948,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23972,10 +23972,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>440651</v>
+        <v>440504</v>
       </c>
       <c r="R226" t="n">
-        <v>6762611</v>
+        <v>6762388</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25656,27 +25656,27 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127275615</v>
+        <v>127275970</v>
       </c>
       <c r="B243" t="n">
-        <v>57654</v>
+        <v>5196</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -25687,7 +25687,7 @@
       <c r="I243" t="inlineStr"/>
       <c r="M243" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
@@ -25696,10 +25696,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>440778</v>
+        <v>440685</v>
       </c>
       <c r="R243" t="n">
-        <v>6762552</v>
+        <v>6762673</v>
       </c>
       <c r="S243" t="n">
         <v>9</v>
@@ -25731,7 +25731,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -25741,7 +25741,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -25768,27 +25768,27 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>127275970</v>
+        <v>127275615</v>
       </c>
       <c r="B244" t="n">
-        <v>5196</v>
+        <v>57654</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -25799,7 +25799,7 @@
       <c r="I244" t="inlineStr"/>
       <c r="M244" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
@@ -25808,10 +25808,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>440685</v>
+        <v>440778</v>
       </c>
       <c r="R244" t="n">
-        <v>6762673</v>
+        <v>6762552</v>
       </c>
       <c r="S244" t="n">
         <v>9</v>
@@ -25843,7 +25843,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -25853,7 +25853,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -25880,45 +25880,50 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127282894</v>
+        <v>127272190</v>
       </c>
       <c r="B245" t="n">
-        <v>79038</v>
+        <v>57654</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>440951</v>
+        <v>440657</v>
       </c>
       <c r="R245" t="n">
-        <v>6762514</v>
+        <v>6762157</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25948,9 +25953,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA245" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -25965,22 +25980,22 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127274466</v>
+        <v>127273155</v>
       </c>
       <c r="B246" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25988,34 +26003,39 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P246" t="inlineStr">
         <is>
           <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>440914</v>
+        <v>440692</v>
       </c>
       <c r="R246" t="n">
-        <v>6762585</v>
+        <v>6762205</v>
       </c>
       <c r="S246" t="n">
         <v>9</v>
@@ -26047,7 +26067,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -26057,7 +26077,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -26084,10 +26104,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>127272935</v>
+        <v>127273433</v>
       </c>
       <c r="B247" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26095,37 +26115,42 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>440613</v>
+        <v>440726</v>
       </c>
       <c r="R247" t="n">
-        <v>6762174</v>
+        <v>6761979</v>
       </c>
       <c r="S247" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -26154,7 +26179,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -26164,7 +26189,12 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>Hackhål/bohål</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -26179,57 +26209,57 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>127272422</v>
+        <v>127282894</v>
       </c>
       <c r="B248" t="n">
-        <v>79014</v>
+        <v>79038</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>440682</v>
+        <v>440951</v>
       </c>
       <c r="R248" t="n">
-        <v>6762093</v>
+        <v>6762514</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -26259,24 +26289,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z248" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA248" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB248" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC248" t="inlineStr">
-        <is>
-          <t>Garnlav på äldre tall, sannoligt äldre än 200 år</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26291,19 +26306,19 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>127270746</v>
+        <v>127274466</v>
       </c>
       <c r="B249" t="n">
         <v>79014</v>
@@ -26338,10 +26353,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>440308</v>
+        <v>440914</v>
       </c>
       <c r="R249" t="n">
-        <v>6762456</v>
+        <v>6762585</v>
       </c>
       <c r="S249" t="n">
         <v>9</v>
@@ -26373,7 +26388,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -26383,7 +26398,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -26410,7 +26425,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>127271817</v>
+        <v>127272935</v>
       </c>
       <c r="B250" t="n">
         <v>79014</v>
@@ -26441,17 +26456,17 @@
       <c r="I250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>440623</v>
+        <v>440613</v>
       </c>
       <c r="R250" t="n">
-        <v>6762126</v>
+        <v>6762174</v>
       </c>
       <c r="S250" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -26480,7 +26495,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -26490,7 +26505,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -26505,22 +26520,22 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>127282891</v>
+        <v>127272422</v>
       </c>
       <c r="B251" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26528,34 +26543,34 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>440416</v>
+        <v>440682</v>
       </c>
       <c r="R251" t="n">
-        <v>6762406</v>
+        <v>6762093</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26585,9 +26600,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>Garnlav på äldre tall, sannoligt äldre än 200 år</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -26602,22 +26632,22 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>127272190</v>
+        <v>127270746</v>
       </c>
       <c r="B252" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -26625,42 +26655,37 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
-      <c r="M252" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>440657</v>
+        <v>440308</v>
       </c>
       <c r="R252" t="n">
-        <v>6762157</v>
+        <v>6762456</v>
       </c>
       <c r="S252" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -26714,22 +26739,22 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>127273155</v>
+        <v>127271817</v>
       </c>
       <c r="B253" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -26737,42 +26762,37 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>440692</v>
+        <v>440623</v>
       </c>
       <c r="R253" t="n">
-        <v>6762205</v>
+        <v>6762126</v>
       </c>
       <c r="S253" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -26801,7 +26821,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -26811,7 +26831,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -26826,22 +26846,22 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>127273433</v>
+        <v>127282891</v>
       </c>
       <c r="B254" t="n">
-        <v>57654</v>
+        <v>79632</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -26849,39 +26869,34 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>440726</v>
+        <v>440416</v>
       </c>
       <c r="R254" t="n">
-        <v>6761979</v>
+        <v>6762406</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26911,24 +26926,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z254" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA254" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB254" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>Hackhål/bohål</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -26943,12 +26943,12 @@
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
@@ -27654,10 +27654,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>127282905</v>
+        <v>127276264</v>
       </c>
       <c r="B262" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -27665,34 +27665,39 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>440780</v>
+        <v>440642</v>
       </c>
       <c r="R262" t="n">
-        <v>6762578</v>
+        <v>6762606</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27722,9 +27727,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA262" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -27739,19 +27754,19 @@
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>127282934</v>
+        <v>127282905</v>
       </c>
       <c r="B263" t="n">
         <v>79014</v>
@@ -27786,10 +27801,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>440387</v>
+        <v>440780</v>
       </c>
       <c r="R263" t="n">
-        <v>6762369</v>
+        <v>6762578</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27848,7 +27863,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>127275330</v>
+        <v>127282934</v>
       </c>
       <c r="B264" t="n">
         <v>79014</v>
@@ -27879,17 +27894,17 @@
       <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>440868</v>
+        <v>440387</v>
       </c>
       <c r="R264" t="n">
-        <v>6762512</v>
+        <v>6762369</v>
       </c>
       <c r="S264" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -27916,19 +27931,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z264" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA264" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB264" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -27943,19 +27948,19 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>127282923</v>
+        <v>127275330</v>
       </c>
       <c r="B265" t="n">
         <v>79014</v>
@@ -27986,17 +27991,17 @@
       <c r="I265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>440658</v>
+        <v>440868</v>
       </c>
       <c r="R265" t="n">
-        <v>6762202</v>
+        <v>6762512</v>
       </c>
       <c r="S265" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -28023,9 +28028,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -28040,19 +28055,19 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>127275346</v>
+        <v>127282923</v>
       </c>
       <c r="B266" t="n">
         <v>79014</v>
@@ -28083,17 +28098,17 @@
       <c r="I266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>440853</v>
+        <v>440658</v>
       </c>
       <c r="R266" t="n">
-        <v>6762514</v>
+        <v>6762202</v>
       </c>
       <c r="S266" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -28120,19 +28135,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z266" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA266" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB266" t="inlineStr">
-        <is>
-          <t>14:33</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -28147,19 +28152,19 @@
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>127282921</v>
+        <v>127275346</v>
       </c>
       <c r="B267" t="n">
         <v>79014</v>
@@ -28190,17 +28195,17 @@
       <c r="I267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>440680</v>
+        <v>440853</v>
       </c>
       <c r="R267" t="n">
-        <v>6762218</v>
+        <v>6762514</v>
       </c>
       <c r="S267" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -28227,9 +28232,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA267" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -28244,60 +28259,60 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>127272941</v>
+        <v>127282921</v>
       </c>
       <c r="B268" t="n">
-        <v>79038</v>
+        <v>79014</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>440613</v>
+        <v>440680</v>
       </c>
       <c r="R268" t="n">
-        <v>6762174</v>
+        <v>6762218</v>
       </c>
       <c r="S268" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -28324,19 +28339,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z268" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AA268" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB268" t="inlineStr">
-        <is>
-          <t>12:31</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -28351,65 +28356,60 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>127276264</v>
+        <v>127272941</v>
       </c>
       <c r="B269" t="n">
-        <v>57654</v>
+        <v>79038</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>440642</v>
+        <v>440613</v>
       </c>
       <c r="R269" t="n">
-        <v>6762606</v>
+        <v>6762174</v>
       </c>
       <c r="S269" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
       </c>
       <c r="Z269" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
@@ -28448,7 +28448,7 @@
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -28463,12 +28463,12 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>

--- a/artfynd/A 29945-2025 artfynd.xlsx
+++ b/artfynd/A 29945-2025 artfynd.xlsx
@@ -11351,7 +11351,7 @@
         <v>127272192</v>
       </c>
       <c r="B104" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>127283121</v>
       </c>
       <c r="B105" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>127275526</v>
       </c>
       <c r="B106" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>127274454</v>
       </c>
       <c r="B107" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>127282929</v>
       </c>
       <c r="B108" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>127273727</v>
       </c>
       <c r="B109" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>127282909</v>
       </c>
       <c r="B110" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>127282922</v>
       </c>
       <c r="B111" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>127282903</v>
       </c>
       <c r="B112" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>127282896</v>
       </c>
       <c r="B113" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>127274251</v>
       </c>
       <c r="B114" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>127273473</v>
       </c>
       <c r="B115" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>127272135</v>
       </c>
       <c r="B116" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12689,10 +12689,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127274057</v>
+        <v>127273755</v>
       </c>
       <c r="B117" t="n">
-        <v>57654</v>
+        <v>79018</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12700,39 +12700,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>440706</v>
+        <v>440744</v>
       </c>
       <c r="R117" t="n">
-        <v>6762058</v>
+        <v>6762065</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12801,10 +12796,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127283110</v>
+        <v>127276304</v>
       </c>
       <c r="B118" t="n">
-        <v>79015</v>
+        <v>79018</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12812,16 +12807,16 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -12832,14 +12827,14 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>440835</v>
+        <v>440642</v>
       </c>
       <c r="R118" t="n">
-        <v>6762564</v>
+        <v>6762606</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12869,9 +12864,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12886,44 +12891,44 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127274061</v>
+        <v>127275131</v>
       </c>
       <c r="B119" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12933,10 +12938,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>440706</v>
+        <v>440709</v>
       </c>
       <c r="R119" t="n">
-        <v>6762058</v>
+        <v>6762405</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13005,10 +13010,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127273755</v>
+        <v>127271820</v>
       </c>
       <c r="B120" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13036,17 +13041,17 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>440744</v>
+        <v>440446</v>
       </c>
       <c r="R120" t="n">
-        <v>6762065</v>
+        <v>6762469</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13075,7 +13080,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13085,7 +13090,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13100,44 +13105,44 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127276304</v>
+        <v>127274061</v>
       </c>
       <c r="B121" t="n">
-        <v>79014</v>
+        <v>8450</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13147,10 +13152,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>440642</v>
+        <v>440706</v>
       </c>
       <c r="R121" t="n">
-        <v>6762606</v>
+        <v>6762058</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13182,7 +13187,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13192,7 +13197,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13219,10 +13224,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127275131</v>
+        <v>127283110</v>
       </c>
       <c r="B122" t="n">
-        <v>79014</v>
+        <v>79019</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13230,16 +13235,16 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -13250,14 +13255,14 @@
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>440709</v>
+        <v>440835</v>
       </c>
       <c r="R122" t="n">
-        <v>6762405</v>
+        <v>6762564</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13287,19 +13292,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13314,22 +13309,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127271820</v>
+        <v>127274057</v>
       </c>
       <c r="B123" t="n">
-        <v>79014</v>
+        <v>57658</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13337,37 +13332,42 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>440446</v>
+        <v>440706</v>
       </c>
       <c r="R123" t="n">
-        <v>6762469</v>
+        <v>6762058</v>
       </c>
       <c r="S123" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13421,12 +13421,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -13436,7 +13436,7 @@
         <v>127283139</v>
       </c>
       <c r="B124" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>127283131</v>
       </c>
       <c r="B125" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>127283135</v>
       </c>
       <c r="B126" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>127273828</v>
       </c>
       <c r="B127" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>127275968</v>
       </c>
       <c r="B128" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>127271992</v>
       </c>
       <c r="B129" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14050,45 +14050,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127283108</v>
+        <v>127274657</v>
       </c>
       <c r="B130" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>440442</v>
+        <v>440689</v>
       </c>
       <c r="R130" t="n">
-        <v>6762471</v>
+        <v>6762214</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14118,9 +14118,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14135,57 +14150,57 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127282895</v>
+        <v>127283117</v>
       </c>
       <c r="B131" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>440382</v>
+        <v>440863</v>
       </c>
       <c r="R131" t="n">
-        <v>6762379</v>
+        <v>6762603</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14232,22 +14247,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127283109</v>
+        <v>127273051</v>
       </c>
       <c r="B132" t="n">
-        <v>79015</v>
+        <v>79018</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14255,16 +14270,16 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -14275,17 +14290,17 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>440875</v>
+        <v>440681</v>
       </c>
       <c r="R132" t="n">
-        <v>6762453</v>
+        <v>6762197</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14312,9 +14327,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14329,22 +14354,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127274657</v>
+        <v>127282932</v>
       </c>
       <c r="B133" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14372,14 +14397,14 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>440689</v>
+        <v>440427</v>
       </c>
       <c r="R133" t="n">
-        <v>6762214</v>
+        <v>6762470</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14409,24 +14434,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14441,22 +14451,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127283117</v>
+        <v>127282912</v>
       </c>
       <c r="B134" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14484,14 +14494,14 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>440863</v>
+        <v>440936</v>
       </c>
       <c r="R134" t="n">
-        <v>6762603</v>
+        <v>6762564</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14538,22 +14548,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127273051</v>
+        <v>127282926</v>
       </c>
       <c r="B135" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14581,17 +14591,17 @@
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>440681</v>
+        <v>440497</v>
       </c>
       <c r="R135" t="n">
-        <v>6762197</v>
+        <v>6762331</v>
       </c>
       <c r="S135" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14618,19 +14628,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>12:38</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14645,22 +14645,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127282932</v>
+        <v>127283130</v>
       </c>
       <c r="B136" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14688,14 +14688,14 @@
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>440427</v>
+        <v>440697</v>
       </c>
       <c r="R136" t="n">
-        <v>6762470</v>
+        <v>6762237</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14742,22 +14742,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127282912</v>
+        <v>127276216</v>
       </c>
       <c r="B137" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14785,14 +14785,14 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>440936</v>
+        <v>440657</v>
       </c>
       <c r="R137" t="n">
-        <v>6762564</v>
+        <v>6762603</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14822,9 +14822,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14839,22 +14849,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127282926</v>
+        <v>127273488</v>
       </c>
       <c r="B138" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14882,14 +14892,14 @@
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>440497</v>
+        <v>440721</v>
       </c>
       <c r="R138" t="n">
-        <v>6762331</v>
+        <v>6761996</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14919,9 +14929,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14936,22 +14956,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127283130</v>
+        <v>127276148</v>
       </c>
       <c r="B139" t="n">
-        <v>79014</v>
+        <v>57658</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14959,34 +14979,39 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>440697</v>
+        <v>440657</v>
       </c>
       <c r="R139" t="n">
-        <v>6762237</v>
+        <v>6762603</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15016,9 +15041,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15033,22 +15068,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127276216</v>
+        <v>127272305</v>
       </c>
       <c r="B140" t="n">
-        <v>79014</v>
+        <v>57658</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15056,34 +15091,39 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>440657</v>
+        <v>440675</v>
       </c>
       <c r="R140" t="n">
-        <v>6762603</v>
+        <v>6762165</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15115,7 +15155,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15125,7 +15165,12 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Diameter ca 4 till 5 cm</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15152,10 +15197,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127273488</v>
+        <v>127271765</v>
       </c>
       <c r="B141" t="n">
-        <v>79014</v>
+        <v>57658</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15163,34 +15208,39 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>440721</v>
+        <v>440627</v>
       </c>
       <c r="R141" t="n">
-        <v>6761996</v>
+        <v>6762119</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15233,6 +15283,11 @@
       <c r="AB141" t="inlineStr">
         <is>
           <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Miljöbild för området</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15259,10 +15314,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127276148</v>
+        <v>127276450</v>
       </c>
       <c r="B142" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15290,7 +15345,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -15299,10 +15354,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>440657</v>
+        <v>440582</v>
       </c>
       <c r="R142" t="n">
-        <v>6762603</v>
+        <v>6762684</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15371,50 +15426,45 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127272305</v>
+        <v>127283108</v>
       </c>
       <c r="B143" t="n">
-        <v>57654</v>
+        <v>8450</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>440675</v>
+        <v>440442</v>
       </c>
       <c r="R143" t="n">
-        <v>6762165</v>
+        <v>6762471</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15444,24 +15494,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Diameter ca 4 till 5 cm</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15476,62 +15511,57 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127271765</v>
+        <v>127282895</v>
       </c>
       <c r="B144" t="n">
-        <v>57654</v>
+        <v>8450</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>440627</v>
+        <v>440382</v>
       </c>
       <c r="R144" t="n">
-        <v>6762119</v>
+        <v>6762379</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15561,24 +15591,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Miljöbild för området</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15593,22 +15608,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127276450</v>
+        <v>127283109</v>
       </c>
       <c r="B145" t="n">
-        <v>57654</v>
+        <v>79019</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15616,39 +15631,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>230405</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>440582</v>
+        <v>440875</v>
       </c>
       <c r="R145" t="n">
-        <v>6762684</v>
+        <v>6762453</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15678,19 +15688,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15705,60 +15705,60 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127283142</v>
+        <v>127274917</v>
       </c>
       <c r="B146" t="n">
-        <v>92616</v>
+        <v>79018</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>440744</v>
+        <v>440752</v>
       </c>
       <c r="R146" t="n">
-        <v>6762615</v>
+        <v>6762337</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15785,9 +15785,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15802,22 +15812,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127274917</v>
+        <v>127283119</v>
       </c>
       <c r="B147" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15845,17 +15855,17 @@
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>440752</v>
+        <v>440881</v>
       </c>
       <c r="R147" t="n">
-        <v>6762337</v>
+        <v>6762591</v>
       </c>
       <c r="S147" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15882,19 +15892,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15909,22 +15909,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127283119</v>
+        <v>127272858</v>
       </c>
       <c r="B148" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15952,17 +15952,17 @@
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>440881</v>
+        <v>440609</v>
       </c>
       <c r="R148" t="n">
-        <v>6762591</v>
+        <v>6762190</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15989,9 +15989,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16006,22 +16016,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127272858</v>
+        <v>127273038</v>
       </c>
       <c r="B149" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16053,10 +16063,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>440609</v>
+        <v>440688</v>
       </c>
       <c r="R149" t="n">
-        <v>6762190</v>
+        <v>6762199</v>
       </c>
       <c r="S149" t="n">
         <v>9</v>
@@ -16088,7 +16098,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16098,7 +16108,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16125,10 +16135,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127273038</v>
+        <v>127274822</v>
       </c>
       <c r="B150" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16156,17 +16166,17 @@
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>440688</v>
+        <v>440760</v>
       </c>
       <c r="R150" t="n">
-        <v>6762199</v>
+        <v>6762313</v>
       </c>
       <c r="S150" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16195,7 +16205,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16205,7 +16215,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16220,22 +16230,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127274822</v>
+        <v>127275416</v>
       </c>
       <c r="B151" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16263,17 +16273,17 @@
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>440760</v>
+        <v>440816</v>
       </c>
       <c r="R151" t="n">
-        <v>6762313</v>
+        <v>6762475</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16302,7 +16312,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16312,7 +16322,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16327,22 +16337,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127275416</v>
+        <v>127273932</v>
       </c>
       <c r="B152" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16374,10 +16384,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>440816</v>
+        <v>440913</v>
       </c>
       <c r="R152" t="n">
-        <v>6762475</v>
+        <v>6762466</v>
       </c>
       <c r="S152" t="n">
         <v>9</v>
@@ -16409,7 +16419,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16419,7 +16429,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16446,48 +16456,48 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127273932</v>
+        <v>127283142</v>
       </c>
       <c r="B153" t="n">
-        <v>79014</v>
+        <v>92620</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>440913</v>
+        <v>440744</v>
       </c>
       <c r="R153" t="n">
-        <v>6762466</v>
+        <v>6762615</v>
       </c>
       <c r="S153" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16514,19 +16524,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>13:23</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16541,22 +16541,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127282904</v>
+        <v>127272237</v>
       </c>
       <c r="B154" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16564,34 +16564,39 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>440776</v>
+        <v>440675</v>
       </c>
       <c r="R154" t="n">
-        <v>6762632</v>
+        <v>6762165</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16621,9 +16626,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16638,22 +16653,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127282914</v>
+        <v>127282904</v>
       </c>
       <c r="B155" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16685,10 +16700,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>440924</v>
+        <v>440776</v>
       </c>
       <c r="R155" t="n">
-        <v>6762509</v>
+        <v>6762632</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16747,10 +16762,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127274354</v>
+        <v>127282914</v>
       </c>
       <c r="B156" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16778,14 +16793,14 @@
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>440686</v>
+        <v>440924</v>
       </c>
       <c r="R156" t="n">
-        <v>6762176</v>
+        <v>6762509</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16815,19 +16830,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16842,22 +16847,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127272746</v>
+        <v>127283105</v>
       </c>
       <c r="B157" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16865,37 +16870,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>440503</v>
+        <v>440909</v>
       </c>
       <c r="R157" t="n">
-        <v>6762308</v>
+        <v>6762467</v>
       </c>
       <c r="S157" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16922,19 +16927,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16949,22 +16944,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127272237</v>
+        <v>127274354</v>
       </c>
       <c r="B158" t="n">
-        <v>57657</v>
+        <v>79018</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16972,39 +16967,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>440675</v>
+        <v>440686</v>
       </c>
       <c r="R158" t="n">
-        <v>6762165</v>
+        <v>6762176</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17073,10 +17063,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127283105</v>
+        <v>127272746</v>
       </c>
       <c r="B159" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17084,37 +17074,37 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>440909</v>
+        <v>440503</v>
       </c>
       <c r="R159" t="n">
-        <v>6762467</v>
+        <v>6762308</v>
       </c>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17141,9 +17131,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17158,12 +17158,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
@@ -17173,7 +17173,7 @@
         <v>127274348</v>
       </c>
       <c r="B160" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17282,10 +17282,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127275098</v>
+        <v>127282900</v>
       </c>
       <c r="B161" t="n">
-        <v>57657</v>
+        <v>79018</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17293,39 +17293,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>440679</v>
+        <v>440757</v>
       </c>
       <c r="R161" t="n">
-        <v>6762388</v>
+        <v>6762544</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17355,19 +17350,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17382,22 +17367,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127282900</v>
+        <v>127276426</v>
       </c>
       <c r="B162" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17425,14 +17410,14 @@
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>440757</v>
+        <v>440582</v>
       </c>
       <c r="R162" t="n">
-        <v>6762544</v>
+        <v>6762684</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17462,9 +17447,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17479,22 +17474,22 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127276426</v>
+        <v>127275877</v>
       </c>
       <c r="B163" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17526,10 +17521,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>440582</v>
+        <v>440732</v>
       </c>
       <c r="R163" t="n">
-        <v>6762684</v>
+        <v>6762635</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17598,10 +17593,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127275877</v>
+        <v>127273900</v>
       </c>
       <c r="B164" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17629,17 +17624,17 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>440732</v>
+        <v>440903</v>
       </c>
       <c r="R164" t="n">
-        <v>6762635</v>
+        <v>6762450</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -17668,7 +17663,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17678,7 +17673,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17693,22 +17688,22 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127273900</v>
+        <v>127282902</v>
       </c>
       <c r="B165" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17736,17 +17731,17 @@
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>440903</v>
+        <v>440760</v>
       </c>
       <c r="R165" t="n">
-        <v>6762450</v>
+        <v>6762569</v>
       </c>
       <c r="S165" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -17773,19 +17768,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>13:21</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17800,22 +17785,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127282902</v>
+        <v>127273086</v>
       </c>
       <c r="B166" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17843,17 +17828,17 @@
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>440760</v>
+        <v>440694</v>
       </c>
       <c r="R166" t="n">
-        <v>6762569</v>
+        <v>6762204</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17880,9 +17865,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17897,22 +17892,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127273086</v>
+        <v>127283137</v>
       </c>
       <c r="B167" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17940,17 +17935,17 @@
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>440694</v>
+        <v>440354</v>
       </c>
       <c r="R167" t="n">
-        <v>6762204</v>
+        <v>6762415</v>
       </c>
       <c r="S167" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -17977,19 +17972,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z167" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>12:40</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18004,22 +17989,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127283137</v>
+        <v>127275098</v>
       </c>
       <c r="B168" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18027,34 +18012,39 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>440354</v>
+        <v>440679</v>
       </c>
       <c r="R168" t="n">
-        <v>6762415</v>
+        <v>6762388</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18084,9 +18074,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18101,60 +18101,60 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127271802</v>
+        <v>127273853</v>
       </c>
       <c r="B169" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>440627</v>
+        <v>440887</v>
       </c>
       <c r="R169" t="n">
-        <v>6762119</v>
+        <v>6762439</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18193,12 +18193,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Rikligt med torrakor med spår efter Mindre Märgborre i området</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18213,65 +18208,60 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127271251</v>
+        <v>127270744</v>
       </c>
       <c r="B170" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>440375</v>
+        <v>440351</v>
       </c>
       <c r="R170" t="n">
-        <v>6762366</v>
+        <v>6762480</v>
       </c>
       <c r="S170" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18300,7 +18290,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18310,7 +18300,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18325,60 +18315,60 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127276271</v>
+        <v>127275337</v>
       </c>
       <c r="B171" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>440642</v>
+        <v>440855</v>
       </c>
       <c r="R171" t="n">
-        <v>6762606</v>
+        <v>6762513</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18407,7 +18397,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18417,7 +18407,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18432,22 +18422,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127273853</v>
+        <v>127282927</v>
       </c>
       <c r="B172" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18475,17 +18465,17 @@
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>440887</v>
+        <v>440488</v>
       </c>
       <c r="R172" t="n">
-        <v>6762439</v>
+        <v>6762419</v>
       </c>
       <c r="S172" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18512,19 +18502,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18539,22 +18519,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127270744</v>
+        <v>127283128</v>
       </c>
       <c r="B173" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18582,14 +18562,14 @@
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>440351</v>
+        <v>440822</v>
       </c>
       <c r="R173" t="n">
-        <v>6762480</v>
+        <v>6762415</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18619,19 +18599,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18646,22 +18616,22 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127275337</v>
+        <v>127274114</v>
       </c>
       <c r="B174" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18689,17 +18659,17 @@
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>440855</v>
+        <v>440711</v>
       </c>
       <c r="R174" t="n">
-        <v>6762513</v>
+        <v>6762111</v>
       </c>
       <c r="S174" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -18728,7 +18698,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -18738,7 +18708,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18753,22 +18723,22 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127282927</v>
+        <v>127283115</v>
       </c>
       <c r="B175" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18796,14 +18766,14 @@
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>440488</v>
+        <v>440803</v>
       </c>
       <c r="R175" t="n">
-        <v>6762419</v>
+        <v>6762557</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18850,22 +18820,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127283128</v>
+        <v>127283134</v>
       </c>
       <c r="B176" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18897,10 +18867,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>440822</v>
+        <v>440487</v>
       </c>
       <c r="R176" t="n">
-        <v>6762415</v>
+        <v>6762321</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18959,10 +18929,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127274114</v>
+        <v>127283133</v>
       </c>
       <c r="B177" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18990,14 +18960,14 @@
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>440711</v>
+        <v>440598</v>
       </c>
       <c r="R177" t="n">
-        <v>6762111</v>
+        <v>6762206</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19027,19 +18997,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19054,57 +19014,57 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127283115</v>
+        <v>127271802</v>
       </c>
       <c r="B178" t="n">
-        <v>79014</v>
+        <v>8450</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>440803</v>
+        <v>440627</v>
       </c>
       <c r="R178" t="n">
-        <v>6762557</v>
+        <v>6762119</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19134,9 +19094,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>Rikligt med torrakor med spår efter Mindre Märgborre i området</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19151,60 +19126,65 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127283134</v>
+        <v>127271251</v>
       </c>
       <c r="B179" t="n">
-        <v>79014</v>
+        <v>8450</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>440487</v>
+        <v>440375</v>
       </c>
       <c r="R179" t="n">
-        <v>6762321</v>
+        <v>6762366</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19231,9 +19211,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19248,57 +19238,57 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127283133</v>
+        <v>127276271</v>
       </c>
       <c r="B180" t="n">
-        <v>79014</v>
+        <v>8450</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>440598</v>
+        <v>440642</v>
       </c>
       <c r="R180" t="n">
-        <v>6762206</v>
+        <v>6762606</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19328,9 +19318,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19345,22 +19345,22 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127274154</v>
+        <v>127283127</v>
       </c>
       <c r="B181" t="n">
-        <v>57657</v>
+        <v>79018</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19368,42 +19368,37 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>440946</v>
+        <v>440843</v>
       </c>
       <c r="R181" t="n">
-        <v>6762537</v>
+        <v>6762431</v>
       </c>
       <c r="S181" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -19430,24 +19425,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19462,12 +19442,12 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
@@ -19477,7 +19457,7 @@
         <v>127283116</v>
       </c>
       <c r="B182" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19574,7 +19554,7 @@
         <v>127282906</v>
       </c>
       <c r="B183" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19671,7 +19651,7 @@
         <v>127275778</v>
       </c>
       <c r="B184" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19778,7 +19758,7 @@
         <v>127282925</v>
       </c>
       <c r="B185" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19872,10 +19852,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127283127</v>
+        <v>127274154</v>
       </c>
       <c r="B186" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19883,37 +19863,42 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>440843</v>
+        <v>440946</v>
       </c>
       <c r="R186" t="n">
-        <v>6762431</v>
+        <v>6762537</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19940,9 +19925,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19957,57 +19957,57 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127276155</v>
+        <v>127282924</v>
       </c>
       <c r="B187" t="n">
-        <v>8447</v>
+        <v>79018</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>440657</v>
+        <v>440623</v>
       </c>
       <c r="R187" t="n">
-        <v>6762603</v>
+        <v>6762194</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20037,19 +20037,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20064,22 +20054,22 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127274877</v>
+        <v>127283136</v>
       </c>
       <c r="B188" t="n">
-        <v>57817</v>
+        <v>79018</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20087,42 +20077,37 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>440752</v>
+        <v>440394</v>
       </c>
       <c r="R188" t="n">
-        <v>6762337</v>
+        <v>6762413</v>
       </c>
       <c r="S188" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -20149,19 +20134,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z188" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20176,22 +20151,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127282924</v>
+        <v>127283138</v>
       </c>
       <c r="B189" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20219,14 +20194,14 @@
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>440623</v>
+        <v>440335</v>
       </c>
       <c r="R189" t="n">
-        <v>6762194</v>
+        <v>6762400</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20273,22 +20248,22 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127283136</v>
+        <v>127282907</v>
       </c>
       <c r="B190" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20316,14 +20291,14 @@
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>440394</v>
+        <v>440793</v>
       </c>
       <c r="R190" t="n">
-        <v>6762413</v>
+        <v>6762525</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20370,22 +20345,22 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127283138</v>
+        <v>127283118</v>
       </c>
       <c r="B191" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20417,10 +20392,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>440335</v>
+        <v>440868</v>
       </c>
       <c r="R191" t="n">
-        <v>6762400</v>
+        <v>6762583</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20479,10 +20454,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127282907</v>
+        <v>127283113</v>
       </c>
       <c r="B192" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20510,14 +20485,14 @@
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>440793</v>
+        <v>440768</v>
       </c>
       <c r="R192" t="n">
-        <v>6762525</v>
+        <v>6762554</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20564,57 +20539,57 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127283118</v>
+        <v>127276155</v>
       </c>
       <c r="B193" t="n">
-        <v>79014</v>
+        <v>8450</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>440868</v>
+        <v>440657</v>
       </c>
       <c r="R193" t="n">
-        <v>6762583</v>
+        <v>6762603</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20644,9 +20619,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20661,22 +20646,22 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127283113</v>
+        <v>127274877</v>
       </c>
       <c r="B194" t="n">
-        <v>79014</v>
+        <v>57821</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20684,37 +20669,42 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>440768</v>
+        <v>440752</v>
       </c>
       <c r="R194" t="n">
-        <v>6762554</v>
+        <v>6762337</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -20741,9 +20731,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20758,12 +20758,12 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
@@ -20773,7 +20773,7 @@
         <v>127276018</v>
       </c>
       <c r="B195" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20880,7 +20880,7 @@
         <v>127275350</v>
       </c>
       <c r="B196" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20987,7 +20987,7 @@
         <v>127283124</v>
       </c>
       <c r="B197" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>127272147</v>
       </c>
       <c r="B198" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21191,7 +21191,7 @@
         <v>127274677</v>
       </c>
       <c r="B199" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>127283143</v>
       </c>
       <c r="B200" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>127272174</v>
       </c>
       <c r="B201" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>127275348</v>
       </c>
       <c r="B202" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>127282910</v>
       </c>
       <c r="B203" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>127271972</v>
       </c>
       <c r="B204" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -21823,7 +21823,7 @@
         <v>127272958</v>
       </c>
       <c r="B205" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>127283114</v>
       </c>
       <c r="B206" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>127282897</v>
       </c>
       <c r="B207" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22124,7 +22124,7 @@
         <v>127282920</v>
       </c>
       <c r="B208" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>127271427</v>
       </c>
       <c r="B209" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -22325,10 +22325,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127274242</v>
+        <v>127282901</v>
       </c>
       <c r="B210" t="n">
-        <v>57654</v>
+        <v>79018</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -22336,39 +22336,34 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>440697</v>
+        <v>440751</v>
       </c>
       <c r="R210" t="n">
-        <v>6762119</v>
+        <v>6762564</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22398,19 +22393,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -22425,22 +22410,22 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>127282901</v>
+        <v>127283112</v>
       </c>
       <c r="B211" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -22468,14 +22453,14 @@
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>440751</v>
+        <v>440663</v>
       </c>
       <c r="R211" t="n">
-        <v>6762564</v>
+        <v>6762599</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22522,22 +22507,22 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127283112</v>
+        <v>127283102</v>
       </c>
       <c r="B212" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -22545,21 +22530,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22569,10 +22554,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>440663</v>
+        <v>440726</v>
       </c>
       <c r="R212" t="n">
-        <v>6762599</v>
+        <v>6762638</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22634,7 +22619,7 @@
         <v>127272352</v>
       </c>
       <c r="B213" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -22741,7 +22726,7 @@
         <v>127273790</v>
       </c>
       <c r="B214" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -22848,7 +22833,7 @@
         <v>127273057</v>
       </c>
       <c r="B215" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -22955,7 +22940,7 @@
         <v>127283104</v>
       </c>
       <c r="B216" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23049,10 +23034,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127283102</v>
+        <v>127274242</v>
       </c>
       <c r="B217" t="n">
-        <v>79632</v>
+        <v>57658</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23060,34 +23045,39 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>440726</v>
+        <v>440697</v>
       </c>
       <c r="R217" t="n">
-        <v>6762638</v>
+        <v>6762119</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23117,9 +23107,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA217" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -23134,22 +23134,22 @@
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127282898</v>
+        <v>127283106</v>
       </c>
       <c r="B218" t="n">
-        <v>79014</v>
+        <v>78777</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23157,34 +23157,34 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>440741</v>
+        <v>440504</v>
       </c>
       <c r="R218" t="n">
-        <v>6762609</v>
+        <v>6762388</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23231,22 +23231,22 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127283122</v>
+        <v>127282898</v>
       </c>
       <c r="B219" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23274,14 +23274,14 @@
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>440912</v>
+        <v>440741</v>
       </c>
       <c r="R219" t="n">
-        <v>6762579</v>
+        <v>6762609</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23328,22 +23328,22 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127282915</v>
+        <v>127283122</v>
       </c>
       <c r="B220" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -23371,14 +23371,14 @@
       <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>440946</v>
+        <v>440912</v>
       </c>
       <c r="R220" t="n">
-        <v>6762514</v>
+        <v>6762579</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23425,22 +23425,22 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127275040</v>
+        <v>127282915</v>
       </c>
       <c r="B221" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23468,14 +23468,14 @@
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>440745</v>
+        <v>440946</v>
       </c>
       <c r="R221" t="n">
-        <v>6762369</v>
+        <v>6762514</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23505,24 +23505,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z221" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB221" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -23537,22 +23522,22 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127282899</v>
+        <v>127275040</v>
       </c>
       <c r="B222" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23580,14 +23565,14 @@
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>440763</v>
+        <v>440745</v>
       </c>
       <c r="R222" t="n">
-        <v>6762529</v>
+        <v>6762369</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23617,9 +23602,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA222" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -23634,22 +23634,22 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127283141</v>
+        <v>127282899</v>
       </c>
       <c r="B223" t="n">
-        <v>78681</v>
+        <v>79018</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23657,34 +23657,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>440651</v>
+        <v>440763</v>
       </c>
       <c r="R223" t="n">
-        <v>6762611</v>
+        <v>6762529</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23731,12 +23731,12 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
@@ -23746,7 +23746,7 @@
         <v>127283100</v>
       </c>
       <c r="B224" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23840,32 +23840,32 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127283107</v>
+        <v>127283141</v>
       </c>
       <c r="B225" t="n">
-        <v>8447</v>
+        <v>78685</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23875,10 +23875,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>440636</v>
+        <v>440651</v>
       </c>
       <c r="R225" t="n">
-        <v>6762585</v>
+        <v>6762611</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23937,32 +23937,32 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127283106</v>
+        <v>127283107</v>
       </c>
       <c r="B226" t="n">
-        <v>78773</v>
+        <v>8450</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23972,10 +23972,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>440504</v>
+        <v>440636</v>
       </c>
       <c r="R226" t="n">
-        <v>6762388</v>
+        <v>6762585</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24037,7 +24037,7 @@
         <v>127283126</v>
       </c>
       <c r="B227" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24134,7 +24134,7 @@
         <v>127282918</v>
       </c>
       <c r="B228" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>127282917</v>
       </c>
       <c r="B229" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>127283125</v>
       </c>
       <c r="B230" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24425,7 +24425,7 @@
         <v>127273660</v>
       </c>
       <c r="B231" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24532,7 +24532,7 @@
         <v>127275120</v>
       </c>
       <c r="B232" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24636,48 +24636,48 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127273585</v>
+        <v>127275544</v>
       </c>
       <c r="B233" t="n">
-        <v>91684</v>
+        <v>8450</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>2062</v>
+        <v>106545</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>440742</v>
+        <v>440811</v>
       </c>
       <c r="R233" t="n">
-        <v>6762004</v>
+        <v>6762474</v>
       </c>
       <c r="S233" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -24706,7 +24706,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -24716,7 +24716,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -24731,60 +24731,60 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>127275544</v>
+        <v>127273585</v>
       </c>
       <c r="B234" t="n">
-        <v>8447</v>
+        <v>91688</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>106545</v>
+        <v>2062</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>440811</v>
+        <v>440742</v>
       </c>
       <c r="R234" t="n">
-        <v>6762474</v>
+        <v>6762004</v>
       </c>
       <c r="S234" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -24823,7 +24823,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -24838,12 +24838,12 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
@@ -24853,7 +24853,7 @@
         <v>127283123</v>
       </c>
       <c r="B235" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>127282930</v>
       </c>
       <c r="B236" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>127271487</v>
       </c>
       <c r="B237" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>127283132</v>
       </c>
       <c r="B238" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>127282933</v>
       </c>
       <c r="B239" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>127273778</v>
       </c>
       <c r="B240" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -25455,7 +25455,7 @@
         <v>127282911</v>
       </c>
       <c r="B241" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>127271764</v>
       </c>
       <c r="B242" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -25656,27 +25656,27 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127275970</v>
+        <v>127275615</v>
       </c>
       <c r="B243" t="n">
-        <v>5196</v>
+        <v>57658</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -25687,7 +25687,7 @@
       <c r="I243" t="inlineStr"/>
       <c r="M243" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
@@ -25696,10 +25696,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>440685</v>
+        <v>440778</v>
       </c>
       <c r="R243" t="n">
-        <v>6762673</v>
+        <v>6762552</v>
       </c>
       <c r="S243" t="n">
         <v>9</v>
@@ -25731,7 +25731,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -25741,7 +25741,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -25768,27 +25768,27 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>127275615</v>
+        <v>127275970</v>
       </c>
       <c r="B244" t="n">
-        <v>57654</v>
+        <v>5197</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -25799,7 +25799,7 @@
       <c r="I244" t="inlineStr"/>
       <c r="M244" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
@@ -25808,10 +25808,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>440778</v>
+        <v>440685</v>
       </c>
       <c r="R244" t="n">
-        <v>6762552</v>
+        <v>6762673</v>
       </c>
       <c r="S244" t="n">
         <v>9</v>
@@ -25843,7 +25843,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -25853,7 +25853,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -25880,50 +25880,45 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127272190</v>
+        <v>127282894</v>
       </c>
       <c r="B245" t="n">
-        <v>57654</v>
+        <v>79042</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>440657</v>
+        <v>440951</v>
       </c>
       <c r="R245" t="n">
-        <v>6762157</v>
+        <v>6762514</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25953,19 +25948,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z245" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA245" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB245" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -25980,22 +25965,22 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127273155</v>
+        <v>127282891</v>
       </c>
       <c r="B246" t="n">
-        <v>57654</v>
+        <v>79636</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -26003,42 +25988,37 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>440692</v>
+        <v>440416</v>
       </c>
       <c r="R246" t="n">
-        <v>6762205</v>
+        <v>6762406</v>
       </c>
       <c r="S246" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -26065,19 +26045,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z246" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA246" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB246" t="inlineStr">
-        <is>
-          <t>12:43</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -26092,22 +26062,22 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>127273433</v>
+        <v>127274466</v>
       </c>
       <c r="B247" t="n">
-        <v>57654</v>
+        <v>79018</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26115,42 +26085,37 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
-      <c r="M247" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>440726</v>
+        <v>440914</v>
       </c>
       <c r="R247" t="n">
-        <v>6761979</v>
+        <v>6762585</v>
       </c>
       <c r="S247" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -26179,7 +26144,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -26189,12 +26154,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC247" t="inlineStr">
-        <is>
-          <t>Hackhål/bohål</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -26209,60 +26169,60 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>127282894</v>
+        <v>127272935</v>
       </c>
       <c r="B248" t="n">
-        <v>79038</v>
+        <v>79018</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>440951</v>
+        <v>440613</v>
       </c>
       <c r="R248" t="n">
-        <v>6762514</v>
+        <v>6762174</v>
       </c>
       <c r="S248" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -26289,9 +26249,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AA248" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26306,22 +26276,22 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>127274466</v>
+        <v>127272422</v>
       </c>
       <c r="B249" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -26349,17 +26319,17 @@
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>440914</v>
+        <v>440682</v>
       </c>
       <c r="R249" t="n">
-        <v>6762585</v>
+        <v>6762093</v>
       </c>
       <c r="S249" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -26388,7 +26358,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -26398,7 +26368,12 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>Garnlav på äldre tall, sannoligt äldre än 200 år</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -26413,22 +26388,22 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>127272935</v>
+        <v>127270746</v>
       </c>
       <c r="B250" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26460,10 +26435,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>440613</v>
+        <v>440308</v>
       </c>
       <c r="R250" t="n">
-        <v>6762174</v>
+        <v>6762456</v>
       </c>
       <c r="S250" t="n">
         <v>9</v>
@@ -26495,7 +26470,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -26505,7 +26480,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -26532,10 +26507,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>127272422</v>
+        <v>127271817</v>
       </c>
       <c r="B251" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26567,10 +26542,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>440682</v>
+        <v>440623</v>
       </c>
       <c r="R251" t="n">
-        <v>6762093</v>
+        <v>6762126</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26613,11 +26588,6 @@
       <c r="AB251" t="inlineStr">
         <is>
           <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>Garnlav på äldre tall, sannoligt äldre än 200 år</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -26644,10 +26614,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>127270746</v>
+        <v>127272190</v>
       </c>
       <c r="B252" t="n">
-        <v>79014</v>
+        <v>57658</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -26655,37 +26625,42 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>440308</v>
+        <v>440657</v>
       </c>
       <c r="R252" t="n">
-        <v>6762456</v>
+        <v>6762157</v>
       </c>
       <c r="S252" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -26739,22 +26714,22 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>127271817</v>
+        <v>127273155</v>
       </c>
       <c r="B253" t="n">
-        <v>79014</v>
+        <v>57658</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -26762,37 +26737,42 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>440623</v>
+        <v>440692</v>
       </c>
       <c r="R253" t="n">
-        <v>6762126</v>
+        <v>6762205</v>
       </c>
       <c r="S253" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -26821,7 +26801,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -26831,7 +26811,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -26846,22 +26826,22 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>127282891</v>
+        <v>127273433</v>
       </c>
       <c r="B254" t="n">
-        <v>79632</v>
+        <v>57658</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -26869,34 +26849,39 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>440416</v>
+        <v>440726</v>
       </c>
       <c r="R254" t="n">
-        <v>6762406</v>
+        <v>6761979</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26926,9 +26911,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA254" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>Hackhål/bohål</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -26943,12 +26943,12 @@
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
@@ -26958,7 +26958,7 @@
         <v>127282913</v>
       </c>
       <c r="B255" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>127282928</v>
       </c>
       <c r="B256" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>127282908</v>
       </c>
       <c r="B257" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>127271449</v>
       </c>
       <c r="B258" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -27353,10 +27353,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>127282893</v>
+        <v>127282916</v>
       </c>
       <c r="B259" t="n">
-        <v>91346</v>
+        <v>79018</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -27364,21 +27364,21 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -27388,10 +27388,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>440925</v>
+        <v>440930</v>
       </c>
       <c r="R259" t="n">
-        <v>6762502</v>
+        <v>6762495</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -27450,10 +27450,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127282916</v>
+        <v>127274471</v>
       </c>
       <c r="B260" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -27481,14 +27481,14 @@
       <c r="I260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>440930</v>
+        <v>440700</v>
       </c>
       <c r="R260" t="n">
-        <v>6762495</v>
+        <v>6762179</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27518,9 +27518,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA260" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB260" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -27535,22 +27545,22 @@
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>127274471</v>
+        <v>127282893</v>
       </c>
       <c r="B261" t="n">
-        <v>79014</v>
+        <v>91350</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -27558,34 +27568,34 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>440700</v>
+        <v>440925</v>
       </c>
       <c r="R261" t="n">
-        <v>6762179</v>
+        <v>6762502</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27615,19 +27625,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z261" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA261" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB261" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -27642,62 +27642,57 @@
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>127276264</v>
+        <v>127274680</v>
       </c>
       <c r="B262" t="n">
-        <v>57654</v>
+        <v>8450</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P262" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>440642</v>
+        <v>440689</v>
       </c>
       <c r="R262" t="n">
-        <v>6762606</v>
+        <v>6762214</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27729,7 +27724,7 @@
       </c>
       <c r="Z262" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
@@ -27739,7 +27734,7 @@
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -27769,7 +27764,7 @@
         <v>127282905</v>
       </c>
       <c r="B263" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -27866,7 +27861,7 @@
         <v>127282934</v>
       </c>
       <c r="B264" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -27963,7 +27958,7 @@
         <v>127275330</v>
       </c>
       <c r="B265" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -28070,7 +28065,7 @@
         <v>127282923</v>
       </c>
       <c r="B266" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -28167,7 +28162,7 @@
         <v>127275346</v>
       </c>
       <c r="B267" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -28274,7 +28269,7 @@
         <v>127282921</v>
       </c>
       <c r="B268" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -28371,7 +28366,7 @@
         <v>127272941</v>
       </c>
       <c r="B269" t="n">
-        <v>79038</v>
+        <v>79042</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -28475,45 +28470,50 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>127274680</v>
+        <v>127276264</v>
       </c>
       <c r="B270" t="n">
-        <v>8447</v>
+        <v>57658</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P270" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>440689</v>
+        <v>440642</v>
       </c>
       <c r="R270" t="n">
-        <v>6762214</v>
+        <v>6762606</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28545,7 +28545,7 @@
       </c>
       <c r="Z270" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
@@ -28555,7 +28555,7 @@
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -28585,7 +28585,7 @@
         <v>127330369</v>
       </c>
       <c r="B271" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>127330346</v>
       </c>
       <c r="B272" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>127330161</v>
       </c>
       <c r="B273" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -28915,7 +28915,7 @@
         <v>127330473</v>
       </c>
       <c r="B274" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -29025,7 +29025,7 @@
         <v>127330280</v>
       </c>
       <c r="B275" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>

--- a/artfynd/A 29945-2025 artfynd.xlsx
+++ b/artfynd/A 29945-2025 artfynd.xlsx
@@ -11455,7 +11455,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127283121</v>
+        <v>127275526</v>
       </c>
       <c r="B105" t="n">
         <v>79018</v>
@@ -11486,14 +11486,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>440883</v>
+        <v>440688</v>
       </c>
       <c r="R105" t="n">
-        <v>6762587</v>
+        <v>6762488</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11523,9 +11523,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11540,19 +11555,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127275526</v>
+        <v>127282929</v>
       </c>
       <c r="B106" t="n">
         <v>79018</v>
@@ -11583,14 +11598,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>440688</v>
+        <v>440440</v>
       </c>
       <c r="R106" t="n">
-        <v>6762488</v>
+        <v>6762463</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11620,24 +11635,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11652,19 +11652,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127274454</v>
+        <v>127283121</v>
       </c>
       <c r="B107" t="n">
         <v>79018</v>
@@ -11695,17 +11695,17 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>440926</v>
+        <v>440883</v>
       </c>
       <c r="R107" t="n">
-        <v>6762599</v>
+        <v>6762587</v>
       </c>
       <c r="S107" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11732,19 +11732,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11759,19 +11749,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127282929</v>
+        <v>127274454</v>
       </c>
       <c r="B108" t="n">
         <v>79018</v>
@@ -11802,17 +11792,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>440440</v>
+        <v>440926</v>
       </c>
       <c r="R108" t="n">
-        <v>6762463</v>
+        <v>6762599</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11839,9 +11829,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11856,12 +11856,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -12169,10 +12169,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127282903</v>
+        <v>127282896</v>
       </c>
       <c r="B112" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12180,21 +12180,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12204,10 +12204,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>440760</v>
+        <v>440416</v>
       </c>
       <c r="R112" t="n">
-        <v>6762626</v>
+        <v>6762406</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12266,10 +12266,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127282896</v>
+        <v>127282903</v>
       </c>
       <c r="B113" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12277,21 +12277,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12301,10 +12301,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>440416</v>
+        <v>440760</v>
       </c>
       <c r="R113" t="n">
-        <v>6762406</v>
+        <v>6762626</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12689,32 +12689,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127273755</v>
+        <v>127274061</v>
       </c>
       <c r="B117" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12724,10 +12724,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>440744</v>
+        <v>440706</v>
       </c>
       <c r="R117" t="n">
-        <v>6762065</v>
+        <v>6762058</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12796,7 +12796,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127276304</v>
+        <v>127271820</v>
       </c>
       <c r="B118" t="n">
         <v>79018</v>
@@ -12827,17 +12827,17 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>440642</v>
+        <v>440446</v>
       </c>
       <c r="R118" t="n">
-        <v>6762606</v>
+        <v>6762469</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12876,7 +12876,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12891,19 +12891,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127275131</v>
+        <v>127273755</v>
       </c>
       <c r="B119" t="n">
         <v>79018</v>
@@ -12938,10 +12938,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>440709</v>
+        <v>440744</v>
       </c>
       <c r="R119" t="n">
-        <v>6762405</v>
+        <v>6762065</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13010,7 +13010,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127271820</v>
+        <v>127276304</v>
       </c>
       <c r="B120" t="n">
         <v>79018</v>
@@ -13041,17 +13041,17 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>440446</v>
+        <v>440642</v>
       </c>
       <c r="R120" t="n">
-        <v>6762469</v>
+        <v>6762606</v>
       </c>
       <c r="S120" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13090,7 +13090,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13105,44 +13105,44 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127274061</v>
+        <v>127275131</v>
       </c>
       <c r="B121" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13152,10 +13152,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>440706</v>
+        <v>440709</v>
       </c>
       <c r="R121" t="n">
-        <v>6762058</v>
+        <v>6762405</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13224,10 +13224,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127283110</v>
+        <v>127274057</v>
       </c>
       <c r="B122" t="n">
-        <v>79019</v>
+        <v>57658</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13235,34 +13235,39 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>230405</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>440835</v>
+        <v>440706</v>
       </c>
       <c r="R122" t="n">
-        <v>6762564</v>
+        <v>6762058</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13292,9 +13297,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13309,22 +13324,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127274057</v>
+        <v>127283110</v>
       </c>
       <c r="B123" t="n">
-        <v>57658</v>
+        <v>79019</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13332,39 +13347,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>230405</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>440706</v>
+        <v>440835</v>
       </c>
       <c r="R123" t="n">
-        <v>6762058</v>
+        <v>6762564</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13394,19 +13404,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13421,12 +13421,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -13627,7 +13627,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127283135</v>
+        <v>127273828</v>
       </c>
       <c r="B126" t="n">
         <v>79018</v>
@@ -13658,17 +13658,17 @@
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>440456</v>
+        <v>440882</v>
       </c>
       <c r="R126" t="n">
-        <v>6762461</v>
+        <v>6762435</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13695,9 +13695,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13712,22 +13722,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127273828</v>
+        <v>127275968</v>
       </c>
       <c r="B127" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13735,37 +13745,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>440882</v>
+        <v>440723</v>
       </c>
       <c r="R127" t="n">
-        <v>6762435</v>
+        <v>6762648</v>
       </c>
       <c r="S127" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13794,7 +13804,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13804,7 +13814,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13819,22 +13829,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127275968</v>
+        <v>127283135</v>
       </c>
       <c r="B128" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13842,34 +13852,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>440723</v>
+        <v>440456</v>
       </c>
       <c r="R128" t="n">
-        <v>6762648</v>
+        <v>6762461</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13899,19 +13909,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13926,12 +13926,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -14050,7 +14050,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127274657</v>
+        <v>127282932</v>
       </c>
       <c r="B130" t="n">
         <v>79018</v>
@@ -14081,14 +14081,14 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>440689</v>
+        <v>440427</v>
       </c>
       <c r="R130" t="n">
-        <v>6762214</v>
+        <v>6762470</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14118,24 +14118,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14150,19 +14135,19 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127283117</v>
+        <v>127276216</v>
       </c>
       <c r="B131" t="n">
         <v>79018</v>
@@ -14193,11 +14178,11 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>440863</v>
+        <v>440657</v>
       </c>
       <c r="R131" t="n">
         <v>6762603</v>
@@ -14230,9 +14215,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14247,22 +14242,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127273051</v>
+        <v>127276148</v>
       </c>
       <c r="B132" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14270,37 +14265,42 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>440681</v>
+        <v>440657</v>
       </c>
       <c r="R132" t="n">
-        <v>6762197</v>
+        <v>6762603</v>
       </c>
       <c r="S132" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14354,22 +14354,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127282932</v>
+        <v>127272305</v>
       </c>
       <c r="B133" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14377,34 +14377,39 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>440427</v>
+        <v>440675</v>
       </c>
       <c r="R133" t="n">
-        <v>6762470</v>
+        <v>6762165</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14434,9 +14439,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Diameter ca 4 till 5 cm</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14451,22 +14471,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127282912</v>
+        <v>127271765</v>
       </c>
       <c r="B134" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14474,34 +14494,39 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>440936</v>
+        <v>440627</v>
       </c>
       <c r="R134" t="n">
-        <v>6762564</v>
+        <v>6762119</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14531,9 +14556,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Miljöbild för området</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14548,22 +14588,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127282926</v>
+        <v>127276450</v>
       </c>
       <c r="B135" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14571,34 +14611,39 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>440497</v>
+        <v>440582</v>
       </c>
       <c r="R135" t="n">
-        <v>6762331</v>
+        <v>6762684</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14628,9 +14673,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14645,44 +14700,44 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127283130</v>
+        <v>127283108</v>
       </c>
       <c r="B136" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14692,10 +14747,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>440697</v>
+        <v>440442</v>
       </c>
       <c r="R136" t="n">
-        <v>6762237</v>
+        <v>6762471</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14754,45 +14809,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127276216</v>
+        <v>127282895</v>
       </c>
       <c r="B137" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>440657</v>
+        <v>440382</v>
       </c>
       <c r="R137" t="n">
-        <v>6762603</v>
+        <v>6762379</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14822,19 +14877,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14849,22 +14894,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127273488</v>
+        <v>127283109</v>
       </c>
       <c r="B138" t="n">
-        <v>79018</v>
+        <v>79019</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14872,16 +14917,16 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -14892,14 +14937,14 @@
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>440721</v>
+        <v>440875</v>
       </c>
       <c r="R138" t="n">
-        <v>6761996</v>
+        <v>6762453</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14929,19 +14974,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14956,22 +14991,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127276148</v>
+        <v>127274657</v>
       </c>
       <c r="B139" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14979,39 +15014,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>440657</v>
+        <v>440689</v>
       </c>
       <c r="R139" t="n">
-        <v>6762603</v>
+        <v>6762214</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15043,7 +15073,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15053,7 +15083,12 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15080,10 +15115,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127272305</v>
+        <v>127283117</v>
       </c>
       <c r="B140" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15091,39 +15126,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>440675</v>
+        <v>440863</v>
       </c>
       <c r="R140" t="n">
-        <v>6762165</v>
+        <v>6762603</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15153,24 +15183,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Diameter ca 4 till 5 cm</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15185,22 +15200,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127271765</v>
+        <v>127273051</v>
       </c>
       <c r="B141" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15208,42 +15223,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>440627</v>
+        <v>440681</v>
       </c>
       <c r="R141" t="n">
-        <v>6762119</v>
+        <v>6762197</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15272,7 +15282,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15282,12 +15292,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Miljöbild för området</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15302,22 +15307,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127276450</v>
+        <v>127282912</v>
       </c>
       <c r="B142" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15325,39 +15330,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>440582</v>
+        <v>440936</v>
       </c>
       <c r="R142" t="n">
-        <v>6762684</v>
+        <v>6762564</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15387,19 +15387,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15414,57 +15404,57 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127283108</v>
+        <v>127282926</v>
       </c>
       <c r="B143" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>440442</v>
+        <v>440497</v>
       </c>
       <c r="R143" t="n">
-        <v>6762471</v>
+        <v>6762331</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15511,57 +15501,57 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127282895</v>
+        <v>127283130</v>
       </c>
       <c r="B144" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>440382</v>
+        <v>440697</v>
       </c>
       <c r="R144" t="n">
-        <v>6762379</v>
+        <v>6762237</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15608,22 +15598,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127283109</v>
+        <v>127273488</v>
       </c>
       <c r="B145" t="n">
-        <v>79019</v>
+        <v>79018</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15631,16 +15621,16 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -15651,14 +15641,14 @@
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>440875</v>
+        <v>440721</v>
       </c>
       <c r="R145" t="n">
-        <v>6762453</v>
+        <v>6761996</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15688,9 +15678,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15705,19 +15705,19 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127274917</v>
+        <v>127283119</v>
       </c>
       <c r="B146" t="n">
         <v>79018</v>
@@ -15748,17 +15748,17 @@
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>440752</v>
+        <v>440881</v>
       </c>
       <c r="R146" t="n">
-        <v>6762337</v>
+        <v>6762591</v>
       </c>
       <c r="S146" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15785,19 +15785,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15812,19 +15802,19 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127283119</v>
+        <v>127273932</v>
       </c>
       <c r="B147" t="n">
         <v>79018</v>
@@ -15855,17 +15845,17 @@
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>440881</v>
+        <v>440913</v>
       </c>
       <c r="R147" t="n">
-        <v>6762591</v>
+        <v>6762466</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15892,9 +15882,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15909,60 +15909,60 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127272858</v>
+        <v>127283142</v>
       </c>
       <c r="B148" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>440609</v>
+        <v>440744</v>
       </c>
       <c r="R148" t="n">
-        <v>6762190</v>
+        <v>6762615</v>
       </c>
       <c r="S148" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15989,19 +15989,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16016,19 +16006,19 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127273038</v>
+        <v>127274917</v>
       </c>
       <c r="B149" t="n">
         <v>79018</v>
@@ -16059,17 +16049,17 @@
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>440688</v>
+        <v>440752</v>
       </c>
       <c r="R149" t="n">
-        <v>6762199</v>
+        <v>6762337</v>
       </c>
       <c r="S149" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16098,7 +16088,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16108,7 +16098,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16123,19 +16113,19 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127274822</v>
+        <v>127272858</v>
       </c>
       <c r="B150" t="n">
         <v>79018</v>
@@ -16166,17 +16156,17 @@
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>440760</v>
+        <v>440609</v>
       </c>
       <c r="R150" t="n">
-        <v>6762313</v>
+        <v>6762190</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16205,7 +16195,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16215,7 +16205,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16230,19 +16220,19 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127275416</v>
+        <v>127273038</v>
       </c>
       <c r="B151" t="n">
         <v>79018</v>
@@ -16277,10 +16267,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>440816</v>
+        <v>440688</v>
       </c>
       <c r="R151" t="n">
-        <v>6762475</v>
+        <v>6762199</v>
       </c>
       <c r="S151" t="n">
         <v>9</v>
@@ -16312,7 +16302,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16322,7 +16312,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16349,7 +16339,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127273932</v>
+        <v>127274822</v>
       </c>
       <c r="B152" t="n">
         <v>79018</v>
@@ -16380,17 +16370,17 @@
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>440913</v>
+        <v>440760</v>
       </c>
       <c r="R152" t="n">
-        <v>6762466</v>
+        <v>6762313</v>
       </c>
       <c r="S152" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16419,7 +16409,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16429,7 +16419,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16444,60 +16434,60 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127283142</v>
+        <v>127275416</v>
       </c>
       <c r="B153" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>440744</v>
+        <v>440816</v>
       </c>
       <c r="R153" t="n">
-        <v>6762615</v>
+        <v>6762475</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16524,9 +16514,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16541,22 +16541,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127272237</v>
+        <v>127282904</v>
       </c>
       <c r="B154" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16564,39 +16564,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>440675</v>
+        <v>440776</v>
       </c>
       <c r="R154" t="n">
-        <v>6762165</v>
+        <v>6762632</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16626,19 +16621,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16653,19 +16638,19 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127282904</v>
+        <v>127282914</v>
       </c>
       <c r="B155" t="n">
         <v>79018</v>
@@ -16700,10 +16685,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>440776</v>
+        <v>440924</v>
       </c>
       <c r="R155" t="n">
-        <v>6762632</v>
+        <v>6762509</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16762,10 +16747,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127282914</v>
+        <v>127283105</v>
       </c>
       <c r="B156" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16773,34 +16758,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>440924</v>
+        <v>440909</v>
       </c>
       <c r="R156" t="n">
-        <v>6762509</v>
+        <v>6762467</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16847,22 +16832,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127283105</v>
+        <v>127274354</v>
       </c>
       <c r="B157" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16870,34 +16855,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>440909</v>
+        <v>440686</v>
       </c>
       <c r="R157" t="n">
-        <v>6762467</v>
+        <v>6762176</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16927,9 +16912,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16944,19 +16939,19 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127274354</v>
+        <v>127272746</v>
       </c>
       <c r="B158" t="n">
         <v>79018</v>
@@ -16987,17 +16982,17 @@
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>440686</v>
+        <v>440503</v>
       </c>
       <c r="R158" t="n">
-        <v>6762176</v>
+        <v>6762308</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17026,7 +17021,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17036,7 +17031,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17051,22 +17046,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127272746</v>
+        <v>127272237</v>
       </c>
       <c r="B159" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17074,37 +17069,42 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>440503</v>
+        <v>440675</v>
       </c>
       <c r="R159" t="n">
-        <v>6762308</v>
+        <v>6762165</v>
       </c>
       <c r="S159" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17143,7 +17143,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17158,22 +17158,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127274348</v>
+        <v>127275098</v>
       </c>
       <c r="B160" t="n">
-        <v>57658</v>
+        <v>57661</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17181,16 +17181,16 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -17210,10 +17210,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>440686</v>
+        <v>440679</v>
       </c>
       <c r="R160" t="n">
-        <v>6762176</v>
+        <v>6762388</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17379,7 +17379,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127276426</v>
+        <v>127282902</v>
       </c>
       <c r="B162" t="n">
         <v>79018</v>
@@ -17410,14 +17410,14 @@
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>440582</v>
+        <v>440760</v>
       </c>
       <c r="R162" t="n">
-        <v>6762684</v>
+        <v>6762569</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17447,19 +17447,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17474,19 +17464,19 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127275877</v>
+        <v>127276426</v>
       </c>
       <c r="B163" t="n">
         <v>79018</v>
@@ -17521,10 +17511,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>440732</v>
+        <v>440582</v>
       </c>
       <c r="R163" t="n">
-        <v>6762635</v>
+        <v>6762684</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17593,7 +17583,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127273900</v>
+        <v>127275877</v>
       </c>
       <c r="B164" t="n">
         <v>79018</v>
@@ -17624,17 +17614,17 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>440903</v>
+        <v>440732</v>
       </c>
       <c r="R164" t="n">
-        <v>6762450</v>
+        <v>6762635</v>
       </c>
       <c r="S164" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -17663,7 +17653,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17673,7 +17663,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17688,19 +17678,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127282902</v>
+        <v>127273900</v>
       </c>
       <c r="B165" t="n">
         <v>79018</v>
@@ -17731,17 +17721,17 @@
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>440760</v>
+        <v>440903</v>
       </c>
       <c r="R165" t="n">
-        <v>6762569</v>
+        <v>6762450</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -17768,9 +17758,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17785,12 +17785,12 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
@@ -18001,10 +18001,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127275098</v>
+        <v>127274348</v>
       </c>
       <c r="B168" t="n">
-        <v>57661</v>
+        <v>57658</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18012,16 +18012,16 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -18041,10 +18041,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>440679</v>
+        <v>440686</v>
       </c>
       <c r="R168" t="n">
-        <v>6762388</v>
+        <v>6762176</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18113,7 +18113,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127273853</v>
+        <v>127270744</v>
       </c>
       <c r="B169" t="n">
         <v>79018</v>
@@ -18144,17 +18144,17 @@
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>440887</v>
+        <v>440351</v>
       </c>
       <c r="R169" t="n">
-        <v>6762439</v>
+        <v>6762480</v>
       </c>
       <c r="S169" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18208,19 +18208,19 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127270744</v>
+        <v>127283128</v>
       </c>
       <c r="B170" t="n">
         <v>79018</v>
@@ -18251,14 +18251,14 @@
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>440351</v>
+        <v>440822</v>
       </c>
       <c r="R170" t="n">
-        <v>6762480</v>
+        <v>6762415</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18288,19 +18288,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18315,19 +18305,19 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127275337</v>
+        <v>127274114</v>
       </c>
       <c r="B171" t="n">
         <v>79018</v>
@@ -18358,17 +18348,17 @@
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>440855</v>
+        <v>440711</v>
       </c>
       <c r="R171" t="n">
-        <v>6762513</v>
+        <v>6762111</v>
       </c>
       <c r="S171" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18397,7 +18387,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18407,7 +18397,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18422,19 +18412,19 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127282927</v>
+        <v>127283134</v>
       </c>
       <c r="B172" t="n">
         <v>79018</v>
@@ -18465,14 +18455,14 @@
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>440488</v>
+        <v>440487</v>
       </c>
       <c r="R172" t="n">
-        <v>6762419</v>
+        <v>6762321</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18519,19 +18509,19 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127283128</v>
+        <v>127283133</v>
       </c>
       <c r="B173" t="n">
         <v>79018</v>
@@ -18566,10 +18556,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>440822</v>
+        <v>440598</v>
       </c>
       <c r="R173" t="n">
-        <v>6762415</v>
+        <v>6762206</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18628,7 +18618,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127274114</v>
+        <v>127273853</v>
       </c>
       <c r="B174" t="n">
         <v>79018</v>
@@ -18659,17 +18649,17 @@
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>440711</v>
+        <v>440887</v>
       </c>
       <c r="R174" t="n">
-        <v>6762111</v>
+        <v>6762439</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -18698,7 +18688,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -18708,7 +18698,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18723,19 +18713,19 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127283115</v>
+        <v>127275337</v>
       </c>
       <c r="B175" t="n">
         <v>79018</v>
@@ -18766,17 +18756,17 @@
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>440803</v>
+        <v>440855</v>
       </c>
       <c r="R175" t="n">
-        <v>6762557</v>
+        <v>6762513</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -18803,9 +18793,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18820,19 +18820,19 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127283134</v>
+        <v>127282927</v>
       </c>
       <c r="B176" t="n">
         <v>79018</v>
@@ -18863,14 +18863,14 @@
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>440487</v>
+        <v>440488</v>
       </c>
       <c r="R176" t="n">
-        <v>6762321</v>
+        <v>6762419</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18917,19 +18917,19 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127283133</v>
+        <v>127283115</v>
       </c>
       <c r="B177" t="n">
         <v>79018</v>
@@ -18964,10 +18964,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>440598</v>
+        <v>440803</v>
       </c>
       <c r="R177" t="n">
-        <v>6762206</v>
+        <v>6762557</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19357,7 +19357,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127283127</v>
+        <v>127282906</v>
       </c>
       <c r="B181" t="n">
         <v>79018</v>
@@ -19388,14 +19388,14 @@
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>440843</v>
+        <v>440782</v>
       </c>
       <c r="R181" t="n">
-        <v>6762431</v>
+        <v>6762562</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19442,19 +19442,19 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127283116</v>
+        <v>127282925</v>
       </c>
       <c r="B182" t="n">
         <v>79018</v>
@@ -19485,14 +19485,14 @@
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>440823</v>
+        <v>440619</v>
       </c>
       <c r="R182" t="n">
-        <v>6762604</v>
+        <v>6762184</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19539,19 +19539,19 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127282906</v>
+        <v>127283127</v>
       </c>
       <c r="B183" t="n">
         <v>79018</v>
@@ -19582,14 +19582,14 @@
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>440782</v>
+        <v>440843</v>
       </c>
       <c r="R183" t="n">
-        <v>6762562</v>
+        <v>6762431</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19636,19 +19636,19 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127275778</v>
+        <v>127283116</v>
       </c>
       <c r="B184" t="n">
         <v>79018</v>
@@ -19679,17 +19679,17 @@
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>440761</v>
+        <v>440823</v>
       </c>
       <c r="R184" t="n">
-        <v>6762597</v>
+        <v>6762604</v>
       </c>
       <c r="S184" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19716,19 +19716,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>15:06</t>
-        </is>
-      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>15:06</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19743,19 +19733,19 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127282925</v>
+        <v>127275778</v>
       </c>
       <c r="B185" t="n">
         <v>79018</v>
@@ -19786,17 +19776,17 @@
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>440619</v>
+        <v>440761</v>
       </c>
       <c r="R185" t="n">
-        <v>6762184</v>
+        <v>6762597</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -19823,9 +19813,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19840,12 +19840,12 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
@@ -20163,7 +20163,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127283138</v>
+        <v>127282907</v>
       </c>
       <c r="B189" t="n">
         <v>79018</v>
@@ -20194,14 +20194,14 @@
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>440335</v>
+        <v>440793</v>
       </c>
       <c r="R189" t="n">
-        <v>6762400</v>
+        <v>6762525</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20248,19 +20248,19 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127282907</v>
+        <v>127283138</v>
       </c>
       <c r="B190" t="n">
         <v>79018</v>
@@ -20291,14 +20291,14 @@
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>440793</v>
+        <v>440335</v>
       </c>
       <c r="R190" t="n">
-        <v>6762525</v>
+        <v>6762400</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20345,12 +20345,12 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
@@ -20551,48 +20551,53 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127276155</v>
+        <v>127274877</v>
       </c>
       <c r="B193" t="n">
-        <v>8450</v>
+        <v>57821</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>440657</v>
+        <v>440752</v>
       </c>
       <c r="R193" t="n">
-        <v>6762603</v>
+        <v>6762337</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -20621,7 +20626,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -20631,7 +20636,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20658,53 +20663,48 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127274877</v>
+        <v>127276155</v>
       </c>
       <c r="B194" t="n">
-        <v>57821</v>
+        <v>8450</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>440752</v>
+        <v>440657</v>
       </c>
       <c r="R194" t="n">
-        <v>6762337</v>
+        <v>6762603</v>
       </c>
       <c r="S194" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -20743,7 +20743,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20877,7 +20877,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127275350</v>
+        <v>127283124</v>
       </c>
       <c r="B196" t="n">
         <v>79018</v>
@@ -20908,17 +20908,17 @@
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>440851</v>
+        <v>440965</v>
       </c>
       <c r="R196" t="n">
-        <v>6762513</v>
+        <v>6762540</v>
       </c>
       <c r="S196" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -20945,19 +20945,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20972,19 +20962,19 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127283124</v>
+        <v>127272147</v>
       </c>
       <c r="B197" t="n">
         <v>79018</v>
@@ -21015,17 +21005,17 @@
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>440965</v>
+        <v>440498</v>
       </c>
       <c r="R197" t="n">
-        <v>6762540</v>
+        <v>6762428</v>
       </c>
       <c r="S197" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -21052,9 +21042,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21069,22 +21069,22 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127272147</v>
+        <v>127274677</v>
       </c>
       <c r="B198" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21092,37 +21092,42 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>440498</v>
+        <v>440689</v>
       </c>
       <c r="R198" t="n">
-        <v>6762428</v>
+        <v>6762214</v>
       </c>
       <c r="S198" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -21151,7 +21156,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21161,7 +21166,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21176,62 +21181,57 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127274677</v>
+        <v>127283143</v>
       </c>
       <c r="B199" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>440689</v>
+        <v>440337</v>
       </c>
       <c r="R199" t="n">
-        <v>6762214</v>
+        <v>6762397</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21261,19 +21261,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z199" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21288,19 +21278,19 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127283143</v>
+        <v>127272174</v>
       </c>
       <c r="B200" t="n">
         <v>8450</v>
@@ -21331,14 +21321,14 @@
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>440337</v>
+        <v>440657</v>
       </c>
       <c r="R200" t="n">
-        <v>6762397</v>
+        <v>6762157</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21368,9 +21358,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21385,60 +21385,60 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127272174</v>
+        <v>127275350</v>
       </c>
       <c r="B201" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>440657</v>
+        <v>440851</v>
       </c>
       <c r="R201" t="n">
-        <v>6762157</v>
+        <v>6762513</v>
       </c>
       <c r="S201" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21477,7 +21477,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21492,19 +21492,19 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127275348</v>
+        <v>127282910</v>
       </c>
       <c r="B202" t="n">
         <v>79018</v>
@@ -21535,14 +21535,14 @@
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>440677</v>
+        <v>440807</v>
       </c>
       <c r="R202" t="n">
-        <v>6762469</v>
+        <v>6762574</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21572,19 +21572,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21599,19 +21589,19 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127282910</v>
+        <v>127272958</v>
       </c>
       <c r="B203" t="n">
         <v>79018</v>
@@ -21642,17 +21632,17 @@
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>440807</v>
+        <v>440619</v>
       </c>
       <c r="R203" t="n">
-        <v>6762574</v>
+        <v>6762170</v>
       </c>
       <c r="S203" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -21679,9 +21669,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21696,19 +21696,19 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127271972</v>
+        <v>127282897</v>
       </c>
       <c r="B204" t="n">
         <v>79018</v>
@@ -21739,17 +21739,17 @@
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>440460</v>
+        <v>440613</v>
       </c>
       <c r="R204" t="n">
-        <v>6762457</v>
+        <v>6762197</v>
       </c>
       <c r="S204" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -21776,24 +21776,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>På Gran</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21808,19 +21793,19 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>127272958</v>
+        <v>127282920</v>
       </c>
       <c r="B205" t="n">
         <v>79018</v>
@@ -21851,17 +21836,17 @@
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>440619</v>
+        <v>440696</v>
       </c>
       <c r="R205" t="n">
-        <v>6762170</v>
+        <v>6762239</v>
       </c>
       <c r="S205" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -21888,19 +21873,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -21915,19 +21890,19 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127283114</v>
+        <v>127275348</v>
       </c>
       <c r="B206" t="n">
         <v>79018</v>
@@ -21958,14 +21933,14 @@
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>440806</v>
+        <v>440677</v>
       </c>
       <c r="R206" t="n">
-        <v>6762533</v>
+        <v>6762469</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21995,9 +21970,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22012,19 +21997,19 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127282897</v>
+        <v>127271972</v>
       </c>
       <c r="B207" t="n">
         <v>79018</v>
@@ -22055,17 +22040,17 @@
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>440613</v>
+        <v>440460</v>
       </c>
       <c r="R207" t="n">
-        <v>6762197</v>
+        <v>6762457</v>
       </c>
       <c r="S207" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -22092,9 +22077,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>På Gran</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22109,19 +22109,19 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127282920</v>
+        <v>127283114</v>
       </c>
       <c r="B208" t="n">
         <v>79018</v>
@@ -22152,14 +22152,14 @@
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>440696</v>
+        <v>440806</v>
       </c>
       <c r="R208" t="n">
-        <v>6762239</v>
+        <v>6762533</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22206,12 +22206,12 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
@@ -22616,7 +22616,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127272352</v>
+        <v>127273057</v>
       </c>
       <c r="B213" t="n">
         <v>79018</v>
@@ -22647,17 +22647,17 @@
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>440685</v>
+        <v>440681</v>
       </c>
       <c r="R213" t="n">
-        <v>6762109</v>
+        <v>6762195</v>
       </c>
       <c r="S213" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -22696,7 +22696,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -22711,22 +22711,22 @@
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127273790</v>
+        <v>127283104</v>
       </c>
       <c r="B214" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -22734,37 +22734,37 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>440854</v>
+        <v>440766</v>
       </c>
       <c r="R214" t="n">
-        <v>6762427</v>
+        <v>6762565</v>
       </c>
       <c r="S214" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -22791,19 +22791,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z214" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA214" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB214" t="inlineStr">
-        <is>
-          <t>13:15</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -22818,19 +22808,19 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127273057</v>
+        <v>127272352</v>
       </c>
       <c r="B215" t="n">
         <v>79018</v>
@@ -22861,17 +22851,17 @@
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>440681</v>
+        <v>440685</v>
       </c>
       <c r="R215" t="n">
-        <v>6762195</v>
+        <v>6762109</v>
       </c>
       <c r="S215" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -22900,7 +22890,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -22910,7 +22900,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -22925,22 +22915,22 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127283104</v>
+        <v>127273790</v>
       </c>
       <c r="B216" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22948,37 +22938,37 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>440766</v>
+        <v>440854</v>
       </c>
       <c r="R216" t="n">
-        <v>6762565</v>
+        <v>6762427</v>
       </c>
       <c r="S216" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -23005,9 +22995,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23022,12 +23022,12 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
@@ -23146,10 +23146,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127283106</v>
+        <v>127282898</v>
       </c>
       <c r="B218" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23157,34 +23157,34 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>440504</v>
+        <v>440741</v>
       </c>
       <c r="R218" t="n">
-        <v>6762388</v>
+        <v>6762609</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23231,19 +23231,19 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127282898</v>
+        <v>127282915</v>
       </c>
       <c r="B219" t="n">
         <v>79018</v>
@@ -23278,10 +23278,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>440741</v>
+        <v>440946</v>
       </c>
       <c r="R219" t="n">
-        <v>6762609</v>
+        <v>6762514</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23340,7 +23340,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127283122</v>
+        <v>127282899</v>
       </c>
       <c r="B220" t="n">
         <v>79018</v>
@@ -23371,14 +23371,14 @@
       <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>440912</v>
+        <v>440763</v>
       </c>
       <c r="R220" t="n">
-        <v>6762579</v>
+        <v>6762529</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23425,22 +23425,22 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127282915</v>
+        <v>127283100</v>
       </c>
       <c r="B221" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23448,34 +23448,34 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>440946</v>
+        <v>440686</v>
       </c>
       <c r="R221" t="n">
-        <v>6762514</v>
+        <v>6762630</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23522,22 +23522,22 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127275040</v>
+        <v>127283141</v>
       </c>
       <c r="B222" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23545,34 +23545,34 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>440745</v>
+        <v>440651</v>
       </c>
       <c r="R222" t="n">
-        <v>6762369</v>
+        <v>6762611</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23602,24 +23602,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z222" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA222" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB222" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -23634,19 +23619,19 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127282899</v>
+        <v>127283122</v>
       </c>
       <c r="B223" t="n">
         <v>79018</v>
@@ -23677,14 +23662,14 @@
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>440763</v>
+        <v>440912</v>
       </c>
       <c r="R223" t="n">
-        <v>6762529</v>
+        <v>6762579</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23731,22 +23716,22 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127283100</v>
+        <v>127275040</v>
       </c>
       <c r="B224" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23754,34 +23739,34 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>440686</v>
+        <v>440745</v>
       </c>
       <c r="R224" t="n">
-        <v>6762630</v>
+        <v>6762369</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23811,9 +23796,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -23828,44 +23828,44 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127283141</v>
+        <v>127283107</v>
       </c>
       <c r="B225" t="n">
-        <v>78685</v>
+        <v>8450</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23875,10 +23875,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>440651</v>
+        <v>440636</v>
       </c>
       <c r="R225" t="n">
-        <v>6762611</v>
+        <v>6762585</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23937,32 +23937,32 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127283107</v>
+        <v>127283106</v>
       </c>
       <c r="B226" t="n">
-        <v>8450</v>
+        <v>78777</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23972,10 +23972,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>440636</v>
+        <v>440504</v>
       </c>
       <c r="R226" t="n">
-        <v>6762585</v>
+        <v>6762388</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24034,48 +24034,48 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127283126</v>
+        <v>127275544</v>
       </c>
       <c r="B227" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>440923</v>
+        <v>440811</v>
       </c>
       <c r="R227" t="n">
-        <v>6762482</v>
+        <v>6762474</v>
       </c>
       <c r="S227" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -24102,9 +24102,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA227" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24119,57 +24129,57 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127282918</v>
+        <v>127273585</v>
       </c>
       <c r="B228" t="n">
-        <v>79018</v>
+        <v>91688</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>440832</v>
+        <v>440742</v>
       </c>
       <c r="R228" t="n">
-        <v>6762387</v>
+        <v>6762004</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24199,9 +24209,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA228" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -24216,19 +24236,19 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127282917</v>
+        <v>127283126</v>
       </c>
       <c r="B229" t="n">
         <v>79018</v>
@@ -24259,14 +24279,14 @@
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>440919</v>
+        <v>440923</v>
       </c>
       <c r="R229" t="n">
-        <v>6762497</v>
+        <v>6762482</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24313,19 +24333,19 @@
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127283125</v>
+        <v>127282917</v>
       </c>
       <c r="B230" t="n">
         <v>79018</v>
@@ -24356,14 +24376,14 @@
       <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>440989</v>
+        <v>440919</v>
       </c>
       <c r="R230" t="n">
-        <v>6762519</v>
+        <v>6762497</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24410,19 +24430,19 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127273660</v>
+        <v>127275120</v>
       </c>
       <c r="B231" t="n">
         <v>79018</v>
@@ -24453,17 +24473,17 @@
       <c r="I231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>440742</v>
+        <v>440897</v>
       </c>
       <c r="R231" t="n">
-        <v>6762004</v>
+        <v>6762548</v>
       </c>
       <c r="S231" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -24492,7 +24512,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -24502,7 +24522,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24517,19 +24537,19 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127275120</v>
+        <v>127282918</v>
       </c>
       <c r="B232" t="n">
         <v>79018</v>
@@ -24560,17 +24580,17 @@
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>440897</v>
+        <v>440832</v>
       </c>
       <c r="R232" t="n">
-        <v>6762548</v>
+        <v>6762387</v>
       </c>
       <c r="S232" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -24597,19 +24617,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z232" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB232" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24624,60 +24634,60 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127275544</v>
+        <v>127283125</v>
       </c>
       <c r="B233" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>440811</v>
+        <v>440989</v>
       </c>
       <c r="R233" t="n">
-        <v>6762474</v>
+        <v>6762519</v>
       </c>
       <c r="S233" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -24704,19 +24714,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z233" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB233" t="inlineStr">
-        <is>
-          <t>14:44</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -24731,44 +24731,44 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>127273585</v>
+        <v>127273660</v>
       </c>
       <c r="B234" t="n">
-        <v>91688</v>
+        <v>79018</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -24850,7 +24850,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>127283123</v>
+        <v>127282930</v>
       </c>
       <c r="B235" t="n">
         <v>79018</v>
@@ -24881,14 +24881,14 @@
       <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>440917</v>
+        <v>440417</v>
       </c>
       <c r="R235" t="n">
-        <v>6762578</v>
+        <v>6762463</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24935,19 +24935,19 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127282930</v>
+        <v>127282933</v>
       </c>
       <c r="B236" t="n">
         <v>79018</v>
@@ -24982,10 +24982,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>440417</v>
+        <v>440395</v>
       </c>
       <c r="R236" t="n">
-        <v>6762463</v>
+        <v>6762359</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -25044,7 +25044,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127271487</v>
+        <v>127273778</v>
       </c>
       <c r="B237" t="n">
         <v>79018</v>
@@ -25079,10 +25079,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>440596</v>
+        <v>440734</v>
       </c>
       <c r="R237" t="n">
-        <v>6762126</v>
+        <v>6762076</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25151,7 +25151,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>127283132</v>
+        <v>127282911</v>
       </c>
       <c r="B238" t="n">
         <v>79018</v>
@@ -25182,14 +25182,14 @@
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>440679</v>
+        <v>440874</v>
       </c>
       <c r="R238" t="n">
-        <v>6762203</v>
+        <v>6762606</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25236,19 +25236,19 @@
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>127282933</v>
+        <v>127271487</v>
       </c>
       <c r="B239" t="n">
         <v>79018</v>
@@ -25279,14 +25279,14 @@
       <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>440395</v>
+        <v>440596</v>
       </c>
       <c r="R239" t="n">
-        <v>6762359</v>
+        <v>6762126</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25316,9 +25316,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA239" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -25333,19 +25343,19 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127273778</v>
+        <v>127283132</v>
       </c>
       <c r="B240" t="n">
         <v>79018</v>
@@ -25376,14 +25386,14 @@
       <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>440734</v>
+        <v>440679</v>
       </c>
       <c r="R240" t="n">
-        <v>6762076</v>
+        <v>6762203</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25413,19 +25423,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z240" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA240" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB240" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -25440,19 +25440,19 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>127282911</v>
+        <v>127271764</v>
       </c>
       <c r="B241" t="n">
         <v>79018</v>
@@ -25483,17 +25483,17 @@
       <c r="I241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>440874</v>
+        <v>440418</v>
       </c>
       <c r="R241" t="n">
-        <v>6762606</v>
+        <v>6762449</v>
       </c>
       <c r="S241" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -25520,9 +25520,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB241" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -25537,19 +25547,19 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>127271764</v>
+        <v>127283123</v>
       </c>
       <c r="B242" t="n">
         <v>79018</v>
@@ -25580,17 +25590,17 @@
       <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>440418</v>
+        <v>440917</v>
       </c>
       <c r="R242" t="n">
-        <v>6762449</v>
+        <v>6762578</v>
       </c>
       <c r="S242" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -25617,19 +25627,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z242" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA242" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB242" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -25644,12 +25644,12 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
@@ -26181,7 +26181,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>127272935</v>
+        <v>127272422</v>
       </c>
       <c r="B248" t="n">
         <v>79018</v>
@@ -26212,17 +26212,17 @@
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>440613</v>
+        <v>440682</v>
       </c>
       <c r="R248" t="n">
-        <v>6762174</v>
+        <v>6762093</v>
       </c>
       <c r="S248" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -26261,7 +26261,12 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>Garnlav på äldre tall, sannoligt äldre än 200 år</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26276,19 +26281,19 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>127272422</v>
+        <v>127271817</v>
       </c>
       <c r="B249" t="n">
         <v>79018</v>
@@ -26323,10 +26328,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>440682</v>
+        <v>440623</v>
       </c>
       <c r="R249" t="n">
-        <v>6762093</v>
+        <v>6762126</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -26369,11 +26374,6 @@
       <c r="AB249" t="inlineStr">
         <is>
           <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>Garnlav på äldre tall, sannoligt äldre än 200 år</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -26400,7 +26400,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>127270746</v>
+        <v>127272935</v>
       </c>
       <c r="B250" t="n">
         <v>79018</v>
@@ -26435,10 +26435,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>440308</v>
+        <v>440613</v>
       </c>
       <c r="R250" t="n">
-        <v>6762456</v>
+        <v>6762174</v>
       </c>
       <c r="S250" t="n">
         <v>9</v>
@@ -26470,7 +26470,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -26480,7 +26480,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -26507,7 +26507,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>127271817</v>
+        <v>127270746</v>
       </c>
       <c r="B251" t="n">
         <v>79018</v>
@@ -26538,17 +26538,17 @@
       <c r="I251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>440623</v>
+        <v>440308</v>
       </c>
       <c r="R251" t="n">
-        <v>6762126</v>
+        <v>6762456</v>
       </c>
       <c r="S251" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -26602,12 +26602,12 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
@@ -27052,7 +27052,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>127282928</v>
+        <v>127282916</v>
       </c>
       <c r="B256" t="n">
         <v>79018</v>
@@ -27087,10 +27087,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>440441</v>
+        <v>440930</v>
       </c>
       <c r="R256" t="n">
-        <v>6762452</v>
+        <v>6762495</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -27149,7 +27149,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>127282908</v>
+        <v>127274471</v>
       </c>
       <c r="B257" t="n">
         <v>79018</v>
@@ -27180,14 +27180,14 @@
       <c r="I257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>440801</v>
+        <v>440700</v>
       </c>
       <c r="R257" t="n">
-        <v>6762524</v>
+        <v>6762179</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -27217,9 +27217,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA257" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -27234,19 +27244,19 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>127271449</v>
+        <v>127282928</v>
       </c>
       <c r="B258" t="n">
         <v>79018</v>
@@ -27277,14 +27287,14 @@
       <c r="I258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>440580</v>
+        <v>440441</v>
       </c>
       <c r="R258" t="n">
-        <v>6762134</v>
+        <v>6762452</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -27314,19 +27324,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z258" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA258" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB258" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -27341,19 +27341,19 @@
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>127282916</v>
+        <v>127282908</v>
       </c>
       <c r="B259" t="n">
         <v>79018</v>
@@ -27388,10 +27388,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>440930</v>
+        <v>440801</v>
       </c>
       <c r="R259" t="n">
-        <v>6762495</v>
+        <v>6762524</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -27450,7 +27450,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127274471</v>
+        <v>127271449</v>
       </c>
       <c r="B260" t="n">
         <v>79018</v>
@@ -27485,10 +27485,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>440700</v>
+        <v>440580</v>
       </c>
       <c r="R260" t="n">
-        <v>6762179</v>
+        <v>6762134</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27654,45 +27654,45 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>127274680</v>
+        <v>127282923</v>
       </c>
       <c r="B262" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>440689</v>
+        <v>440658</v>
       </c>
       <c r="R262" t="n">
-        <v>6762214</v>
+        <v>6762202</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27722,19 +27722,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z262" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA262" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB262" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -27749,19 +27739,19 @@
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>127282905</v>
+        <v>127275346</v>
       </c>
       <c r="B263" t="n">
         <v>79018</v>
@@ -27792,17 +27782,17 @@
       <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>440780</v>
+        <v>440853</v>
       </c>
       <c r="R263" t="n">
-        <v>6762578</v>
+        <v>6762514</v>
       </c>
       <c r="S263" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -27829,9 +27819,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA263" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -27846,19 +27846,19 @@
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>127282934</v>
+        <v>127282921</v>
       </c>
       <c r="B264" t="n">
         <v>79018</v>
@@ -27893,10 +27893,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>440387</v>
+        <v>440680</v>
       </c>
       <c r="R264" t="n">
-        <v>6762369</v>
+        <v>6762218</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27955,32 +27955,32 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>127275330</v>
+        <v>127272941</v>
       </c>
       <c r="B265" t="n">
-        <v>79018</v>
+        <v>79042</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -27990,10 +27990,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>440868</v>
+        <v>440613</v>
       </c>
       <c r="R265" t="n">
-        <v>6762512</v>
+        <v>6762174</v>
       </c>
       <c r="S265" t="n">
         <v>9</v>
@@ -28025,7 +28025,7 @@
       </c>
       <c r="Z265" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
@@ -28035,7 +28035,7 @@
       </c>
       <c r="AB265" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -28062,7 +28062,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>127282923</v>
+        <v>127282934</v>
       </c>
       <c r="B266" t="n">
         <v>79018</v>
@@ -28097,10 +28097,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>440658</v>
+        <v>440387</v>
       </c>
       <c r="R266" t="n">
-        <v>6762202</v>
+        <v>6762369</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -28159,48 +28159,48 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>127275346</v>
+        <v>127274680</v>
       </c>
       <c r="B267" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>440853</v>
+        <v>440689</v>
       </c>
       <c r="R267" t="n">
-        <v>6762514</v>
+        <v>6762214</v>
       </c>
       <c r="S267" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
       </c>
       <c r="Z267" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
@@ -28239,7 +28239,7 @@
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -28254,19 +28254,19 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>127282921</v>
+        <v>127282905</v>
       </c>
       <c r="B268" t="n">
         <v>79018</v>
@@ -28301,10 +28301,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>440680</v>
+        <v>440780</v>
       </c>
       <c r="R268" t="n">
-        <v>6762218</v>
+        <v>6762578</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -28363,32 +28363,32 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>127272941</v>
+        <v>127275330</v>
       </c>
       <c r="B269" t="n">
-        <v>79042</v>
+        <v>79018</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -28398,10 +28398,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>440613</v>
+        <v>440868</v>
       </c>
       <c r="R269" t="n">
-        <v>6762174</v>
+        <v>6762512</v>
       </c>
       <c r="S269" t="n">
         <v>9</v>
@@ -28433,7 +28433,7 @@
       </c>
       <c r="Z269" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
@@ -28443,7 +28443,7 @@
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD269" t="b">

--- a/artfynd/A 29945-2025 artfynd.xlsx
+++ b/artfynd/A 29945-2025 artfynd.xlsx
@@ -11868,10 +11868,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127273727</v>
+        <v>127273473</v>
       </c>
       <c r="B109" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11879,34 +11879,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>440754</v>
+        <v>440721</v>
       </c>
       <c r="R109" t="n">
-        <v>6762035</v>
+        <v>6761996</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11975,7 +11980,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127282909</v>
+        <v>127273727</v>
       </c>
       <c r="B110" t="n">
         <v>79018</v>
@@ -12006,14 +12011,14 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>440797</v>
+        <v>440754</v>
       </c>
       <c r="R110" t="n">
-        <v>6762555</v>
+        <v>6762035</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12043,9 +12048,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12060,19 +12075,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127282922</v>
+        <v>127282909</v>
       </c>
       <c r="B111" t="n">
         <v>79018</v>
@@ -12107,10 +12122,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>440685</v>
+        <v>440797</v>
       </c>
       <c r="R111" t="n">
-        <v>6762213</v>
+        <v>6762555</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12169,10 +12184,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127282896</v>
+        <v>127282922</v>
       </c>
       <c r="B112" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12180,21 +12195,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12204,10 +12219,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>440416</v>
+        <v>440685</v>
       </c>
       <c r="R112" t="n">
-        <v>6762406</v>
+        <v>6762213</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12266,10 +12281,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127282903</v>
+        <v>127282896</v>
       </c>
       <c r="B113" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12277,21 +12292,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12301,10 +12316,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>440760</v>
+        <v>440416</v>
       </c>
       <c r="R113" t="n">
-        <v>6762626</v>
+        <v>6762406</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12363,7 +12378,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127274251</v>
+        <v>127282903</v>
       </c>
       <c r="B114" t="n">
         <v>79018</v>
@@ -12394,14 +12409,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>440687</v>
+        <v>440760</v>
       </c>
       <c r="R114" t="n">
-        <v>6762120</v>
+        <v>6762626</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12431,19 +12446,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12458,22 +12463,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127273473</v>
+        <v>127274251</v>
       </c>
       <c r="B115" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12481,39 +12486,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>440721</v>
+        <v>440687</v>
       </c>
       <c r="R115" t="n">
-        <v>6761996</v>
+        <v>6762120</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12689,32 +12689,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127274061</v>
+        <v>127273755</v>
       </c>
       <c r="B117" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12724,10 +12724,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>440706</v>
+        <v>440744</v>
       </c>
       <c r="R117" t="n">
-        <v>6762058</v>
+        <v>6762065</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12796,7 +12796,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127271820</v>
+        <v>127276304</v>
       </c>
       <c r="B118" t="n">
         <v>79018</v>
@@ -12827,17 +12827,17 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>440446</v>
+        <v>440642</v>
       </c>
       <c r="R118" t="n">
-        <v>6762469</v>
+        <v>6762606</v>
       </c>
       <c r="S118" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12876,7 +12876,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12891,19 +12891,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127273755</v>
+        <v>127275131</v>
       </c>
       <c r="B119" t="n">
         <v>79018</v>
@@ -12938,10 +12938,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>440744</v>
+        <v>440709</v>
       </c>
       <c r="R119" t="n">
-        <v>6762065</v>
+        <v>6762405</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13010,10 +13010,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127276304</v>
+        <v>127274057</v>
       </c>
       <c r="B120" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13021,34 +13021,39 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>440642</v>
+        <v>440706</v>
       </c>
       <c r="R120" t="n">
-        <v>6762606</v>
+        <v>6762058</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13080,7 +13085,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13090,7 +13095,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13117,10 +13122,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127275131</v>
+        <v>127283110</v>
       </c>
       <c r="B121" t="n">
-        <v>79018</v>
+        <v>79019</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13128,16 +13133,16 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -13148,14 +13153,14 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>440709</v>
+        <v>440835</v>
       </c>
       <c r="R121" t="n">
-        <v>6762405</v>
+        <v>6762564</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13185,19 +13190,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13212,22 +13207,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127274057</v>
+        <v>127271820</v>
       </c>
       <c r="B122" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13235,42 +13230,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>440706</v>
+        <v>440446</v>
       </c>
       <c r="R122" t="n">
-        <v>6762058</v>
+        <v>6762469</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13299,7 +13289,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13309,7 +13299,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13324,57 +13314,57 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127283110</v>
+        <v>127274061</v>
       </c>
       <c r="B123" t="n">
-        <v>79019</v>
+        <v>8450</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>440835</v>
+        <v>440706</v>
       </c>
       <c r="R123" t="n">
-        <v>6762564</v>
+        <v>6762058</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13404,9 +13394,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13421,12 +13421,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -17170,10 +17170,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127275098</v>
+        <v>127282900</v>
       </c>
       <c r="B160" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17181,39 +17181,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>440679</v>
+        <v>440757</v>
       </c>
       <c r="R160" t="n">
-        <v>6762388</v>
+        <v>6762544</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17243,19 +17238,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17270,19 +17255,19 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127282900</v>
+        <v>127282902</v>
       </c>
       <c r="B161" t="n">
         <v>79018</v>
@@ -17317,10 +17302,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>440757</v>
+        <v>440760</v>
       </c>
       <c r="R161" t="n">
-        <v>6762544</v>
+        <v>6762569</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17379,7 +17364,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127282902</v>
+        <v>127276426</v>
       </c>
       <c r="B162" t="n">
         <v>79018</v>
@@ -17410,14 +17395,14 @@
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>440760</v>
+        <v>440582</v>
       </c>
       <c r="R162" t="n">
-        <v>6762569</v>
+        <v>6762684</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17447,9 +17432,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17464,19 +17459,19 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127276426</v>
+        <v>127275877</v>
       </c>
       <c r="B163" t="n">
         <v>79018</v>
@@ -17511,10 +17506,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>440582</v>
+        <v>440732</v>
       </c>
       <c r="R163" t="n">
-        <v>6762684</v>
+        <v>6762635</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17583,7 +17578,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127275877</v>
+        <v>127273900</v>
       </c>
       <c r="B164" t="n">
         <v>79018</v>
@@ -17614,17 +17609,17 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>440732</v>
+        <v>440903</v>
       </c>
       <c r="R164" t="n">
-        <v>6762635</v>
+        <v>6762450</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -17653,7 +17648,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17663,7 +17658,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17678,19 +17673,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127273900</v>
+        <v>127283137</v>
       </c>
       <c r="B165" t="n">
         <v>79018</v>
@@ -17721,17 +17716,17 @@
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>440903</v>
+        <v>440354</v>
       </c>
       <c r="R165" t="n">
-        <v>6762450</v>
+        <v>6762415</v>
       </c>
       <c r="S165" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -17758,19 +17753,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>13:21</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17785,22 +17770,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127273086</v>
+        <v>127274348</v>
       </c>
       <c r="B166" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17808,37 +17793,42 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>440694</v>
+        <v>440686</v>
       </c>
       <c r="R166" t="n">
-        <v>6762204</v>
+        <v>6762176</v>
       </c>
       <c r="S166" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17867,7 +17857,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -17877,7 +17867,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17892,22 +17882,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127283137</v>
+        <v>127275098</v>
       </c>
       <c r="B167" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17915,34 +17905,39 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>440354</v>
+        <v>440679</v>
       </c>
       <c r="R167" t="n">
-        <v>6762415</v>
+        <v>6762388</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17972,9 +17967,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17989,22 +17994,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127274348</v>
+        <v>127273086</v>
       </c>
       <c r="B168" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18012,42 +18017,37 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>440686</v>
+        <v>440694</v>
       </c>
       <c r="R168" t="n">
-        <v>6762176</v>
+        <v>6762204</v>
       </c>
       <c r="S168" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -18086,7 +18086,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18101,12 +18101,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
@@ -18618,48 +18618,48 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127273853</v>
+        <v>127271802</v>
       </c>
       <c r="B174" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>440887</v>
+        <v>440627</v>
       </c>
       <c r="R174" t="n">
-        <v>6762439</v>
+        <v>6762119</v>
       </c>
       <c r="S174" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -18688,7 +18688,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -18698,7 +18698,12 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Rikligt med torrakor med spår efter Mindre Märgborre i området</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18713,57 +18718,62 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127275337</v>
+        <v>127271251</v>
       </c>
       <c r="B175" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>440855</v>
+        <v>440375</v>
       </c>
       <c r="R175" t="n">
-        <v>6762513</v>
+        <v>6762366</v>
       </c>
       <c r="S175" t="n">
         <v>9</v>
@@ -18795,7 +18805,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -18805,7 +18815,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18832,45 +18842,45 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127282927</v>
+        <v>127276271</v>
       </c>
       <c r="B176" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>440488</v>
+        <v>440642</v>
       </c>
       <c r="R176" t="n">
-        <v>6762419</v>
+        <v>6762606</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18900,9 +18910,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18917,19 +18937,19 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127283115</v>
+        <v>127273853</v>
       </c>
       <c r="B177" t="n">
         <v>79018</v>
@@ -18960,17 +18980,17 @@
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>440803</v>
+        <v>440887</v>
       </c>
       <c r="R177" t="n">
-        <v>6762557</v>
+        <v>6762439</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -18997,9 +19017,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19014,60 +19044,60 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127271802</v>
+        <v>127275337</v>
       </c>
       <c r="B178" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>440627</v>
+        <v>440855</v>
       </c>
       <c r="R178" t="n">
-        <v>6762119</v>
+        <v>6762513</v>
       </c>
       <c r="S178" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19096,7 +19126,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -19106,12 +19136,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Rikligt med torrakor med spår efter Mindre Märgborre i området</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19126,65 +19151,60 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127271251</v>
+        <v>127282927</v>
       </c>
       <c r="B179" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>440375</v>
+        <v>440488</v>
       </c>
       <c r="R179" t="n">
-        <v>6762366</v>
+        <v>6762419</v>
       </c>
       <c r="S179" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19211,19 +19231,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>10:53</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19238,57 +19248,57 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127276271</v>
+        <v>127283115</v>
       </c>
       <c r="B180" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>440642</v>
+        <v>440803</v>
       </c>
       <c r="R180" t="n">
-        <v>6762606</v>
+        <v>6762557</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19318,19 +19328,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19345,22 +19345,22 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127282906</v>
+        <v>127274154</v>
       </c>
       <c r="B181" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19368,37 +19368,42 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>440782</v>
+        <v>440946</v>
       </c>
       <c r="R181" t="n">
-        <v>6762562</v>
+        <v>6762537</v>
       </c>
       <c r="S181" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -19425,9 +19430,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19442,19 +19462,19 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127282925</v>
+        <v>127282906</v>
       </c>
       <c r="B182" t="n">
         <v>79018</v>
@@ -19489,10 +19509,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>440619</v>
+        <v>440782</v>
       </c>
       <c r="R182" t="n">
-        <v>6762184</v>
+        <v>6762562</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19551,7 +19571,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127283127</v>
+        <v>127282925</v>
       </c>
       <c r="B183" t="n">
         <v>79018</v>
@@ -19582,14 +19602,14 @@
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>440843</v>
+        <v>440619</v>
       </c>
       <c r="R183" t="n">
-        <v>6762431</v>
+        <v>6762184</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19636,19 +19656,19 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127283116</v>
+        <v>127283127</v>
       </c>
       <c r="B184" t="n">
         <v>79018</v>
@@ -19683,10 +19703,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>440823</v>
+        <v>440843</v>
       </c>
       <c r="R184" t="n">
-        <v>6762604</v>
+        <v>6762431</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19745,7 +19765,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127275778</v>
+        <v>127283116</v>
       </c>
       <c r="B185" t="n">
         <v>79018</v>
@@ -19776,17 +19796,17 @@
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>440761</v>
+        <v>440823</v>
       </c>
       <c r="R185" t="n">
-        <v>6762597</v>
+        <v>6762604</v>
       </c>
       <c r="S185" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -19813,19 +19833,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>15:06</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>15:06</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19840,22 +19850,22 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127274154</v>
+        <v>127275778</v>
       </c>
       <c r="B186" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19863,39 +19873,34 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>440946</v>
+        <v>440761</v>
       </c>
       <c r="R186" t="n">
-        <v>6762537</v>
+        <v>6762597</v>
       </c>
       <c r="S186" t="n">
         <v>9</v>
@@ -19927,7 +19932,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -19937,12 +19942,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20770,45 +20770,45 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127276018</v>
+        <v>127283143</v>
       </c>
       <c r="B195" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>440697</v>
+        <v>440337</v>
       </c>
       <c r="R195" t="n">
-        <v>6762625</v>
+        <v>6762397</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20838,19 +20838,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20865,57 +20855,57 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127283124</v>
+        <v>127272174</v>
       </c>
       <c r="B196" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>440965</v>
+        <v>440657</v>
       </c>
       <c r="R196" t="n">
-        <v>6762540</v>
+        <v>6762157</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20945,9 +20935,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20962,12 +20962,12 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
@@ -21081,10 +21081,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127274677</v>
+        <v>127276018</v>
       </c>
       <c r="B198" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21092,39 +21092,34 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>440689</v>
+        <v>440697</v>
       </c>
       <c r="R198" t="n">
-        <v>6762214</v>
+        <v>6762625</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21156,7 +21151,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21166,7 +21161,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21193,32 +21188,32 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127283143</v>
+        <v>127283124</v>
       </c>
       <c r="B199" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21228,10 +21223,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>440337</v>
+        <v>440965</v>
       </c>
       <c r="R199" t="n">
-        <v>6762397</v>
+        <v>6762540</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21290,48 +21285,48 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127272174</v>
+        <v>127275350</v>
       </c>
       <c r="B200" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>440657</v>
+        <v>440851</v>
       </c>
       <c r="R200" t="n">
-        <v>6762157</v>
+        <v>6762513</v>
       </c>
       <c r="S200" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -21360,7 +21355,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -21370,7 +21365,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21385,22 +21380,22 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127275350</v>
+        <v>127274677</v>
       </c>
       <c r="B201" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21408,37 +21403,42 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>440851</v>
+        <v>440689</v>
       </c>
       <c r="R201" t="n">
-        <v>6762513</v>
+        <v>6762214</v>
       </c>
       <c r="S201" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21477,7 +21477,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21492,12 +21492,12 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
@@ -24850,48 +24850,53 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>127282930</v>
+        <v>127275970</v>
       </c>
       <c r="B235" t="n">
-        <v>79018</v>
+        <v>5197</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>440417</v>
+        <v>440685</v>
       </c>
       <c r="R235" t="n">
-        <v>6762463</v>
+        <v>6762673</v>
       </c>
       <c r="S235" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -24918,9 +24923,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA235" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -24935,22 +24950,22 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127282933</v>
+        <v>127275615</v>
       </c>
       <c r="B236" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24958,37 +24973,42 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>440395</v>
+        <v>440778</v>
       </c>
       <c r="R236" t="n">
-        <v>6762359</v>
+        <v>6762552</v>
       </c>
       <c r="S236" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -25015,9 +25035,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA236" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -25032,19 +25062,19 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127273778</v>
+        <v>127282930</v>
       </c>
       <c r="B237" t="n">
         <v>79018</v>
@@ -25075,14 +25105,14 @@
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>440734</v>
+        <v>440417</v>
       </c>
       <c r="R237" t="n">
-        <v>6762076</v>
+        <v>6762463</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25112,19 +25142,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z237" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA237" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB237" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25139,19 +25159,19 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>127282911</v>
+        <v>127282933</v>
       </c>
       <c r="B238" t="n">
         <v>79018</v>
@@ -25186,10 +25206,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>440874</v>
+        <v>440395</v>
       </c>
       <c r="R238" t="n">
-        <v>6762606</v>
+        <v>6762359</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25248,7 +25268,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>127271487</v>
+        <v>127273778</v>
       </c>
       <c r="B239" t="n">
         <v>79018</v>
@@ -25283,10 +25303,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>440596</v>
+        <v>440734</v>
       </c>
       <c r="R239" t="n">
-        <v>6762126</v>
+        <v>6762076</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25355,7 +25375,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127283132</v>
+        <v>127282911</v>
       </c>
       <c r="B240" t="n">
         <v>79018</v>
@@ -25386,14 +25406,14 @@
       <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>440679</v>
+        <v>440874</v>
       </c>
       <c r="R240" t="n">
-        <v>6762203</v>
+        <v>6762606</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25440,19 +25460,19 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>127271764</v>
+        <v>127283123</v>
       </c>
       <c r="B241" t="n">
         <v>79018</v>
@@ -25483,17 +25503,17 @@
       <c r="I241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>440418</v>
+        <v>440917</v>
       </c>
       <c r="R241" t="n">
-        <v>6762449</v>
+        <v>6762578</v>
       </c>
       <c r="S241" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -25520,19 +25540,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z241" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB241" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -25547,19 +25557,19 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>127283123</v>
+        <v>127271487</v>
       </c>
       <c r="B242" t="n">
         <v>79018</v>
@@ -25590,14 +25600,14 @@
       <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>440917</v>
+        <v>440596</v>
       </c>
       <c r="R242" t="n">
-        <v>6762578</v>
+        <v>6762126</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25627,9 +25637,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA242" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -25644,22 +25664,22 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127275615</v>
+        <v>127283132</v>
       </c>
       <c r="B243" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25667,42 +25687,37 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>440778</v>
+        <v>440679</v>
       </c>
       <c r="R243" t="n">
-        <v>6762552</v>
+        <v>6762203</v>
       </c>
       <c r="S243" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -25729,19 +25744,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z243" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA243" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB243" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -25756,62 +25761,57 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>127275970</v>
+        <v>127271764</v>
       </c>
       <c r="B244" t="n">
-        <v>5197</v>
+        <v>79018</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P244" t="inlineStr">
         <is>
           <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>440685</v>
+        <v>440418</v>
       </c>
       <c r="R244" t="n">
-        <v>6762673</v>
+        <v>6762449</v>
       </c>
       <c r="S244" t="n">
         <v>9</v>
@@ -25843,7 +25843,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -25853,7 +25853,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD244" t="b">

--- a/artfynd/A 29945-2025 artfynd.xlsx
+++ b/artfynd/A 29945-2025 artfynd.xlsx
@@ -14254,10 +14254,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127276148</v>
+        <v>127274657</v>
       </c>
       <c r="B132" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14265,39 +14265,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>440657</v>
+        <v>440689</v>
       </c>
       <c r="R132" t="n">
-        <v>6762603</v>
+        <v>6762214</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14329,7 +14324,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14339,7 +14334,12 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14366,10 +14366,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127272305</v>
+        <v>127283117</v>
       </c>
       <c r="B133" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14377,39 +14377,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>440675</v>
+        <v>440863</v>
       </c>
       <c r="R133" t="n">
-        <v>6762165</v>
+        <v>6762603</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14439,24 +14434,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Diameter ca 4 till 5 cm</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14471,22 +14451,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127271765</v>
+        <v>127273051</v>
       </c>
       <c r="B134" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14494,42 +14474,37 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>440627</v>
+        <v>440681</v>
       </c>
       <c r="R134" t="n">
-        <v>6762119</v>
+        <v>6762197</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14558,7 +14533,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14568,12 +14543,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Miljöbild för området</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14588,22 +14558,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127276450</v>
+        <v>127282912</v>
       </c>
       <c r="B135" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14611,39 +14581,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>440582</v>
+        <v>440936</v>
       </c>
       <c r="R135" t="n">
-        <v>6762684</v>
+        <v>6762564</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14673,19 +14638,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14700,57 +14655,57 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127283108</v>
+        <v>127282926</v>
       </c>
       <c r="B136" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>440442</v>
+        <v>440497</v>
       </c>
       <c r="R136" t="n">
-        <v>6762471</v>
+        <v>6762331</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14797,57 +14752,57 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127282895</v>
+        <v>127283130</v>
       </c>
       <c r="B137" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>440382</v>
+        <v>440697</v>
       </c>
       <c r="R137" t="n">
-        <v>6762379</v>
+        <v>6762237</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14894,22 +14849,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127283109</v>
+        <v>127273488</v>
       </c>
       <c r="B138" t="n">
-        <v>79019</v>
+        <v>79018</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14917,16 +14872,16 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -14937,14 +14892,14 @@
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>440875</v>
+        <v>440721</v>
       </c>
       <c r="R138" t="n">
-        <v>6762453</v>
+        <v>6761996</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14974,9 +14929,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14991,22 +14956,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127274657</v>
+        <v>127276148</v>
       </c>
       <c r="B139" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15014,34 +14979,39 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>440689</v>
+        <v>440657</v>
       </c>
       <c r="R139" t="n">
-        <v>6762214</v>
+        <v>6762603</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15073,7 +15043,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15083,12 +15053,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15115,10 +15080,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127283117</v>
+        <v>127272305</v>
       </c>
       <c r="B140" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15126,34 +15091,39 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>440863</v>
+        <v>440675</v>
       </c>
       <c r="R140" t="n">
-        <v>6762603</v>
+        <v>6762165</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15183,9 +15153,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Diameter ca 4 till 5 cm</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15200,22 +15185,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127273051</v>
+        <v>127271765</v>
       </c>
       <c r="B141" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15223,37 +15208,42 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>440681</v>
+        <v>440627</v>
       </c>
       <c r="R141" t="n">
-        <v>6762197</v>
+        <v>6762119</v>
       </c>
       <c r="S141" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15282,7 +15272,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15292,7 +15282,12 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Miljöbild för området</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15307,22 +15302,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127282912</v>
+        <v>127276450</v>
       </c>
       <c r="B142" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15330,34 +15325,39 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>440936</v>
+        <v>440582</v>
       </c>
       <c r="R142" t="n">
-        <v>6762564</v>
+        <v>6762684</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15387,9 +15387,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15404,57 +15414,57 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127282926</v>
+        <v>127283108</v>
       </c>
       <c r="B143" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>440497</v>
+        <v>440442</v>
       </c>
       <c r="R143" t="n">
-        <v>6762331</v>
+        <v>6762471</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15501,57 +15511,57 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127283130</v>
+        <v>127282895</v>
       </c>
       <c r="B144" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>440697</v>
+        <v>440382</v>
       </c>
       <c r="R144" t="n">
-        <v>6762237</v>
+        <v>6762379</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15598,22 +15608,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127273488</v>
+        <v>127283109</v>
       </c>
       <c r="B145" t="n">
-        <v>79018</v>
+        <v>79019</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15621,16 +15631,16 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -15641,14 +15651,14 @@
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>440721</v>
+        <v>440875</v>
       </c>
       <c r="R145" t="n">
-        <v>6761996</v>
+        <v>6762453</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15678,19 +15688,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15705,12 +15705,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
@@ -17170,10 +17170,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127282900</v>
+        <v>127275098</v>
       </c>
       <c r="B160" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17181,34 +17181,39 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>440757</v>
+        <v>440679</v>
       </c>
       <c r="R160" t="n">
-        <v>6762544</v>
+        <v>6762388</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17238,9 +17243,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17255,19 +17270,19 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127282902</v>
+        <v>127282900</v>
       </c>
       <c r="B161" t="n">
         <v>79018</v>
@@ -17302,10 +17317,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>440760</v>
+        <v>440757</v>
       </c>
       <c r="R161" t="n">
-        <v>6762569</v>
+        <v>6762544</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17364,7 +17379,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127276426</v>
+        <v>127282902</v>
       </c>
       <c r="B162" t="n">
         <v>79018</v>
@@ -17395,14 +17410,14 @@
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>440582</v>
+        <v>440760</v>
       </c>
       <c r="R162" t="n">
-        <v>6762684</v>
+        <v>6762569</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17432,19 +17447,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17459,19 +17464,19 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127275877</v>
+        <v>127276426</v>
       </c>
       <c r="B163" t="n">
         <v>79018</v>
@@ -17506,10 +17511,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>440732</v>
+        <v>440582</v>
       </c>
       <c r="R163" t="n">
-        <v>6762635</v>
+        <v>6762684</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17578,7 +17583,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127273900</v>
+        <v>127275877</v>
       </c>
       <c r="B164" t="n">
         <v>79018</v>
@@ -17609,17 +17614,17 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>440903</v>
+        <v>440732</v>
       </c>
       <c r="R164" t="n">
-        <v>6762450</v>
+        <v>6762635</v>
       </c>
       <c r="S164" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -17648,7 +17653,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17658,7 +17663,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17673,19 +17678,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127283137</v>
+        <v>127273900</v>
       </c>
       <c r="B165" t="n">
         <v>79018</v>
@@ -17716,17 +17721,17 @@
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>440354</v>
+        <v>440903</v>
       </c>
       <c r="R165" t="n">
-        <v>6762415</v>
+        <v>6762450</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -17753,9 +17758,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17770,22 +17785,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127274348</v>
+        <v>127273086</v>
       </c>
       <c r="B166" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17793,42 +17808,37 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>440686</v>
+        <v>440694</v>
       </c>
       <c r="R166" t="n">
-        <v>6762176</v>
+        <v>6762204</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17857,7 +17867,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -17867,7 +17877,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17882,22 +17892,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127275098</v>
+        <v>127283137</v>
       </c>
       <c r="B167" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17905,39 +17915,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>440679</v>
+        <v>440354</v>
       </c>
       <c r="R167" t="n">
-        <v>6762388</v>
+        <v>6762415</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17967,19 +17972,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z167" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17994,22 +17989,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127273086</v>
+        <v>127274348</v>
       </c>
       <c r="B168" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18017,37 +18012,42 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>440694</v>
+        <v>440686</v>
       </c>
       <c r="R168" t="n">
-        <v>6762204</v>
+        <v>6762176</v>
       </c>
       <c r="S168" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -18086,7 +18086,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18101,12 +18101,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
@@ -19357,10 +19357,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127274154</v>
+        <v>127282906</v>
       </c>
       <c r="B181" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19368,42 +19368,37 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>440946</v>
+        <v>440782</v>
       </c>
       <c r="R181" t="n">
-        <v>6762537</v>
+        <v>6762562</v>
       </c>
       <c r="S181" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -19430,24 +19425,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19462,19 +19442,19 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127282906</v>
+        <v>127282925</v>
       </c>
       <c r="B182" t="n">
         <v>79018</v>
@@ -19509,10 +19489,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>440782</v>
+        <v>440619</v>
       </c>
       <c r="R182" t="n">
-        <v>6762562</v>
+        <v>6762184</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19571,7 +19551,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127282925</v>
+        <v>127283127</v>
       </c>
       <c r="B183" t="n">
         <v>79018</v>
@@ -19602,14 +19582,14 @@
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>440619</v>
+        <v>440843</v>
       </c>
       <c r="R183" t="n">
-        <v>6762184</v>
+        <v>6762431</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19656,19 +19636,19 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127283127</v>
+        <v>127283116</v>
       </c>
       <c r="B184" t="n">
         <v>79018</v>
@@ -19703,10 +19683,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>440843</v>
+        <v>440823</v>
       </c>
       <c r="R184" t="n">
-        <v>6762431</v>
+        <v>6762604</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19765,7 +19745,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127283116</v>
+        <v>127275778</v>
       </c>
       <c r="B185" t="n">
         <v>79018</v>
@@ -19796,17 +19776,17 @@
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>440823</v>
+        <v>440761</v>
       </c>
       <c r="R185" t="n">
-        <v>6762604</v>
+        <v>6762597</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -19833,9 +19813,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19850,22 +19840,22 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127275778</v>
+        <v>127274154</v>
       </c>
       <c r="B186" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19873,34 +19863,39 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>440761</v>
+        <v>440946</v>
       </c>
       <c r="R186" t="n">
-        <v>6762597</v>
+        <v>6762537</v>
       </c>
       <c r="S186" t="n">
         <v>9</v>
@@ -19932,7 +19927,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -19942,7 +19937,12 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19969,10 +19969,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127282924</v>
+        <v>127274877</v>
       </c>
       <c r="B187" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19980,37 +19980,42 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>440623</v>
+        <v>440752</v>
       </c>
       <c r="R187" t="n">
-        <v>6762194</v>
+        <v>6762337</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -20037,9 +20042,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20054,57 +20069,57 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127283136</v>
+        <v>127276155</v>
       </c>
       <c r="B188" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>440394</v>
+        <v>440657</v>
       </c>
       <c r="R188" t="n">
-        <v>6762413</v>
+        <v>6762603</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20134,9 +20149,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20151,19 +20176,19 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127282907</v>
+        <v>127282924</v>
       </c>
       <c r="B189" t="n">
         <v>79018</v>
@@ -20198,10 +20223,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>440793</v>
+        <v>440623</v>
       </c>
       <c r="R189" t="n">
-        <v>6762525</v>
+        <v>6762194</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20260,7 +20285,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127283138</v>
+        <v>127283136</v>
       </c>
       <c r="B190" t="n">
         <v>79018</v>
@@ -20295,10 +20320,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>440335</v>
+        <v>440394</v>
       </c>
       <c r="R190" t="n">
-        <v>6762400</v>
+        <v>6762413</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20357,7 +20382,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127283118</v>
+        <v>127282907</v>
       </c>
       <c r="B191" t="n">
         <v>79018</v>
@@ -20388,14 +20413,14 @@
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>440868</v>
+        <v>440793</v>
       </c>
       <c r="R191" t="n">
-        <v>6762583</v>
+        <v>6762525</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20442,19 +20467,19 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127283113</v>
+        <v>127283138</v>
       </c>
       <c r="B192" t="n">
         <v>79018</v>
@@ -20489,10 +20514,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>440768</v>
+        <v>440335</v>
       </c>
       <c r="R192" t="n">
-        <v>6762554</v>
+        <v>6762400</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20551,10 +20576,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127274877</v>
+        <v>127283118</v>
       </c>
       <c r="B193" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20562,42 +20587,37 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>440752</v>
+        <v>440868</v>
       </c>
       <c r="R193" t="n">
-        <v>6762337</v>
+        <v>6762583</v>
       </c>
       <c r="S193" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -20624,19 +20644,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20651,57 +20661,57 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127276155</v>
+        <v>127283113</v>
       </c>
       <c r="B194" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>440657</v>
+        <v>440768</v>
       </c>
       <c r="R194" t="n">
-        <v>6762603</v>
+        <v>6762554</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20731,19 +20741,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20758,57 +20758,57 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127283143</v>
+        <v>127276018</v>
       </c>
       <c r="B195" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>440337</v>
+        <v>440697</v>
       </c>
       <c r="R195" t="n">
-        <v>6762397</v>
+        <v>6762625</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20838,9 +20838,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20855,57 +20865,57 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127272174</v>
+        <v>127283124</v>
       </c>
       <c r="B196" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>440657</v>
+        <v>440965</v>
       </c>
       <c r="R196" t="n">
-        <v>6762157</v>
+        <v>6762540</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20935,19 +20945,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20962,12 +20962,12 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
@@ -21081,10 +21081,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127276018</v>
+        <v>127274677</v>
       </c>
       <c r="B198" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21092,34 +21092,39 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>440697</v>
+        <v>440689</v>
       </c>
       <c r="R198" t="n">
-        <v>6762625</v>
+        <v>6762214</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21151,7 +21156,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21161,7 +21166,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21188,32 +21193,32 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127283124</v>
+        <v>127283143</v>
       </c>
       <c r="B199" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21223,10 +21228,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>440965</v>
+        <v>440337</v>
       </c>
       <c r="R199" t="n">
-        <v>6762540</v>
+        <v>6762397</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21285,48 +21290,48 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127275350</v>
+        <v>127272174</v>
       </c>
       <c r="B200" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>440851</v>
+        <v>440657</v>
       </c>
       <c r="R200" t="n">
-        <v>6762513</v>
+        <v>6762157</v>
       </c>
       <c r="S200" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -21355,7 +21360,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -21365,7 +21370,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21380,22 +21385,22 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127274677</v>
+        <v>127275350</v>
       </c>
       <c r="B201" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21403,42 +21408,37 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>440689</v>
+        <v>440851</v>
       </c>
       <c r="R201" t="n">
-        <v>6762214</v>
+        <v>6762513</v>
       </c>
       <c r="S201" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21477,7 +21477,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21492,22 +21492,22 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127282910</v>
+        <v>127271427</v>
       </c>
       <c r="B202" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21515,37 +21515,37 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>440807</v>
+        <v>440457</v>
       </c>
       <c r="R202" t="n">
-        <v>6762574</v>
+        <v>6762399</v>
       </c>
       <c r="S202" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -21572,9 +21572,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21589,19 +21599,19 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127272958</v>
+        <v>127282910</v>
       </c>
       <c r="B203" t="n">
         <v>79018</v>
@@ -21632,17 +21642,17 @@
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>440619</v>
+        <v>440807</v>
       </c>
       <c r="R203" t="n">
-        <v>6762170</v>
+        <v>6762574</v>
       </c>
       <c r="S203" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -21669,19 +21679,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21696,19 +21696,19 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127282897</v>
+        <v>127272958</v>
       </c>
       <c r="B204" t="n">
         <v>79018</v>
@@ -21739,17 +21739,17 @@
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>440613</v>
+        <v>440619</v>
       </c>
       <c r="R204" t="n">
-        <v>6762197</v>
+        <v>6762170</v>
       </c>
       <c r="S204" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -21776,9 +21776,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21793,19 +21803,19 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>127282920</v>
+        <v>127282897</v>
       </c>
       <c r="B205" t="n">
         <v>79018</v>
@@ -21840,10 +21850,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>440696</v>
+        <v>440613</v>
       </c>
       <c r="R205" t="n">
-        <v>6762239</v>
+        <v>6762197</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21902,7 +21912,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127275348</v>
+        <v>127282920</v>
       </c>
       <c r="B206" t="n">
         <v>79018</v>
@@ -21933,14 +21943,14 @@
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>440677</v>
+        <v>440696</v>
       </c>
       <c r="R206" t="n">
-        <v>6762469</v>
+        <v>6762239</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21970,19 +21980,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -21997,19 +21997,19 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127271972</v>
+        <v>127275348</v>
       </c>
       <c r="B207" t="n">
         <v>79018</v>
@@ -22040,17 +22040,17 @@
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>440460</v>
+        <v>440677</v>
       </c>
       <c r="R207" t="n">
-        <v>6762457</v>
+        <v>6762469</v>
       </c>
       <c r="S207" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -22089,12 +22089,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>På Gran</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22109,19 +22104,19 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127283114</v>
+        <v>127271972</v>
       </c>
       <c r="B208" t="n">
         <v>79018</v>
@@ -22152,17 +22147,17 @@
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>440806</v>
+        <v>440460</v>
       </c>
       <c r="R208" t="n">
-        <v>6762533</v>
+        <v>6762457</v>
       </c>
       <c r="S208" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -22189,9 +22184,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>På Gran</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22206,22 +22216,22 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127271427</v>
+        <v>127283114</v>
       </c>
       <c r="B209" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -22229,37 +22239,37 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>440457</v>
+        <v>440806</v>
       </c>
       <c r="R209" t="n">
-        <v>6762399</v>
+        <v>6762533</v>
       </c>
       <c r="S209" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -22286,19 +22296,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -22313,12 +22313,12 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>

--- a/artfynd/A 29945-2025 artfynd.xlsx
+++ b/artfynd/A 29945-2025 artfynd.xlsx
@@ -11567,7 +11567,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127282929</v>
+        <v>127274454</v>
       </c>
       <c r="B106" t="n">
         <v>79018</v>
@@ -11598,17 +11598,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>440440</v>
+        <v>440926</v>
       </c>
       <c r="R106" t="n">
-        <v>6762463</v>
+        <v>6762599</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11635,9 +11635,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11652,19 +11662,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127283121</v>
+        <v>127282929</v>
       </c>
       <c r="B107" t="n">
         <v>79018</v>
@@ -11695,14 +11705,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>440883</v>
+        <v>440440</v>
       </c>
       <c r="R107" t="n">
-        <v>6762587</v>
+        <v>6762463</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11749,19 +11759,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127274454</v>
+        <v>127283121</v>
       </c>
       <c r="B108" t="n">
         <v>79018</v>
@@ -11792,17 +11802,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>440926</v>
+        <v>440883</v>
       </c>
       <c r="R108" t="n">
-        <v>6762599</v>
+        <v>6762587</v>
       </c>
       <c r="S108" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11829,19 +11839,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11856,22 +11856,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127273473</v>
+        <v>127273727</v>
       </c>
       <c r="B109" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11879,39 +11879,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>440721</v>
+        <v>440754</v>
       </c>
       <c r="R109" t="n">
-        <v>6761996</v>
+        <v>6762035</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11980,7 +11975,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127273727</v>
+        <v>127282909</v>
       </c>
       <c r="B110" t="n">
         <v>79018</v>
@@ -12011,14 +12006,14 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>440754</v>
+        <v>440797</v>
       </c>
       <c r="R110" t="n">
-        <v>6762035</v>
+        <v>6762555</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12048,19 +12043,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12075,19 +12060,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127282909</v>
+        <v>127282922</v>
       </c>
       <c r="B111" t="n">
         <v>79018</v>
@@ -12122,10 +12107,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>440797</v>
+        <v>440685</v>
       </c>
       <c r="R111" t="n">
-        <v>6762555</v>
+        <v>6762213</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12184,7 +12169,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127282922</v>
+        <v>127282903</v>
       </c>
       <c r="B112" t="n">
         <v>79018</v>
@@ -12219,10 +12204,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>440685</v>
+        <v>440760</v>
       </c>
       <c r="R112" t="n">
-        <v>6762213</v>
+        <v>6762626</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12281,10 +12266,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127282896</v>
+        <v>127274251</v>
       </c>
       <c r="B113" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12292,34 +12277,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>440416</v>
+        <v>440687</v>
       </c>
       <c r="R113" t="n">
-        <v>6762406</v>
+        <v>6762120</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12349,9 +12334,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12366,22 +12361,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127282903</v>
+        <v>127282896</v>
       </c>
       <c r="B114" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12389,21 +12384,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12413,10 +12408,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>440760</v>
+        <v>440416</v>
       </c>
       <c r="R114" t="n">
-        <v>6762626</v>
+        <v>6762406</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12475,10 +12470,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127274251</v>
+        <v>127273473</v>
       </c>
       <c r="B115" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12486,34 +12481,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>440687</v>
+        <v>440721</v>
       </c>
       <c r="R115" t="n">
-        <v>6762120</v>
+        <v>6761996</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12689,10 +12689,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127273755</v>
+        <v>127274057</v>
       </c>
       <c r="B117" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12700,34 +12700,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>440744</v>
+        <v>440706</v>
       </c>
       <c r="R117" t="n">
-        <v>6762065</v>
+        <v>6762058</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12796,7 +12801,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127276304</v>
+        <v>127273755</v>
       </c>
       <c r="B118" t="n">
         <v>79018</v>
@@ -12831,10 +12836,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>440642</v>
+        <v>440744</v>
       </c>
       <c r="R118" t="n">
-        <v>6762606</v>
+        <v>6762065</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12866,7 +12871,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12876,7 +12881,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12903,7 +12908,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127275131</v>
+        <v>127276304</v>
       </c>
       <c r="B119" t="n">
         <v>79018</v>
@@ -12938,10 +12943,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>440709</v>
+        <v>440642</v>
       </c>
       <c r="R119" t="n">
-        <v>6762405</v>
+        <v>6762606</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12973,7 +12978,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -12983,7 +12988,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13010,10 +13015,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127274057</v>
+        <v>127275131</v>
       </c>
       <c r="B120" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13021,39 +13026,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>440706</v>
+        <v>440709</v>
       </c>
       <c r="R120" t="n">
-        <v>6762058</v>
+        <v>6762405</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13122,10 +13122,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127283110</v>
+        <v>127271820</v>
       </c>
       <c r="B121" t="n">
-        <v>79019</v>
+        <v>79018</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13133,16 +13133,16 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -13153,17 +13153,17 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>440835</v>
+        <v>440446</v>
       </c>
       <c r="R121" t="n">
-        <v>6762564</v>
+        <v>6762469</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13190,9 +13190,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13207,60 +13217,60 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127271820</v>
+        <v>127274061</v>
       </c>
       <c r="B122" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>440446</v>
+        <v>440706</v>
       </c>
       <c r="R122" t="n">
-        <v>6762469</v>
+        <v>6762058</v>
       </c>
       <c r="S122" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13289,7 +13299,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13299,7 +13309,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13314,57 +13324,57 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127274061</v>
+        <v>127283110</v>
       </c>
       <c r="B123" t="n">
-        <v>8450</v>
+        <v>79019</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>440706</v>
+        <v>440835</v>
       </c>
       <c r="R123" t="n">
-        <v>6762058</v>
+        <v>6762564</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13394,19 +13404,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13421,22 +13421,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127283139</v>
+        <v>127275968</v>
       </c>
       <c r="B124" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13444,34 +13444,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
         <v>440723</v>
       </c>
       <c r="R124" t="n">
-        <v>6762373</v>
+        <v>6762648</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13501,9 +13501,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13518,19 +13528,19 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127283131</v>
+        <v>127283139</v>
       </c>
       <c r="B125" t="n">
         <v>79018</v>
@@ -13565,10 +13575,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>440682</v>
+        <v>440723</v>
       </c>
       <c r="R125" t="n">
-        <v>6762208</v>
+        <v>6762373</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13627,7 +13637,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127273828</v>
+        <v>127283131</v>
       </c>
       <c r="B126" t="n">
         <v>79018</v>
@@ -13658,17 +13668,17 @@
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>440882</v>
+        <v>440682</v>
       </c>
       <c r="R126" t="n">
-        <v>6762435</v>
+        <v>6762208</v>
       </c>
       <c r="S126" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13695,19 +13705,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13722,22 +13722,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127275968</v>
+        <v>127283135</v>
       </c>
       <c r="B127" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13745,34 +13745,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>440723</v>
+        <v>440456</v>
       </c>
       <c r="R127" t="n">
-        <v>6762648</v>
+        <v>6762461</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13802,19 +13802,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13829,19 +13819,19 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127283135</v>
+        <v>127273828</v>
       </c>
       <c r="B128" t="n">
         <v>79018</v>
@@ -13872,17 +13862,17 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>440456</v>
+        <v>440882</v>
       </c>
       <c r="R128" t="n">
-        <v>6762461</v>
+        <v>6762435</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13909,9 +13899,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13926,12 +13926,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -14050,7 +14050,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127282932</v>
+        <v>127274657</v>
       </c>
       <c r="B130" t="n">
         <v>79018</v>
@@ -14081,14 +14081,14 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>440427</v>
+        <v>440689</v>
       </c>
       <c r="R130" t="n">
-        <v>6762470</v>
+        <v>6762214</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14118,9 +14118,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14135,19 +14150,19 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127276216</v>
+        <v>127283117</v>
       </c>
       <c r="B131" t="n">
         <v>79018</v>
@@ -14178,11 +14193,11 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>440657</v>
+        <v>440863</v>
       </c>
       <c r="R131" t="n">
         <v>6762603</v>
@@ -14215,19 +14230,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14242,19 +14247,19 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127274657</v>
+        <v>127273051</v>
       </c>
       <c r="B132" t="n">
         <v>79018</v>
@@ -14285,17 +14290,17 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>440689</v>
+        <v>440681</v>
       </c>
       <c r="R132" t="n">
-        <v>6762214</v>
+        <v>6762197</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14324,7 +14329,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14334,12 +14339,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14354,19 +14354,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127283117</v>
+        <v>127282932</v>
       </c>
       <c r="B133" t="n">
         <v>79018</v>
@@ -14397,14 +14397,14 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>440863</v>
+        <v>440427</v>
       </c>
       <c r="R133" t="n">
-        <v>6762603</v>
+        <v>6762470</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14451,19 +14451,19 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127273051</v>
+        <v>127282912</v>
       </c>
       <c r="B134" t="n">
         <v>79018</v>
@@ -14494,17 +14494,17 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>440681</v>
+        <v>440936</v>
       </c>
       <c r="R134" t="n">
-        <v>6762197</v>
+        <v>6762564</v>
       </c>
       <c r="S134" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14531,19 +14531,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>12:38</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14558,19 +14548,19 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127282912</v>
+        <v>127282926</v>
       </c>
       <c r="B135" t="n">
         <v>79018</v>
@@ -14605,10 +14595,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>440936</v>
+        <v>440497</v>
       </c>
       <c r="R135" t="n">
-        <v>6762564</v>
+        <v>6762331</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14667,7 +14657,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127282926</v>
+        <v>127283130</v>
       </c>
       <c r="B136" t="n">
         <v>79018</v>
@@ -14698,14 +14688,14 @@
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>440497</v>
+        <v>440697</v>
       </c>
       <c r="R136" t="n">
-        <v>6762331</v>
+        <v>6762237</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14752,19 +14742,19 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127283130</v>
+        <v>127276216</v>
       </c>
       <c r="B137" t="n">
         <v>79018</v>
@@ -14795,14 +14785,14 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>440697</v>
+        <v>440657</v>
       </c>
       <c r="R137" t="n">
-        <v>6762237</v>
+        <v>6762603</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14832,9 +14822,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14849,12 +14849,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -15717,32 +15717,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127283119</v>
+        <v>127283142</v>
       </c>
       <c r="B146" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15752,10 +15752,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>440881</v>
+        <v>440744</v>
       </c>
       <c r="R146" t="n">
-        <v>6762591</v>
+        <v>6762615</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15814,7 +15814,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127273932</v>
+        <v>127274917</v>
       </c>
       <c r="B147" t="n">
         <v>79018</v>
@@ -15845,17 +15845,17 @@
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>440913</v>
+        <v>440752</v>
       </c>
       <c r="R147" t="n">
-        <v>6762466</v>
+        <v>6762337</v>
       </c>
       <c r="S147" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15894,7 +15894,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15909,44 +15909,44 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127283142</v>
+        <v>127283119</v>
       </c>
       <c r="B148" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15956,10 +15956,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>440744</v>
+        <v>440881</v>
       </c>
       <c r="R148" t="n">
-        <v>6762615</v>
+        <v>6762591</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16018,7 +16018,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127274917</v>
+        <v>127272858</v>
       </c>
       <c r="B149" t="n">
         <v>79018</v>
@@ -16049,17 +16049,17 @@
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>440752</v>
+        <v>440609</v>
       </c>
       <c r="R149" t="n">
-        <v>6762337</v>
+        <v>6762190</v>
       </c>
       <c r="S149" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16098,7 +16098,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16113,19 +16113,19 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127272858</v>
+        <v>127273038</v>
       </c>
       <c r="B150" t="n">
         <v>79018</v>
@@ -16160,10 +16160,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>440609</v>
+        <v>440688</v>
       </c>
       <c r="R150" t="n">
-        <v>6762190</v>
+        <v>6762199</v>
       </c>
       <c r="S150" t="n">
         <v>9</v>
@@ -16195,7 +16195,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16205,7 +16205,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16232,7 +16232,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127273038</v>
+        <v>127274822</v>
       </c>
       <c r="B151" t="n">
         <v>79018</v>
@@ -16263,17 +16263,17 @@
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>440688</v>
+        <v>440760</v>
       </c>
       <c r="R151" t="n">
-        <v>6762199</v>
+        <v>6762313</v>
       </c>
       <c r="S151" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16312,7 +16312,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16327,19 +16327,19 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127274822</v>
+        <v>127275416</v>
       </c>
       <c r="B152" t="n">
         <v>79018</v>
@@ -16370,17 +16370,17 @@
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>440760</v>
+        <v>440816</v>
       </c>
       <c r="R152" t="n">
-        <v>6762313</v>
+        <v>6762475</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16409,7 +16409,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16434,19 +16434,19 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127275416</v>
+        <v>127273932</v>
       </c>
       <c r="B153" t="n">
         <v>79018</v>
@@ -16481,10 +16481,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>440816</v>
+        <v>440913</v>
       </c>
       <c r="R153" t="n">
-        <v>6762475</v>
+        <v>6762466</v>
       </c>
       <c r="S153" t="n">
         <v>9</v>
@@ -16516,7 +16516,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16526,7 +16526,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16747,10 +16747,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127283105</v>
+        <v>127274354</v>
       </c>
       <c r="B156" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16758,34 +16758,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>440909</v>
+        <v>440686</v>
       </c>
       <c r="R156" t="n">
-        <v>6762467</v>
+        <v>6762176</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16815,9 +16815,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16832,19 +16842,19 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127274354</v>
+        <v>127272746</v>
       </c>
       <c r="B157" t="n">
         <v>79018</v>
@@ -16875,17 +16885,17 @@
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>440686</v>
+        <v>440503</v>
       </c>
       <c r="R157" t="n">
-        <v>6762176</v>
+        <v>6762308</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16914,7 +16924,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16924,7 +16934,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16939,22 +16949,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127272746</v>
+        <v>127283105</v>
       </c>
       <c r="B158" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16962,37 +16972,37 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>440503</v>
+        <v>440909</v>
       </c>
       <c r="R158" t="n">
-        <v>6762308</v>
+        <v>6762467</v>
       </c>
       <c r="S158" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17019,19 +17029,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17046,12 +17046,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -17170,10 +17170,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127275098</v>
+        <v>127282900</v>
       </c>
       <c r="B160" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17181,39 +17181,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>440679</v>
+        <v>440757</v>
       </c>
       <c r="R160" t="n">
-        <v>6762388</v>
+        <v>6762544</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17243,19 +17238,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17270,19 +17255,19 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127282900</v>
+        <v>127276426</v>
       </c>
       <c r="B161" t="n">
         <v>79018</v>
@@ -17313,14 +17298,14 @@
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>440757</v>
+        <v>440582</v>
       </c>
       <c r="R161" t="n">
-        <v>6762544</v>
+        <v>6762684</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17350,9 +17335,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17367,19 +17362,19 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127282902</v>
+        <v>127275877</v>
       </c>
       <c r="B162" t="n">
         <v>79018</v>
@@ -17410,14 +17405,14 @@
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>440760</v>
+        <v>440732</v>
       </c>
       <c r="R162" t="n">
-        <v>6762569</v>
+        <v>6762635</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17447,9 +17442,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17464,19 +17469,19 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127276426</v>
+        <v>127273900</v>
       </c>
       <c r="B163" t="n">
         <v>79018</v>
@@ -17507,17 +17512,17 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>440582</v>
+        <v>440903</v>
       </c>
       <c r="R163" t="n">
-        <v>6762684</v>
+        <v>6762450</v>
       </c>
       <c r="S163" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -17546,7 +17551,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17556,7 +17561,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17571,19 +17576,19 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127275877</v>
+        <v>127282902</v>
       </c>
       <c r="B164" t="n">
         <v>79018</v>
@@ -17614,14 +17619,14 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>440732</v>
+        <v>440760</v>
       </c>
       <c r="R164" t="n">
-        <v>6762635</v>
+        <v>6762569</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17651,19 +17656,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17678,19 +17673,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127273900</v>
+        <v>127273086</v>
       </c>
       <c r="B165" t="n">
         <v>79018</v>
@@ -17725,10 +17720,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>440903</v>
+        <v>440694</v>
       </c>
       <c r="R165" t="n">
-        <v>6762450</v>
+        <v>6762204</v>
       </c>
       <c r="S165" t="n">
         <v>9</v>
@@ -17760,7 +17755,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17770,7 +17765,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17797,7 +17792,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127273086</v>
+        <v>127283137</v>
       </c>
       <c r="B166" t="n">
         <v>79018</v>
@@ -17828,17 +17823,17 @@
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>440694</v>
+        <v>440354</v>
       </c>
       <c r="R166" t="n">
-        <v>6762204</v>
+        <v>6762415</v>
       </c>
       <c r="S166" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17865,19 +17860,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>12:40</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17892,22 +17877,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127283137</v>
+        <v>127275098</v>
       </c>
       <c r="B167" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17915,34 +17900,39 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>440354</v>
+        <v>440679</v>
       </c>
       <c r="R167" t="n">
-        <v>6762415</v>
+        <v>6762388</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17972,9 +17962,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17989,12 +17989,12 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
@@ -18113,7 +18113,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127270744</v>
+        <v>127273853</v>
       </c>
       <c r="B169" t="n">
         <v>79018</v>
@@ -18144,17 +18144,17 @@
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>440351</v>
+        <v>440887</v>
       </c>
       <c r="R169" t="n">
-        <v>6762480</v>
+        <v>6762439</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18208,19 +18208,19 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127283128</v>
+        <v>127270744</v>
       </c>
       <c r="B170" t="n">
         <v>79018</v>
@@ -18251,14 +18251,14 @@
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>440822</v>
+        <v>440351</v>
       </c>
       <c r="R170" t="n">
-        <v>6762415</v>
+        <v>6762480</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18288,9 +18288,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18305,19 +18315,19 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127274114</v>
+        <v>127275337</v>
       </c>
       <c r="B171" t="n">
         <v>79018</v>
@@ -18348,17 +18358,17 @@
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>440711</v>
+        <v>440855</v>
       </c>
       <c r="R171" t="n">
-        <v>6762111</v>
+        <v>6762513</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18387,7 +18397,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -18397,7 +18407,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18412,19 +18422,19 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127283134</v>
+        <v>127282927</v>
       </c>
       <c r="B172" t="n">
         <v>79018</v>
@@ -18455,14 +18465,14 @@
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>440487</v>
+        <v>440488</v>
       </c>
       <c r="R172" t="n">
-        <v>6762321</v>
+        <v>6762419</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18509,19 +18519,19 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127283133</v>
+        <v>127283128</v>
       </c>
       <c r="B173" t="n">
         <v>79018</v>
@@ -18556,10 +18566,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>440598</v>
+        <v>440822</v>
       </c>
       <c r="R173" t="n">
-        <v>6762206</v>
+        <v>6762415</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18618,32 +18628,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127271802</v>
+        <v>127274114</v>
       </c>
       <c r="B174" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18653,10 +18663,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>440627</v>
+        <v>440711</v>
       </c>
       <c r="R174" t="n">
-        <v>6762119</v>
+        <v>6762111</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18699,11 +18709,6 @@
       <c r="AB174" t="inlineStr">
         <is>
           <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Rikligt med torrakor med spår efter Mindre Märgborre i området</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18730,53 +18735,48 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127271251</v>
+        <v>127283115</v>
       </c>
       <c r="B175" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>440375</v>
+        <v>440803</v>
       </c>
       <c r="R175" t="n">
-        <v>6762366</v>
+        <v>6762557</v>
       </c>
       <c r="S175" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -18803,19 +18803,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>10:53</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18830,57 +18820,57 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127276271</v>
+        <v>127283134</v>
       </c>
       <c r="B176" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>440642</v>
+        <v>440487</v>
       </c>
       <c r="R176" t="n">
-        <v>6762606</v>
+        <v>6762321</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18910,19 +18900,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18937,19 +18917,19 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127273853</v>
+        <v>127283133</v>
       </c>
       <c r="B177" t="n">
         <v>79018</v>
@@ -18980,17 +18960,17 @@
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>440887</v>
+        <v>440598</v>
       </c>
       <c r="R177" t="n">
-        <v>6762439</v>
+        <v>6762206</v>
       </c>
       <c r="S177" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -19017,19 +18997,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19044,60 +19014,60 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127275337</v>
+        <v>127271802</v>
       </c>
       <c r="B178" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>440855</v>
+        <v>440627</v>
       </c>
       <c r="R178" t="n">
-        <v>6762513</v>
+        <v>6762119</v>
       </c>
       <c r="S178" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19126,7 +19096,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -19136,7 +19106,12 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>Rikligt med torrakor med spår efter Mindre Märgborre i området</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19151,60 +19126,65 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127282927</v>
+        <v>127271251</v>
       </c>
       <c r="B179" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>440488</v>
+        <v>440375</v>
       </c>
       <c r="R179" t="n">
-        <v>6762419</v>
+        <v>6762366</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19231,9 +19211,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19248,57 +19238,57 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127283115</v>
+        <v>127276271</v>
       </c>
       <c r="B180" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>440803</v>
+        <v>440642</v>
       </c>
       <c r="R180" t="n">
-        <v>6762557</v>
+        <v>6762606</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19328,9 +19318,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19345,19 +19345,19 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127282906</v>
+        <v>127283127</v>
       </c>
       <c r="B181" t="n">
         <v>79018</v>
@@ -19388,14 +19388,14 @@
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>440782</v>
+        <v>440843</v>
       </c>
       <c r="R181" t="n">
-        <v>6762562</v>
+        <v>6762431</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19442,19 +19442,19 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127282925</v>
+        <v>127283116</v>
       </c>
       <c r="B182" t="n">
         <v>79018</v>
@@ -19485,14 +19485,14 @@
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>440619</v>
+        <v>440823</v>
       </c>
       <c r="R182" t="n">
-        <v>6762184</v>
+        <v>6762604</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19539,19 +19539,19 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127283127</v>
+        <v>127282906</v>
       </c>
       <c r="B183" t="n">
         <v>79018</v>
@@ -19582,14 +19582,14 @@
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>440843</v>
+        <v>440782</v>
       </c>
       <c r="R183" t="n">
-        <v>6762431</v>
+        <v>6762562</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19636,19 +19636,19 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127283116</v>
+        <v>127275778</v>
       </c>
       <c r="B184" t="n">
         <v>79018</v>
@@ -19679,17 +19679,17 @@
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>440823</v>
+        <v>440761</v>
       </c>
       <c r="R184" t="n">
-        <v>6762604</v>
+        <v>6762597</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19716,9 +19716,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19733,19 +19743,19 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127275778</v>
+        <v>127282925</v>
       </c>
       <c r="B185" t="n">
         <v>79018</v>
@@ -19776,17 +19786,17 @@
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>440761</v>
+        <v>440619</v>
       </c>
       <c r="R185" t="n">
-        <v>6762597</v>
+        <v>6762184</v>
       </c>
       <c r="S185" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -19813,19 +19823,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>15:06</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>15:06</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19840,12 +19840,12 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
@@ -19969,53 +19969,48 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127274877</v>
+        <v>127276155</v>
       </c>
       <c r="B187" t="n">
-        <v>57821</v>
+        <v>8450</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>440752</v>
+        <v>440657</v>
       </c>
       <c r="R187" t="n">
-        <v>6762337</v>
+        <v>6762603</v>
       </c>
       <c r="S187" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -20044,7 +20039,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20054,7 +20049,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20081,45 +20076,45 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127276155</v>
+        <v>127282924</v>
       </c>
       <c r="B188" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>440657</v>
+        <v>440623</v>
       </c>
       <c r="R188" t="n">
-        <v>6762603</v>
+        <v>6762194</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20149,19 +20144,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z188" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20176,19 +20161,19 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127282924</v>
+        <v>127283136</v>
       </c>
       <c r="B189" t="n">
         <v>79018</v>
@@ -20219,14 +20204,14 @@
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>440623</v>
+        <v>440394</v>
       </c>
       <c r="R189" t="n">
-        <v>6762194</v>
+        <v>6762413</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20273,19 +20258,19 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127283136</v>
+        <v>127283138</v>
       </c>
       <c r="B190" t="n">
         <v>79018</v>
@@ -20320,10 +20305,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>440394</v>
+        <v>440335</v>
       </c>
       <c r="R190" t="n">
-        <v>6762413</v>
+        <v>6762400</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20479,7 +20464,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127283138</v>
+        <v>127283118</v>
       </c>
       <c r="B192" t="n">
         <v>79018</v>
@@ -20514,10 +20499,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>440335</v>
+        <v>440868</v>
       </c>
       <c r="R192" t="n">
-        <v>6762400</v>
+        <v>6762583</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20576,7 +20561,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127283118</v>
+        <v>127283113</v>
       </c>
       <c r="B193" t="n">
         <v>79018</v>
@@ -20611,10 +20596,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>440868</v>
+        <v>440768</v>
       </c>
       <c r="R193" t="n">
-        <v>6762583</v>
+        <v>6762554</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20673,10 +20658,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127283113</v>
+        <v>127274877</v>
       </c>
       <c r="B194" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20684,37 +20669,42 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>440768</v>
+        <v>440752</v>
       </c>
       <c r="R194" t="n">
-        <v>6762554</v>
+        <v>6762337</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -20741,9 +20731,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20758,12 +20758,12 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
@@ -20877,7 +20877,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127283124</v>
+        <v>127275350</v>
       </c>
       <c r="B196" t="n">
         <v>79018</v>
@@ -20908,17 +20908,17 @@
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>440965</v>
+        <v>440851</v>
       </c>
       <c r="R196" t="n">
-        <v>6762540</v>
+        <v>6762513</v>
       </c>
       <c r="S196" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -20945,9 +20945,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20962,19 +20972,19 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127272147</v>
+        <v>127283124</v>
       </c>
       <c r="B197" t="n">
         <v>79018</v>
@@ -21005,17 +21015,17 @@
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>440498</v>
+        <v>440965</v>
       </c>
       <c r="R197" t="n">
-        <v>6762428</v>
+        <v>6762540</v>
       </c>
       <c r="S197" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -21042,19 +21052,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21069,22 +21069,22 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127274677</v>
+        <v>127272147</v>
       </c>
       <c r="B198" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21092,42 +21092,37 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>440689</v>
+        <v>440498</v>
       </c>
       <c r="R198" t="n">
-        <v>6762214</v>
+        <v>6762428</v>
       </c>
       <c r="S198" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -21156,7 +21151,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21166,7 +21161,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21181,57 +21176,62 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127283143</v>
+        <v>127274677</v>
       </c>
       <c r="B199" t="n">
-        <v>8450</v>
+        <v>57658</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>440337</v>
+        <v>440689</v>
       </c>
       <c r="R199" t="n">
-        <v>6762397</v>
+        <v>6762214</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21261,9 +21261,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21278,19 +21288,19 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127272174</v>
+        <v>127283143</v>
       </c>
       <c r="B200" t="n">
         <v>8450</v>
@@ -21321,14 +21331,14 @@
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>440657</v>
+        <v>440337</v>
       </c>
       <c r="R200" t="n">
-        <v>6762157</v>
+        <v>6762397</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21358,19 +21368,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21385,60 +21385,60 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127275350</v>
+        <v>127272174</v>
       </c>
       <c r="B201" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>440851</v>
+        <v>440657</v>
       </c>
       <c r="R201" t="n">
-        <v>6762513</v>
+        <v>6762157</v>
       </c>
       <c r="S201" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -21477,7 +21477,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21492,22 +21492,22 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127271427</v>
+        <v>127275348</v>
       </c>
       <c r="B202" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21515,37 +21515,37 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>440457</v>
+        <v>440677</v>
       </c>
       <c r="R202" t="n">
-        <v>6762399</v>
+        <v>6762469</v>
       </c>
       <c r="S202" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -21584,7 +21584,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21599,12 +21599,12 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
@@ -21708,7 +21708,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>127272958</v>
+        <v>127271972</v>
       </c>
       <c r="B204" t="n">
         <v>79018</v>
@@ -21743,10 +21743,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>440619</v>
+        <v>440460</v>
       </c>
       <c r="R204" t="n">
-        <v>6762170</v>
+        <v>6762457</v>
       </c>
       <c r="S204" t="n">
         <v>9</v>
@@ -21778,7 +21778,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -21788,7 +21788,12 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>På Gran</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21815,7 +21820,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>127282897</v>
+        <v>127272958</v>
       </c>
       <c r="B205" t="n">
         <v>79018</v>
@@ -21846,17 +21851,17 @@
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>440613</v>
+        <v>440619</v>
       </c>
       <c r="R205" t="n">
-        <v>6762197</v>
+        <v>6762170</v>
       </c>
       <c r="S205" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -21883,9 +21888,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -21900,19 +21915,19 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127282920</v>
+        <v>127283114</v>
       </c>
       <c r="B206" t="n">
         <v>79018</v>
@@ -21943,14 +21958,14 @@
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>440696</v>
+        <v>440806</v>
       </c>
       <c r="R206" t="n">
-        <v>6762239</v>
+        <v>6762533</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21997,19 +22012,19 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>127275348</v>
+        <v>127282897</v>
       </c>
       <c r="B207" t="n">
         <v>79018</v>
@@ -22040,14 +22055,14 @@
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>440677</v>
+        <v>440613</v>
       </c>
       <c r="R207" t="n">
-        <v>6762469</v>
+        <v>6762197</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22077,19 +22092,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z207" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB207" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22104,19 +22109,19 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127271972</v>
+        <v>127282920</v>
       </c>
       <c r="B208" t="n">
         <v>79018</v>
@@ -22147,17 +22152,17 @@
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>440460</v>
+        <v>440696</v>
       </c>
       <c r="R208" t="n">
-        <v>6762457</v>
+        <v>6762239</v>
       </c>
       <c r="S208" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -22184,24 +22189,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>På Gran</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22216,22 +22206,22 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127283114</v>
+        <v>127271427</v>
       </c>
       <c r="B209" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -22239,37 +22229,37 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>440806</v>
+        <v>440457</v>
       </c>
       <c r="R209" t="n">
-        <v>6762533</v>
+        <v>6762399</v>
       </c>
       <c r="S209" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -22296,9 +22286,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -22313,12 +22313,12 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
@@ -22519,10 +22519,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>127283102</v>
+        <v>127272352</v>
       </c>
       <c r="B212" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -22530,34 +22530,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>440726</v>
+        <v>440685</v>
       </c>
       <c r="R212" t="n">
-        <v>6762638</v>
+        <v>6762109</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22587,9 +22587,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -22604,19 +22614,19 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127273057</v>
+        <v>127273790</v>
       </c>
       <c r="B213" t="n">
         <v>79018</v>
@@ -22651,10 +22661,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>440681</v>
+        <v>440854</v>
       </c>
       <c r="R213" t="n">
-        <v>6762195</v>
+        <v>6762427</v>
       </c>
       <c r="S213" t="n">
         <v>9</v>
@@ -22686,7 +22696,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -22696,7 +22706,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -22723,10 +22733,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127283104</v>
+        <v>127273057</v>
       </c>
       <c r="B214" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -22734,37 +22744,37 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>440766</v>
+        <v>440681</v>
       </c>
       <c r="R214" t="n">
-        <v>6762565</v>
+        <v>6762195</v>
       </c>
       <c r="S214" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -22791,9 +22801,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
       <c r="AA214" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -22808,22 +22828,22 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>127272352</v>
+        <v>127283102</v>
       </c>
       <c r="B215" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -22831,34 +22851,34 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>440685</v>
+        <v>440726</v>
       </c>
       <c r="R215" t="n">
-        <v>6762109</v>
+        <v>6762638</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22888,19 +22908,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z215" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA215" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB215" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -22915,22 +22925,22 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>127273790</v>
+        <v>127283104</v>
       </c>
       <c r="B216" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22938,37 +22948,37 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>440854</v>
+        <v>440766</v>
       </c>
       <c r="R216" t="n">
-        <v>6762427</v>
+        <v>6762565</v>
       </c>
       <c r="S216" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -22995,19 +23005,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z216" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB216" t="inlineStr">
-        <is>
-          <t>13:15</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23022,12 +23022,12 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
@@ -23146,10 +23146,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127282898</v>
+        <v>127283100</v>
       </c>
       <c r="B218" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23157,34 +23157,34 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>440741</v>
+        <v>440686</v>
       </c>
       <c r="R218" t="n">
-        <v>6762609</v>
+        <v>6762630</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23231,57 +23231,57 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127282915</v>
+        <v>127283107</v>
       </c>
       <c r="B219" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>440946</v>
+        <v>440636</v>
       </c>
       <c r="R219" t="n">
-        <v>6762514</v>
+        <v>6762585</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23328,19 +23328,19 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127282899</v>
+        <v>127282898</v>
       </c>
       <c r="B220" t="n">
         <v>79018</v>
@@ -23375,10 +23375,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>440763</v>
+        <v>440741</v>
       </c>
       <c r="R220" t="n">
-        <v>6762529</v>
+        <v>6762609</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23437,10 +23437,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127283100</v>
+        <v>127283122</v>
       </c>
       <c r="B221" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23448,21 +23448,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -23472,10 +23472,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>440686</v>
+        <v>440912</v>
       </c>
       <c r="R221" t="n">
-        <v>6762630</v>
+        <v>6762579</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23534,10 +23534,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127283141</v>
+        <v>127282915</v>
       </c>
       <c r="B222" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23545,34 +23545,34 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>440651</v>
+        <v>440946</v>
       </c>
       <c r="R222" t="n">
-        <v>6762611</v>
+        <v>6762514</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23619,19 +23619,19 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127283122</v>
+        <v>127275040</v>
       </c>
       <c r="B223" t="n">
         <v>79018</v>
@@ -23662,14 +23662,14 @@
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>440912</v>
+        <v>440745</v>
       </c>
       <c r="R223" t="n">
-        <v>6762579</v>
+        <v>6762369</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23699,9 +23699,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA223" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -23716,19 +23731,19 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127275040</v>
+        <v>127282899</v>
       </c>
       <c r="B224" t="n">
         <v>79018</v>
@@ -23759,14 +23774,14 @@
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>440745</v>
+        <v>440763</v>
       </c>
       <c r="R224" t="n">
-        <v>6762369</v>
+        <v>6762529</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23796,24 +23811,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB224" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -23828,44 +23828,44 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127283107</v>
+        <v>127283141</v>
       </c>
       <c r="B225" t="n">
-        <v>8450</v>
+        <v>78685</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23875,10 +23875,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>440636</v>
+        <v>440651</v>
       </c>
       <c r="R225" t="n">
-        <v>6762585</v>
+        <v>6762611</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24034,48 +24034,48 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>127275544</v>
+        <v>127283126</v>
       </c>
       <c r="B227" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>440811</v>
+        <v>440923</v>
       </c>
       <c r="R227" t="n">
-        <v>6762474</v>
+        <v>6762482</v>
       </c>
       <c r="S227" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -24102,19 +24102,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z227" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA227" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB227" t="inlineStr">
-        <is>
-          <t>14:44</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24129,57 +24119,57 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>127273585</v>
+        <v>127282918</v>
       </c>
       <c r="B228" t="n">
-        <v>91688</v>
+        <v>79018</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>440742</v>
+        <v>440832</v>
       </c>
       <c r="R228" t="n">
-        <v>6762004</v>
+        <v>6762387</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24209,19 +24199,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z228" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA228" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB228" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -24236,19 +24216,19 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>127283126</v>
+        <v>127282917</v>
       </c>
       <c r="B229" t="n">
         <v>79018</v>
@@ -24279,14 +24259,14 @@
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>440923</v>
+        <v>440919</v>
       </c>
       <c r="R229" t="n">
-        <v>6762482</v>
+        <v>6762497</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24333,19 +24313,19 @@
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>127282917</v>
+        <v>127283125</v>
       </c>
       <c r="B230" t="n">
         <v>79018</v>
@@ -24376,14 +24356,14 @@
       <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>440919</v>
+        <v>440989</v>
       </c>
       <c r="R230" t="n">
-        <v>6762497</v>
+        <v>6762519</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24430,19 +24410,19 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>127275120</v>
+        <v>127273660</v>
       </c>
       <c r="B231" t="n">
         <v>79018</v>
@@ -24473,17 +24453,17 @@
       <c r="I231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>440897</v>
+        <v>440742</v>
       </c>
       <c r="R231" t="n">
-        <v>6762548</v>
+        <v>6762004</v>
       </c>
       <c r="S231" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -24512,7 +24492,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -24522,7 +24502,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24537,19 +24517,19 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>127282918</v>
+        <v>127275120</v>
       </c>
       <c r="B232" t="n">
         <v>79018</v>
@@ -24580,17 +24560,17 @@
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>440832</v>
+        <v>440897</v>
       </c>
       <c r="R232" t="n">
-        <v>6762387</v>
+        <v>6762548</v>
       </c>
       <c r="S232" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -24617,9 +24597,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24634,57 +24624,57 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>127283125</v>
+        <v>127273585</v>
       </c>
       <c r="B233" t="n">
-        <v>79018</v>
+        <v>91688</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>440989</v>
+        <v>440742</v>
       </c>
       <c r="R233" t="n">
-        <v>6762519</v>
+        <v>6762004</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24714,9 +24704,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA233" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -24731,60 +24731,60 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>127273660</v>
+        <v>127275544</v>
       </c>
       <c r="B234" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>440742</v>
+        <v>440811</v>
       </c>
       <c r="R234" t="n">
-        <v>6762004</v>
+        <v>6762474</v>
       </c>
       <c r="S234" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -24823,7 +24823,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -24838,65 +24838,60 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>127275970</v>
+        <v>127283123</v>
       </c>
       <c r="B235" t="n">
-        <v>5197</v>
+        <v>79018</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>440685</v>
+        <v>440917</v>
       </c>
       <c r="R235" t="n">
-        <v>6762673</v>
+        <v>6762578</v>
       </c>
       <c r="S235" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -24923,19 +24918,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z235" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA235" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB235" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -24950,22 +24935,22 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127275615</v>
+        <v>127282930</v>
       </c>
       <c r="B236" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24973,42 +24958,37 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>440778</v>
+        <v>440417</v>
       </c>
       <c r="R236" t="n">
-        <v>6762552</v>
+        <v>6762463</v>
       </c>
       <c r="S236" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -25035,19 +25015,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z236" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA236" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB236" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -25062,19 +25032,19 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127282930</v>
+        <v>127271487</v>
       </c>
       <c r="B237" t="n">
         <v>79018</v>
@@ -25105,14 +25075,14 @@
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>440417</v>
+        <v>440596</v>
       </c>
       <c r="R237" t="n">
-        <v>6762463</v>
+        <v>6762126</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25142,9 +25112,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA237" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB237" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25159,19 +25139,19 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>127282933</v>
+        <v>127283132</v>
       </c>
       <c r="B238" t="n">
         <v>79018</v>
@@ -25202,14 +25182,14 @@
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>440395</v>
+        <v>440679</v>
       </c>
       <c r="R238" t="n">
-        <v>6762359</v>
+        <v>6762203</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25256,19 +25236,19 @@
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>127273778</v>
+        <v>127282933</v>
       </c>
       <c r="B239" t="n">
         <v>79018</v>
@@ -25299,14 +25279,14 @@
       <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>440734</v>
+        <v>440395</v>
       </c>
       <c r="R239" t="n">
-        <v>6762076</v>
+        <v>6762359</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25336,19 +25316,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z239" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA239" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB239" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -25363,19 +25333,19 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127282911</v>
+        <v>127273778</v>
       </c>
       <c r="B240" t="n">
         <v>79018</v>
@@ -25406,14 +25376,14 @@
       <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>440874</v>
+        <v>440734</v>
       </c>
       <c r="R240" t="n">
-        <v>6762606</v>
+        <v>6762076</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25443,9 +25413,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA240" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB240" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -25460,19 +25440,19 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>127283123</v>
+        <v>127282911</v>
       </c>
       <c r="B241" t="n">
         <v>79018</v>
@@ -25503,14 +25483,14 @@
       <c r="I241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>440917</v>
+        <v>440874</v>
       </c>
       <c r="R241" t="n">
-        <v>6762578</v>
+        <v>6762606</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25557,19 +25537,19 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>127271487</v>
+        <v>127271764</v>
       </c>
       <c r="B242" t="n">
         <v>79018</v>
@@ -25600,17 +25580,17 @@
       <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>440596</v>
+        <v>440418</v>
       </c>
       <c r="R242" t="n">
-        <v>6762126</v>
+        <v>6762449</v>
       </c>
       <c r="S242" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -25639,7 +25619,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -25649,7 +25629,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -25664,60 +25644,65 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127283132</v>
+        <v>127275970</v>
       </c>
       <c r="B243" t="n">
-        <v>79018</v>
+        <v>5197</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>440679</v>
+        <v>440685</v>
       </c>
       <c r="R243" t="n">
-        <v>6762203</v>
+        <v>6762673</v>
       </c>
       <c r="S243" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -25744,9 +25729,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA243" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB243" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -25761,22 +25756,22 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>127271764</v>
+        <v>127275615</v>
       </c>
       <c r="B244" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25784,34 +25779,39 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P244" t="inlineStr">
         <is>
           <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>440418</v>
+        <v>440778</v>
       </c>
       <c r="R244" t="n">
-        <v>6762449</v>
+        <v>6762552</v>
       </c>
       <c r="S244" t="n">
         <v>9</v>
@@ -25843,7 +25843,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -25853,7 +25853,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -25880,48 +25880,48 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127282894</v>
+        <v>127274466</v>
       </c>
       <c r="B245" t="n">
-        <v>79042</v>
+        <v>79018</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>440951</v>
+        <v>440914</v>
       </c>
       <c r="R245" t="n">
-        <v>6762514</v>
+        <v>6762585</v>
       </c>
       <c r="S245" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -25948,9 +25948,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA245" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -25965,22 +25975,22 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127282891</v>
+        <v>127272935</v>
       </c>
       <c r="B246" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25988,37 +25998,37 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>440416</v>
+        <v>440613</v>
       </c>
       <c r="R246" t="n">
-        <v>6762406</v>
+        <v>6762174</v>
       </c>
       <c r="S246" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -26045,9 +26055,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AA246" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -26062,19 +26082,19 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>127274466</v>
+        <v>127272422</v>
       </c>
       <c r="B247" t="n">
         <v>79018</v>
@@ -26105,17 +26125,17 @@
       <c r="I247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>440914</v>
+        <v>440682</v>
       </c>
       <c r="R247" t="n">
-        <v>6762585</v>
+        <v>6762093</v>
       </c>
       <c r="S247" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -26144,7 +26164,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -26154,7 +26174,12 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>Garnlav på äldre tall, sannoligt äldre än 200 år</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -26169,19 +26194,19 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>127272422</v>
+        <v>127270746</v>
       </c>
       <c r="B248" t="n">
         <v>79018</v>
@@ -26212,17 +26237,17 @@
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>440682</v>
+        <v>440308</v>
       </c>
       <c r="R248" t="n">
-        <v>6762093</v>
+        <v>6762456</v>
       </c>
       <c r="S248" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -26262,11 +26287,6 @@
       <c r="AB248" t="inlineStr">
         <is>
           <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC248" t="inlineStr">
-        <is>
-          <t>Garnlav på äldre tall, sannoligt äldre än 200 år</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26281,12 +26301,12 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
@@ -26400,48 +26420,48 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>127272935</v>
+        <v>127282894</v>
       </c>
       <c r="B250" t="n">
-        <v>79018</v>
+        <v>79042</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>440613</v>
+        <v>440951</v>
       </c>
       <c r="R250" t="n">
-        <v>6762174</v>
+        <v>6762514</v>
       </c>
       <c r="S250" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -26468,19 +26488,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z250" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AA250" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB250" t="inlineStr">
-        <is>
-          <t>12:31</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -26495,22 +26505,22 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>127270746</v>
+        <v>127282891</v>
       </c>
       <c r="B251" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26518,37 +26528,37 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>440308</v>
+        <v>440416</v>
       </c>
       <c r="R251" t="n">
-        <v>6762456</v>
+        <v>6762406</v>
       </c>
       <c r="S251" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -26575,19 +26585,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z251" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB251" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -26602,12 +26602,12 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
@@ -27052,7 +27052,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>127282916</v>
+        <v>127282928</v>
       </c>
       <c r="B256" t="n">
         <v>79018</v>
@@ -27087,10 +27087,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>440930</v>
+        <v>440441</v>
       </c>
       <c r="R256" t="n">
-        <v>6762495</v>
+        <v>6762452</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -27149,7 +27149,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>127274471</v>
+        <v>127282908</v>
       </c>
       <c r="B257" t="n">
         <v>79018</v>
@@ -27180,14 +27180,14 @@
       <c r="I257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>440700</v>
+        <v>440801</v>
       </c>
       <c r="R257" t="n">
-        <v>6762179</v>
+        <v>6762524</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -27217,19 +27217,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z257" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA257" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB257" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -27244,19 +27234,19 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>127282928</v>
+        <v>127271449</v>
       </c>
       <c r="B258" t="n">
         <v>79018</v>
@@ -27287,14 +27277,14 @@
       <c r="I258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>440441</v>
+        <v>440580</v>
       </c>
       <c r="R258" t="n">
-        <v>6762452</v>
+        <v>6762134</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -27324,9 +27314,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA258" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -27341,22 +27341,22 @@
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>127282908</v>
+        <v>127282893</v>
       </c>
       <c r="B259" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -27364,21 +27364,21 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -27388,10 +27388,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>440801</v>
+        <v>440925</v>
       </c>
       <c r="R259" t="n">
-        <v>6762524</v>
+        <v>6762502</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -27450,7 +27450,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>127271449</v>
+        <v>127282916</v>
       </c>
       <c r="B260" t="n">
         <v>79018</v>
@@ -27481,14 +27481,14 @@
       <c r="I260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>440580</v>
+        <v>440930</v>
       </c>
       <c r="R260" t="n">
-        <v>6762134</v>
+        <v>6762495</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27518,19 +27518,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z260" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA260" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB260" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -27545,22 +27535,22 @@
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>127282893</v>
+        <v>127274471</v>
       </c>
       <c r="B261" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -27568,34 +27558,34 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>440925</v>
+        <v>440700</v>
       </c>
       <c r="R261" t="n">
-        <v>6762502</v>
+        <v>6762179</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27625,9 +27615,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA261" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -27642,19 +27642,19 @@
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>127282923</v>
+        <v>127282905</v>
       </c>
       <c r="B262" t="n">
         <v>79018</v>
@@ -27689,10 +27689,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>440658</v>
+        <v>440780</v>
       </c>
       <c r="R262" t="n">
-        <v>6762202</v>
+        <v>6762578</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27751,7 +27751,7 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>127275346</v>
+        <v>127282934</v>
       </c>
       <c r="B263" t="n">
         <v>79018</v>
@@ -27782,17 +27782,17 @@
       <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>440853</v>
+        <v>440387</v>
       </c>
       <c r="R263" t="n">
-        <v>6762514</v>
+        <v>6762369</v>
       </c>
       <c r="S263" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -27819,19 +27819,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z263" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA263" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB263" t="inlineStr">
-        <is>
-          <t>14:33</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -27846,19 +27836,19 @@
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>127282921</v>
+        <v>127275330</v>
       </c>
       <c r="B264" t="n">
         <v>79018</v>
@@ -27889,17 +27879,17 @@
       <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>440680</v>
+        <v>440868</v>
       </c>
       <c r="R264" t="n">
-        <v>6762218</v>
+        <v>6762512</v>
       </c>
       <c r="S264" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -27926,9 +27916,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA264" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB264" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -27943,60 +27943,60 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>127272941</v>
+        <v>127282923</v>
       </c>
       <c r="B265" t="n">
-        <v>79042</v>
+        <v>79018</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>440613</v>
+        <v>440658</v>
       </c>
       <c r="R265" t="n">
-        <v>6762174</v>
+        <v>6762202</v>
       </c>
       <c r="S265" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -28023,19 +28023,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z265" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB265" t="inlineStr">
-        <is>
-          <t>12:31</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -28050,19 +28040,19 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>127282934</v>
+        <v>127275346</v>
       </c>
       <c r="B266" t="n">
         <v>79018</v>
@@ -28093,17 +28083,17 @@
       <c r="I266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>440387</v>
+        <v>440853</v>
       </c>
       <c r="R266" t="n">
-        <v>6762369</v>
+        <v>6762514</v>
       </c>
       <c r="S266" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -28130,9 +28120,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA266" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB266" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -28147,57 +28147,57 @@
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>127274680</v>
+        <v>127282921</v>
       </c>
       <c r="B267" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>440689</v>
+        <v>440680</v>
       </c>
       <c r="R267" t="n">
-        <v>6762214</v>
+        <v>6762218</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -28227,19 +28227,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z267" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA267" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB267" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -28254,60 +28244,60 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>127282905</v>
+        <v>127272941</v>
       </c>
       <c r="B268" t="n">
-        <v>79018</v>
+        <v>79042</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>440780</v>
+        <v>440613</v>
       </c>
       <c r="R268" t="n">
-        <v>6762578</v>
+        <v>6762174</v>
       </c>
       <c r="S268" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -28334,9 +28324,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AA268" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -28351,22 +28351,22 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>127275330</v>
+        <v>127276264</v>
       </c>
       <c r="B269" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -28374,37 +28374,42 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>440868</v>
+        <v>440642</v>
       </c>
       <c r="R269" t="n">
-        <v>6762512</v>
+        <v>6762606</v>
       </c>
       <c r="S269" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -28433,7 +28438,7 @@
       </c>
       <c r="Z269" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
@@ -28443,7 +28448,7 @@
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -28458,62 +28463,57 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>127276264</v>
+        <v>127274680</v>
       </c>
       <c r="B270" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
-      <c r="M270" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P270" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>440642</v>
+        <v>440689</v>
       </c>
       <c r="R270" t="n">
-        <v>6762606</v>
+        <v>6762214</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28545,7 +28545,7 @@
       </c>
       <c r="Z270" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
@@ -28555,7 +28555,7 @@
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD270" t="b">

--- a/artfynd/A 29945-2025 artfynd.xlsx
+++ b/artfynd/A 29945-2025 artfynd.xlsx
@@ -11348,7 +11348,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127272192</v>
+        <v>127282929</v>
       </c>
       <c r="B104" t="n">
         <v>79018</v>
@@ -11379,17 +11379,17 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>440522</v>
+        <v>440440</v>
       </c>
       <c r="R104" t="n">
-        <v>6762378</v>
+        <v>6762463</v>
       </c>
       <c r="S104" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11416,19 +11416,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>11:38</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11443,19 +11433,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127275526</v>
+        <v>127272192</v>
       </c>
       <c r="B105" t="n">
         <v>79018</v>
@@ -11486,17 +11476,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>440688</v>
+        <v>440522</v>
       </c>
       <c r="R105" t="n">
-        <v>6762488</v>
+        <v>6762378</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11525,7 +11515,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11535,12 +11525,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11555,19 +11540,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127274454</v>
+        <v>127283121</v>
       </c>
       <c r="B106" t="n">
         <v>79018</v>
@@ -11598,17 +11583,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>440926</v>
+        <v>440883</v>
       </c>
       <c r="R106" t="n">
-        <v>6762599</v>
+        <v>6762587</v>
       </c>
       <c r="S106" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11635,19 +11620,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11662,19 +11637,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127282929</v>
+        <v>127275526</v>
       </c>
       <c r="B107" t="n">
         <v>79018</v>
@@ -11705,14 +11680,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>440440</v>
+        <v>440688</v>
       </c>
       <c r="R107" t="n">
-        <v>6762463</v>
+        <v>6762488</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11742,9 +11717,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11759,19 +11749,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127283121</v>
+        <v>127274454</v>
       </c>
       <c r="B108" t="n">
         <v>79018</v>
@@ -11802,17 +11792,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>440883</v>
+        <v>440926</v>
       </c>
       <c r="R108" t="n">
-        <v>6762587</v>
+        <v>6762599</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11839,9 +11829,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11856,12 +11856,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -13540,10 +13540,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127283139</v>
+        <v>127271992</v>
       </c>
       <c r="B125" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13551,34 +13551,39 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>440723</v>
+        <v>440647</v>
       </c>
       <c r="R125" t="n">
-        <v>6762373</v>
+        <v>6762125</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13608,9 +13613,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13625,19 +13640,19 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127283131</v>
+        <v>127283139</v>
       </c>
       <c r="B126" t="n">
         <v>79018</v>
@@ -13672,10 +13687,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>440682</v>
+        <v>440723</v>
       </c>
       <c r="R126" t="n">
-        <v>6762208</v>
+        <v>6762373</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13734,7 +13749,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127283135</v>
+        <v>127283131</v>
       </c>
       <c r="B127" t="n">
         <v>79018</v>
@@ -13769,10 +13784,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>440456</v>
+        <v>440682</v>
       </c>
       <c r="R127" t="n">
-        <v>6762461</v>
+        <v>6762208</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13831,7 +13846,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127273828</v>
+        <v>127283135</v>
       </c>
       <c r="B128" t="n">
         <v>79018</v>
@@ -13862,17 +13877,17 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>440882</v>
+        <v>440456</v>
       </c>
       <c r="R128" t="n">
-        <v>6762435</v>
+        <v>6762461</v>
       </c>
       <c r="S128" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13899,19 +13914,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13926,22 +13931,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127271992</v>
+        <v>127273828</v>
       </c>
       <c r="B129" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13949,42 +13954,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>440647</v>
+        <v>440882</v>
       </c>
       <c r="R129" t="n">
-        <v>6762125</v>
+        <v>6762435</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14038,12 +14038,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -17170,10 +17170,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127282900</v>
+        <v>127275098</v>
       </c>
       <c r="B160" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17181,34 +17181,39 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>440757</v>
+        <v>440679</v>
       </c>
       <c r="R160" t="n">
-        <v>6762544</v>
+        <v>6762388</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17238,9 +17243,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17255,22 +17270,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127276426</v>
+        <v>127274348</v>
       </c>
       <c r="B161" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17278,34 +17293,39 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>440582</v>
+        <v>440686</v>
       </c>
       <c r="R161" t="n">
-        <v>6762684</v>
+        <v>6762176</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17337,7 +17357,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17347,7 +17367,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17374,7 +17394,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127275877</v>
+        <v>127282900</v>
       </c>
       <c r="B162" t="n">
         <v>79018</v>
@@ -17405,14 +17425,14 @@
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>440732</v>
+        <v>440757</v>
       </c>
       <c r="R162" t="n">
-        <v>6762635</v>
+        <v>6762544</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17442,19 +17462,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17469,19 +17479,19 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127273900</v>
+        <v>127276426</v>
       </c>
       <c r="B163" t="n">
         <v>79018</v>
@@ -17512,17 +17522,17 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>440903</v>
+        <v>440582</v>
       </c>
       <c r="R163" t="n">
-        <v>6762450</v>
+        <v>6762684</v>
       </c>
       <c r="S163" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -17551,7 +17561,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -17561,7 +17571,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17576,19 +17586,19 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127282902</v>
+        <v>127275877</v>
       </c>
       <c r="B164" t="n">
         <v>79018</v>
@@ -17619,14 +17629,14 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>440760</v>
+        <v>440732</v>
       </c>
       <c r="R164" t="n">
-        <v>6762569</v>
+        <v>6762635</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17656,9 +17666,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17673,19 +17693,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127273086</v>
+        <v>127273900</v>
       </c>
       <c r="B165" t="n">
         <v>79018</v>
@@ -17720,10 +17740,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>440694</v>
+        <v>440903</v>
       </c>
       <c r="R165" t="n">
-        <v>6762204</v>
+        <v>6762450</v>
       </c>
       <c r="S165" t="n">
         <v>9</v>
@@ -17755,7 +17775,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -17765,7 +17785,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17792,7 +17812,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127283137</v>
+        <v>127282902</v>
       </c>
       <c r="B166" t="n">
         <v>79018</v>
@@ -17823,14 +17843,14 @@
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>440354</v>
+        <v>440760</v>
       </c>
       <c r="R166" t="n">
-        <v>6762415</v>
+        <v>6762569</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17877,22 +17897,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127275098</v>
+        <v>127273086</v>
       </c>
       <c r="B167" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17900,42 +17920,37 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>440679</v>
+        <v>440694</v>
       </c>
       <c r="R167" t="n">
-        <v>6762388</v>
+        <v>6762204</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -17964,7 +17979,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -17974,7 +17989,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17989,22 +18004,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127274348</v>
+        <v>127283137</v>
       </c>
       <c r="B168" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18012,39 +18027,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>440686</v>
+        <v>440354</v>
       </c>
       <c r="R168" t="n">
-        <v>6762176</v>
+        <v>6762415</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18074,19 +18084,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18101,12 +18101,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
@@ -19969,48 +19969,53 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127276155</v>
+        <v>127274877</v>
       </c>
       <c r="B187" t="n">
-        <v>8450</v>
+        <v>57821</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>440657</v>
+        <v>440752</v>
       </c>
       <c r="R187" t="n">
-        <v>6762603</v>
+        <v>6762337</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -20039,7 +20044,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20049,7 +20054,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20076,45 +20081,45 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127282924</v>
+        <v>127276155</v>
       </c>
       <c r="B188" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>440623</v>
+        <v>440657</v>
       </c>
       <c r="R188" t="n">
-        <v>6762194</v>
+        <v>6762603</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20144,9 +20149,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20161,19 +20176,19 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127283136</v>
+        <v>127282924</v>
       </c>
       <c r="B189" t="n">
         <v>79018</v>
@@ -20204,14 +20219,14 @@
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>440394</v>
+        <v>440623</v>
       </c>
       <c r="R189" t="n">
-        <v>6762413</v>
+        <v>6762194</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20258,19 +20273,19 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127283138</v>
+        <v>127283136</v>
       </c>
       <c r="B190" t="n">
         <v>79018</v>
@@ -20305,10 +20320,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>440335</v>
+        <v>440394</v>
       </c>
       <c r="R190" t="n">
-        <v>6762400</v>
+        <v>6762413</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20367,7 +20382,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127282907</v>
+        <v>127283138</v>
       </c>
       <c r="B191" t="n">
         <v>79018</v>
@@ -20398,14 +20413,14 @@
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>440793</v>
+        <v>440335</v>
       </c>
       <c r="R191" t="n">
-        <v>6762525</v>
+        <v>6762400</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20452,19 +20467,19 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127283118</v>
+        <v>127282907</v>
       </c>
       <c r="B192" t="n">
         <v>79018</v>
@@ -20495,14 +20510,14 @@
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>440868</v>
+        <v>440793</v>
       </c>
       <c r="R192" t="n">
-        <v>6762583</v>
+        <v>6762525</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20549,19 +20564,19 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127283113</v>
+        <v>127283118</v>
       </c>
       <c r="B193" t="n">
         <v>79018</v>
@@ -20596,10 +20611,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>440768</v>
+        <v>440868</v>
       </c>
       <c r="R193" t="n">
-        <v>6762554</v>
+        <v>6762583</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20658,10 +20673,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127274877</v>
+        <v>127283113</v>
       </c>
       <c r="B194" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20669,42 +20684,37 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>440752</v>
+        <v>440768</v>
       </c>
       <c r="R194" t="n">
-        <v>6762337</v>
+        <v>6762554</v>
       </c>
       <c r="S194" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -20731,19 +20741,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20758,19 +20758,19 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127276018</v>
+        <v>127283124</v>
       </c>
       <c r="B195" t="n">
         <v>79018</v>
@@ -20801,14 +20801,14 @@
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>440697</v>
+        <v>440965</v>
       </c>
       <c r="R195" t="n">
-        <v>6762625</v>
+        <v>6762540</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20838,19 +20838,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20865,19 +20855,19 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127275350</v>
+        <v>127272147</v>
       </c>
       <c r="B196" t="n">
         <v>79018</v>
@@ -20912,10 +20902,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>440851</v>
+        <v>440498</v>
       </c>
       <c r="R196" t="n">
-        <v>6762513</v>
+        <v>6762428</v>
       </c>
       <c r="S196" t="n">
         <v>9</v>
@@ -20947,7 +20937,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -20957,7 +20947,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20984,10 +20974,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127283124</v>
+        <v>127274677</v>
       </c>
       <c r="B197" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20995,34 +20985,39 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>440965</v>
+        <v>440689</v>
       </c>
       <c r="R197" t="n">
-        <v>6762540</v>
+        <v>6762214</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21052,9 +21047,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21069,19 +21074,19 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127272147</v>
+        <v>127276018</v>
       </c>
       <c r="B198" t="n">
         <v>79018</v>
@@ -21112,17 +21117,17 @@
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>440498</v>
+        <v>440697</v>
       </c>
       <c r="R198" t="n">
-        <v>6762428</v>
+        <v>6762625</v>
       </c>
       <c r="S198" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -21151,7 +21156,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21161,7 +21166,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21176,22 +21181,22 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127274677</v>
+        <v>127275350</v>
       </c>
       <c r="B199" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21199,42 +21204,37 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>440689</v>
+        <v>440851</v>
       </c>
       <c r="R199" t="n">
-        <v>6762214</v>
+        <v>6762513</v>
       </c>
       <c r="S199" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21288,12 +21288,12 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
@@ -23146,10 +23146,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127283100</v>
+        <v>127282898</v>
       </c>
       <c r="B218" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23157,34 +23157,34 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>440686</v>
+        <v>440741</v>
       </c>
       <c r="R218" t="n">
-        <v>6762630</v>
+        <v>6762609</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23231,44 +23231,44 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127283107</v>
+        <v>127283122</v>
       </c>
       <c r="B219" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -23278,10 +23278,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>440636</v>
+        <v>440912</v>
       </c>
       <c r="R219" t="n">
-        <v>6762585</v>
+        <v>6762579</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23340,7 +23340,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127282898</v>
+        <v>127282915</v>
       </c>
       <c r="B220" t="n">
         <v>79018</v>
@@ -23375,10 +23375,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>440741</v>
+        <v>440946</v>
       </c>
       <c r="R220" t="n">
-        <v>6762609</v>
+        <v>6762514</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23437,7 +23437,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>127283122</v>
+        <v>127275040</v>
       </c>
       <c r="B221" t="n">
         <v>79018</v>
@@ -23468,14 +23468,14 @@
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>440912</v>
+        <v>440745</v>
       </c>
       <c r="R221" t="n">
-        <v>6762579</v>
+        <v>6762369</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23505,9 +23505,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -23522,19 +23537,19 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>127282915</v>
+        <v>127282899</v>
       </c>
       <c r="B222" t="n">
         <v>79018</v>
@@ -23569,10 +23584,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>440946</v>
+        <v>440763</v>
       </c>
       <c r="R222" t="n">
-        <v>6762514</v>
+        <v>6762529</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23631,10 +23646,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>127275040</v>
+        <v>127283100</v>
       </c>
       <c r="B223" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23642,34 +23657,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>440745</v>
+        <v>440686</v>
       </c>
       <c r="R223" t="n">
-        <v>6762369</v>
+        <v>6762630</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23699,24 +23714,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z223" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA223" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB223" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -23731,57 +23731,57 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>127282899</v>
+        <v>127283107</v>
       </c>
       <c r="B224" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>440763</v>
+        <v>440636</v>
       </c>
       <c r="R224" t="n">
-        <v>6762529</v>
+        <v>6762585</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23828,22 +23828,22 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>127283141</v>
+        <v>127283106</v>
       </c>
       <c r="B225" t="n">
-        <v>78685</v>
+        <v>78777</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23851,21 +23851,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23875,10 +23875,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>440651</v>
+        <v>440504</v>
       </c>
       <c r="R225" t="n">
-        <v>6762611</v>
+        <v>6762388</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23937,10 +23937,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>127283106</v>
+        <v>127283141</v>
       </c>
       <c r="B226" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23948,21 +23948,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23972,10 +23972,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>440504</v>
+        <v>440651</v>
       </c>
       <c r="R226" t="n">
-        <v>6762388</v>
+        <v>6762611</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24850,48 +24850,53 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>127283123</v>
+        <v>127275970</v>
       </c>
       <c r="B235" t="n">
-        <v>79018</v>
+        <v>5197</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>440917</v>
+        <v>440685</v>
       </c>
       <c r="R235" t="n">
-        <v>6762578</v>
+        <v>6762673</v>
       </c>
       <c r="S235" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -24918,9 +24923,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA235" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -24935,19 +24950,19 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>127282930</v>
+        <v>127283123</v>
       </c>
       <c r="B236" t="n">
         <v>79018</v>
@@ -24978,14 +24993,14 @@
       <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>440417</v>
+        <v>440917</v>
       </c>
       <c r="R236" t="n">
-        <v>6762463</v>
+        <v>6762578</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -25032,19 +25047,19 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>127271487</v>
+        <v>127282930</v>
       </c>
       <c r="B237" t="n">
         <v>79018</v>
@@ -25075,14 +25090,14 @@
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>440596</v>
+        <v>440417</v>
       </c>
       <c r="R237" t="n">
-        <v>6762126</v>
+        <v>6762463</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25112,19 +25127,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z237" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA237" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB237" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25139,19 +25144,19 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>127283132</v>
+        <v>127271487</v>
       </c>
       <c r="B238" t="n">
         <v>79018</v>
@@ -25182,14 +25187,14 @@
       <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>440679</v>
+        <v>440596</v>
       </c>
       <c r="R238" t="n">
-        <v>6762203</v>
+        <v>6762126</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25219,9 +25224,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -25236,19 +25251,19 @@
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>127282933</v>
+        <v>127283132</v>
       </c>
       <c r="B239" t="n">
         <v>79018</v>
@@ -25279,14 +25294,14 @@
       <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>440395</v>
+        <v>440679</v>
       </c>
       <c r="R239" t="n">
-        <v>6762359</v>
+        <v>6762203</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25333,19 +25348,19 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>127273778</v>
+        <v>127282933</v>
       </c>
       <c r="B240" t="n">
         <v>79018</v>
@@ -25376,14 +25391,14 @@
       <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>440734</v>
+        <v>440395</v>
       </c>
       <c r="R240" t="n">
-        <v>6762076</v>
+        <v>6762359</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25413,19 +25428,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z240" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA240" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB240" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -25440,19 +25445,19 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>127282911</v>
+        <v>127273778</v>
       </c>
       <c r="B241" t="n">
         <v>79018</v>
@@ -25483,14 +25488,14 @@
       <c r="I241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>440874</v>
+        <v>440734</v>
       </c>
       <c r="R241" t="n">
-        <v>6762606</v>
+        <v>6762076</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25520,9 +25525,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB241" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -25537,19 +25552,19 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>127271764</v>
+        <v>127282911</v>
       </c>
       <c r="B242" t="n">
         <v>79018</v>
@@ -25580,17 +25595,17 @@
       <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>440418</v>
+        <v>440874</v>
       </c>
       <c r="R242" t="n">
-        <v>6762449</v>
+        <v>6762606</v>
       </c>
       <c r="S242" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -25617,19 +25632,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z242" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA242" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB242" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -25644,62 +25649,57 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>127275970</v>
+        <v>127271764</v>
       </c>
       <c r="B243" t="n">
-        <v>5197</v>
+        <v>79018</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P243" t="inlineStr">
         <is>
           <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>440685</v>
+        <v>440418</v>
       </c>
       <c r="R243" t="n">
-        <v>6762673</v>
+        <v>6762449</v>
       </c>
       <c r="S243" t="n">
         <v>9</v>
@@ -25731,7 +25731,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -25741,7 +25741,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -27654,10 +27654,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>127282905</v>
+        <v>127276264</v>
       </c>
       <c r="B262" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -27665,34 +27665,39 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>440780</v>
+        <v>440642</v>
       </c>
       <c r="R262" t="n">
-        <v>6762578</v>
+        <v>6762606</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27722,9 +27727,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA262" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -27739,19 +27754,19 @@
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>127282934</v>
+        <v>127282905</v>
       </c>
       <c r="B263" t="n">
         <v>79018</v>
@@ -27786,10 +27801,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>440387</v>
+        <v>440780</v>
       </c>
       <c r="R263" t="n">
-        <v>6762369</v>
+        <v>6762578</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27848,7 +27863,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>127275330</v>
+        <v>127282934</v>
       </c>
       <c r="B264" t="n">
         <v>79018</v>
@@ -27879,17 +27894,17 @@
       <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>440868</v>
+        <v>440387</v>
       </c>
       <c r="R264" t="n">
-        <v>6762512</v>
+        <v>6762369</v>
       </c>
       <c r="S264" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -27916,19 +27931,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z264" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA264" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB264" t="inlineStr">
-        <is>
-          <t>14:32</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -27943,19 +27948,19 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>127282923</v>
+        <v>127275330</v>
       </c>
       <c r="B265" t="n">
         <v>79018</v>
@@ -27986,17 +27991,17 @@
       <c r="I265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>440658</v>
+        <v>440868</v>
       </c>
       <c r="R265" t="n">
-        <v>6762202</v>
+        <v>6762512</v>
       </c>
       <c r="S265" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -28023,9 +28028,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -28040,19 +28055,19 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>127275346</v>
+        <v>127282923</v>
       </c>
       <c r="B266" t="n">
         <v>79018</v>
@@ -28083,17 +28098,17 @@
       <c r="I266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>440853</v>
+        <v>440658</v>
       </c>
       <c r="R266" t="n">
-        <v>6762514</v>
+        <v>6762202</v>
       </c>
       <c r="S266" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -28120,19 +28135,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z266" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA266" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB266" t="inlineStr">
-        <is>
-          <t>14:33</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -28147,19 +28152,19 @@
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>127282921</v>
+        <v>127275346</v>
       </c>
       <c r="B267" t="n">
         <v>79018</v>
@@ -28190,17 +28195,17 @@
       <c r="I267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>440680</v>
+        <v>440853</v>
       </c>
       <c r="R267" t="n">
-        <v>6762218</v>
+        <v>6762514</v>
       </c>
       <c r="S267" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -28227,9 +28232,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA267" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -28244,60 +28259,60 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>127272941</v>
+        <v>127282921</v>
       </c>
       <c r="B268" t="n">
-        <v>79042</v>
+        <v>79018</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>440613</v>
+        <v>440680</v>
       </c>
       <c r="R268" t="n">
-        <v>6762174</v>
+        <v>6762218</v>
       </c>
       <c r="S268" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -28324,19 +28339,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z268" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AA268" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB268" t="inlineStr">
-        <is>
-          <t>12:31</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -28351,65 +28356,60 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>127276264</v>
+        <v>127272941</v>
       </c>
       <c r="B269" t="n">
-        <v>57658</v>
+        <v>79042</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>440642</v>
+        <v>440613</v>
       </c>
       <c r="R269" t="n">
-        <v>6762606</v>
+        <v>6762174</v>
       </c>
       <c r="S269" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
       </c>
       <c r="Z269" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
@@ -28448,7 +28448,7 @@
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -28463,12 +28463,12 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>

--- a/artfynd/A 29945-2025 artfynd.xlsx
+++ b/artfynd/A 29945-2025 artfynd.xlsx
@@ -11348,10 +11348,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127282929</v>
+        <v>127283121</v>
       </c>
       <c r="B104" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11379,14 +11379,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>440440</v>
+        <v>440883</v>
       </c>
       <c r="R104" t="n">
-        <v>6762463</v>
+        <v>6762587</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11433,22 +11433,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127272192</v>
+        <v>127282929</v>
       </c>
       <c r="B105" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11476,17 +11476,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>440522</v>
+        <v>440440</v>
       </c>
       <c r="R105" t="n">
-        <v>6762378</v>
+        <v>6762463</v>
       </c>
       <c r="S105" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11513,19 +11513,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>11:38</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11540,22 +11530,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127283121</v>
+        <v>127274454</v>
       </c>
       <c r="B106" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11583,17 +11573,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>440883</v>
+        <v>440926</v>
       </c>
       <c r="R106" t="n">
-        <v>6762587</v>
+        <v>6762599</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11620,9 +11610,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11637,22 +11637,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127275526</v>
+        <v>127272192</v>
       </c>
       <c r="B107" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11680,17 +11680,17 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>440688</v>
+        <v>440522</v>
       </c>
       <c r="R107" t="n">
-        <v>6762488</v>
+        <v>6762378</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11729,12 +11729,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11749,22 +11744,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127274454</v>
+        <v>127275526</v>
       </c>
       <c r="B108" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11792,17 +11787,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>440926</v>
+        <v>440688</v>
       </c>
       <c r="R108" t="n">
-        <v>6762599</v>
+        <v>6762488</v>
       </c>
       <c r="S108" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11831,7 +11826,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11841,7 +11836,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11856,44 +11856,44 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127273727</v>
+        <v>127272135</v>
       </c>
       <c r="B109" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11903,10 +11903,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>440754</v>
+        <v>440647</v>
       </c>
       <c r="R109" t="n">
-        <v>6762035</v>
+        <v>6762125</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11978,7 +11978,7 @@
         <v>127282909</v>
       </c>
       <c r="B110" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12072,10 +12072,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127282922</v>
+        <v>127282896</v>
       </c>
       <c r="B111" t="n">
-        <v>79018</v>
+        <v>78778</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12083,21 +12083,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12107,10 +12107,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>440685</v>
+        <v>440416</v>
       </c>
       <c r="R111" t="n">
-        <v>6762213</v>
+        <v>6762406</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12172,7 +12172,7 @@
         <v>127282903</v>
       </c>
       <c r="B112" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12266,10 +12266,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127274251</v>
+        <v>127273727</v>
       </c>
       <c r="B113" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12301,10 +12301,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>440687</v>
+        <v>440754</v>
       </c>
       <c r="R113" t="n">
-        <v>6762120</v>
+        <v>6762035</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12373,10 +12373,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127282896</v>
+        <v>127282922</v>
       </c>
       <c r="B114" t="n">
-        <v>78776</v>
+        <v>79020</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12384,21 +12384,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12408,10 +12408,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>440416</v>
+        <v>440685</v>
       </c>
       <c r="R114" t="n">
-        <v>6762406</v>
+        <v>6762213</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12470,10 +12470,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127273473</v>
+        <v>127274251</v>
       </c>
       <c r="B115" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12481,39 +12481,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>440721</v>
+        <v>440687</v>
       </c>
       <c r="R115" t="n">
-        <v>6761996</v>
+        <v>6762120</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12582,45 +12577,50 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127272135</v>
+        <v>127273473</v>
       </c>
       <c r="B116" t="n">
-        <v>8450</v>
+        <v>57663</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>440647</v>
+        <v>440721</v>
       </c>
       <c r="R116" t="n">
-        <v>6762125</v>
+        <v>6761996</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12689,40 +12689,35 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127274057</v>
+        <v>127274061</v>
       </c>
       <c r="B117" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
@@ -12801,10 +12796,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127273755</v>
+        <v>127271820</v>
       </c>
       <c r="B118" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12832,17 +12827,17 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>440744</v>
+        <v>440446</v>
       </c>
       <c r="R118" t="n">
-        <v>6762065</v>
+        <v>6762469</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12871,7 +12866,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12881,7 +12876,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12896,22 +12891,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127276304</v>
+        <v>127274057</v>
       </c>
       <c r="B119" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12919,34 +12914,39 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>440642</v>
+        <v>440706</v>
       </c>
       <c r="R119" t="n">
-        <v>6762606</v>
+        <v>6762058</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12978,7 +12978,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13015,10 +13015,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127275131</v>
+        <v>127273755</v>
       </c>
       <c r="B120" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13050,10 +13050,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>440709</v>
+        <v>440744</v>
       </c>
       <c r="R120" t="n">
-        <v>6762405</v>
+        <v>6762065</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13122,10 +13122,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127271820</v>
+        <v>127276304</v>
       </c>
       <c r="B121" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13153,17 +13153,17 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>440446</v>
+        <v>440642</v>
       </c>
       <c r="R121" t="n">
-        <v>6762469</v>
+        <v>6762606</v>
       </c>
       <c r="S121" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13202,7 +13202,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13217,44 +13217,44 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127274061</v>
+        <v>127275131</v>
       </c>
       <c r="B122" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13264,10 +13264,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>440706</v>
+        <v>440709</v>
       </c>
       <c r="R122" t="n">
-        <v>6762058</v>
+        <v>6762405</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13339,7 +13339,7 @@
         <v>127283110</v>
       </c>
       <c r="B123" t="n">
-        <v>79019</v>
+        <v>79021</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>127275968</v>
       </c>
       <c r="B124" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13540,10 +13540,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127271992</v>
+        <v>127283135</v>
       </c>
       <c r="B125" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13551,39 +13551,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>440647</v>
+        <v>440456</v>
       </c>
       <c r="R125" t="n">
-        <v>6762125</v>
+        <v>6762461</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13613,19 +13608,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13640,22 +13625,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127283139</v>
+        <v>127283131</v>
       </c>
       <c r="B126" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13687,10 +13672,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>440723</v>
+        <v>440682</v>
       </c>
       <c r="R126" t="n">
-        <v>6762373</v>
+        <v>6762208</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13749,10 +13734,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127283131</v>
+        <v>127283139</v>
       </c>
       <c r="B127" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13784,10 +13769,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>440682</v>
+        <v>440723</v>
       </c>
       <c r="R127" t="n">
-        <v>6762208</v>
+        <v>6762373</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13846,10 +13831,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127283135</v>
+        <v>127273828</v>
       </c>
       <c r="B128" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13877,17 +13862,17 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>440456</v>
+        <v>440882</v>
       </c>
       <c r="R128" t="n">
-        <v>6762461</v>
+        <v>6762435</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13914,9 +13899,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13931,22 +13926,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127273828</v>
+        <v>127271992</v>
       </c>
       <c r="B129" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13954,37 +13949,42 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>440882</v>
+        <v>440647</v>
       </c>
       <c r="R129" t="n">
-        <v>6762435</v>
+        <v>6762125</v>
       </c>
       <c r="S129" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14038,22 +14038,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127274657</v>
+        <v>127276148</v>
       </c>
       <c r="B130" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14061,34 +14061,39 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>440689</v>
+        <v>440657</v>
       </c>
       <c r="R130" t="n">
-        <v>6762214</v>
+        <v>6762603</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14120,7 +14125,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14130,12 +14135,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14162,10 +14162,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127283117</v>
+        <v>127272305</v>
       </c>
       <c r="B131" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14173,34 +14173,39 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>440863</v>
+        <v>440675</v>
       </c>
       <c r="R131" t="n">
-        <v>6762603</v>
+        <v>6762165</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14230,9 +14235,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Diameter ca 4 till 5 cm</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14247,22 +14267,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127273051</v>
+        <v>127271765</v>
       </c>
       <c r="B132" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14270,37 +14290,42 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>440681</v>
+        <v>440627</v>
       </c>
       <c r="R132" t="n">
-        <v>6762197</v>
+        <v>6762119</v>
       </c>
       <c r="S132" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14329,7 +14354,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14339,7 +14364,12 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Miljöbild för området</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14354,22 +14384,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127282932</v>
+        <v>127276450</v>
       </c>
       <c r="B133" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14377,34 +14407,39 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>440427</v>
+        <v>440582</v>
       </c>
       <c r="R133" t="n">
-        <v>6762470</v>
+        <v>6762684</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14434,9 +14469,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14451,44 +14496,44 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127282912</v>
+        <v>127282895</v>
       </c>
       <c r="B134" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14498,10 +14543,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>440936</v>
+        <v>440382</v>
       </c>
       <c r="R134" t="n">
-        <v>6762564</v>
+        <v>6762379</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14560,45 +14605,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127282926</v>
+        <v>127283108</v>
       </c>
       <c r="B135" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>440497</v>
+        <v>440442</v>
       </c>
       <c r="R135" t="n">
-        <v>6762331</v>
+        <v>6762471</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14645,22 +14690,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127283130</v>
+        <v>127274657</v>
       </c>
       <c r="B136" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14688,14 +14733,14 @@
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>440697</v>
+        <v>440689</v>
       </c>
       <c r="R136" t="n">
-        <v>6762237</v>
+        <v>6762214</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14725,9 +14770,24 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14742,22 +14802,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127276216</v>
+        <v>127273051</v>
       </c>
       <c r="B137" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14785,17 +14845,17 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>440657</v>
+        <v>440681</v>
       </c>
       <c r="R137" t="n">
-        <v>6762603</v>
+        <v>6762197</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14824,7 +14884,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14834,7 +14894,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14849,22 +14909,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127273488</v>
+        <v>127276216</v>
       </c>
       <c r="B138" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14896,10 +14956,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>440721</v>
+        <v>440657</v>
       </c>
       <c r="R138" t="n">
-        <v>6761996</v>
+        <v>6762603</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14931,7 +14991,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14941,7 +15001,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14968,10 +15028,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127276148</v>
+        <v>127273488</v>
       </c>
       <c r="B139" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14979,39 +15039,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>440657</v>
+        <v>440721</v>
       </c>
       <c r="R139" t="n">
-        <v>6762603</v>
+        <v>6761996</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15043,7 +15098,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15053,7 +15108,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15080,10 +15135,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127272305</v>
+        <v>127283109</v>
       </c>
       <c r="B140" t="n">
-        <v>57658</v>
+        <v>79021</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15091,39 +15146,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100049</v>
+        <v>230405</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>440675</v>
+        <v>440875</v>
       </c>
       <c r="R140" t="n">
-        <v>6762165</v>
+        <v>6762453</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15153,24 +15203,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Diameter ca 4 till 5 cm</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15185,22 +15220,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127271765</v>
+        <v>127282932</v>
       </c>
       <c r="B141" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15208,39 +15243,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>440627</v>
+        <v>440427</v>
       </c>
       <c r="R141" t="n">
-        <v>6762119</v>
+        <v>6762470</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15270,24 +15300,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Miljöbild för området</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15302,22 +15317,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127276450</v>
+        <v>127283117</v>
       </c>
       <c r="B142" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15325,39 +15340,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>440582</v>
+        <v>440863</v>
       </c>
       <c r="R142" t="n">
-        <v>6762684</v>
+        <v>6762603</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15387,19 +15397,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15414,57 +15414,57 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127283108</v>
+        <v>127282926</v>
       </c>
       <c r="B143" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>440442</v>
+        <v>440497</v>
       </c>
       <c r="R143" t="n">
-        <v>6762471</v>
+        <v>6762331</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15511,44 +15511,44 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127282895</v>
+        <v>127282912</v>
       </c>
       <c r="B144" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15558,10 +15558,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>440382</v>
+        <v>440936</v>
       </c>
       <c r="R144" t="n">
-        <v>6762379</v>
+        <v>6762564</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15620,10 +15620,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127283109</v>
+        <v>127283130</v>
       </c>
       <c r="B145" t="n">
-        <v>79019</v>
+        <v>79020</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15631,16 +15631,16 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -15655,10 +15655,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>440875</v>
+        <v>440697</v>
       </c>
       <c r="R145" t="n">
-        <v>6762453</v>
+        <v>6762237</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15717,32 +15717,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127283142</v>
+        <v>127283119</v>
       </c>
       <c r="B146" t="n">
-        <v>92620</v>
+        <v>79020</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15752,10 +15752,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>440744</v>
+        <v>440881</v>
       </c>
       <c r="R146" t="n">
-        <v>6762615</v>
+        <v>6762591</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15814,10 +15814,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127274917</v>
+        <v>127275416</v>
       </c>
       <c r="B147" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15845,17 +15845,17 @@
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>440752</v>
+        <v>440816</v>
       </c>
       <c r="R147" t="n">
-        <v>6762337</v>
+        <v>6762475</v>
       </c>
       <c r="S147" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15894,7 +15894,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15909,22 +15909,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127283119</v>
+        <v>127273932</v>
       </c>
       <c r="B148" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15952,17 +15952,17 @@
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>440881</v>
+        <v>440913</v>
       </c>
       <c r="R148" t="n">
-        <v>6762591</v>
+        <v>6762466</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15989,9 +15989,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16006,60 +16016,60 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127272858</v>
+        <v>127283142</v>
       </c>
       <c r="B149" t="n">
-        <v>79018</v>
+        <v>92622</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>440609</v>
+        <v>440744</v>
       </c>
       <c r="R149" t="n">
-        <v>6762190</v>
+        <v>6762615</v>
       </c>
       <c r="S149" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16086,19 +16096,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16113,22 +16113,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127273038</v>
+        <v>127274917</v>
       </c>
       <c r="B150" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16156,17 +16156,17 @@
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>440688</v>
+        <v>440752</v>
       </c>
       <c r="R150" t="n">
-        <v>6762199</v>
+        <v>6762337</v>
       </c>
       <c r="S150" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16205,7 +16205,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16220,22 +16220,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127274822</v>
+        <v>127272858</v>
       </c>
       <c r="B151" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16263,17 +16263,17 @@
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>440760</v>
+        <v>440609</v>
       </c>
       <c r="R151" t="n">
-        <v>6762313</v>
+        <v>6762190</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16312,7 +16312,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16327,22 +16327,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127275416</v>
+        <v>127273038</v>
       </c>
       <c r="B152" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16374,10 +16374,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>440816</v>
+        <v>440688</v>
       </c>
       <c r="R152" t="n">
-        <v>6762475</v>
+        <v>6762199</v>
       </c>
       <c r="S152" t="n">
         <v>9</v>
@@ -16409,7 +16409,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16446,10 +16446,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127273932</v>
+        <v>127274822</v>
       </c>
       <c r="B153" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16477,17 +16477,17 @@
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>440913</v>
+        <v>440760</v>
       </c>
       <c r="R153" t="n">
-        <v>6762466</v>
+        <v>6762313</v>
       </c>
       <c r="S153" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16526,7 +16526,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16541,22 +16541,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127282904</v>
+        <v>127282914</v>
       </c>
       <c r="B154" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16588,10 +16588,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>440776</v>
+        <v>440924</v>
       </c>
       <c r="R154" t="n">
-        <v>6762632</v>
+        <v>6762509</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16650,10 +16650,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127282914</v>
+        <v>127282904</v>
       </c>
       <c r="B155" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16685,10 +16685,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>440924</v>
+        <v>440776</v>
       </c>
       <c r="R155" t="n">
-        <v>6762509</v>
+        <v>6762632</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16747,10 +16747,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127274354</v>
+        <v>127272746</v>
       </c>
       <c r="B156" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16778,17 +16778,17 @@
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>440686</v>
+        <v>440503</v>
       </c>
       <c r="R156" t="n">
-        <v>6762176</v>
+        <v>6762308</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -16827,7 +16827,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16842,22 +16842,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127272746</v>
+        <v>127283105</v>
       </c>
       <c r="B157" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16865,37 +16865,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>440503</v>
+        <v>440909</v>
       </c>
       <c r="R157" t="n">
-        <v>6762308</v>
+        <v>6762467</v>
       </c>
       <c r="S157" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16922,19 +16922,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16949,22 +16939,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127283105</v>
+        <v>127272237</v>
       </c>
       <c r="B158" t="n">
-        <v>79636</v>
+        <v>57663</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16972,34 +16962,39 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>440909</v>
+        <v>440675</v>
       </c>
       <c r="R158" t="n">
-        <v>6762467</v>
+        <v>6762165</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17029,9 +17024,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17046,22 +17051,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127272237</v>
+        <v>127274354</v>
       </c>
       <c r="B159" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17069,39 +17074,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>440675</v>
+        <v>440686</v>
       </c>
       <c r="R159" t="n">
-        <v>6762165</v>
+        <v>6762176</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17173,7 +17173,7 @@
         <v>127275098</v>
       </c>
       <c r="B160" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17282,10 +17282,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127274348</v>
+        <v>127276426</v>
       </c>
       <c r="B161" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17293,39 +17293,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>440686</v>
+        <v>440582</v>
       </c>
       <c r="R161" t="n">
-        <v>6762176</v>
+        <v>6762684</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17357,7 +17352,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17367,7 +17362,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17394,10 +17389,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127282900</v>
+        <v>127275877</v>
       </c>
       <c r="B162" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17425,14 +17420,14 @@
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>440757</v>
+        <v>440732</v>
       </c>
       <c r="R162" t="n">
-        <v>6762544</v>
+        <v>6762635</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17462,9 +17457,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17479,22 +17484,22 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127276426</v>
+        <v>127282900</v>
       </c>
       <c r="B163" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17522,14 +17527,14 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>440582</v>
+        <v>440757</v>
       </c>
       <c r="R163" t="n">
-        <v>6762684</v>
+        <v>6762544</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17559,19 +17564,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17586,22 +17581,22 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127275877</v>
+        <v>127273900</v>
       </c>
       <c r="B164" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17629,17 +17624,17 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>440732</v>
+        <v>440903</v>
       </c>
       <c r="R164" t="n">
-        <v>6762635</v>
+        <v>6762450</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -17668,7 +17663,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -17678,7 +17673,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17693,22 +17688,22 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127273900</v>
+        <v>127283137</v>
       </c>
       <c r="B165" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17736,17 +17731,17 @@
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>440903</v>
+        <v>440354</v>
       </c>
       <c r="R165" t="n">
-        <v>6762450</v>
+        <v>6762415</v>
       </c>
       <c r="S165" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -17773,19 +17768,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>13:21</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17800,22 +17785,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127282902</v>
+        <v>127273086</v>
       </c>
       <c r="B166" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17843,17 +17828,17 @@
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>440760</v>
+        <v>440694</v>
       </c>
       <c r="R166" t="n">
-        <v>6762569</v>
+        <v>6762204</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17880,9 +17865,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17897,22 +17892,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127273086</v>
+        <v>127282902</v>
       </c>
       <c r="B167" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17940,17 +17935,17 @@
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>440694</v>
+        <v>440760</v>
       </c>
       <c r="R167" t="n">
-        <v>6762204</v>
+        <v>6762569</v>
       </c>
       <c r="S167" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -17977,19 +17972,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z167" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>12:40</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18004,22 +17989,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127283137</v>
+        <v>127274348</v>
       </c>
       <c r="B168" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18027,34 +18012,39 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>440354</v>
+        <v>440686</v>
       </c>
       <c r="R168" t="n">
-        <v>6762415</v>
+        <v>6762176</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18084,9 +18074,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18101,22 +18101,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127273853</v>
+        <v>127275337</v>
       </c>
       <c r="B169" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18148,10 +18148,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>440887</v>
+        <v>440855</v>
       </c>
       <c r="R169" t="n">
-        <v>6762439</v>
+        <v>6762513</v>
       </c>
       <c r="S169" t="n">
         <v>9</v>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18220,10 +18220,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127270744</v>
+        <v>127273853</v>
       </c>
       <c r="B170" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18251,17 +18251,17 @@
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Hästdiken, Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>440351</v>
+        <v>440887</v>
       </c>
       <c r="R170" t="n">
-        <v>6762480</v>
+        <v>6762439</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18290,7 +18290,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18315,22 +18315,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127275337</v>
+        <v>127282927</v>
       </c>
       <c r="B171" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18358,17 +18358,17 @@
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Hästdiken, Hästdiken, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>440855</v>
+        <v>440488</v>
       </c>
       <c r="R171" t="n">
-        <v>6762513</v>
+        <v>6762419</v>
       </c>
       <c r="S171" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18395,19 +18395,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>14:33</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18422,22 +18412,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127282927</v>
+        <v>127283133</v>
       </c>
       <c r="B172" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18465,14 +18455,14 @@
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>440488</v>
+        <v>440598</v>
       </c>
       <c r="R172" t="n">
-        <v>6762419</v>
+        <v>6762206</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18519,22 +18509,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127283128</v>
+        <v>127283115</v>
       </c>
       <c r="B173" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18566,10 +18556,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>440822</v>
+        <v>440803</v>
       </c>
       <c r="R173" t="n">
-        <v>6762415</v>
+        <v>6762557</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18628,10 +18618,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127274114</v>
+        <v>127283134</v>
       </c>
       <c r="B174" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18659,14 +18649,14 @@
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>440711</v>
+        <v>440487</v>
       </c>
       <c r="R174" t="n">
-        <v>6762111</v>
+        <v>6762321</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18696,19 +18686,9 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18723,22 +18703,22 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127283115</v>
+        <v>127283128</v>
       </c>
       <c r="B175" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18770,10 +18750,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>440803</v>
+        <v>440822</v>
       </c>
       <c r="R175" t="n">
-        <v>6762557</v>
+        <v>6762415</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18832,10 +18812,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127283134</v>
+        <v>127270744</v>
       </c>
       <c r="B176" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18863,14 +18843,14 @@
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>440487</v>
+        <v>440351</v>
       </c>
       <c r="R176" t="n">
-        <v>6762321</v>
+        <v>6762480</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18900,9 +18880,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18917,22 +18907,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127283133</v>
+        <v>127274114</v>
       </c>
       <c r="B177" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18960,14 +18950,14 @@
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>Hästdiken, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>440598</v>
+        <v>440711</v>
       </c>
       <c r="R177" t="n">
-        <v>6762206</v>
+        <v>6762111</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18997,9 +18987,19 @@
           <t>2025-08-06</t>
         </is>
       </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19014,12 +19014,12 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
@@ -19357,10 +19357,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127283127</v>
+        <v>127282925</v>
       </c>
       <c r="B181" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19388,14 +19388,14 @@
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Norra Dåstjärnen, Dlr</t>
+          <t>N Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>440843</v>
+        <v>440619</v>
       </c>
       <c r="R181" t="n">
-        <v>6762431</v>
+        <v>6762184</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19442,12 +19442,12 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
@@ -19457,7 +19457,7 @@
         <v>127283116</v>
       </c>
       <c r="B182" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19551,10 +19551,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127282906</v>
+        <v>127283127</v>
       </c>
       <c r="B183" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19582,14 +19582,14 @@
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>N Dåstjärnen, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>440782</v>
+        <v>440843</v>
       </c>
       <c r="R183" t="n">
-        <v>6762562</v>
+        <v>6762431</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19636,12 +19636,12 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
@@ -19651,7 +19651,7 @@
         <v>127275778</v>
       </c>
       <c r="B184" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19755,10 +19755,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127282925</v>
+        <v>127282906</v>
       </c>
       <c r="B185" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19790,10 +19790,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>440619</v>
+        <v>440782</v>
       </c>
       <c r="R185" t="n">
-        <v>6762184</v>
+        <v>6762562</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19855,7 +19855,7 @@
         <v>127274154</v>
       </c>
       <c r="B186" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19969,10 +19969,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127274877</v>
+        <v>127283138</v>
       </c>
       <c r="B187" t="n">
-        <v>57821</v>
+        <v>79020</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19980,42 +19980,37 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Hästdiken, Dlr</t>
+          <t>Norra Dåstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>440752</v>
+      